--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA7B8A78-BDE7-431F-BC4D-C8F5A5FCA515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{520CE17F-C8F5-423E-8979-3992A064B1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="945" yWindow="1245" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2535" yWindow="1080" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -1921,7 +1921,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1932,10 +1932,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2426,732 +2423,732 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="4">
+    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3">
         <v>10000</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4">
-        <v>2</v>
-      </c>
-      <c r="I3" s="4">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>12</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3">
         <v>31</v>
       </c>
-      <c r="K3" s="4">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4">
-        <v>0</v>
-      </c>
-      <c r="N3" s="4">
-        <v>1</v>
-      </c>
-      <c r="O3" s="4">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
         <v>99</v>
       </c>
-      <c r="Q3" s="4">
-        <v>1</v>
-      </c>
-      <c r="R3" s="4">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4">
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <v>3</v>
       </c>
-      <c r="T3" s="4">
-        <v>0</v>
-      </c>
-      <c r="U3" s="4">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4" t="s">
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3" t="s">
         <v>112</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="W3" t="s">
         <v>116</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="X3" t="s">
         <v>118</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Y3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="4">
+      <c r="Z3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
+    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>10300</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" t="s">
         <v>95</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4">
+        <v>31</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
         <v>2</v>
       </c>
-      <c r="I4" s="4">
-        <v>12</v>
-      </c>
-      <c r="J4" s="4">
-        <v>31</v>
-      </c>
-      <c r="K4" s="4">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4">
-        <v>2</v>
-      </c>
-      <c r="M4" s="4">
-        <v>1</v>
-      </c>
-      <c r="N4" s="4">
-        <v>1</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4">
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
         <v>99</v>
       </c>
-      <c r="Q4" s="4">
-        <v>1</v>
-      </c>
-      <c r="R4" s="4">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4">
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>3</v>
       </c>
-      <c r="T4" s="4">
-        <v>0</v>
-      </c>
-      <c r="U4" s="4">
-        <v>0</v>
-      </c>
-      <c r="V4" s="4" t="s">
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4" t="s">
         <v>112</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="W4" t="s">
         <v>116</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="X4" t="s">
         <v>118</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Y4" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="Z4" s="4">
+      <c r="Z4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
+    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>10800</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" t="s">
         <v>78</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
+      <c r="J5">
+        <v>31</v>
+      </c>
+      <c r="K5">
+        <v>300</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>99</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>3</v>
       </c>
-      <c r="I5" s="4">
-        <v>12</v>
-      </c>
-      <c r="J5" s="4">
-        <v>31</v>
-      </c>
-      <c r="K5" s="4">
-        <v>300</v>
-      </c>
-      <c r="L5" s="4">
-        <v>2</v>
-      </c>
-      <c r="M5" s="4">
-        <v>1</v>
-      </c>
-      <c r="N5" s="4">
-        <v>2</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4">
-        <v>99</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>1</v>
-      </c>
-      <c r="R5" s="4">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4">
-        <v>3</v>
-      </c>
-      <c r="T5" s="4">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="s">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
         <v>112</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="W5" t="s">
         <v>116</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="X5" t="s">
         <v>118</v>
       </c>
-      <c r="Y5" s="5" t="s">
+      <c r="Y5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z5" s="4">
+      <c r="Z5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
+    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>10100</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" t="s">
         <v>90</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>3</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6">
         <v>12</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6">
         <v>31</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6">
         <v>1500</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6">
         <v>4</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6">
         <v>10</v>
       </c>
-      <c r="N6" s="4">
+      <c r="N6">
         <v>3</v>
       </c>
-      <c r="O6" s="4">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4">
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
         <v>99</v>
       </c>
-      <c r="Q6" s="4">
-        <v>1</v>
-      </c>
-      <c r="R6" s="4">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4">
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>5</v>
       </c>
-      <c r="T6" s="4">
-        <v>0</v>
-      </c>
-      <c r="U6" s="4">
-        <v>0</v>
-      </c>
-      <c r="V6" s="4" t="s">
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
         <v>112</v>
       </c>
-      <c r="W6" s="4" t="s">
+      <c r="W6" t="s">
         <v>116</v>
       </c>
-      <c r="X6" s="4" t="s">
+      <c r="X6" t="s">
         <v>118</v>
       </c>
-      <c r="Y6" s="5" t="s">
+      <c r="Y6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z6" s="4">
+      <c r="Z6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
+    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>10200</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>12</v>
+      </c>
+      <c r="J7">
+        <v>31</v>
+      </c>
+      <c r="K7">
+        <v>1000</v>
+      </c>
+      <c r="L7">
         <v>3</v>
       </c>
-      <c r="I7" s="4">
-        <v>12</v>
-      </c>
-      <c r="J7" s="4">
-        <v>31</v>
-      </c>
-      <c r="K7" s="4">
-        <v>1000</v>
-      </c>
-      <c r="L7" s="4">
+      <c r="M7">
+        <v>5</v>
+      </c>
+      <c r="N7">
         <v>3</v>
       </c>
-      <c r="M7" s="4">
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>99</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>5</v>
       </c>
-      <c r="N7" s="4">
-        <v>3</v>
-      </c>
-      <c r="O7" s="4">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4">
-        <v>99</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>1</v>
-      </c>
-      <c r="R7" s="4">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4">
-        <v>5</v>
-      </c>
-      <c r="T7" s="4">
-        <v>0</v>
-      </c>
-      <c r="U7" s="4">
-        <v>0</v>
-      </c>
-      <c r="V7" s="4" t="s">
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
         <v>112</v>
       </c>
-      <c r="W7" s="4" t="s">
+      <c r="W7" t="s">
         <v>116</v>
       </c>
-      <c r="X7" s="4" t="s">
+      <c r="X7" t="s">
         <v>118</v>
       </c>
-      <c r="Y7" s="5" t="s">
+      <c r="Y7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z7" s="4">
+      <c r="Z7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
+    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>10400</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" t="s">
         <v>92</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4">
-        <v>4</v>
-      </c>
-      <c r="I8" s="4">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
         <v>12</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8">
         <v>31</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8">
         <v>1000</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8">
         <v>3</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8">
         <v>5</v>
       </c>
-      <c r="N8" s="4">
+      <c r="N8">
         <v>3</v>
       </c>
-      <c r="O8" s="4">
-        <v>0</v>
-      </c>
-      <c r="P8" s="4">
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
         <v>99</v>
       </c>
-      <c r="Q8" s="4">
-        <v>1</v>
-      </c>
-      <c r="R8" s="4">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4">
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>5</v>
       </c>
-      <c r="T8" s="4">
-        <v>0</v>
-      </c>
-      <c r="U8" s="4">
-        <v>0</v>
-      </c>
-      <c r="V8" s="4" t="s">
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8" t="s">
         <v>112</v>
       </c>
-      <c r="W8" s="4" t="s">
+      <c r="W8" t="s">
         <v>116</v>
       </c>
-      <c r="X8" s="4" t="s">
+      <c r="X8" t="s">
         <v>118</v>
       </c>
-      <c r="Y8" s="5" t="s">
+      <c r="Y8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z8" s="4">
+      <c r="Z8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="4">
+    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9">
         <v>10500</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" t="s">
         <v>93</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>4</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9">
         <v>12</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9">
         <v>31</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9">
         <v>1500</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9">
         <v>5</v>
       </c>
-      <c r="M9" s="4">
+      <c r="M9">
         <v>10</v>
       </c>
-      <c r="N9" s="4">
+      <c r="N9">
         <v>4</v>
       </c>
-      <c r="O9" s="4">
-        <v>0</v>
-      </c>
-      <c r="P9" s="4">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
         <v>99</v>
       </c>
-      <c r="Q9" s="4">
-        <v>1</v>
-      </c>
-      <c r="R9" s="4">
-        <v>0</v>
-      </c>
-      <c r="S9" s="4">
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>5</v>
       </c>
-      <c r="T9" s="4">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4">
-        <v>0</v>
-      </c>
-      <c r="V9" s="4" t="s">
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
         <v>112</v>
       </c>
-      <c r="W9" s="4" t="s">
+      <c r="W9" t="s">
         <v>116</v>
       </c>
-      <c r="X9" s="4" t="s">
+      <c r="X9" t="s">
         <v>118</v>
       </c>
-      <c r="Y9" s="5" t="s">
+      <c r="Y9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z9" s="4">
+      <c r="Z9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="4">
+    <row r="10" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10">
         <v>10600</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="C10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" t="s">
         <v>86</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>5</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10">
         <v>12</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10">
         <v>31</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10">
         <v>2000</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10">
         <v>5</v>
       </c>
-      <c r="M10" s="4">
+      <c r="M10">
         <v>15</v>
       </c>
-      <c r="N10" s="4">
+      <c r="N10">
         <v>4</v>
       </c>
-      <c r="O10" s="4">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4">
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
         <v>99</v>
       </c>
-      <c r="Q10" s="4">
-        <v>1</v>
-      </c>
-      <c r="R10" s="4">
-        <v>0</v>
-      </c>
-      <c r="S10" s="4">
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <v>5</v>
       </c>
-      <c r="T10" s="4">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4">
-        <v>0</v>
-      </c>
-      <c r="V10" s="4" t="s">
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10" t="s">
         <v>112</v>
       </c>
-      <c r="W10" s="4" t="s">
+      <c r="W10" t="s">
         <v>116</v>
       </c>
-      <c r="X10" s="4" t="s">
+      <c r="X10" t="s">
         <v>118</v>
       </c>
-      <c r="Y10" s="5" t="s">
+      <c r="Y10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z10" s="4">
+      <c r="Z10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="4">
+    <row r="11" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11">
         <v>10700</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="C11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" t="s">
         <v>94</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>5</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11">
         <v>12</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11">
         <v>31</v>
       </c>
-      <c r="K11" s="4">
+      <c r="K11">
         <v>3000</v>
       </c>
-      <c r="L11" s="4">
+      <c r="L11">
         <v>5</v>
       </c>
-      <c r="M11" s="4">
+      <c r="M11">
         <v>15</v>
       </c>
-      <c r="N11" s="4">
-        <v>3</v>
-      </c>
-      <c r="O11" s="4">
-        <v>0</v>
-      </c>
-      <c r="P11" s="4">
+      <c r="N11">
+        <v>5</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
         <v>99</v>
       </c>
-      <c r="Q11" s="4">
-        <v>1</v>
-      </c>
-      <c r="R11" s="4">
-        <v>0</v>
-      </c>
-      <c r="S11" s="4">
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <v>5</v>
       </c>
-      <c r="T11" s="4">
-        <v>0</v>
-      </c>
-      <c r="U11" s="4">
-        <v>0</v>
-      </c>
-      <c r="V11" s="4" t="s">
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11" t="s">
         <v>112</v>
       </c>
-      <c r="W11" s="4" t="s">
+      <c r="W11" t="s">
         <v>116</v>
       </c>
-      <c r="X11" s="4" t="s">
+      <c r="X11" t="s">
         <v>118</v>
       </c>
-      <c r="Y11" s="5" t="s">
+      <c r="Y11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z11" s="4">
+      <c r="Z11">
         <v>1</v>
       </c>
     </row>
@@ -3257,732 +3254,732 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="4">
+    <row r="2" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2">
         <f>ROW()-2+1000</f>
         <v>1000</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2">
         <v>2000</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>5</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2">
         <v>12</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2">
         <v>31</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2">
         <v>3000</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2">
         <v>100</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2">
         <v>15</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2">
         <v>5</v>
       </c>
-      <c r="O2" s="4">
-        <v>0</v>
-      </c>
-      <c r="P2" s="4">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
         <v>99</v>
       </c>
-      <c r="Q2" s="4">
-        <v>0</v>
-      </c>
-      <c r="R2" s="4">
-        <v>0</v>
-      </c>
-      <c r="S2" s="4">
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <v>10</v>
       </c>
-      <c r="T2" s="4">
-        <v>0</v>
-      </c>
-      <c r="U2" s="4">
-        <v>0</v>
-      </c>
-      <c r="V2" s="4" t="s">
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2" t="s">
         <v>119</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="W2" t="s">
         <v>122</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" t="s">
         <v>117</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="Y2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z2" s="4">
+      <c r="Z2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="4">
+    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3">
         <f t="shared" ref="A3:A10" si="0">ROW()-2+1000</f>
         <v>1001</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3">
         <v>20000</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" t="s">
         <v>66</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3">
         <v>12</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3">
         <v>31</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3">
         <v>100</v>
       </c>
-      <c r="L3" s="4">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4">
-        <v>0</v>
-      </c>
-      <c r="N3" s="4">
-        <v>1</v>
-      </c>
-      <c r="O3" s="4">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4">
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
         <v>99</v>
       </c>
-      <c r="Q3" s="4">
-        <v>1</v>
-      </c>
-      <c r="R3" s="4">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4">
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <v>3</v>
       </c>
-      <c r="T3" s="4">
-        <v>0</v>
-      </c>
-      <c r="U3" s="4">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4" t="s">
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3" t="s">
         <v>119</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="W3" t="s">
         <v>122</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="X3" t="s">
         <v>118</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Y3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="4">
+      <c r="Z3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
+    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4">
         <f t="shared" si="0"/>
         <v>1002</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>20100</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4">
         <v>12</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4">
         <v>31</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4">
         <v>200</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4">
         <v>10</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4">
         <v>5</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4">
         <v>2</v>
       </c>
-      <c r="O4" s="4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4">
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
         <v>99</v>
       </c>
-      <c r="Q4" s="4">
-        <v>1</v>
-      </c>
-      <c r="R4" s="4">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4">
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>3</v>
       </c>
-      <c r="T4" s="4">
-        <v>0</v>
-      </c>
-      <c r="U4" s="4">
-        <v>0</v>
-      </c>
-      <c r="V4" s="4" t="s">
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4" t="s">
         <v>119</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="W4" t="s">
         <v>122</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="X4" t="s">
         <v>118</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Y4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z4" s="4">
+      <c r="Z4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
+    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
         <f t="shared" si="0"/>
         <v>1003</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>20200</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>3</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5">
         <v>12</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5">
         <v>31</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5">
         <v>300</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5">
         <v>10</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5">
         <v>5</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5">
         <v>3</v>
       </c>
-      <c r="O5" s="4">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4">
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
         <v>99</v>
       </c>
-      <c r="Q5" s="4">
-        <v>1</v>
-      </c>
-      <c r="R5" s="4">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4">
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>3</v>
       </c>
-      <c r="T5" s="4">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="s">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
         <v>119</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="W5" t="s">
         <v>122</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="X5" t="s">
         <v>118</v>
       </c>
-      <c r="Y5" s="5" t="s">
+      <c r="Y5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z5" s="4">
+      <c r="Z5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
+    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6">
         <f t="shared" si="0"/>
         <v>1004</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>20300</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4">
-        <v>4</v>
-      </c>
-      <c r="I6" s="4">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
         <v>12</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6">
         <v>31</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6">
         <v>500</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6">
         <v>11</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6">
         <v>10</v>
       </c>
-      <c r="N6" s="4">
+      <c r="N6">
         <v>3</v>
       </c>
-      <c r="O6" s="4">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4">
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
         <v>99</v>
       </c>
-      <c r="Q6" s="4">
-        <v>1</v>
-      </c>
-      <c r="R6" s="4">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4">
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>3</v>
       </c>
-      <c r="T6" s="4">
-        <v>0</v>
-      </c>
-      <c r="U6" s="4">
-        <v>0</v>
-      </c>
-      <c r="V6" s="4" t="s">
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
         <v>119</v>
       </c>
-      <c r="W6" s="4" t="s">
+      <c r="W6" t="s">
         <v>122</v>
       </c>
-      <c r="X6" s="4" t="s">
+      <c r="X6" t="s">
         <v>118</v>
       </c>
-      <c r="Y6" s="5" t="s">
+      <c r="Y6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z6" s="4">
+      <c r="Z6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
+    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>1005</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>20400</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" t="s">
         <v>69</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>12</v>
+      </c>
+      <c r="J7">
+        <v>31</v>
+      </c>
+      <c r="K7">
+        <v>1000</v>
+      </c>
+      <c r="L7">
+        <v>11</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+      <c r="N7">
+        <v>4</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>99</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>5</v>
       </c>
-      <c r="I7" s="4">
-        <v>12</v>
-      </c>
-      <c r="J7" s="4">
-        <v>31</v>
-      </c>
-      <c r="K7" s="4">
-        <v>1000</v>
-      </c>
-      <c r="L7" s="4">
-        <v>11</v>
-      </c>
-      <c r="M7" s="4">
-        <v>10</v>
-      </c>
-      <c r="N7" s="4">
-        <v>4</v>
-      </c>
-      <c r="O7" s="4">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4">
-        <v>99</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>1</v>
-      </c>
-      <c r="R7" s="4">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4">
-        <v>5</v>
-      </c>
-      <c r="T7" s="4">
-        <v>0</v>
-      </c>
-      <c r="U7" s="4">
-        <v>0</v>
-      </c>
-      <c r="V7" s="4" t="s">
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
         <v>119</v>
       </c>
-      <c r="W7" s="4" t="s">
+      <c r="W7" t="s">
         <v>122</v>
       </c>
-      <c r="X7" s="4" t="s">
+      <c r="X7" t="s">
         <v>118</v>
       </c>
-      <c r="Y7" s="5" t="s">
+      <c r="Y7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z7" s="4">
+      <c r="Z7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
+    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>1006</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>20500</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" t="s">
         <v>103</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4">
-        <v>6</v>
-      </c>
-      <c r="I8" s="4">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
         <v>12</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8">
         <v>31</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8">
         <v>1500</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8">
         <v>10</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8">
         <v>15</v>
       </c>
-      <c r="N8" s="4">
+      <c r="N8">
         <v>4</v>
       </c>
-      <c r="O8" s="4">
-        <v>0</v>
-      </c>
-      <c r="P8" s="4">
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
         <v>99</v>
       </c>
-      <c r="Q8" s="4">
-        <v>1</v>
-      </c>
-      <c r="R8" s="4">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4">
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>7</v>
       </c>
-      <c r="T8" s="4">
-        <v>0</v>
-      </c>
-      <c r="U8" s="4">
-        <v>0</v>
-      </c>
-      <c r="V8" s="4" t="s">
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8" t="s">
         <v>119</v>
       </c>
-      <c r="W8" s="4" t="s">
+      <c r="W8" t="s">
         <v>122</v>
       </c>
-      <c r="X8" s="4" t="s">
+      <c r="X8" t="s">
         <v>118</v>
       </c>
-      <c r="Y8" s="5" t="s">
+      <c r="Y8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z8" s="4">
+      <c r="Z8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="4">
+    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9">
         <f t="shared" si="0"/>
         <v>1007</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9">
         <v>20600</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9">
+        <v>12</v>
+      </c>
+      <c r="J9">
+        <v>31</v>
+      </c>
+      <c r="K9">
+        <v>2000</v>
+      </c>
+      <c r="L9">
+        <v>12</v>
+      </c>
+      <c r="M9">
+        <v>20</v>
+      </c>
+      <c r="N9">
         <v>4</v>
       </c>
-      <c r="I9" s="4">
-        <v>12</v>
-      </c>
-      <c r="J9" s="4">
-        <v>31</v>
-      </c>
-      <c r="K9" s="4">
-        <v>2000</v>
-      </c>
-      <c r="L9" s="4">
-        <v>12</v>
-      </c>
-      <c r="M9" s="4">
-        <v>20</v>
-      </c>
-      <c r="N9" s="4">
-        <v>4</v>
-      </c>
-      <c r="O9" s="4">
-        <v>0</v>
-      </c>
-      <c r="P9" s="4">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
         <v>99</v>
       </c>
-      <c r="Q9" s="4">
-        <v>1</v>
-      </c>
-      <c r="R9" s="4">
-        <v>0</v>
-      </c>
-      <c r="S9" s="4">
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>7</v>
       </c>
-      <c r="T9" s="4">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4">
-        <v>0</v>
-      </c>
-      <c r="V9" s="4" t="s">
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
         <v>119</v>
       </c>
-      <c r="W9" s="4" t="s">
+      <c r="W9" t="s">
         <v>122</v>
       </c>
-      <c r="X9" s="4" t="s">
+      <c r="X9" t="s">
         <v>118</v>
       </c>
-      <c r="Y9" s="5" t="s">
+      <c r="Y9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z9" s="4">
+      <c r="Z9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="4">
+    <row r="10" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10">
         <f t="shared" si="0"/>
         <v>1008</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10">
         <v>20700</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="C10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>5</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10">
         <v>12</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10">
         <v>31</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10">
         <v>5000</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10">
         <v>12</v>
       </c>
-      <c r="M10" s="4">
+      <c r="M10">
         <v>35</v>
       </c>
-      <c r="N10" s="4">
+      <c r="N10">
         <v>5</v>
       </c>
-      <c r="O10" s="4">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4">
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
         <v>99</v>
       </c>
-      <c r="Q10" s="4">
-        <v>1</v>
-      </c>
-      <c r="R10" s="4">
-        <v>0</v>
-      </c>
-      <c r="S10" s="4">
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <v>10</v>
       </c>
-      <c r="T10" s="4">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4">
-        <v>0</v>
-      </c>
-      <c r="V10" s="4" t="s">
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10" t="s">
         <v>119</v>
       </c>
-      <c r="W10" s="4" t="s">
+      <c r="W10" t="s">
         <v>122</v>
       </c>
-      <c r="X10" s="4" t="s">
+      <c r="X10" t="s">
         <v>118</v>
       </c>
-      <c r="Y10" s="5" t="s">
+      <c r="Y10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z10" s="4">
+      <c r="Z10">
         <v>1</v>
       </c>
     </row>
@@ -4088,732 +4085,732 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="4">
+    <row r="2" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2">
         <f>ROW()-2+2000</f>
         <v>2000</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2">
         <v>3000</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" t="s">
         <v>151</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>5</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2">
         <v>12</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2">
         <v>31</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2">
         <v>5000</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2">
         <v>200</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2">
         <v>30</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2">
         <v>5</v>
       </c>
-      <c r="O2" s="4">
-        <v>0</v>
-      </c>
-      <c r="P2" s="4">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
         <v>99</v>
       </c>
-      <c r="Q2" s="4">
-        <v>0</v>
-      </c>
-      <c r="R2" s="4">
-        <v>0</v>
-      </c>
-      <c r="S2" s="4">
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <v>10</v>
       </c>
-      <c r="T2" s="4">
-        <v>0</v>
-      </c>
-      <c r="U2" s="4">
-        <v>0</v>
-      </c>
-      <c r="V2" s="4" t="s">
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2" t="s">
         <v>120</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="W2" t="s">
         <v>124</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" t="s">
         <v>117</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="Y2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z2" s="4">
+      <c r="Z2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="4">
+    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3">
         <f t="shared" ref="A3:A11" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3">
         <v>30000</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>12</v>
+      </c>
+      <c r="J3">
+        <v>31</v>
+      </c>
+      <c r="K3">
+        <v>300</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
         <v>2</v>
       </c>
-      <c r="I3" s="4">
-        <v>12</v>
-      </c>
-      <c r="J3" s="4">
-        <v>31</v>
-      </c>
-      <c r="K3" s="4">
-        <v>300</v>
-      </c>
-      <c r="L3" s="4">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4">
-        <v>0</v>
-      </c>
-      <c r="N3" s="4">
-        <v>2</v>
-      </c>
-      <c r="O3" s="4">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4">
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
         <v>99</v>
       </c>
-      <c r="Q3" s="4">
-        <v>1</v>
-      </c>
-      <c r="R3" s="4">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4">
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <v>3</v>
       </c>
-      <c r="T3" s="4">
-        <v>0</v>
-      </c>
-      <c r="U3" s="4">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4" t="s">
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3" t="s">
         <v>120</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="W3" t="s">
         <v>124</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="X3" t="s">
         <v>118</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Y3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="4">
+      <c r="Z3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
+    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4">
         <f t="shared" si="0"/>
         <v>2002</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>30100</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" t="s">
         <v>84</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4">
         <v>12</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4">
         <v>31</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4">
         <v>500</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4">
         <v>20</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4">
         <v>20</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4">
         <v>2</v>
       </c>
-      <c r="O4" s="4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4">
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
         <v>99</v>
       </c>
-      <c r="Q4" s="4">
-        <v>1</v>
-      </c>
-      <c r="R4" s="4">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4">
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>3</v>
       </c>
-      <c r="T4" s="4">
-        <v>0</v>
-      </c>
-      <c r="U4" s="4">
-        <v>0</v>
-      </c>
-      <c r="V4" s="4" t="s">
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4" t="s">
         <v>120</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="W4" t="s">
         <v>124</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="X4" t="s">
         <v>118</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Y4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z4" s="4">
+      <c r="Z4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
+    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
         <f t="shared" si="0"/>
         <v>2003</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>30200</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>3</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5">
         <v>12</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5">
         <v>31</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5">
         <v>1200</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5">
         <v>20</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5">
         <v>20</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5">
         <v>3</v>
       </c>
-      <c r="O5" s="4">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4">
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
         <v>99</v>
       </c>
-      <c r="Q5" s="4">
-        <v>1</v>
-      </c>
-      <c r="R5" s="4">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4">
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>5</v>
       </c>
-      <c r="T5" s="4">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="s">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
         <v>120</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="W5" t="s">
         <v>124</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="X5" t="s">
         <v>118</v>
       </c>
-      <c r="Y5" s="5" t="s">
+      <c r="Y5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z5" s="4">
+      <c r="Z5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
+    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6">
         <f t="shared" si="0"/>
         <v>2004</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>30300</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>4</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6">
         <v>12</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6">
         <v>31</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6">
         <v>500</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6">
         <v>20</v>
       </c>
-      <c r="M6" s="4">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4">
-        <v>2</v>
-      </c>
-      <c r="O6" s="4">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4">
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
         <v>99</v>
       </c>
-      <c r="Q6" s="4">
-        <v>1</v>
-      </c>
-      <c r="R6" s="4">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4">
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>3</v>
       </c>
-      <c r="T6" s="4">
-        <v>0</v>
-      </c>
-      <c r="U6" s="4">
-        <v>0</v>
-      </c>
-      <c r="V6" s="4" t="s">
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
         <v>120</v>
       </c>
-      <c r="W6" s="4" t="s">
+      <c r="W6" t="s">
         <v>124</v>
       </c>
-      <c r="X6" s="4" t="s">
+      <c r="X6" t="s">
         <v>118</v>
       </c>
-      <c r="Y6" s="5" t="s">
+      <c r="Y6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z6" s="4">
+      <c r="Z6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
+    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>2005</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>30400</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>3</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7">
         <v>12</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7">
         <v>31</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7">
         <v>1000</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7">
         <v>21</v>
       </c>
-      <c r="M7" s="4">
+      <c r="M7">
         <v>25</v>
       </c>
-      <c r="N7" s="4">
-        <v>2</v>
-      </c>
-      <c r="O7" s="4">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4">
+      <c r="N7">
+        <v>4</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
         <v>99</v>
       </c>
-      <c r="Q7" s="4">
-        <v>1</v>
-      </c>
-      <c r="R7" s="4">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4">
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>3</v>
       </c>
-      <c r="T7" s="4">
-        <v>0</v>
-      </c>
-      <c r="U7" s="4">
-        <v>0</v>
-      </c>
-      <c r="V7" s="4" t="s">
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
         <v>120</v>
       </c>
-      <c r="W7" s="4" t="s">
+      <c r="W7" t="s">
         <v>124</v>
       </c>
-      <c r="X7" s="4" t="s">
+      <c r="X7" t="s">
         <v>118</v>
       </c>
-      <c r="Y7" s="5" t="s">
+      <c r="Y7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z7" s="4">
+      <c r="Z7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
+    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>2006</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>30500</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" t="s">
         <v>87</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8">
         <v>12</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8">
         <v>31</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8">
         <v>2000</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8">
         <v>21</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8">
         <v>30</v>
       </c>
-      <c r="N8" s="4">
-        <v>4</v>
-      </c>
-      <c r="O8" s="4">
-        <v>0</v>
-      </c>
-      <c r="P8" s="4">
+      <c r="N8">
+        <v>5</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
         <v>99</v>
       </c>
-      <c r="Q8" s="4">
-        <v>1</v>
-      </c>
-      <c r="R8" s="4">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4">
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>5</v>
       </c>
-      <c r="T8" s="4">
-        <v>0</v>
-      </c>
-      <c r="U8" s="4">
-        <v>0</v>
-      </c>
-      <c r="V8" s="4" t="s">
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8" t="s">
         <v>120</v>
       </c>
-      <c r="W8" s="4" t="s">
+      <c r="W8" t="s">
         <v>124</v>
       </c>
-      <c r="X8" s="4" t="s">
+      <c r="X8" t="s">
         <v>118</v>
       </c>
-      <c r="Y8" s="5" t="s">
+      <c r="Y8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z8" s="4">
+      <c r="Z8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="4">
+    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9">
         <f t="shared" si="0"/>
         <v>2007</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9">
         <v>30600</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>3</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9">
         <v>12</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9">
         <v>31</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9">
         <v>2000</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9">
         <v>22</v>
       </c>
-      <c r="M9" s="4">
+      <c r="M9">
         <v>35</v>
       </c>
-      <c r="N9" s="4">
-        <v>4</v>
-      </c>
-      <c r="O9" s="4">
-        <v>0</v>
-      </c>
-      <c r="P9" s="4">
+      <c r="N9">
+        <v>5</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
         <v>99</v>
       </c>
-      <c r="Q9" s="4">
-        <v>1</v>
-      </c>
-      <c r="R9" s="4">
-        <v>0</v>
-      </c>
-      <c r="S9" s="4">
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>5</v>
       </c>
-      <c r="T9" s="4">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4">
-        <v>0</v>
-      </c>
-      <c r="V9" s="4" t="s">
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
         <v>120</v>
       </c>
-      <c r="W9" s="4" t="s">
+      <c r="W9" t="s">
         <v>124</v>
       </c>
-      <c r="X9" s="4" t="s">
+      <c r="X9" t="s">
         <v>118</v>
       </c>
-      <c r="Y9" s="5" t="s">
+      <c r="Y9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z9" s="4">
+      <c r="Z9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="4">
+    <row r="10" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10">
         <f t="shared" si="0"/>
         <v>2008</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10">
         <v>30700</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="C10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" t="s">
         <v>75</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>5</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10">
         <v>12</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10">
         <v>31</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10">
         <v>3000</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10">
         <v>22</v>
       </c>
-      <c r="M10" s="4">
+      <c r="M10">
         <v>38</v>
       </c>
-      <c r="N10" s="4">
-        <v>3</v>
-      </c>
-      <c r="O10" s="4">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4">
+      <c r="N10">
+        <v>4</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
         <v>99</v>
       </c>
-      <c r="Q10" s="4">
-        <v>1</v>
-      </c>
-      <c r="R10" s="4">
-        <v>0</v>
-      </c>
-      <c r="S10" s="4">
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <v>5</v>
       </c>
-      <c r="T10" s="4">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4">
-        <v>0</v>
-      </c>
-      <c r="V10" s="4" t="s">
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10" t="s">
         <v>120</v>
       </c>
-      <c r="W10" s="4" t="s">
+      <c r="W10" t="s">
         <v>124</v>
       </c>
-      <c r="X10" s="4" t="s">
+      <c r="X10" t="s">
         <v>118</v>
       </c>
-      <c r="Y10" s="5" t="s">
+      <c r="Y10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z10" s="4">
+      <c r="Z10">
         <v>1</v>
       </c>
     </row>
@@ -5000,732 +4997,732 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="4">
+    <row r="2" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2">
         <f>ROW()-2+3000</f>
         <v>3000</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2">
         <v>4000</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" t="s">
         <v>150</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>5</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2">
         <v>12</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2">
         <v>31</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2">
         <v>7000</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2">
         <v>300</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2">
         <v>30</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2">
         <v>5</v>
       </c>
-      <c r="O2" s="4">
-        <v>0</v>
-      </c>
-      <c r="P2" s="4">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
         <v>99</v>
       </c>
-      <c r="Q2" s="4">
-        <v>0</v>
-      </c>
-      <c r="R2" s="4">
-        <v>0</v>
-      </c>
-      <c r="S2" s="4">
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <v>10</v>
       </c>
-      <c r="T2" s="4">
-        <v>0</v>
-      </c>
-      <c r="U2" s="4">
-        <v>0</v>
-      </c>
-      <c r="V2" s="4" t="s">
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2" t="s">
         <v>121</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="W2" t="s">
         <v>123</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" t="s">
         <v>117</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="Y2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z2" s="4">
+      <c r="Z2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="4">
+    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3">
         <f t="shared" ref="A3:A10" si="0">ROW()-2+3000</f>
         <v>3001</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3">
         <v>40000</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4">
-        <v>2</v>
-      </c>
-      <c r="I3" s="4">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>12</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3">
         <v>31</v>
       </c>
-      <c r="K3" s="4">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4">
-        <v>0</v>
-      </c>
-      <c r="N3" s="4">
-        <v>1</v>
-      </c>
-      <c r="O3" s="4">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
         <v>99</v>
       </c>
-      <c r="Q3" s="4">
-        <v>1</v>
-      </c>
-      <c r="R3" s="4">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4">
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <v>3</v>
       </c>
-      <c r="T3" s="4">
-        <v>0</v>
-      </c>
-      <c r="U3" s="4">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4" t="s">
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3" t="s">
         <v>121</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="W3" t="s">
         <v>123</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="X3" t="s">
         <v>118</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Y3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="4">
+      <c r="Z3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
+    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4">
         <f t="shared" si="0"/>
         <v>3002</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>40100</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" t="s">
         <v>83</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4">
         <v>12</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4">
         <v>31</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4">
         <v>800</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4">
         <v>30</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4">
         <v>20</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4">
         <v>3</v>
       </c>
-      <c r="O4" s="4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4">
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
         <v>99</v>
       </c>
-      <c r="Q4" s="4">
-        <v>1</v>
-      </c>
-      <c r="R4" s="4">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4">
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>5</v>
       </c>
-      <c r="T4" s="4">
-        <v>0</v>
-      </c>
-      <c r="U4" s="4">
-        <v>0</v>
-      </c>
-      <c r="V4" s="4" t="s">
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4" t="s">
         <v>121</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="W4" t="s">
         <v>123</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="X4" t="s">
         <v>118</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Y4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z4" s="4">
+      <c r="Z4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
+    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
         <f t="shared" si="0"/>
         <v>3003</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>40200</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>3</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5">
         <v>12</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5">
         <v>31</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5">
         <v>1000</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5">
         <v>30</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5">
         <v>30</v>
       </c>
-      <c r="N5" s="4">
-        <v>3</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4">
+      <c r="N5">
+        <v>4</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
         <v>99</v>
       </c>
-      <c r="Q5" s="4">
-        <v>1</v>
-      </c>
-      <c r="R5" s="4">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4">
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>5</v>
       </c>
-      <c r="T5" s="4">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="s">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
         <v>121</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="W5" t="s">
         <v>123</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="X5" t="s">
         <v>118</v>
       </c>
-      <c r="Y5" s="5" t="s">
+      <c r="Y5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z5" s="4">
+      <c r="Z5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
+    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6">
         <f t="shared" si="0"/>
         <v>3004</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>40300</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" t="s">
         <v>101</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4">
-        <v>4</v>
-      </c>
-      <c r="I6" s="4">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
         <v>12</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6">
         <v>31</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6">
         <v>1200</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6">
         <v>31</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6">
         <v>40</v>
       </c>
-      <c r="N6" s="4">
-        <v>2</v>
-      </c>
-      <c r="O6" s="4">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4">
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
         <v>99</v>
       </c>
-      <c r="Q6" s="4">
-        <v>1</v>
-      </c>
-      <c r="R6" s="4">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4">
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>3</v>
       </c>
-      <c r="T6" s="4">
-        <v>0</v>
-      </c>
-      <c r="U6" s="4">
-        <v>0</v>
-      </c>
-      <c r="V6" s="4" t="s">
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
         <v>121</v>
       </c>
-      <c r="W6" s="4" t="s">
+      <c r="W6" t="s">
         <v>123</v>
       </c>
-      <c r="X6" s="4" t="s">
+      <c r="X6" t="s">
         <v>118</v>
       </c>
-      <c r="Y6" s="5" t="s">
+      <c r="Y6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z6" s="4">
+      <c r="Z6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
+    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>3005</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>40400</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" t="s">
         <v>146</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>12</v>
+      </c>
+      <c r="J7">
+        <v>31</v>
+      </c>
+      <c r="K7">
+        <v>1000</v>
+      </c>
+      <c r="L7">
+        <v>30</v>
+      </c>
+      <c r="M7">
+        <v>50</v>
+      </c>
+      <c r="N7">
+        <v>4</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>99</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>5</v>
       </c>
-      <c r="I7" s="4">
-        <v>12</v>
-      </c>
-      <c r="J7" s="4">
-        <v>31</v>
-      </c>
-      <c r="K7" s="4">
-        <v>1000</v>
-      </c>
-      <c r="L7" s="4">
-        <v>30</v>
-      </c>
-      <c r="M7" s="4">
-        <v>50</v>
-      </c>
-      <c r="N7" s="4">
-        <v>3</v>
-      </c>
-      <c r="O7" s="4">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4">
-        <v>99</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>1</v>
-      </c>
-      <c r="R7" s="4">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4">
-        <v>5</v>
-      </c>
-      <c r="T7" s="4">
-        <v>0</v>
-      </c>
-      <c r="U7" s="4">
-        <v>0</v>
-      </c>
-      <c r="V7" s="4" t="s">
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
         <v>121</v>
       </c>
-      <c r="W7" s="4" t="s">
+      <c r="W7" t="s">
         <v>123</v>
       </c>
-      <c r="X7" s="4" t="s">
+      <c r="X7" t="s">
         <v>118</v>
       </c>
-      <c r="Y7" s="5" t="s">
+      <c r="Y7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z7" s="4">
+      <c r="Z7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
+    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>3006</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>40500</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4">
-        <v>6</v>
-      </c>
-      <c r="I8" s="4">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
         <v>12</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8">
         <v>31</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8">
         <v>700</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8">
         <v>31</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8">
         <v>55</v>
       </c>
-      <c r="N8" s="4">
-        <v>4</v>
-      </c>
-      <c r="O8" s="4">
-        <v>0</v>
-      </c>
-      <c r="P8" s="4">
+      <c r="N8">
+        <v>5</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
         <v>99</v>
       </c>
-      <c r="Q8" s="4">
-        <v>1</v>
-      </c>
-      <c r="R8" s="4">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4">
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>5</v>
       </c>
-      <c r="T8" s="4">
-        <v>0</v>
-      </c>
-      <c r="U8" s="4">
-        <v>0</v>
-      </c>
-      <c r="V8" s="4" t="s">
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8" t="s">
         <v>121</v>
       </c>
-      <c r="W8" s="4" t="s">
+      <c r="W8" t="s">
         <v>123</v>
       </c>
-      <c r="X8" s="4" t="s">
+      <c r="X8" t="s">
         <v>118</v>
       </c>
-      <c r="Y8" s="5" t="s">
+      <c r="Y8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z8" s="4">
+      <c r="Z8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="4">
+    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9">
         <f t="shared" si="0"/>
         <v>3007</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9">
         <v>40600</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" t="s">
         <v>81</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>5</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9">
         <v>12</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9">
         <v>31</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9">
         <v>1500</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9">
         <v>32</v>
       </c>
-      <c r="M9" s="4">
+      <c r="M9">
         <v>60</v>
       </c>
-      <c r="N9" s="4">
-        <v>4</v>
-      </c>
-      <c r="O9" s="4">
-        <v>0</v>
-      </c>
-      <c r="P9" s="4">
+      <c r="N9">
+        <v>5</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
         <v>99</v>
       </c>
-      <c r="Q9" s="4">
-        <v>1</v>
-      </c>
-      <c r="R9" s="4">
-        <v>0</v>
-      </c>
-      <c r="S9" s="4">
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>5</v>
       </c>
-      <c r="T9" s="4">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4">
-        <v>0</v>
-      </c>
-      <c r="V9" s="4" t="s">
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
         <v>121</v>
       </c>
-      <c r="W9" s="4" t="s">
+      <c r="W9" t="s">
         <v>123</v>
       </c>
-      <c r="X9" s="4" t="s">
+      <c r="X9" t="s">
         <v>118</v>
       </c>
-      <c r="Y9" s="5" t="s">
+      <c r="Y9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z9" s="4">
+      <c r="Z9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="4" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="4">
+    <row r="10" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10">
         <f t="shared" si="0"/>
         <v>3008</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10">
         <v>40700</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="C10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" t="s">
         <v>131</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>6</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10">
         <v>12</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10">
         <v>31</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10">
         <v>3000</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10">
         <v>32</v>
       </c>
-      <c r="M10" s="4">
+      <c r="M10">
         <v>65</v>
       </c>
-      <c r="N10" s="4">
+      <c r="N10">
         <v>5</v>
       </c>
-      <c r="O10" s="4">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4">
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
         <v>99</v>
       </c>
-      <c r="Q10" s="4">
-        <v>1</v>
-      </c>
-      <c r="R10" s="4">
-        <v>0</v>
-      </c>
-      <c r="S10" s="4">
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <v>10</v>
       </c>
-      <c r="T10" s="4">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4">
-        <v>0</v>
-      </c>
-      <c r="V10" s="4" t="s">
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10" t="s">
         <v>121</v>
       </c>
-      <c r="W10" s="4" t="s">
+      <c r="W10" t="s">
         <v>123</v>
       </c>
-      <c r="X10" s="4" t="s">
+      <c r="X10" t="s">
         <v>118</v>
       </c>
-      <c r="Y10" s="5" t="s">
+      <c r="Y10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z10" s="4">
+      <c r="Z10">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{520CE17F-C8F5-423E-8979-3992A064B1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A92F3BE8-9EBB-4ED8-AAB6-18F3B182DE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2535" yWindow="1080" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2865" yWindow="1020" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A92F3BE8-9EBB-4ED8-AAB6-18F3B182DE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F889C685-6C22-43CD-AAC4-2C6CB6D11028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2865" yWindow="1020" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -4286,7 +4286,7 @@
         <v>20</v>
       </c>
       <c r="M4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>2</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F889C685-6C22-43CD-AAC4-2C6CB6D11028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B95AF7A-763B-477F-BA9B-6EA065AFE823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -1582,42 +1582,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>自由課題
-冬の名物となるような、雪国のお菓子を募集しています。
-どんな種類でも結構です！お気軽にご応募ください。</t>
-    <rPh sb="0" eb="4">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>フユ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>メイブツ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ユキクニ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>シュルイ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ケッコウ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>キガル</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>オウボ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>お花をモチーフにしたお菓子限定
 お花をメインに使った華やかなお菓子を募集しています。
 クッキー・チョコレート・ケーキ・チーズケーキから１種類を募集します。</t>
@@ -1850,6 +1814,42 @@
     </rPh>
     <rPh sb="70" eb="72">
       <t>タイカイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自由課題
+冬の名物となる、雪国のお菓子を募集しています。
+どんな種類でも結構です！お気軽にご応募ください。</t>
+    <rPh sb="0" eb="4">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>フユ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>メイブツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ユキクニ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ケッコウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>キガル</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>オウボ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3272,7 +3272,7 @@
         <v>29</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -4100,10 +4100,10 @@
         <v>46</v>
       </c>
       <c r="E2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>152</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -5012,10 +5012,10 @@
         <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>71</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>101</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -5417,10 +5417,10 @@
         <v>60</v>
       </c>
       <c r="E7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>147</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -5582,7 +5582,7 @@
         <v>81</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -5663,7 +5663,7 @@
         <v>131</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G10">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B95AF7A-763B-477F-BA9B-6EA065AFE823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5110BA-EFFA-406C-A7CA-1F06A3AB6576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1560" yWindow="840" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -3254,31 +3254,31 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f>ROW()-2+1000</f>
+        <f t="shared" ref="A2:A9" si="0">ROW()-2+1000</f>
         <v>1000</v>
       </c>
       <c r="B2">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>12</v>
@@ -3287,16 +3287,16 @@
         <v>31</v>
       </c>
       <c r="K2">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="L2">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -3305,13 +3305,13 @@
         <v>99</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         <v>122</v>
       </c>
       <c r="X2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -3337,23 +3337,23 @@
     </row>
     <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
-        <f t="shared" ref="A3:A10" si="0">ROW()-2+1000</f>
+        <f t="shared" si="0"/>
         <v>1001</v>
       </c>
       <c r="B3">
-        <v>20000</v>
+        <v>20100</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>135</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -3368,16 +3368,16 @@
         <v>31</v>
       </c>
       <c r="K3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>118</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -3422,25 +3422,25 @@
         <v>1002</v>
       </c>
       <c r="B4">
-        <v>20100</v>
+        <v>20200</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>12</v>
@@ -3449,7 +3449,7 @@
         <v>31</v>
       </c>
       <c r="K4">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -3458,7 +3458,7 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -3491,7 +3491,7 @@
         <v>118</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -3503,19 +3503,19 @@
         <v>1003</v>
       </c>
       <c r="B5">
-        <v>20200</v>
+        <v>20300</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -3530,13 +3530,13 @@
         <v>31</v>
       </c>
       <c r="K5">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
         <v>10</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
       </c>
       <c r="N5">
         <v>3</v>
@@ -3584,25 +3584,25 @@
         <v>1004</v>
       </c>
       <c r="B6">
-        <v>20300</v>
+        <v>20400</v>
       </c>
       <c r="C6" t="s">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>12</v>
@@ -3611,7 +3611,7 @@
         <v>31</v>
       </c>
       <c r="K6">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L6">
         <v>11</v>
@@ -3620,7 +3620,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -3665,19 +3665,19 @@
         <v>1005</v>
       </c>
       <c r="B7">
-        <v>20400</v>
+        <v>20500</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -3692,13 +3692,13 @@
         <v>31</v>
       </c>
       <c r="K7">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="L7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N7">
         <v>4</v>
@@ -3716,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -3746,25 +3746,25 @@
         <v>1006</v>
       </c>
       <c r="B8">
-        <v>20500</v>
+        <v>20600</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I8">
         <v>12</v>
@@ -3773,13 +3773,13 @@
         <v>31</v>
       </c>
       <c r="K8">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="L8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M8">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N8">
         <v>4</v>
@@ -3827,25 +3827,25 @@
         <v>1007</v>
       </c>
       <c r="B9">
-        <v>20600</v>
+        <v>20700</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>12</v>
@@ -3854,16 +3854,16 @@
         <v>31</v>
       </c>
       <c r="K9">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="L9">
         <v>12</v>
       </c>
       <c r="M9">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -3902,25 +3902,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+1000</f>
         <v>1008</v>
       </c>
       <c r="B10">
-        <v>20700</v>
+        <v>2000</v>
       </c>
       <c r="C10" t="s">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3935,13 +3935,13 @@
         <v>31</v>
       </c>
       <c r="K10">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="L10">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="M10">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="N10">
         <v>5</v>
@@ -3953,7 +3953,7 @@
         <v>99</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3974,10 +3974,10 @@
         <v>122</v>
       </c>
       <c r="X10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z10">
         <v>1</v>
@@ -4085,31 +4085,31 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f>ROW()-2+2000</f>
+        <f t="shared" ref="A2:A10" si="0">ROW()-2+2000</f>
         <v>2000</v>
       </c>
       <c r="B2">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>12</v>
@@ -4118,16 +4118,16 @@
         <v>31</v>
       </c>
       <c r="K2">
-        <v>5000</v>
+        <v>300</v>
       </c>
       <c r="L2">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -4136,13 +4136,13 @@
         <v>99</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4157,10 +4157,10 @@
         <v>124</v>
       </c>
       <c r="X2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -4168,29 +4168,29 @@
     </row>
     <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
-        <f t="shared" ref="A3:A11" si="0">ROW()-2+2000</f>
+        <f t="shared" si="0"/>
         <v>2001</v>
       </c>
       <c r="B3">
-        <v>30000</v>
+        <v>30100</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>12</v>
@@ -4199,13 +4199,13 @@
         <v>31</v>
       </c>
       <c r="K3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N3">
         <v>2</v>
@@ -4241,7 +4241,7 @@
         <v>118</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -4253,25 +4253,25 @@
         <v>2002</v>
       </c>
       <c r="B4">
-        <v>30100</v>
+        <v>30200</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>12</v>
@@ -4280,16 +4280,16 @@
         <v>31</v>
       </c>
       <c r="K4">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="L4">
         <v>20</v>
       </c>
       <c r="M4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -4304,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4322,7 +4322,7 @@
         <v>118</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -4334,25 +4334,25 @@
         <v>2003</v>
       </c>
       <c r="B5">
-        <v>30200</v>
+        <v>30300</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>12</v>
@@ -4361,13 +4361,13 @@
         <v>31</v>
       </c>
       <c r="K5">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="L5">
         <v>20</v>
       </c>
       <c r="M5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>3</v>
@@ -4385,7 +4385,7 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4415,25 +4415,25 @@
         <v>2004</v>
       </c>
       <c r="B6">
-        <v>30300</v>
+        <v>30400</v>
       </c>
       <c r="C6" t="s">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>12</v>
@@ -4442,16 +4442,16 @@
         <v>31</v>
       </c>
       <c r="K6">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -4496,25 +4496,25 @@
         <v>2005</v>
       </c>
       <c r="B7">
-        <v>30400</v>
+        <v>30500</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>12</v>
@@ -4523,16 +4523,16 @@
         <v>31</v>
       </c>
       <c r="K7">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="L7">
         <v>21</v>
       </c>
       <c r="M7">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -4547,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -4577,25 +4577,25 @@
         <v>2006</v>
       </c>
       <c r="B8">
-        <v>30500</v>
+        <v>30600</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I8">
         <v>12</v>
@@ -4607,10 +4607,10 @@
         <v>2000</v>
       </c>
       <c r="L8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M8">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="N8">
         <v>5</v>
@@ -4658,25 +4658,25 @@
         <v>2007</v>
       </c>
       <c r="B9">
-        <v>30600</v>
+        <v>30700</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>12</v>
@@ -4685,16 +4685,16 @@
         <v>31</v>
       </c>
       <c r="K9">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="L9">
         <v>22</v>
       </c>
       <c r="M9">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -4733,165 +4733,165 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10">
+    <row r="10" spans="1:26" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>2008</v>
       </c>
-      <c r="B10">
-        <v>30700</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="B10" s="2">
+        <v>30800</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
         <v>5</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>12</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="2">
         <v>31</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="2">
         <v>3000</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="2">
         <v>22</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="2">
         <v>38</v>
       </c>
-      <c r="N10">
-        <v>4</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
+      <c r="N10" s="2">
+        <v>3</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2">
         <v>99</v>
       </c>
-      <c r="Q10">
-        <v>1</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
+      <c r="Q10" s="2">
+        <v>1</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
         <v>5</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10" t="s">
+      <c r="T10" s="2">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="W10" t="s">
+      <c r="W10" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="X10" t="s">
+      <c r="X10" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="Y10" s="4" t="s">
+      <c r="Y10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="Z10">
-        <v>1</v>
+      <c r="Z10" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="2">
-        <f t="shared" si="0"/>
+    <row r="11" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <f>ROW()-2+2000</f>
         <v>2009</v>
       </c>
-      <c r="B11" s="2">
-        <v>30800</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
+      <c r="B11">
+        <v>3000</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>150</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>5</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11">
         <v>12</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11">
         <v>31</v>
       </c>
-      <c r="K11" s="2">
-        <v>3000</v>
-      </c>
-      <c r="L11" s="2">
-        <v>22</v>
-      </c>
-      <c r="M11" s="2">
-        <v>38</v>
-      </c>
-      <c r="N11" s="2">
-        <v>3</v>
-      </c>
-      <c r="O11" s="2">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2">
+      <c r="K11">
+        <v>5000</v>
+      </c>
+      <c r="L11">
+        <v>200</v>
+      </c>
+      <c r="M11">
+        <v>30</v>
+      </c>
+      <c r="N11">
+        <v>5</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
         <v>99</v>
       </c>
-      <c r="Q11" s="2">
-        <v>1</v>
-      </c>
-      <c r="R11" s="2">
-        <v>0</v>
-      </c>
-      <c r="S11" s="2">
-        <v>5</v>
-      </c>
-      <c r="T11" s="2">
-        <v>0</v>
-      </c>
-      <c r="U11" s="2">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="s">
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>10</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11" t="s">
         <v>120</v>
       </c>
-      <c r="W11" s="2" t="s">
+      <c r="W11" t="s">
         <v>124</v>
       </c>
-      <c r="X11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z11" s="2">
+      <c r="X11" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z11">
         <v>1</v>
       </c>
     </row>
@@ -4997,31 +4997,31 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f>ROW()-2+3000</f>
+        <f t="shared" ref="A2:A9" si="0">ROW()-2+3000</f>
         <v>3000</v>
       </c>
       <c r="B2">
-        <v>4000</v>
+        <v>40000</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>149</v>
+        <v>71</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>12</v>
@@ -5030,16 +5030,16 @@
         <v>31</v>
       </c>
       <c r="K2">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -5048,13 +5048,13 @@
         <v>99</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5069,10 +5069,10 @@
         <v>123</v>
       </c>
       <c r="X2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -5080,29 +5080,29 @@
     </row>
     <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
-        <f t="shared" ref="A3:A10" si="0">ROW()-2+3000</f>
+        <f t="shared" si="0"/>
         <v>3001</v>
       </c>
       <c r="B3">
-        <v>40000</v>
+        <v>40100</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>12</v>
@@ -5111,16 +5111,16 @@
         <v>31</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -5135,7 +5135,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5153,7 +5153,7 @@
         <v>118</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -5165,25 +5165,25 @@
         <v>3002</v>
       </c>
       <c r="B4">
-        <v>40100</v>
+        <v>40200</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>12</v>
@@ -5192,16 +5192,16 @@
         <v>31</v>
       </c>
       <c r="K4">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="L4">
         <v>30</v>
       </c>
       <c r="M4">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -5234,7 +5234,7 @@
         <v>118</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -5246,25 +5246,25 @@
         <v>3003</v>
       </c>
       <c r="B5">
-        <v>40200</v>
+        <v>40300</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>12</v>
@@ -5273,16 +5273,16 @@
         <v>31</v>
       </c>
       <c r="K5">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="L5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -5297,7 +5297,7 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5327,25 +5327,25 @@
         <v>3004</v>
       </c>
       <c r="B6">
-        <v>40300</v>
+        <v>40400</v>
       </c>
       <c r="C6" t="s">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>12</v>
@@ -5354,16 +5354,16 @@
         <v>31</v>
       </c>
       <c r="K6">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="L6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5408,25 +5408,25 @@
         <v>3005</v>
       </c>
       <c r="B7">
-        <v>40400</v>
+        <v>40500</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>12</v>
@@ -5435,16 +5435,16 @@
         <v>31</v>
       </c>
       <c r="K7">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="L7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -5489,19 +5489,19 @@
         <v>3006</v>
       </c>
       <c r="B8">
-        <v>40500</v>
+        <v>40600</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -5516,13 +5516,13 @@
         <v>31</v>
       </c>
       <c r="K8">
-        <v>700</v>
+        <v>1500</v>
       </c>
       <c r="L8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N8">
         <v>5</v>
@@ -5570,25 +5570,25 @@
         <v>3007</v>
       </c>
       <c r="B9">
-        <v>40600</v>
+        <v>40700</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>12</v>
@@ -5597,13 +5597,13 @@
         <v>31</v>
       </c>
       <c r="K9">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="L9">
         <v>32</v>
       </c>
       <c r="M9">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="N9">
         <v>5</v>
@@ -5621,7 +5621,7 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -5645,31 +5645,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+3000</f>
         <v>3008</v>
       </c>
       <c r="B10">
-        <v>40700</v>
+        <v>4000</v>
       </c>
       <c r="C10" t="s">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>12</v>
@@ -5678,13 +5678,13 @@
         <v>31</v>
       </c>
       <c r="K10">
-        <v>3000</v>
+        <v>7000</v>
       </c>
       <c r="L10">
-        <v>32</v>
+        <v>300</v>
       </c>
       <c r="M10">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="N10">
         <v>5</v>
@@ -5696,7 +5696,7 @@
         <v>99</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -5717,10 +5717,10 @@
         <v>123</v>
       </c>
       <c r="X10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z10">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5110BA-EFFA-406C-A7CA-1F06A3AB6576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A882A5A8-0D19-4865-818E-3645BB056CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="840" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="900" yWindow="690" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A882A5A8-0D19-4865-818E-3645BB056CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B8D79A-7718-412F-A2D6-AC0673C6B5CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="690" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2070" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B8D79A-7718-412F-A2D6-AC0673C6B5CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FFC14C-B079-4C73-A6A5-B1498BFFFAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2205" yWindow="1065" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -2861,7 +2861,7 @@
         <v>31</v>
       </c>
       <c r="K8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L8">
         <v>3</v>
@@ -2942,7 +2942,7 @@
         <v>31</v>
       </c>
       <c r="K9">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="L9">
         <v>5</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FFC14C-B079-4C73-A6A5-B1498BFFFAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FC538B-9084-488F-B713-5FE755E48F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="1065" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1425" yWindow="900" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -315,29 +315,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>至高のお菓子の決定戦
-主にチョコレートからランダムでお題が決められる</t>
-    <rPh sb="0" eb="2">
-      <t>シコウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>ケッテイセン</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>オモ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>英国ティータイムコンテスト</t>
     <rPh sb="0" eb="2">
       <t>エイコク</t>
@@ -1850,6 +1827,16 @@
     </rPh>
     <rPh sb="46" eb="48">
       <t>オウボ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黄色は、まだコンテスト優勝者セリフいれてない</t>
+    <rPh sb="0" eb="2">
+      <t>キイロ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ユウショウシャ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1887,7 +1874,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1906,6 +1893,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1921,7 +1914,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1933,6 +1926,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2321,19 +2320,19 @@
         <v>28</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>19</v>
@@ -2360,7 +2359,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -2408,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="X2" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="Y2" s="3" t="s">
         <v>20</v>
@@ -2441,7 +2440,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2489,13 +2488,13 @@
         <v>0</v>
       </c>
       <c r="V3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="X3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y3" s="4" t="s">
         <v>21</v>
@@ -2519,10 +2518,10 @@
         <v>30</v>
       </c>
       <c r="E4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2570,99 +2569,99 @@
         <v>0</v>
       </c>
       <c r="V4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="X4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5">
+    <row r="5" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>10800</v>
       </c>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="C5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>12</v>
+      </c>
+      <c r="J5" s="5">
+        <v>31</v>
+      </c>
+      <c r="K5" s="5">
+        <v>300</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2</v>
+      </c>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="5">
         <v>99</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>12</v>
-      </c>
-      <c r="J5">
-        <v>31</v>
-      </c>
-      <c r="K5">
-        <v>300</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>2</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>99</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
+      <c r="Q5" s="5">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
         <v>3</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5" t="s">
-        <v>112</v>
-      </c>
-      <c r="W5" t="s">
-        <v>116</v>
-      </c>
-      <c r="X5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y5" s="4" t="s">
+      <c r="T5" s="5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5">
+        <v>0</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2681,10 +2680,10 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2732,13 +2731,13 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="X6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y6" s="4" t="s">
         <v>24</v>
@@ -2762,10 +2761,10 @@
         <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2813,13 +2812,13 @@
         <v>0</v>
       </c>
       <c r="V7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="X7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y7" s="4" t="s">
         <v>21</v>
@@ -2843,10 +2842,10 @@
         <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2894,13 +2893,13 @@
         <v>0</v>
       </c>
       <c r="V8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="X8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y8" s="4" t="s">
         <v>21</v>
@@ -2924,10 +2923,10 @@
         <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2975,13 +2974,13 @@
         <v>0</v>
       </c>
       <c r="V9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="X9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y9" s="4" t="s">
         <v>21</v>
@@ -3005,10 +3004,10 @@
         <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3056,13 +3055,13 @@
         <v>0</v>
       </c>
       <c r="V10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="X10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y10" s="4" t="s">
         <v>21</v>
@@ -3071,84 +3070,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11">
+    <row r="11" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="5">
         <v>10700</v>
       </c>
-      <c r="C11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="C11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
+      <c r="E11" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
         <v>5</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="5">
         <v>12</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="5">
         <v>31</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="5">
         <v>3000</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="5">
         <v>5</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="5">
         <v>15</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="5">
         <v>5</v>
       </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
+      <c r="O11" s="5">
+        <v>0</v>
+      </c>
+      <c r="P11" s="5">
         <v>99</v>
       </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
+      <c r="Q11" s="5">
+        <v>1</v>
+      </c>
+      <c r="R11" s="5">
+        <v>0</v>
+      </c>
+      <c r="S11" s="5">
         <v>5</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11" t="s">
-        <v>112</v>
-      </c>
-      <c r="W11" t="s">
-        <v>116</v>
-      </c>
-      <c r="X11" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y11" s="4" t="s">
+      <c r="T11" s="5">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="W11" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="X11" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z11">
+      <c r="Z11" s="5">
         <v>1</v>
       </c>
     </row>
@@ -3233,19 +3232,19 @@
         <v>28</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>19</v>
@@ -3254,732 +3253,732 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2">
+    <row r="2" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="5">
         <f t="shared" ref="A2:A9" si="0">ROW()-2+1000</f>
         <v>1000</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="5">
         <v>20000</v>
       </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
+      <c r="E2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
         <v>2</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="5">
         <v>12</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="5">
         <v>31</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="5">
         <v>100</v>
       </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
+      <c r="L2" s="5">
+        <v>1</v>
+      </c>
+      <c r="M2" s="5">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5">
+        <v>1</v>
+      </c>
+      <c r="O2" s="5">
+        <v>1</v>
+      </c>
+      <c r="P2" s="5">
         <v>99</v>
       </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
+      <c r="Q2" s="5">
+        <v>1</v>
+      </c>
+      <c r="R2" s="5">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5">
         <v>3</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2" t="s">
-        <v>119</v>
-      </c>
-      <c r="W2" t="s">
-        <v>122</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="T2" s="5">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="W2" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3">
+    <row r="3" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="5">
         <f t="shared" si="0"/>
         <v>1001</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="5">
         <v>20100</v>
       </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
+      <c r="E3" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
         <v>2</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="5">
         <v>12</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="5">
         <v>31</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="5">
         <v>200</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="5">
         <v>10</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="5">
         <v>5</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="5">
         <v>2</v>
       </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="5">
         <v>99</v>
       </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
+      <c r="Q3" s="5">
+        <v>1</v>
+      </c>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
         <v>3</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3" t="s">
-        <v>119</v>
-      </c>
-      <c r="W3" t="s">
-        <v>122</v>
-      </c>
-      <c r="X3" t="s">
+      <c r="T3" s="5">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5">
+        <v>0</v>
+      </c>
+      <c r="V3" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="W3" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z3">
+      <c r="Z3" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4">
+    <row r="4" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="5">
         <f t="shared" si="0"/>
         <v>1002</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>20200</v>
       </c>
-      <c r="C4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
+      <c r="E4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="5">
         <v>12</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="5">
         <v>31</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="5">
         <v>300</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="5">
         <v>10</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="5">
         <v>5</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="5">
         <v>3</v>
       </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="5">
         <v>99</v>
       </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
+      <c r="Q4" s="5">
+        <v>1</v>
+      </c>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
         <v>3</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4" t="s">
-        <v>119</v>
-      </c>
-      <c r="W4" t="s">
-        <v>122</v>
-      </c>
-      <c r="X4" t="s">
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="W4" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5">
+    <row r="5" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>1003</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>20300</v>
       </c>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="E5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
         <v>3</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="5">
         <v>12</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="5">
         <v>31</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="5">
         <v>500</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="5">
         <v>11</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="5">
         <v>10</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="5">
         <v>3</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="5">
         <v>99</v>
       </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
+      <c r="Q5" s="5">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
         <v>3</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5" t="s">
-        <v>119</v>
-      </c>
-      <c r="W5" t="s">
-        <v>122</v>
-      </c>
-      <c r="X5" t="s">
+      <c r="T5" s="5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5">
+        <v>0</v>
+      </c>
+      <c r="V5" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="Y5" s="4" t="s">
+      <c r="W5" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6">
+    <row r="6" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>1004</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>20400</v>
       </c>
-      <c r="C6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
         <v>4</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="5">
         <v>12</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="5">
         <v>31</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="5">
         <v>1000</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="5">
         <v>11</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="5">
         <v>10</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="5">
         <v>4</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="5">
         <v>99</v>
       </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
+      <c r="Q6" s="5">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
         <v>5</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6" t="s">
-        <v>119</v>
-      </c>
-      <c r="W6" t="s">
-        <v>122</v>
-      </c>
-      <c r="X6" t="s">
+      <c r="T6" s="5">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="Y6" s="4" t="s">
+      <c r="W6" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7">
+    <row r="7" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>1005</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>20500</v>
       </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E7" t="s">
-        <v>103</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="E7" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
         <v>4</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="5">
         <v>12</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="5">
         <v>31</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="5">
         <v>1500</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="5">
         <v>10</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="5">
         <v>15</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="5">
         <v>4</v>
       </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="5">
         <v>99</v>
       </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
+      <c r="Q7" s="5">
+        <v>1</v>
+      </c>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
         <v>7</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7" t="s">
-        <v>119</v>
-      </c>
-      <c r="W7" t="s">
-        <v>122</v>
-      </c>
-      <c r="X7" t="s">
+      <c r="T7" s="5">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="Y7" s="4" t="s">
+      <c r="W7" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="X7" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8">
+    <row r="8" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>1006</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="5">
         <v>20600</v>
       </c>
-      <c r="C8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
+      <c r="E8" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
         <v>3</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="5">
         <v>12</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="5">
         <v>31</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="5">
         <v>2000</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="5">
         <v>12</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="5">
         <v>20</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="5">
         <v>4</v>
       </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="5">
         <v>99</v>
       </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
+      <c r="Q8" s="5">
+        <v>1</v>
+      </c>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
         <v>7</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8" t="s">
-        <v>119</v>
-      </c>
-      <c r="W8" t="s">
-        <v>122</v>
-      </c>
-      <c r="X8" t="s">
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="Y8" s="4" t="s">
+      <c r="W8" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="X8" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9">
+    <row r="9" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>1007</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="5">
         <v>20700</v>
       </c>
-      <c r="C9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="E9" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
         <v>5</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="5">
         <v>12</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="5">
         <v>31</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="5">
         <v>5000</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="5">
         <v>12</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="5">
         <v>35</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="5">
         <v>5</v>
       </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
+      <c r="O9" s="5">
+        <v>1</v>
+      </c>
+      <c r="P9" s="5">
         <v>99</v>
       </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
+      <c r="Q9" s="5">
+        <v>1</v>
+      </c>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
         <v>10</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9" t="s">
-        <v>119</v>
-      </c>
-      <c r="W9" t="s">
-        <v>122</v>
-      </c>
-      <c r="X9" t="s">
+      <c r="T9" s="5">
+        <v>0</v>
+      </c>
+      <c r="U9" s="5">
+        <v>0</v>
+      </c>
+      <c r="V9" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="Y9" s="4" t="s">
+      <c r="W9" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="X9" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10">
+    <row r="10" spans="1:26" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="5">
         <f>ROW()-2+1000</f>
         <v>1008</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="5">
         <v>2000</v>
       </c>
-      <c r="C10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="F10" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
         <v>5</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="5">
         <v>12</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="5">
         <v>31</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="5">
         <v>3000</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="5">
         <v>100</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="5">
         <v>15</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="5">
         <v>5</v>
       </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
+      <c r="O10" s="5">
+        <v>1</v>
+      </c>
+      <c r="P10" s="5">
         <v>99</v>
       </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
+      <c r="Q10" s="5">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5">
         <v>10</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10" t="s">
-        <v>119</v>
-      </c>
-      <c r="W10" t="s">
-        <v>122</v>
-      </c>
-      <c r="X10" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y10" s="4" t="s">
+      <c r="T10" s="5">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="Z10">
+      <c r="Z10" s="5">
         <v>1</v>
       </c>
     </row>
@@ -4064,19 +4063,19 @@
         <v>28</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>19</v>
@@ -4085,651 +4084,651 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2">
+    <row r="2" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="5">
         <f t="shared" ref="A2:A10" si="0">ROW()-2+2000</f>
         <v>2000</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="5">
         <v>30000</v>
       </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
+      <c r="E2" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5">
         <v>12</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="5">
         <v>31</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="5">
         <v>300</v>
       </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
+      <c r="L2" s="5">
+        <v>1</v>
+      </c>
+      <c r="M2" s="5">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5">
         <v>2</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
+      <c r="O2" s="5">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5">
         <v>99</v>
       </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
+      <c r="Q2" s="5">
+        <v>1</v>
+      </c>
+      <c r="R2" s="5">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5">
         <v>3</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2" t="s">
-        <v>120</v>
-      </c>
-      <c r="W2" t="s">
-        <v>124</v>
-      </c>
-      <c r="X2" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y2" s="4" t="s">
+      <c r="T2" s="5">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3">
+    <row r="3" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="5">
         <f t="shared" si="0"/>
         <v>2001</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="5">
         <v>30100</v>
       </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
+      <c r="E3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
         <v>2</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="5">
         <v>12</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="5">
         <v>31</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="5">
         <v>500</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="5">
         <v>20</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="5">
         <v>10</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="5">
         <v>2</v>
       </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="5">
         <v>99</v>
       </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
+      <c r="Q3" s="5">
+        <v>1</v>
+      </c>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
         <v>3</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3" t="s">
-        <v>120</v>
-      </c>
-      <c r="W3" t="s">
-        <v>124</v>
-      </c>
-      <c r="X3" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y3" s="4" t="s">
+      <c r="T3" s="5">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5">
+        <v>0</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z3">
+      <c r="Z3" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4">
+    <row r="4" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="5">
         <f t="shared" si="0"/>
         <v>2002</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>30200</v>
       </c>
-      <c r="C4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
+      <c r="E4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="5">
         <v>12</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="5">
         <v>31</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="5">
         <v>1200</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="5">
         <v>20</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="5">
         <v>20</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="5">
         <v>3</v>
       </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="5">
         <v>99</v>
       </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
+      <c r="Q4" s="5">
+        <v>1</v>
+      </c>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
         <v>5</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4" t="s">
-        <v>120</v>
-      </c>
-      <c r="W4" t="s">
-        <v>124</v>
-      </c>
-      <c r="X4" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y4" s="4" t="s">
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5">
+    <row r="5" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>2003</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>30300</v>
       </c>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="E5" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
         <v>4</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="5">
         <v>12</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="5">
         <v>31</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="5">
         <v>500</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="5">
         <v>20</v>
       </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
         <v>3</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="5">
         <v>99</v>
       </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
+      <c r="Q5" s="5">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
         <v>3</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5" t="s">
-        <v>120</v>
-      </c>
-      <c r="W5" t="s">
-        <v>124</v>
-      </c>
-      <c r="X5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y5" s="4" t="s">
+      <c r="T5" s="5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5">
+        <v>0</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6">
+    <row r="6" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>2004</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>30400</v>
       </c>
-      <c r="C6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
+      <c r="E6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
         <v>3</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="5">
         <v>12</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="5">
         <v>31</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="5">
         <v>1000</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="5">
         <v>21</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="5">
         <v>25</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="5">
         <v>4</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="5">
         <v>99</v>
       </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
+      <c r="Q6" s="5">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
         <v>3</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6" t="s">
-        <v>120</v>
-      </c>
-      <c r="W6" t="s">
-        <v>124</v>
-      </c>
-      <c r="X6" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y6" s="4" t="s">
+      <c r="T6" s="5">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7">
+    <row r="7" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>2005</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>30500</v>
       </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="E7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
         <v>5</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="5">
         <v>12</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="5">
         <v>31</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="5">
         <v>2000</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="5">
         <v>21</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="5">
         <v>30</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="5">
         <v>5</v>
       </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="5">
         <v>99</v>
       </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
+      <c r="Q7" s="5">
+        <v>1</v>
+      </c>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
         <v>5</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7" t="s">
-        <v>120</v>
-      </c>
-      <c r="W7" t="s">
-        <v>124</v>
-      </c>
-      <c r="X7" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y7" s="4" t="s">
+      <c r="T7" s="5">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="W7" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="X7" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8">
+    <row r="8" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>2006</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="5">
         <v>30600</v>
       </c>
-      <c r="C8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
+      <c r="E8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
         <v>3</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="5">
         <v>12</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="5">
         <v>31</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="5">
         <v>2000</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="5">
         <v>22</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="5">
         <v>35</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="5">
         <v>5</v>
       </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="5">
         <v>99</v>
       </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
+      <c r="Q8" s="5">
+        <v>1</v>
+      </c>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
         <v>5</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8" t="s">
-        <v>120</v>
-      </c>
-      <c r="W8" t="s">
-        <v>124</v>
-      </c>
-      <c r="X8" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y8" s="4" t="s">
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="W8" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="X8" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9">
+    <row r="9" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>2007</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="5">
         <v>30700</v>
       </c>
-      <c r="C9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="E9" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
         <v>5</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="5">
         <v>12</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="5">
         <v>31</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="5">
         <v>3000</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="5">
         <v>22</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="5">
         <v>38</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="5">
         <v>4</v>
       </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
+      <c r="O9" s="5">
+        <v>1</v>
+      </c>
+      <c r="P9" s="5">
         <v>99</v>
       </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
+      <c r="Q9" s="5">
+        <v>1</v>
+      </c>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
         <v>5</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9" t="s">
-        <v>120</v>
-      </c>
-      <c r="W9" t="s">
-        <v>124</v>
-      </c>
-      <c r="X9" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y9" s="4" t="s">
+      <c r="T9" s="5">
+        <v>0</v>
+      </c>
+      <c r="U9" s="5">
+        <v>0</v>
+      </c>
+      <c r="V9" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="W9" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="X9" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4745,13 +4744,13 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
@@ -4799,13 +4798,13 @@
         <v>0</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>21</v>
@@ -4814,84 +4813,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11">
+    <row r="11" spans="1:26" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="5">
         <f>ROW()-2+2000</f>
         <v>2009</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="5">
         <v>3000</v>
       </c>
-      <c r="C11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="C11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
         <v>5</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="5">
         <v>12</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="5">
         <v>31</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="5">
         <v>5000</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="5">
         <v>200</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="5">
         <v>30</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="5">
         <v>5</v>
       </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
+      <c r="O11" s="5">
+        <v>1</v>
+      </c>
+      <c r="P11" s="5">
         <v>99</v>
       </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
+      <c r="Q11" s="5">
+        <v>0</v>
+      </c>
+      <c r="R11" s="5">
+        <v>0</v>
+      </c>
+      <c r="S11" s="5">
         <v>10</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11" t="s">
-        <v>120</v>
-      </c>
-      <c r="W11" t="s">
-        <v>124</v>
-      </c>
-      <c r="X11" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y11" s="4" t="s">
+      <c r="T11" s="5">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="W11" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="X11" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="Z11">
+      <c r="Z11" s="5">
         <v>1</v>
       </c>
     </row>
@@ -4976,19 +4975,19 @@
         <v>28</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>19</v>
@@ -4997,732 +4996,732 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2">
+    <row r="2" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="5">
         <f t="shared" ref="A2:A9" si="0">ROW()-2+3000</f>
         <v>3000</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="5">
         <v>40000</v>
       </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
+      <c r="E2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5">
         <v>12</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="5">
         <v>31</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
+      <c r="K2" s="5">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5">
+        <v>1</v>
+      </c>
+      <c r="M2" s="5">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5">
+        <v>1</v>
+      </c>
+      <c r="O2" s="5">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5">
         <v>99</v>
       </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
+      <c r="Q2" s="5">
+        <v>1</v>
+      </c>
+      <c r="R2" s="5">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5">
         <v>3</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2" t="s">
-        <v>121</v>
-      </c>
-      <c r="W2" t="s">
-        <v>123</v>
-      </c>
-      <c r="X2" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y2" s="4" t="s">
+      <c r="T2" s="5">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3">
+    <row r="3" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="5">
         <f t="shared" si="0"/>
         <v>3001</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="5">
         <v>40100</v>
       </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
+      <c r="E3" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
         <v>2</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="5">
         <v>12</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="5">
         <v>31</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="5">
         <v>800</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="5">
         <v>30</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="5">
         <v>20</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="5">
         <v>3</v>
       </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="5">
         <v>99</v>
       </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
+      <c r="Q3" s="5">
+        <v>1</v>
+      </c>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
         <v>5</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3" t="s">
-        <v>121</v>
-      </c>
-      <c r="W3" t="s">
-        <v>123</v>
-      </c>
-      <c r="X3" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y3" s="4" t="s">
+      <c r="T3" s="5">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5">
+        <v>0</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z3">
+      <c r="Z3" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4">
+    <row r="4" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="5">
         <f t="shared" si="0"/>
         <v>3002</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>40200</v>
       </c>
-      <c r="C4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
+      <c r="E4" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="5">
         <v>12</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="5">
         <v>31</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="5">
         <v>1000</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="5">
         <v>30</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="5">
         <v>30</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="5">
         <v>4</v>
       </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="5">
         <v>99</v>
       </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
+      <c r="Q4" s="5">
+        <v>1</v>
+      </c>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
         <v>5</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4" t="s">
-        <v>121</v>
-      </c>
-      <c r="W4" t="s">
-        <v>123</v>
-      </c>
-      <c r="X4" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y4" s="4" t="s">
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5">
+    <row r="5" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>3003</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>40300</v>
       </c>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="E5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
         <v>2</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="5">
         <v>12</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="5">
         <v>31</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="5">
         <v>1200</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="5">
         <v>31</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="5">
         <v>40</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="5">
         <v>3</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="5">
         <v>99</v>
       </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
+      <c r="Q5" s="5">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
         <v>3</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5" t="s">
-        <v>121</v>
-      </c>
-      <c r="W5" t="s">
-        <v>123</v>
-      </c>
-      <c r="X5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y5" s="4" t="s">
+      <c r="T5" s="5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5">
+        <v>0</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6">
+    <row r="6" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3004</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>40400</v>
       </c>
-      <c r="C6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
         <v>3</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="5">
         <v>12</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="5">
         <v>31</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="5">
         <v>1000</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="5">
         <v>30</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="5">
         <v>50</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="5">
         <v>4</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="5">
         <v>99</v>
       </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
+      <c r="Q6" s="5">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
         <v>5</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6" t="s">
-        <v>121</v>
-      </c>
-      <c r="W6" t="s">
-        <v>123</v>
-      </c>
-      <c r="X6" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y6" s="4" t="s">
+      <c r="T6" s="5">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7">
+    <row r="7" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>3005</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>40500</v>
       </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
         <v>5</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="5">
         <v>12</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="5">
         <v>31</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="5">
         <v>700</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="5">
         <v>31</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="5">
         <v>55</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="5">
         <v>5</v>
       </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="5">
         <v>99</v>
       </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
+      <c r="Q7" s="5">
+        <v>1</v>
+      </c>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
         <v>5</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7" t="s">
-        <v>121</v>
-      </c>
-      <c r="W7" t="s">
-        <v>123</v>
-      </c>
-      <c r="X7" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y7" s="4" t="s">
+      <c r="T7" s="5">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="W7" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="X7" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8">
+    <row r="8" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>3006</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="5">
         <v>40600</v>
       </c>
-      <c r="C8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E8" t="s">
-        <v>81</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
+      <c r="E8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
         <v>5</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="5">
         <v>12</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="5">
         <v>31</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="5">
         <v>1500</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="5">
         <v>32</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="5">
         <v>60</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="5">
         <v>5</v>
       </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="5">
         <v>99</v>
       </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
+      <c r="Q8" s="5">
+        <v>1</v>
+      </c>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
         <v>5</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8" t="s">
-        <v>121</v>
-      </c>
-      <c r="W8" t="s">
-        <v>123</v>
-      </c>
-      <c r="X8" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y8" s="4" t="s">
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="W8" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="X8" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9">
+    <row r="9" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>3007</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="5">
         <v>40700</v>
       </c>
-      <c r="C9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E9" t="s">
-        <v>131</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="E9" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
         <v>6</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="5">
         <v>12</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="5">
         <v>31</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="5">
         <v>3000</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="5">
         <v>32</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="5">
         <v>65</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="5">
         <v>5</v>
       </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
+      <c r="O9" s="5">
+        <v>1</v>
+      </c>
+      <c r="P9" s="5">
         <v>99</v>
       </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
+      <c r="Q9" s="5">
+        <v>1</v>
+      </c>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
         <v>10</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9" t="s">
-        <v>121</v>
-      </c>
-      <c r="W9" t="s">
-        <v>123</v>
-      </c>
-      <c r="X9" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y9" s="4" t="s">
+      <c r="T9" s="5">
+        <v>0</v>
+      </c>
+      <c r="U9" s="5">
+        <v>0</v>
+      </c>
+      <c r="V9" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="W9" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="X9" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10">
+    <row r="10" spans="1:26" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="5">
         <f>ROW()-2+3000</f>
         <v>3008</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="5">
         <v>4000</v>
       </c>
-      <c r="C10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E10" t="s">
-        <v>149</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="E10" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
         <v>5</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="5">
         <v>12</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="5">
         <v>31</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="5">
         <v>7000</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="5">
         <v>300</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="5">
         <v>30</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="5">
         <v>5</v>
       </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
+      <c r="O10" s="5">
+        <v>1</v>
+      </c>
+      <c r="P10" s="5">
         <v>99</v>
       </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
+      <c r="Q10" s="5">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5">
         <v>10</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10" t="s">
-        <v>121</v>
-      </c>
-      <c r="W10" t="s">
-        <v>123</v>
-      </c>
-      <c r="X10" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y10" s="4" t="s">
+      <c r="T10" s="5">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="Z10">
+      <c r="Z10" s="5">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FC538B-9084-488F-B713-5FE755E48F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C9BBCE-40E5-49CB-A68B-B427E3966BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="900" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1770" yWindow="1245" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -1697,104 +1697,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>◆ケーキ・チョコレートの国際コンクール◆
-優勝者には、エデンのレシピを進呈します。虹のように、様々なチョコレートとケーキで参加してください！</t>
-    <rPh sb="12" eb="14">
-      <t>コクサイ</t>
-    </rPh>
-    <rPh sb="21" eb="24">
-      <t>ユウショウシャ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>シンテイ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>ニジ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>サマザマ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>サンカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>◆アカデミー至高のお菓子の決定戦◆
-トーナメント形式3回戦。各回ごとにお題があり。
-優勝者には、エデンのレシピを進呈します。至高の一品をお待ちしております！</t>
-    <rPh sb="6" eb="8">
-      <t>シコウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="13" eb="16">
-      <t>ケッテイセン</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ケイシキ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>カイセン</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>カクカイ</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="42" eb="45">
-      <t>ユウショウシャ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>シンテイ</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>シコウ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>イッピン</t>
-    </rPh>
-    <rPh sb="69" eb="70">
-      <t>マ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>◆世界のお菓子コンクール◆
-賞品には、エデンのレシピを進呈します。
-オランジーナ国で古くから開催されている、パティシエのナンバーワンを決める大会です。</t>
-    <rPh sb="1" eb="3">
-      <t>セカイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ショウヒン</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>シンテイ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>コク</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>フル</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>カイサイ</t>
-    </rPh>
-    <rPh sb="67" eb="68">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>タイカイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>自由課題
 冬の名物となる、雪国のお菓子を募集しています。
 どんな種類でも結構です！お気軽にご応募ください。</t>
@@ -1837,6 +1739,119 @@
     </rPh>
     <rPh sb="11" eb="14">
       <t>ユウショウシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆アカデミー至高のお菓子の決定戦◆
+トーナメント形式3回戦。各回ごとにお題があり。
+優勝者には、特別なレシピを進呈します。至高の一品をお待ちしております！</t>
+    <rPh sb="6" eb="8">
+      <t>シコウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ケッテイセン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カイセン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カクカイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="42" eb="45">
+      <t>ユウショウシャ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>トクベツ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>シンテイ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>シコウ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>イッピン</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆ケーキ・チョコレートの国際コンクール◆
+優勝者には、特別レシピを進呈します。自信のある様々なチョコレートとケーキで参加してください！</t>
+    <rPh sb="12" eb="14">
+      <t>コクサイ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>ユウショウシャ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>トクベツ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>シンテイ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>サマザマ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>サンカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆世界のお菓子コンクール◆
+オランジーナ国で古くから開催されている、パティシエのナンバーワンを決める大会です。
+誉れを求めて、ぜひ優勝を勝ち取ってください。</t>
+    <rPh sb="1" eb="3">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>コク</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>フル</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カイサイ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>タイカイ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>ホマレ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>ユウショウ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ト</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2359,7 +2374,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -3919,7 +3934,7 @@
         <v>29</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>
@@ -4831,7 +4846,7 @@
         <v>149</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G11" s="5">
         <v>0</v>
@@ -5014,7 +5029,7 @@
         <v>70</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G2" s="5">
         <v>0</v>
@@ -5662,7 +5677,7 @@
         <v>148</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C9BBCE-40E5-49CB-A68B-B427E3966BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2436D750-D5A3-4EFD-BF47-4C53D953C5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="1245" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -1929,7 +1929,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1947,6 +1947,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2599,84 +2605,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="5">
+    <row r="5" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="7">
         <v>10800</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
         <v>2</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="7">
         <v>12</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="7">
         <v>31</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="7">
         <v>300</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="7">
         <v>2</v>
       </c>
-      <c r="M5" s="5">
-        <v>1</v>
-      </c>
-      <c r="N5" s="5">
+      <c r="M5" s="7">
+        <v>1</v>
+      </c>
+      <c r="N5" s="7">
         <v>2</v>
       </c>
-      <c r="O5" s="5">
-        <v>0</v>
-      </c>
-      <c r="P5" s="5">
+      <c r="O5" s="7">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7">
         <v>99</v>
       </c>
-      <c r="Q5" s="5">
-        <v>1</v>
-      </c>
-      <c r="R5" s="5">
-        <v>0</v>
-      </c>
-      <c r="S5" s="5">
+      <c r="Q5" s="7">
+        <v>1</v>
+      </c>
+      <c r="R5" s="7">
+        <v>0</v>
+      </c>
+      <c r="S5" s="7">
         <v>3</v>
       </c>
-      <c r="T5" s="5">
-        <v>0</v>
-      </c>
-      <c r="U5" s="5">
-        <v>0</v>
-      </c>
-      <c r="V5" s="5" t="s">
+      <c r="T5" s="7">
+        <v>0</v>
+      </c>
+      <c r="U5" s="7">
+        <v>0</v>
+      </c>
+      <c r="V5" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="W5" s="5" t="s">
+      <c r="W5" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="X5" s="5" t="s">
+      <c r="X5" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Y5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="Z5" s="5">
+      <c r="Z5" s="7">
         <v>0</v>
       </c>
     </row>
@@ -3085,84 +3091,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="5">
+    <row r="11" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11">
         <v>10700</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="C11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G11" s="5">
-        <v>0</v>
-      </c>
-      <c r="H11" s="5">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>5</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11">
         <v>12</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11">
         <v>31</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11">
         <v>3000</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11">
         <v>5</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11">
         <v>15</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N11">
         <v>5</v>
       </c>
-      <c r="O11" s="5">
-        <v>0</v>
-      </c>
-      <c r="P11" s="5">
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
         <v>99</v>
       </c>
-      <c r="Q11" s="5">
-        <v>1</v>
-      </c>
-      <c r="R11" s="5">
-        <v>0</v>
-      </c>
-      <c r="S11" s="5">
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
         <v>5</v>
       </c>
-      <c r="T11" s="5">
-        <v>0</v>
-      </c>
-      <c r="U11" s="5">
-        <v>0</v>
-      </c>
-      <c r="V11" s="5" t="s">
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11" t="s">
         <v>111</v>
       </c>
-      <c r="W11" s="5" t="s">
+      <c r="W11" t="s">
         <v>115</v>
       </c>
-      <c r="X11" s="5" t="s">
+      <c r="X11" t="s">
         <v>117</v>
       </c>
-      <c r="Y11" s="6" t="s">
+      <c r="Y11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z11" s="5">
+      <c r="Z11">
         <v>1</v>
       </c>
     </row>
@@ -3268,651 +3274,651 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="5">
+    <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2">
         <f t="shared" ref="A2:A9" si="0">ROW()-2+1000</f>
         <v>1000</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2">
         <v>20000</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>2</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2">
         <v>12</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2">
         <v>31</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2">
         <v>100</v>
       </c>
-      <c r="L2" s="5">
-        <v>1</v>
-      </c>
-      <c r="M2" s="5">
-        <v>0</v>
-      </c>
-      <c r="N2" s="5">
-        <v>1</v>
-      </c>
-      <c r="O2" s="5">
-        <v>1</v>
-      </c>
-      <c r="P2" s="5">
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
         <v>99</v>
       </c>
-      <c r="Q2" s="5">
-        <v>1</v>
-      </c>
-      <c r="R2" s="5">
-        <v>0</v>
-      </c>
-      <c r="S2" s="5">
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <v>3</v>
       </c>
-      <c r="T2" s="5">
-        <v>0</v>
-      </c>
-      <c r="U2" s="5">
-        <v>0</v>
-      </c>
-      <c r="V2" s="5" t="s">
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2" t="s">
         <v>118</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="W2" t="s">
         <v>121</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="X2" t="s">
         <v>117</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="Y2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z2" s="5">
+      <c r="Z2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="5">
+    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3">
         <f t="shared" si="0"/>
         <v>1001</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3">
         <v>20100</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" t="s">
         <v>103</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3">
         <v>12</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3">
         <v>31</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3">
         <v>200</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3">
         <v>10</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3">
         <v>5</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3">
         <v>2</v>
       </c>
-      <c r="O3" s="5">
-        <v>1</v>
-      </c>
-      <c r="P3" s="5">
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
         <v>99</v>
       </c>
-      <c r="Q3" s="5">
-        <v>1</v>
-      </c>
-      <c r="R3" s="5">
-        <v>0</v>
-      </c>
-      <c r="S3" s="5">
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <v>3</v>
       </c>
-      <c r="T3" s="5">
-        <v>0</v>
-      </c>
-      <c r="U3" s="5">
-        <v>0</v>
-      </c>
-      <c r="V3" s="5" t="s">
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3" t="s">
         <v>118</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="W3" t="s">
         <v>121</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="X3" t="s">
         <v>117</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Y3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z3" s="5">
+      <c r="Z3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="5">
+    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4">
         <f t="shared" si="0"/>
         <v>1002</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>20200</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>3</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4">
         <v>12</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4">
         <v>31</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4">
         <v>300</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4">
         <v>10</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4">
         <v>5</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4">
         <v>3</v>
       </c>
-      <c r="O4" s="5">
-        <v>1</v>
-      </c>
-      <c r="P4" s="5">
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
         <v>99</v>
       </c>
-      <c r="Q4" s="5">
-        <v>1</v>
-      </c>
-      <c r="R4" s="5">
-        <v>0</v>
-      </c>
-      <c r="S4" s="5">
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>3</v>
       </c>
-      <c r="T4" s="5">
-        <v>0</v>
-      </c>
-      <c r="U4" s="5">
-        <v>0</v>
-      </c>
-      <c r="V4" s="5" t="s">
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4" t="s">
         <v>118</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="W4" t="s">
         <v>121</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="X4" t="s">
         <v>117</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Y4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z4" s="5">
+      <c r="Z4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="5">
+    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
         <f t="shared" si="0"/>
         <v>1003</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>20300</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>3</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5">
         <v>12</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5">
         <v>31</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5">
         <v>500</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5">
         <v>11</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5">
         <v>10</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N5">
         <v>3</v>
       </c>
-      <c r="O5" s="5">
-        <v>1</v>
-      </c>
-      <c r="P5" s="5">
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
         <v>99</v>
       </c>
-      <c r="Q5" s="5">
-        <v>1</v>
-      </c>
-      <c r="R5" s="5">
-        <v>0</v>
-      </c>
-      <c r="S5" s="5">
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>3</v>
       </c>
-      <c r="T5" s="5">
-        <v>0</v>
-      </c>
-      <c r="U5" s="5">
-        <v>0</v>
-      </c>
-      <c r="V5" s="5" t="s">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
         <v>118</v>
       </c>
-      <c r="W5" s="5" t="s">
+      <c r="W5" t="s">
         <v>121</v>
       </c>
-      <c r="X5" s="5" t="s">
+      <c r="X5" t="s">
         <v>117</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Y5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z5" s="5">
+      <c r="Z5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="5">
+    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6">
         <f t="shared" si="0"/>
         <v>1004</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>20400</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>4</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6">
         <v>12</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6">
         <v>31</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6">
         <v>1000</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6">
         <v>11</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6">
         <v>10</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6">
         <v>4</v>
       </c>
-      <c r="O6" s="5">
-        <v>1</v>
-      </c>
-      <c r="P6" s="5">
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
         <v>99</v>
       </c>
-      <c r="Q6" s="5">
-        <v>1</v>
-      </c>
-      <c r="R6" s="5">
-        <v>0</v>
-      </c>
-      <c r="S6" s="5">
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>5</v>
       </c>
-      <c r="T6" s="5">
-        <v>0</v>
-      </c>
-      <c r="U6" s="5">
-        <v>0</v>
-      </c>
-      <c r="V6" s="5" t="s">
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
         <v>118</v>
       </c>
-      <c r="W6" s="5" t="s">
+      <c r="W6" t="s">
         <v>121</v>
       </c>
-      <c r="X6" s="5" t="s">
+      <c r="X6" t="s">
         <v>117</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="Y6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z6" s="5">
+      <c r="Z6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="5">
+    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>1005</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>20500</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>4</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7">
         <v>12</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7">
         <v>31</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7">
         <v>1500</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7">
         <v>10</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7">
         <v>15</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7">
         <v>4</v>
       </c>
-      <c r="O7" s="5">
-        <v>1</v>
-      </c>
-      <c r="P7" s="5">
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
         <v>99</v>
       </c>
-      <c r="Q7" s="5">
-        <v>1</v>
-      </c>
-      <c r="R7" s="5">
-        <v>0</v>
-      </c>
-      <c r="S7" s="5">
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>7</v>
       </c>
-      <c r="T7" s="5">
-        <v>0</v>
-      </c>
-      <c r="U7" s="5">
-        <v>0</v>
-      </c>
-      <c r="V7" s="5" t="s">
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
         <v>118</v>
       </c>
-      <c r="W7" s="5" t="s">
+      <c r="W7" t="s">
         <v>121</v>
       </c>
-      <c r="X7" s="5" t="s">
+      <c r="X7" t="s">
         <v>117</v>
       </c>
-      <c r="Y7" s="6" t="s">
+      <c r="Y7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z7" s="5">
+      <c r="Z7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="5">
+    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>1006</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>20600</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="H8" s="5">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>3</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8">
         <v>12</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8">
         <v>31</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8">
         <v>2000</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8">
         <v>12</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8">
         <v>20</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8">
         <v>4</v>
       </c>
-      <c r="O8" s="5">
-        <v>1</v>
-      </c>
-      <c r="P8" s="5">
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
         <v>99</v>
       </c>
-      <c r="Q8" s="5">
-        <v>1</v>
-      </c>
-      <c r="R8" s="5">
-        <v>0</v>
-      </c>
-      <c r="S8" s="5">
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>7</v>
       </c>
-      <c r="T8" s="5">
-        <v>0</v>
-      </c>
-      <c r="U8" s="5">
-        <v>0</v>
-      </c>
-      <c r="V8" s="5" t="s">
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8" t="s">
         <v>118</v>
       </c>
-      <c r="W8" s="5" t="s">
+      <c r="W8" t="s">
         <v>121</v>
       </c>
-      <c r="X8" s="5" t="s">
+      <c r="X8" t="s">
         <v>117</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="Y8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z8" s="5">
+      <c r="Z8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="5">
+    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9">
         <f t="shared" si="0"/>
         <v>1007</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9">
         <v>20700</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>5</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9">
         <v>12</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9">
         <v>31</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9">
         <v>5000</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9">
         <v>12</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9">
         <v>35</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9">
         <v>5</v>
       </c>
-      <c r="O9" s="5">
-        <v>1</v>
-      </c>
-      <c r="P9" s="5">
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
         <v>99</v>
       </c>
-      <c r="Q9" s="5">
-        <v>1</v>
-      </c>
-      <c r="R9" s="5">
-        <v>0</v>
-      </c>
-      <c r="S9" s="5">
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>10</v>
       </c>
-      <c r="T9" s="5">
-        <v>0</v>
-      </c>
-      <c r="U9" s="5">
-        <v>0</v>
-      </c>
-      <c r="V9" s="5" t="s">
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
         <v>118</v>
       </c>
-      <c r="W9" s="5" t="s">
+      <c r="W9" t="s">
         <v>121</v>
       </c>
-      <c r="X9" s="5" t="s">
+      <c r="X9" t="s">
         <v>117</v>
       </c>
-      <c r="Y9" s="6" t="s">
+      <c r="Y9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z9" s="5">
+      <c r="Z9">
         <v>0</v>
       </c>
     </row>
@@ -4099,651 +4105,651 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="5">
+    <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2">
         <f t="shared" ref="A2:A10" si="0">ROW()-2+2000</f>
         <v>2000</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2">
         <v>30000</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
-        <v>1</v>
-      </c>
-      <c r="I2" s="5">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>12</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2">
         <v>31</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2">
         <v>300</v>
       </c>
-      <c r="L2" s="5">
-        <v>1</v>
-      </c>
-      <c r="M2" s="5">
-        <v>0</v>
-      </c>
-      <c r="N2" s="5">
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
         <v>2</v>
       </c>
-      <c r="O2" s="5">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
         <v>99</v>
       </c>
-      <c r="Q2" s="5">
-        <v>1</v>
-      </c>
-      <c r="R2" s="5">
-        <v>0</v>
-      </c>
-      <c r="S2" s="5">
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <v>3</v>
       </c>
-      <c r="T2" s="5">
-        <v>0</v>
-      </c>
-      <c r="U2" s="5">
-        <v>0</v>
-      </c>
-      <c r="V2" s="5" t="s">
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2" t="s">
         <v>119</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="W2" t="s">
         <v>123</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="X2" t="s">
         <v>117</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="Y2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z2" s="5">
+      <c r="Z2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="5">
+    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3">
         <f t="shared" si="0"/>
         <v>2001</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3">
         <v>30100</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" t="s">
         <v>83</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3">
         <v>12</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3">
         <v>31</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3">
         <v>500</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3">
         <v>20</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3">
         <v>10</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3">
         <v>2</v>
       </c>
-      <c r="O3" s="5">
-        <v>1</v>
-      </c>
-      <c r="P3" s="5">
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
         <v>99</v>
       </c>
-      <c r="Q3" s="5">
-        <v>1</v>
-      </c>
-      <c r="R3" s="5">
-        <v>0</v>
-      </c>
-      <c r="S3" s="5">
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <v>3</v>
       </c>
-      <c r="T3" s="5">
-        <v>0</v>
-      </c>
-      <c r="U3" s="5">
-        <v>0</v>
-      </c>
-      <c r="V3" s="5" t="s">
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3" t="s">
         <v>119</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="W3" t="s">
         <v>123</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="X3" t="s">
         <v>117</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Y3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z3" s="5">
+      <c r="Z3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="5">
+    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4">
         <f t="shared" si="0"/>
         <v>2002</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>30200</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>3</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4">
         <v>12</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4">
         <v>31</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4">
         <v>1200</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4">
         <v>20</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4">
         <v>20</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4">
         <v>3</v>
       </c>
-      <c r="O4" s="5">
-        <v>1</v>
-      </c>
-      <c r="P4" s="5">
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
         <v>99</v>
       </c>
-      <c r="Q4" s="5">
-        <v>1</v>
-      </c>
-      <c r="R4" s="5">
-        <v>0</v>
-      </c>
-      <c r="S4" s="5">
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>5</v>
       </c>
-      <c r="T4" s="5">
-        <v>0</v>
-      </c>
-      <c r="U4" s="5">
-        <v>0</v>
-      </c>
-      <c r="V4" s="5" t="s">
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4" t="s">
         <v>119</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="W4" t="s">
         <v>123</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="X4" t="s">
         <v>117</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Y4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z4" s="5">
+      <c r="Z4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="5">
+    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
         <f t="shared" si="0"/>
         <v>2003</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>30300</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>4</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5">
         <v>12</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5">
         <v>31</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5">
         <v>500</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5">
         <v>20</v>
       </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-      <c r="N5" s="5">
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
         <v>3</v>
       </c>
-      <c r="O5" s="5">
-        <v>1</v>
-      </c>
-      <c r="P5" s="5">
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
         <v>99</v>
       </c>
-      <c r="Q5" s="5">
-        <v>1</v>
-      </c>
-      <c r="R5" s="5">
-        <v>0</v>
-      </c>
-      <c r="S5" s="5">
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>3</v>
       </c>
-      <c r="T5" s="5">
-        <v>0</v>
-      </c>
-      <c r="U5" s="5">
-        <v>0</v>
-      </c>
-      <c r="V5" s="5" t="s">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
         <v>119</v>
       </c>
-      <c r="W5" s="5" t="s">
+      <c r="W5" t="s">
         <v>123</v>
       </c>
-      <c r="X5" s="5" t="s">
+      <c r="X5" t="s">
         <v>117</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Y5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z5" s="5">
+      <c r="Z5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="5">
+    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6">
         <f t="shared" si="0"/>
         <v>2004</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>30400</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>3</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6">
         <v>12</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6">
         <v>31</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6">
         <v>1000</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6">
         <v>21</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6">
         <v>25</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6">
         <v>4</v>
       </c>
-      <c r="O6" s="5">
-        <v>1</v>
-      </c>
-      <c r="P6" s="5">
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
         <v>99</v>
       </c>
-      <c r="Q6" s="5">
-        <v>1</v>
-      </c>
-      <c r="R6" s="5">
-        <v>0</v>
-      </c>
-      <c r="S6" s="5">
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>3</v>
       </c>
-      <c r="T6" s="5">
-        <v>0</v>
-      </c>
-      <c r="U6" s="5">
-        <v>0</v>
-      </c>
-      <c r="V6" s="5" t="s">
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
         <v>119</v>
       </c>
-      <c r="W6" s="5" t="s">
+      <c r="W6" t="s">
         <v>123</v>
       </c>
-      <c r="X6" s="5" t="s">
+      <c r="X6" t="s">
         <v>117</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="Y6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z6" s="5">
+      <c r="Z6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="5">
+    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>2005</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>30500</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" t="s">
         <v>86</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>5</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7">
         <v>12</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7">
         <v>31</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7">
         <v>2000</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7">
         <v>21</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7">
         <v>30</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7">
         <v>5</v>
       </c>
-      <c r="O7" s="5">
-        <v>1</v>
-      </c>
-      <c r="P7" s="5">
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
         <v>99</v>
       </c>
-      <c r="Q7" s="5">
-        <v>1</v>
-      </c>
-      <c r="R7" s="5">
-        <v>0</v>
-      </c>
-      <c r="S7" s="5">
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>5</v>
       </c>
-      <c r="T7" s="5">
-        <v>0</v>
-      </c>
-      <c r="U7" s="5">
-        <v>0</v>
-      </c>
-      <c r="V7" s="5" t="s">
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
         <v>119</v>
       </c>
-      <c r="W7" s="5" t="s">
+      <c r="W7" t="s">
         <v>123</v>
       </c>
-      <c r="X7" s="5" t="s">
+      <c r="X7" t="s">
         <v>117</v>
       </c>
-      <c r="Y7" s="6" t="s">
+      <c r="Y7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z7" s="5">
+      <c r="Z7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="5">
+    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>2006</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>30600</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" t="s">
         <v>87</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="H8" s="5">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>3</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8">
         <v>12</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8">
         <v>31</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8">
         <v>2000</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8">
         <v>22</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8">
         <v>35</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8">
         <v>5</v>
       </c>
-      <c r="O8" s="5">
-        <v>1</v>
-      </c>
-      <c r="P8" s="5">
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
         <v>99</v>
       </c>
-      <c r="Q8" s="5">
-        <v>1</v>
-      </c>
-      <c r="R8" s="5">
-        <v>0</v>
-      </c>
-      <c r="S8" s="5">
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>5</v>
       </c>
-      <c r="T8" s="5">
-        <v>0</v>
-      </c>
-      <c r="U8" s="5">
-        <v>0</v>
-      </c>
-      <c r="V8" s="5" t="s">
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8" t="s">
         <v>119</v>
       </c>
-      <c r="W8" s="5" t="s">
+      <c r="W8" t="s">
         <v>123</v>
       </c>
-      <c r="X8" s="5" t="s">
+      <c r="X8" t="s">
         <v>117</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="Y8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z8" s="5">
+      <c r="Z8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="5">
+    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9">
         <f t="shared" si="0"/>
         <v>2007</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9">
         <v>30700</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" t="s">
         <v>74</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>5</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9">
         <v>12</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9">
         <v>31</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9">
         <v>3000</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9">
         <v>22</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9">
         <v>38</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9">
         <v>4</v>
       </c>
-      <c r="O9" s="5">
-        <v>1</v>
-      </c>
-      <c r="P9" s="5">
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
         <v>99</v>
       </c>
-      <c r="Q9" s="5">
-        <v>1</v>
-      </c>
-      <c r="R9" s="5">
-        <v>0</v>
-      </c>
-      <c r="S9" s="5">
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>5</v>
       </c>
-      <c r="T9" s="5">
-        <v>0</v>
-      </c>
-      <c r="U9" s="5">
-        <v>0</v>
-      </c>
-      <c r="V9" s="5" t="s">
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
         <v>119</v>
       </c>
-      <c r="W9" s="5" t="s">
+      <c r="W9" t="s">
         <v>123</v>
       </c>
-      <c r="X9" s="5" t="s">
+      <c r="X9" t="s">
         <v>117</v>
       </c>
-      <c r="Y9" s="6" t="s">
+      <c r="Y9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z9" s="5">
+      <c r="Z9">
         <v>0</v>
       </c>
     </row>
@@ -5011,651 +5017,651 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="5">
+    <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2">
         <f t="shared" ref="A2:A9" si="0">ROW()-2+3000</f>
         <v>3000</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2">
         <v>40000</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
-        <v>1</v>
-      </c>
-      <c r="I2" s="5">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>12</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2">
         <v>31</v>
       </c>
-      <c r="K2" s="5">
-        <v>0</v>
-      </c>
-      <c r="L2" s="5">
-        <v>1</v>
-      </c>
-      <c r="M2" s="5">
-        <v>0</v>
-      </c>
-      <c r="N2" s="5">
-        <v>1</v>
-      </c>
-      <c r="O2" s="5">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
         <v>99</v>
       </c>
-      <c r="Q2" s="5">
-        <v>1</v>
-      </c>
-      <c r="R2" s="5">
-        <v>0</v>
-      </c>
-      <c r="S2" s="5">
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <v>3</v>
       </c>
-      <c r="T2" s="5">
-        <v>0</v>
-      </c>
-      <c r="U2" s="5">
-        <v>0</v>
-      </c>
-      <c r="V2" s="5" t="s">
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2" t="s">
         <v>120</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="W2" t="s">
         <v>122</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="X2" t="s">
         <v>117</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="Y2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z2" s="5">
+      <c r="Z2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="5">
+    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3">
         <f t="shared" si="0"/>
         <v>3001</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3">
         <v>40100</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3">
         <v>12</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3">
         <v>31</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3">
         <v>800</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3">
         <v>30</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3">
         <v>20</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3">
         <v>3</v>
       </c>
-      <c r="O3" s="5">
-        <v>1</v>
-      </c>
-      <c r="P3" s="5">
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
         <v>99</v>
       </c>
-      <c r="Q3" s="5">
-        <v>1</v>
-      </c>
-      <c r="R3" s="5">
-        <v>0</v>
-      </c>
-      <c r="S3" s="5">
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <v>5</v>
       </c>
-      <c r="T3" s="5">
-        <v>0</v>
-      </c>
-      <c r="U3" s="5">
-        <v>0</v>
-      </c>
-      <c r="V3" s="5" t="s">
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3" t="s">
         <v>120</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="W3" t="s">
         <v>122</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="X3" t="s">
         <v>117</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Y3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z3" s="5">
+      <c r="Z3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="5">
+    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4">
         <f t="shared" si="0"/>
         <v>3002</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>40200</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>3</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4">
         <v>12</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4">
         <v>31</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4">
         <v>1000</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4">
         <v>30</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4">
         <v>30</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4">
         <v>4</v>
       </c>
-      <c r="O4" s="5">
-        <v>1</v>
-      </c>
-      <c r="P4" s="5">
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
         <v>99</v>
       </c>
-      <c r="Q4" s="5">
-        <v>1</v>
-      </c>
-      <c r="R4" s="5">
-        <v>0</v>
-      </c>
-      <c r="S4" s="5">
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>5</v>
       </c>
-      <c r="T4" s="5">
-        <v>0</v>
-      </c>
-      <c r="U4" s="5">
-        <v>0</v>
-      </c>
-      <c r="V4" s="5" t="s">
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4" t="s">
         <v>120</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="W4" t="s">
         <v>122</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="X4" t="s">
         <v>117</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Y4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z4" s="5">
+      <c r="Z4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="5">
+    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
         <f t="shared" si="0"/>
         <v>3003</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>40300</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" t="s">
         <v>100</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>2</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5">
         <v>12</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5">
         <v>31</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5">
         <v>1200</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5">
         <v>31</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5">
         <v>40</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N5">
         <v>3</v>
       </c>
-      <c r="O5" s="5">
-        <v>1</v>
-      </c>
-      <c r="P5" s="5">
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
         <v>99</v>
       </c>
-      <c r="Q5" s="5">
-        <v>1</v>
-      </c>
-      <c r="R5" s="5">
-        <v>0</v>
-      </c>
-      <c r="S5" s="5">
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>3</v>
       </c>
-      <c r="T5" s="5">
-        <v>0</v>
-      </c>
-      <c r="U5" s="5">
-        <v>0</v>
-      </c>
-      <c r="V5" s="5" t="s">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
         <v>120</v>
       </c>
-      <c r="W5" s="5" t="s">
+      <c r="W5" t="s">
         <v>122</v>
       </c>
-      <c r="X5" s="5" t="s">
+      <c r="X5" t="s">
         <v>117</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Y5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z5" s="5">
+      <c r="Z5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="5">
+    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6">
         <f t="shared" si="0"/>
         <v>3004</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>40400</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" t="s">
         <v>144</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>3</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6">
         <v>12</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6">
         <v>31</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6">
         <v>1000</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6">
         <v>30</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6">
         <v>50</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6">
         <v>4</v>
       </c>
-      <c r="O6" s="5">
-        <v>1</v>
-      </c>
-      <c r="P6" s="5">
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
         <v>99</v>
       </c>
-      <c r="Q6" s="5">
-        <v>1</v>
-      </c>
-      <c r="R6" s="5">
-        <v>0</v>
-      </c>
-      <c r="S6" s="5">
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>5</v>
       </c>
-      <c r="T6" s="5">
-        <v>0</v>
-      </c>
-      <c r="U6" s="5">
-        <v>0</v>
-      </c>
-      <c r="V6" s="5" t="s">
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
         <v>120</v>
       </c>
-      <c r="W6" s="5" t="s">
+      <c r="W6" t="s">
         <v>122</v>
       </c>
-      <c r="X6" s="5" t="s">
+      <c r="X6" t="s">
         <v>117</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="Y6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z6" s="5">
+      <c r="Z6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="5">
+    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>3005</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>40500</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>5</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7">
         <v>12</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7">
         <v>31</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7">
         <v>700</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7">
         <v>31</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7">
         <v>55</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7">
         <v>5</v>
       </c>
-      <c r="O7" s="5">
-        <v>1</v>
-      </c>
-      <c r="P7" s="5">
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
         <v>99</v>
       </c>
-      <c r="Q7" s="5">
-        <v>1</v>
-      </c>
-      <c r="R7" s="5">
-        <v>0</v>
-      </c>
-      <c r="S7" s="5">
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>5</v>
       </c>
-      <c r="T7" s="5">
-        <v>0</v>
-      </c>
-      <c r="U7" s="5">
-        <v>0</v>
-      </c>
-      <c r="V7" s="5" t="s">
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
         <v>120</v>
       </c>
-      <c r="W7" s="5" t="s">
+      <c r="W7" t="s">
         <v>122</v>
       </c>
-      <c r="X7" s="5" t="s">
+      <c r="X7" t="s">
         <v>117</v>
       </c>
-      <c r="Y7" s="6" t="s">
+      <c r="Y7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z7" s="5">
+      <c r="Z7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="5">
+    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>3006</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>40600</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="H8" s="5">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8">
         <v>12</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8">
         <v>31</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8">
         <v>1500</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8">
         <v>32</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8">
         <v>60</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8">
         <v>5</v>
       </c>
-      <c r="O8" s="5">
-        <v>1</v>
-      </c>
-      <c r="P8" s="5">
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
         <v>99</v>
       </c>
-      <c r="Q8" s="5">
-        <v>1</v>
-      </c>
-      <c r="R8" s="5">
-        <v>0</v>
-      </c>
-      <c r="S8" s="5">
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>5</v>
       </c>
-      <c r="T8" s="5">
-        <v>0</v>
-      </c>
-      <c r="U8" s="5">
-        <v>0</v>
-      </c>
-      <c r="V8" s="5" t="s">
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8" t="s">
         <v>120</v>
       </c>
-      <c r="W8" s="5" t="s">
+      <c r="W8" t="s">
         <v>122</v>
       </c>
-      <c r="X8" s="5" t="s">
+      <c r="X8" t="s">
         <v>117</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="Y8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z8" s="5">
+      <c r="Z8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="5">
+    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9">
         <f t="shared" si="0"/>
         <v>3007</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9">
         <v>40700</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" t="s">
         <v>130</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>6</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9">
         <v>12</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9">
         <v>31</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9">
         <v>3000</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9">
         <v>32</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9">
         <v>65</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9">
         <v>5</v>
       </c>
-      <c r="O9" s="5">
-        <v>1</v>
-      </c>
-      <c r="P9" s="5">
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
         <v>99</v>
       </c>
-      <c r="Q9" s="5">
-        <v>1</v>
-      </c>
-      <c r="R9" s="5">
-        <v>0</v>
-      </c>
-      <c r="S9" s="5">
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>10</v>
       </c>
-      <c r="T9" s="5">
-        <v>0</v>
-      </c>
-      <c r="U9" s="5">
-        <v>0</v>
-      </c>
-      <c r="V9" s="5" t="s">
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
         <v>120</v>
       </c>
-      <c r="W9" s="5" t="s">
+      <c r="W9" t="s">
         <v>122</v>
       </c>
-      <c r="X9" s="5" t="s">
+      <c r="X9" t="s">
         <v>117</v>
       </c>
-      <c r="Y9" s="6" t="s">
+      <c r="Y9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z9" s="5">
+      <c r="Z9">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2436D750-D5A3-4EFD-BF47-4C53D953C5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7866610E-D4AC-4767-810E-408C044D27E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -1929,7 +1929,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1947,12 +1947,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2605,84 +2599,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="7">
+    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5">
         <v>10800</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" t="s">
         <v>77</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="7">
-        <v>0</v>
-      </c>
-      <c r="H5" s="7">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>2</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5">
         <v>12</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5">
         <v>31</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5">
         <v>300</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5">
         <v>2</v>
       </c>
-      <c r="M5" s="7">
-        <v>1</v>
-      </c>
-      <c r="N5" s="7">
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
         <v>2</v>
       </c>
-      <c r="O5" s="7">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7">
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
         <v>99</v>
       </c>
-      <c r="Q5" s="7">
-        <v>1</v>
-      </c>
-      <c r="R5" s="7">
-        <v>0</v>
-      </c>
-      <c r="S5" s="7">
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>3</v>
       </c>
-      <c r="T5" s="7">
-        <v>0</v>
-      </c>
-      <c r="U5" s="7">
-        <v>0</v>
-      </c>
-      <c r="V5" s="7" t="s">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
         <v>111</v>
       </c>
-      <c r="W5" s="7" t="s">
+      <c r="W5" t="s">
         <v>115</v>
       </c>
-      <c r="X5" s="7" t="s">
+      <c r="X5" t="s">
         <v>117</v>
       </c>
-      <c r="Y5" s="8" t="s">
+      <c r="Y5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z5" s="7">
+      <c r="Z5">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7866610E-D4AC-4767-810E-408C044D27E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEFAE32-F29C-442E-95C7-96A2DC839053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
@@ -2263,7 +2263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -3163,6 +3163,87 @@
         <v>21</v>
       </c>
       <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="5">
+        <f>ROW()-2</f>
+        <v>10</v>
+      </c>
+      <c r="B12" s="5">
+        <v>2000</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>5</v>
+      </c>
+      <c r="I12" s="5">
+        <v>12</v>
+      </c>
+      <c r="J12" s="5">
+        <v>31</v>
+      </c>
+      <c r="K12" s="5">
+        <v>3000</v>
+      </c>
+      <c r="L12" s="5">
+        <v>100</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>5</v>
+      </c>
+      <c r="O12" s="5">
+        <v>1</v>
+      </c>
+      <c r="P12" s="5">
+        <v>99</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>0</v>
+      </c>
+      <c r="R12" s="5">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5">
+        <v>10</v>
+      </c>
+      <c r="T12" s="5">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="W12" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="X12" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z12" s="5">
         <v>1</v>
       </c>
     </row>
@@ -3175,7 +3256,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B615D1EB-7EB0-40A6-B71A-0773034D7CD2}">
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -3913,87 +3994,6 @@
         <v>21</v>
       </c>
       <c r="Z9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="5">
-        <f>ROW()-2+1000</f>
-        <v>1008</v>
-      </c>
-      <c r="B10" s="5">
-        <v>2000</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5">
-        <v>5</v>
-      </c>
-      <c r="I10" s="5">
-        <v>12</v>
-      </c>
-      <c r="J10" s="5">
-        <v>31</v>
-      </c>
-      <c r="K10" s="5">
-        <v>3000</v>
-      </c>
-      <c r="L10" s="5">
-        <v>100</v>
-      </c>
-      <c r="M10" s="5">
-        <v>15</v>
-      </c>
-      <c r="N10" s="5">
-        <v>5</v>
-      </c>
-      <c r="O10" s="5">
-        <v>1</v>
-      </c>
-      <c r="P10" s="5">
-        <v>99</v>
-      </c>
-      <c r="Q10" s="5">
-        <v>0</v>
-      </c>
-      <c r="R10" s="5">
-        <v>0</v>
-      </c>
-      <c r="S10" s="5">
-        <v>10</v>
-      </c>
-      <c r="T10" s="5">
-        <v>0</v>
-      </c>
-      <c r="U10" s="5">
-        <v>0</v>
-      </c>
-      <c r="V10" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="W10" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="X10" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z10" s="5">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEFAE32-F29C-442E-95C7-96A2DC839053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921A2572-1323-4840-871D-611BDE6E1B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1275" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -1743,51 +1743,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>◆アカデミー至高のお菓子の決定戦◆
-トーナメント形式3回戦。各回ごとにお題があり。
-優勝者には、特別なレシピを進呈します。至高の一品をお待ちしております！</t>
-    <rPh sb="6" eb="8">
-      <t>シコウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="13" eb="16">
-      <t>ケッテイセン</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ケイシキ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>カイセン</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>カクカイ</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="42" eb="45">
-      <t>ユウショウシャ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>トクベツ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>シンテイ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>シコウ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>イッピン</t>
-    </rPh>
-    <rPh sb="68" eb="69">
-      <t>マ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>◆ケーキ・チョコレートの国際コンクール◆
 優勝者には、特別レシピを進呈します。自信のある様々なチョコレートとケーキで参加してください！</t>
     <rPh sb="12" eb="14">
@@ -1852,6 +1807,42 @@
     </rPh>
     <rPh sb="70" eb="71">
       <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆アカデミー至高のお菓子の決定戦◆
+テーマ：自由課題
+優勝者には、特別なレシピを進呈します。至高の一品をお待ちしております！</t>
+    <rPh sb="6" eb="8">
+      <t>シコウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ケッテイセン</t>
+    </rPh>
+    <rPh sb="22" eb="26">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>ユウショウシャ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>トクベツ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>シンテイ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>シコウ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>イッピン</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>マ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2461,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>12</v>
@@ -2542,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>12</v>
@@ -3184,7 +3175,7 @@
         <v>29</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G12" s="5">
         <v>0</v>
@@ -3199,7 +3190,7 @@
         <v>31</v>
       </c>
       <c r="K12" s="5">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5">
         <v>100</v>
@@ -3223,7 +3214,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T12" s="5">
         <v>0</v>
@@ -3973,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -4846,7 +4837,7 @@
         <v>149</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G11" s="5">
         <v>0</v>
@@ -4885,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T11" s="5">
         <v>0</v>
@@ -5677,7 +5668,7 @@
         <v>148</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>
@@ -5716,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T10" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921A2572-1323-4840-871D-611BDE6E1B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6773D509-1802-4292-AEEB-A0F03AD7780C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2610" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6773D509-1802-4292-AEEB-A0F03AD7780C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65AA9DC-A4F1-4A9D-AC6E-5E47EDD502E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3015" yWindow="1170" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="157">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -1844,6 +1844,14 @@
     <rPh sb="53" eb="54">
       <t>マ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サマードリームスフェスティバル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Or_Contest_999</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2353,13 +2361,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="2">
-        <v>1000</v>
+        <v>9999</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>156</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -3163,13 +3171,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="5">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>29</v>
@@ -3247,7 +3255,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B615D1EB-7EB0-40A6-B71A-0773034D7CD2}">
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -3909,7 +3917,7 @@
     </row>
     <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+1000</f>
         <v>1007</v>
       </c>
       <c r="B9">
@@ -3985,6 +3993,87 @@
         <v>21</v>
       </c>
       <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="5">
+        <f>ROW()-2+1000</f>
+        <v>1008</v>
+      </c>
+      <c r="B10" s="5">
+        <v>2000</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>5</v>
+      </c>
+      <c r="I10" s="5">
+        <v>12</v>
+      </c>
+      <c r="J10" s="5">
+        <v>31</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>100</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>5</v>
+      </c>
+      <c r="O10" s="5">
+        <v>1</v>
+      </c>
+      <c r="P10" s="5">
+        <v>99</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z10" s="5">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65AA9DC-A4F1-4A9D-AC6E-5E47EDD502E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8595061-FAF3-474E-91E6-B70F762B13D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3015" yWindow="1170" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2430" yWindow="1035" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -3231,10 +3231,10 @@
         <v>0</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="W12" s="5" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="X12" s="5" t="s">
         <v>116</v>
@@ -3350,7 +3350,7 @@
     </row>
     <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A9" si="0">ROW()-2+1000</f>
+        <f t="shared" ref="A2:A8" si="0">ROW()-2+1000</f>
         <v>1000</v>
       </c>
       <c r="B2">

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8595061-FAF3-474E-91E6-B70F762B13D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5973E3C-48A4-45A9-90CF-C7B6C65BDDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2430" yWindow="1035" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2430" yWindow="1035" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -3468,7 +3468,7 @@
         <v>10</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N3">
         <v>2</v>
@@ -3630,7 +3630,7 @@
         <v>11</v>
       </c>
       <c r="M5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N5">
         <v>3</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5973E3C-48A4-45A9-90CF-C7B6C65BDDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E798B557-E026-40D2-8A72-660C2AFD9E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2430" yWindow="1035" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2340" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -792,39 +792,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ジュース限定
-ビーチで泳ぐ美女に、オシャレな飲み物を提供したいデース！
-ゴージャス飲み物を募集してマス！</t>
-    <rPh sb="4" eb="6">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>オヨ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ビジョ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ノ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>モノ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>テイキョウ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>ノ</t>
-    </rPh>
-    <rPh sb="43" eb="44">
-      <t>モノ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ボシュウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ContestVictory</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1315,42 +1282,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>メルヘンでかわいいお菓子限定
-メルヘンでかわいいお菓子を募集しています♪
-食べた人に夢を見せるかわいいお菓子を持ってきてね☆</t>
-    <rPh sb="10" eb="12">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>ユメ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>モ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>お子様向けのお菓子限定
 お子様が喜ぶ色々なお菓子を募集しています！
 かわいいや不思議なお菓子など.. ぜひ応募お待ちしてます！</t>
@@ -1457,54 +1388,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>彫刻お菓子限定
-名門ハイネ家の招待パーティーに飾るお菓子を募集しています。
-パーティーの目玉になる、派手な彫刻お菓子が希望ですわ♪</t>
-    <rPh sb="0" eb="2">
-      <t>チョウコク</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>メイモン</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ケ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ショウタイ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>カザ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>メダマ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>ハデ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>チョウコク</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>キボウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>青色をテーマにしたお菓子
 秋の大演奏会で、お客様へのお土産に渡すお菓子を募集しています。
 美しい青のお菓子をぜひ作って頂きたいです。</t>
@@ -1852,6 +1735,120 @@
   </si>
   <si>
     <t>Or_Contest_999</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自由課題
+オランジーナビーチを象徴する、オシャレなおかしを募集してます！
+腕によりをかけたお菓子を見せてください！</t>
+    <rPh sb="0" eb="4">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ショウチョウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ウデ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>見た目が派手なお菓子限定
+名門ハイネ家の招待パーティーに飾るお菓子を募集しています。
+パーティーの目玉になる、派手な見た目のお菓子が希望ですわ♪</t>
+    <rPh sb="0" eb="1">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハデ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>メイモン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ショウタイ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>カザ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>メダマ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ハデ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>キボウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自由課題
+メルヘンでかわいいお菓子を募集しています♪
+食べた人に夢を見せるかわいいお菓子を見せてくださ～い！</t>
+    <rPh sb="0" eb="4">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ミ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2334,19 +2331,19 @@
         <v>28</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>19</v>
@@ -2367,13 +2364,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -2421,13 +2418,13 @@
         <v>0</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="X2" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="Y2" s="3" t="s">
         <v>20</v>
@@ -2454,7 +2451,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2502,13 +2499,13 @@
         <v>0</v>
       </c>
       <c r="V3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y3" s="4" t="s">
         <v>21</v>
@@ -2583,16 +2580,16 @@
         <v>0</v>
       </c>
       <c r="V4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2664,13 +2661,13 @@
         <v>0</v>
       </c>
       <c r="V5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y5" s="4" t="s">
         <v>21</v>
@@ -2697,7 +2694,7 @@
         <v>89</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2745,13 +2742,13 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y6" s="4" t="s">
         <v>24</v>
@@ -2826,13 +2823,13 @@
         <v>0</v>
       </c>
       <c r="V7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y7" s="4" t="s">
         <v>21</v>
@@ -2859,7 +2856,7 @@
         <v>91</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2907,13 +2904,13 @@
         <v>0</v>
       </c>
       <c r="V8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y8" s="4" t="s">
         <v>21</v>
@@ -2940,7 +2937,7 @@
         <v>92</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2988,13 +2985,13 @@
         <v>0</v>
       </c>
       <c r="V9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y9" s="4" t="s">
         <v>21</v>
@@ -3021,7 +3018,7 @@
         <v>85</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3069,13 +3066,13 @@
         <v>0</v>
       </c>
       <c r="V10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y10" s="4" t="s">
         <v>21</v>
@@ -3150,13 +3147,13 @@
         <v>0</v>
       </c>
       <c r="V11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y11" s="4" t="s">
         <v>21</v>
@@ -3183,7 +3180,7 @@
         <v>29</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G12" s="5">
         <v>0</v>
@@ -3231,13 +3228,13 @@
         <v>0</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W12" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="X12" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="X12" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="Y12" s="6" t="s">
         <v>20</v>
@@ -3327,19 +3324,19 @@
         <v>28</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>19</v>
@@ -3366,7 +3363,7 @@
         <v>65</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -3414,13 +3411,13 @@
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="X2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y2" s="4" t="s">
         <v>21</v>
@@ -3495,13 +3492,13 @@
         <v>0</v>
       </c>
       <c r="V3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="X3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y3" s="4" t="s">
         <v>24</v>
@@ -3528,7 +3525,7 @@
         <v>101</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3576,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="V4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="X4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y4" s="4" t="s">
         <v>21</v>
@@ -3609,7 +3606,7 @@
         <v>67</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -3657,13 +3654,13 @@
         <v>0</v>
       </c>
       <c r="V5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="X5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y5" s="4" t="s">
         <v>21</v>
@@ -3738,13 +3735,13 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="X6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y6" s="4" t="s">
         <v>21</v>
@@ -3819,13 +3816,13 @@
         <v>0</v>
       </c>
       <c r="V7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="X7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y7" s="4" t="s">
         <v>21</v>
@@ -3900,13 +3897,13 @@
         <v>0</v>
       </c>
       <c r="V8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="X8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y8" s="4" t="s">
         <v>21</v>
@@ -3933,7 +3930,7 @@
         <v>88</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3981,13 +3978,13 @@
         <v>0</v>
       </c>
       <c r="V9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="X9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y9" s="4" t="s">
         <v>21</v>
@@ -4011,10 +4008,10 @@
         <v>37</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>
@@ -4062,13 +4059,13 @@
         <v>0</v>
       </c>
       <c r="V10" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W10" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="X10" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Y10" s="6" t="s">
         <v>20</v>
@@ -4158,19 +4155,19 @@
         <v>28</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>19</v>
@@ -4245,13 +4242,13 @@
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y2" s="4" t="s">
         <v>21</v>
@@ -4278,7 +4275,7 @@
         <v>83</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -4326,13 +4323,13 @@
         <v>0</v>
       </c>
       <c r="V3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y3" s="4" t="s">
         <v>24</v>
@@ -4359,7 +4356,7 @@
         <v>73</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -4407,13 +4404,13 @@
         <v>0</v>
       </c>
       <c r="V4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y4" s="4" t="s">
         <v>21</v>
@@ -4440,7 +4437,7 @@
         <v>84</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -4488,13 +4485,13 @@
         <v>0</v>
       </c>
       <c r="V5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y5" s="4" t="s">
         <v>21</v>
@@ -4521,7 +4518,7 @@
         <v>64</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -4569,13 +4566,13 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y6" s="4" t="s">
         <v>21</v>
@@ -4602,7 +4599,7 @@
         <v>86</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -4650,13 +4647,13 @@
         <v>0</v>
       </c>
       <c r="V7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y7" s="4" t="s">
         <v>21</v>
@@ -4683,7 +4680,7 @@
         <v>87</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -4731,13 +4728,13 @@
         <v>0</v>
       </c>
       <c r="V8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y8" s="4" t="s">
         <v>21</v>
@@ -4764,7 +4761,7 @@
         <v>74</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -4812,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="V9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y9" s="4" t="s">
         <v>21</v>
@@ -4839,13 +4836,13 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
@@ -4893,13 +4890,13 @@
         <v>0</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>21</v>
@@ -4923,10 +4920,10 @@
         <v>46</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>152</v>
       </c>
       <c r="G11" s="5">
         <v>0</v>
@@ -4974,13 +4971,13 @@
         <v>0</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W11" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X11" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Y11" s="6" t="s">
         <v>20</v>
@@ -5070,19 +5067,19 @@
         <v>28</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>19</v>
@@ -5109,7 +5106,7 @@
         <v>70</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -5157,13 +5154,13 @@
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="X2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y2" s="4" t="s">
         <v>21</v>
@@ -5190,7 +5187,7 @@
         <v>82</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -5238,13 +5235,13 @@
         <v>0</v>
       </c>
       <c r="V3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="X3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y3" s="4" t="s">
         <v>24</v>
@@ -5319,13 +5316,13 @@
         <v>0</v>
       </c>
       <c r="V4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="X4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y4" s="4" t="s">
         <v>21</v>
@@ -5352,7 +5349,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -5400,13 +5397,13 @@
         <v>0</v>
       </c>
       <c r="V5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="X5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y5" s="4" t="s">
         <v>21</v>
@@ -5430,10 +5427,10 @@
         <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -5481,13 +5478,13 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="X6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y6" s="4" t="s">
         <v>21</v>
@@ -5562,13 +5559,13 @@
         <v>0</v>
       </c>
       <c r="V7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="X7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y7" s="4" t="s">
         <v>21</v>
@@ -5595,7 +5592,7 @@
         <v>80</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -5643,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="V8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="X8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y8" s="4" t="s">
         <v>21</v>
@@ -5673,10 +5670,10 @@
         <v>63</v>
       </c>
       <c r="E9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -5724,13 +5721,13 @@
         <v>0</v>
       </c>
       <c r="V9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="X9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y9" s="4" t="s">
         <v>21</v>
@@ -5754,10 +5751,10 @@
         <v>47</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>
@@ -5805,13 +5802,13 @@
         <v>0</v>
       </c>
       <c r="V10" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W10" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="X10" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Y10" s="6" t="s">
         <v>20</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E798B557-E026-40D2-8A72-660C2AFD9E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447682DE-C6B1-47F5-A155-11965CB331B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2565" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="158">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -1626,32 +1626,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>◆ケーキ・チョコレートの国際コンクール◆
-優勝者には、特別レシピを進呈します。自信のある様々なチョコレートとケーキで参加してください！</t>
-    <rPh sb="12" eb="14">
-      <t>コクサイ</t>
-    </rPh>
-    <rPh sb="21" eb="24">
-      <t>ユウショウシャ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>トクベツ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>シンテイ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>サマザマ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>サンカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>◆世界のお菓子コンクール◆
 オランジーナ国で古くから開催されている、パティシエのナンバーワンを決める大会です。
 誉れを求めて、ぜひ優勝を勝ち取ってください。</t>
@@ -1848,6 +1822,69 @@
     </rPh>
     <rPh sb="45" eb="46">
       <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆夏エリア最大のお菓子エキシビジョン◆
+テーマ：自由課題
+優勝者には、特別なレシピを進呈します。至高の一品をお待ちしております！</t>
+    <rPh sb="1" eb="2">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="24" eb="28">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>ユウショウシャ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>トクベツ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>シンテイ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>シコウ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>イッピン</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆おかしの国際コンクール◆
+テーマ：自由課題
+優勝者には、特別レシピを進呈します。自信のあるお菓子で参加してください！</t>
+    <rPh sb="5" eb="7">
+      <t>コクサイ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>ユウショウシャ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>トクベツ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>シンテイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>サンカ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2364,7 +2401,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -3180,7 +3217,7 @@
         <v>29</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G12" s="5">
         <v>0</v>
@@ -3525,7 +3562,7 @@
         <v>101</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -4008,10 +4045,10 @@
         <v>37</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>
@@ -4356,7 +4393,7 @@
         <v>73</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -4599,7 +4636,7 @@
         <v>86</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -4923,7 +4960,7 @@
         <v>146</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G11" s="5">
         <v>0</v>
@@ -4938,13 +4975,13 @@
         <v>31</v>
       </c>
       <c r="K11" s="5">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
         <v>200</v>
       </c>
       <c r="M11" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N11" s="5">
         <v>5</v>
@@ -5754,7 +5791,7 @@
         <v>145</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447682DE-C6B1-47F5-A155-11965CB331B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0A1225-FE02-441E-87E6-5098F35A5794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2565" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2850" yWindow="1200" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -3238,7 +3238,7 @@
         <v>100</v>
       </c>
       <c r="M12" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N12" s="5">
         <v>5</v>
@@ -4069,7 +4069,7 @@
         <v>100</v>
       </c>
       <c r="M10" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N10" s="5">
         <v>5</v>
@@ -4414,7 +4414,7 @@
         <v>20</v>
       </c>
       <c r="M4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N4">
         <v>3</v>
@@ -4576,7 +4576,7 @@
         <v>21</v>
       </c>
       <c r="M6">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N6">
         <v>4</v>
@@ -4657,7 +4657,7 @@
         <v>21</v>
       </c>
       <c r="M7">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="N7">
         <v>5</v>
@@ -4738,7 +4738,7 @@
         <v>22</v>
       </c>
       <c r="M8">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N8">
         <v>5</v>
@@ -4981,7 +4981,7 @@
         <v>200</v>
       </c>
       <c r="M11" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N11" s="5">
         <v>5</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0A1225-FE02-441E-87E6-5098F35A5794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C276261-BB82-4F7A-833F-15747B9EBDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2850" yWindow="1200" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2145" yWindow="750" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="159">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -1886,6 +1886,10 @@
     <rPh sb="50" eb="52">
       <t>サンカ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sound73</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -5014,7 +5018,7 @@
         <v>122</v>
       </c>
       <c r="X11" s="5" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="Y11" s="6" t="s">
         <v>20</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C276261-BB82-4F7A-833F-15747B9EBDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FB6E38-4D9A-43D1-A1FC-18F36353A51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2145" yWindow="750" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FB6E38-4D9A-43D1-A1FC-18F36353A51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77BD26B0-B079-4933-B35D-55DA5ACD83E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -2594,7 +2594,7 @@
         <v>2</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -2675,7 +2675,7 @@
         <v>2</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N5">
         <v>2</v>
@@ -2837,7 +2837,7 @@
         <v>3</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>3</v>
@@ -2918,7 +2918,7 @@
         <v>3</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>3</v>
@@ -2999,7 +2999,7 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N9">
         <v>4</v>
@@ -3080,7 +3080,7 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N10">
         <v>4</v>
@@ -3161,7 +3161,7 @@
         <v>5</v>
       </c>
       <c r="M11">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N11">
         <v>5</v>
@@ -3242,7 +3242,7 @@
         <v>100</v>
       </c>
       <c r="M12" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N12" s="5">
         <v>5</v>
@@ -4070,10 +4070,10 @@
         <v>0</v>
       </c>
       <c r="L10" s="5">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M10" s="5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N10" s="5">
         <v>5</v>
@@ -4982,7 +4982,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M11" s="5">
         <v>15</v>
@@ -5813,7 +5813,7 @@
         <v>7000</v>
       </c>
       <c r="L10" s="5">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M10" s="5">
         <v>30</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77BD26B0-B079-4933-B35D-55DA5ACD83E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9973A09-5E46-494F-878C-AAD4BFE3AD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -2594,7 +2594,7 @@
         <v>2</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -2675,7 +2675,7 @@
         <v>2</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N5">
         <v>2</v>
@@ -2756,7 +2756,7 @@
         <v>4</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>3</v>
@@ -2837,7 +2837,7 @@
         <v>3</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>3</v>
@@ -2918,7 +2918,7 @@
         <v>3</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>3</v>
@@ -2999,7 +2999,7 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>4</v>
@@ -3080,7 +3080,7 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N10">
         <v>4</v>
@@ -3242,7 +3242,7 @@
         <v>100</v>
       </c>
       <c r="M12" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N12" s="5">
         <v>5</v>
@@ -4010,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -4985,7 +4985,7 @@
         <v>300</v>
       </c>
       <c r="M11" s="5">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N11" s="5">
         <v>5</v>
@@ -5249,7 +5249,7 @@
         <v>30</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N3">
         <v>3</v>
@@ -5330,7 +5330,7 @@
         <v>30</v>
       </c>
       <c r="M4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N4">
         <v>4</v>
@@ -5411,7 +5411,7 @@
         <v>31</v>
       </c>
       <c r="M5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="N5">
         <v>3</v>
@@ -5429,7 +5429,7 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>30</v>
       </c>
       <c r="M6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N6">
         <v>4</v>
@@ -5510,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5573,7 +5573,7 @@
         <v>31</v>
       </c>
       <c r="M7">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N7">
         <v>5</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -5672,7 +5672,7 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -5816,7 +5816,7 @@
         <v>400</v>
       </c>
       <c r="M10" s="5">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="N10" s="5">
         <v>5</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9973A09-5E46-494F-878C-AAD4BFE3AD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B46D78-B08C-480B-800E-6072740C6720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2775" yWindow="900" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -1110,42 +1110,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ケーキ限定
-春の王様が年に一度開くケーキコンテストです。
-自信のある豪華なケーキを見せてください！</t>
-    <rPh sb="3" eb="5">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ハル</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>サマ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>イチド</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ヒラ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ゴウカ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ひんやりお菓子限定
 暑さを吹き飛ばす！
 つめた～いお菓子を募集シテマース！
@@ -1174,45 +1138,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>おみやげお菓子限定＜クッキー・ラスク除く＞
-パパがおみやげに持って帰れるお菓子を募集しますじゃ。
-小さめで子供が喜ぶお菓子がいいのお。</t>
-    <rPh sb="5" eb="7">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ノゾ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>モ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>カエ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="49" eb="50">
-      <t>チイ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>コドモ</t>
-    </rPh>
-    <rPh sb="56" eb="57">
-      <t>ヨロコ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>カシ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ケーキ限定
 王国プラムで行われるケーキコンテストです。
 各界隈の著名人が注目するトップレベルのコンテストです。</t>
@@ -1616,16 +1541,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>黄色は、まだコンテスト優勝者セリフいれてない</t>
-    <rPh sb="0" eb="2">
-      <t>キイロ</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>ユウショウシャ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>◆世界のお菓子コンクール◆
 オランジーナ国で古くから開催されている、パティシエのナンバーワンを決める大会です。
 誉れを求めて、ぜひ優勝を勝ち取ってください。</t>
@@ -1890,6 +1805,91 @@
   </si>
   <si>
     <t>sound73</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ケーキ限定
+春の大精霊様が年に一度開くケーキコンテストです。
+自信のある豪華なケーキを見せてください！</t>
+    <rPh sb="3" eb="5">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハル</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ダイセイレイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ゴウカ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黄色は、まだ判定の未調整</t>
+    <rPh sb="0" eb="2">
+      <t>キイロ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ミチョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自由課題＜クッキー・ラスク除く＞
+パパがおみやげに持って帰れるお菓子を募集しますじゃ。
+小さめで子供が喜ぶお菓子がいいのお。</t>
+    <rPh sb="0" eb="4">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>チイ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ヨロコ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>カシ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2405,13 +2405,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -2750,7 +2750,7 @@
         <v>31</v>
       </c>
       <c r="K6">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -2831,7 +2831,7 @@
         <v>31</v>
       </c>
       <c r="K7">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="L7">
         <v>3</v>
@@ -2912,7 +2912,7 @@
         <v>31</v>
       </c>
       <c r="K8">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L8">
         <v>3</v>
@@ -3059,7 +3059,7 @@
         <v>85</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3077,7 +3077,7 @@
         <v>2000</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>15</v>
@@ -3158,7 +3158,7 @@
         <v>3000</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>20</v>
@@ -3203,84 +3203,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="5">
+    <row r="12" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12">
         <f>ROW()-2</f>
         <v>10</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12">
         <v>1000</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="C12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="G12" s="5">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5">
+      <c r="F12" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>5</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12">
         <v>12</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12">
         <v>31</v>
       </c>
-      <c r="K12" s="5">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5">
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
         <v>100</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12">
         <v>5</v>
       </c>
-      <c r="N12" s="5">
-        <v>5</v>
-      </c>
-      <c r="O12" s="5">
-        <v>1</v>
-      </c>
-      <c r="P12" s="5">
+      <c r="N12">
+        <v>4</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
         <v>99</v>
       </c>
-      <c r="Q12" s="5">
-        <v>0</v>
-      </c>
-      <c r="R12" s="5">
-        <v>0</v>
-      </c>
-      <c r="S12" s="5">
-        <v>0</v>
-      </c>
-      <c r="T12" s="5">
-        <v>0</v>
-      </c>
-      <c r="U12" s="5">
-        <v>0</v>
-      </c>
-      <c r="V12" s="5" t="s">
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12" t="s">
         <v>110</v>
       </c>
-      <c r="W12" s="5" t="s">
+      <c r="W12" t="s">
         <v>114</v>
       </c>
-      <c r="X12" s="5" t="s">
+      <c r="X12" t="s">
         <v>115</v>
       </c>
-      <c r="Y12" s="6" t="s">
+      <c r="Y12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z12" s="5">
+      <c r="Z12">
         <v>1</v>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
         <v>65</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -3431,7 +3431,7 @@
         <v>1</v>
       </c>
       <c r="O2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>99</v>
@@ -3566,7 +3566,7 @@
         <v>101</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3629,489 +3629,489 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5">
+    <row r="5" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>1003</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>20300</v>
       </c>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="F5" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
         <v>3</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="5">
         <v>12</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="5">
         <v>31</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="5">
         <v>500</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="5">
         <v>11</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="5">
         <v>7</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="5">
         <v>3</v>
       </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="5">
         <v>99</v>
       </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
+      <c r="Q5" s="5">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
         <v>3</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5" t="s">
+      <c r="T5" s="5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5">
+        <v>0</v>
+      </c>
+      <c r="V5" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="W5" t="s">
+      <c r="W5" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="X5" t="s">
+      <c r="X5" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y5" s="4" t="s">
+      <c r="Y5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6">
+    <row r="6" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>1004</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>20400</v>
       </c>
-      <c r="C6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
         <v>4</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="5">
         <v>12</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="5">
         <v>31</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="5">
         <v>1000</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="5">
         <v>11</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="5">
         <v>10</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="5">
         <v>4</v>
       </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="5">
         <v>99</v>
       </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
+      <c r="Q6" s="5">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
         <v>5</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6" t="s">
+      <c r="T6" s="5">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="W6" t="s">
+      <c r="W6" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="X6" t="s">
+      <c r="X6" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y6" s="4" t="s">
+      <c r="Y6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7">
+    <row r="7" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>1005</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>20500</v>
       </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
         <v>4</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="5">
         <v>12</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="5">
         <v>31</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="5">
         <v>1500</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="5">
         <v>10</v>
       </c>
-      <c r="M7">
-        <v>15</v>
-      </c>
-      <c r="N7">
+      <c r="M7" s="5">
+        <v>10</v>
+      </c>
+      <c r="N7" s="5">
         <v>4</v>
       </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="5">
         <v>99</v>
       </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
+      <c r="Q7" s="5">
+        <v>1</v>
+      </c>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
         <v>7</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7" t="s">
+      <c r="T7" s="5">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="W7" t="s">
+      <c r="W7" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="X7" t="s">
+      <c r="X7" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y7" s="4" t="s">
+      <c r="Y7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8">
+    <row r="8" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>1006</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="5">
         <v>20600</v>
       </c>
-      <c r="C8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
         <v>3</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="5">
         <v>12</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="5">
         <v>31</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="5">
         <v>2000</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="5">
         <v>12</v>
       </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-      <c r="N8">
+      <c r="M8" s="5">
+        <v>15</v>
+      </c>
+      <c r="N8" s="5">
         <v>4</v>
       </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="5">
         <v>99</v>
       </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
+      <c r="Q8" s="5">
+        <v>1</v>
+      </c>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
         <v>7</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8" t="s">
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="W8" t="s">
+      <c r="W8" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="X8" t="s">
+      <c r="X8" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y8" s="4" t="s">
+      <c r="Y8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9">
+    <row r="9" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="5">
         <f>ROW()-2+1000</f>
         <v>1007</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="5">
         <v>20700</v>
       </c>
-      <c r="C9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="F9" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
         <v>5</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="5">
         <v>12</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="5">
         <v>31</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="5">
         <v>5000</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="5">
         <v>12</v>
       </c>
-      <c r="M9">
-        <v>35</v>
-      </c>
-      <c r="N9">
+      <c r="M9" s="5">
+        <v>18</v>
+      </c>
+      <c r="N9" s="5">
         <v>5</v>
       </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9">
+      <c r="O9" s="5">
+        <v>1</v>
+      </c>
+      <c r="P9" s="5">
         <v>99</v>
       </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
+      <c r="Q9" s="5">
+        <v>1</v>
+      </c>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
         <v>10</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9" t="s">
+      <c r="T9" s="5">
+        <v>0</v>
+      </c>
+      <c r="U9" s="5">
+        <v>0</v>
+      </c>
+      <c r="V9" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="W9" t="s">
+      <c r="W9" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="X9" t="s">
+      <c r="X9" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y9" s="4" t="s">
+      <c r="Y9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="5">
+    <row r="10" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10">
         <f>ROW()-2+1000</f>
         <v>1008</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10">
         <v>2000</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="C10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5">
+      <c r="E10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>5</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10">
         <v>12</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10">
         <v>31</v>
       </c>
-      <c r="K10" s="5">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5">
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
         <v>200</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10">
         <v>15</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10">
         <v>5</v>
       </c>
-      <c r="O10" s="5">
-        <v>1</v>
-      </c>
-      <c r="P10" s="5">
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
         <v>99</v>
       </c>
-      <c r="Q10" s="5">
-        <v>0</v>
-      </c>
-      <c r="R10" s="5">
-        <v>0</v>
-      </c>
-      <c r="S10" s="5">
-        <v>0</v>
-      </c>
-      <c r="T10" s="5">
-        <v>0</v>
-      </c>
-      <c r="U10" s="5">
-        <v>0</v>
-      </c>
-      <c r="V10" s="5" t="s">
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10" t="s">
         <v>117</v>
       </c>
-      <c r="W10" s="5" t="s">
+      <c r="W10" t="s">
         <v>120</v>
       </c>
-      <c r="X10" s="5" t="s">
+      <c r="X10" t="s">
         <v>115</v>
       </c>
-      <c r="Y10" s="6" t="s">
+      <c r="Y10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z10" s="5">
+      <c r="Z10">
         <v>1</v>
       </c>
     </row>
@@ -4217,651 +4217,651 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2">
+    <row r="2" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="5">
         <f t="shared" ref="A2:A10" si="0">ROW()-2+2000</f>
         <v>2000</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="5">
         <v>30000</v>
       </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5">
         <v>12</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="5">
         <v>31</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="5">
         <v>300</v>
       </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
+      <c r="L2" s="5">
+        <v>1</v>
+      </c>
+      <c r="M2" s="5">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5">
         <v>2</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
+      <c r="O2" s="5">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5">
         <v>99</v>
       </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
+      <c r="Q2" s="5">
+        <v>1</v>
+      </c>
+      <c r="R2" s="5">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5">
         <v>3</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="T2" s="5">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="Y2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3">
+    <row r="3" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="5">
         <f t="shared" si="0"/>
         <v>2001</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="5">
         <v>30100</v>
       </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
+      <c r="F3" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
         <v>2</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="5">
         <v>12</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="5">
         <v>31</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="5">
         <v>500</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="5">
         <v>20</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="5">
         <v>10</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="5">
         <v>2</v>
       </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="5">
         <v>99</v>
       </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
+      <c r="Q3" s="5">
+        <v>1</v>
+      </c>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
         <v>3</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3" t="s">
+      <c r="T3" s="5">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5">
+        <v>0</v>
+      </c>
+      <c r="V3" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="W3" t="s">
+      <c r="W3" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="X3" t="s">
+      <c r="X3" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="Y3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z3">
+      <c r="Z3" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4">
+    <row r="4" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="5">
         <f t="shared" si="0"/>
         <v>2002</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>30200</v>
       </c>
-      <c r="C4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
+      <c r="F4" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="5">
         <v>12</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="5">
         <v>31</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="5">
         <v>1200</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="5">
         <v>20</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="5">
         <v>15</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="5">
         <v>3</v>
       </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="5">
         <v>99</v>
       </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
+      <c r="Q4" s="5">
+        <v>1</v>
+      </c>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
         <v>5</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4" t="s">
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="W4" t="s">
+      <c r="W4" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="X4" t="s">
+      <c r="X4" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="Y4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5">
+    <row r="5" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>2003</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>30300</v>
       </c>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="F5" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
         <v>4</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="5">
         <v>12</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="5">
         <v>31</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="5">
         <v>500</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="5">
         <v>20</v>
       </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
         <v>3</v>
       </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="5">
         <v>99</v>
       </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
+      <c r="Q5" s="5">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
         <v>3</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5" t="s">
+      <c r="T5" s="5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5">
+        <v>0</v>
+      </c>
+      <c r="V5" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="W5" t="s">
+      <c r="W5" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="X5" t="s">
+      <c r="X5" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y5" s="4" t="s">
+      <c r="Y5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6">
+    <row r="6" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>2004</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>30400</v>
       </c>
-      <c r="C6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
+      <c r="F6" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
         <v>3</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="5">
         <v>12</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="5">
         <v>31</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="5">
         <v>1000</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="5">
         <v>21</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="5">
         <v>20</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="5">
         <v>4</v>
       </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="5">
         <v>99</v>
       </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
+      <c r="Q6" s="5">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
         <v>3</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6" t="s">
+      <c r="T6" s="5">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="W6" t="s">
+      <c r="W6" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="X6" t="s">
+      <c r="X6" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y6" s="4" t="s">
+      <c r="Y6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7">
+    <row r="7" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>2005</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>30500</v>
       </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="F7" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
         <v>5</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="5">
         <v>12</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="5">
         <v>31</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="5">
         <v>2000</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="5">
         <v>21</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="5">
         <v>23</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="5">
         <v>5</v>
       </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="5">
         <v>99</v>
       </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
+      <c r="Q7" s="5">
+        <v>1</v>
+      </c>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
         <v>5</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7" t="s">
+      <c r="T7" s="5">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="W7" t="s">
+      <c r="W7" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="X7" t="s">
+      <c r="X7" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y7" s="4" t="s">
+      <c r="Y7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8">
+    <row r="8" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>2006</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="5">
         <v>30600</v>
       </c>
-      <c r="C8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
+      <c r="F8" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
         <v>3</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="5">
         <v>12</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="5">
         <v>31</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="5">
         <v>2000</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="5">
         <v>22</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="5">
         <v>30</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="5">
         <v>5</v>
       </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="5">
         <v>99</v>
       </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
+      <c r="Q8" s="5">
+        <v>1</v>
+      </c>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
         <v>5</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8" t="s">
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="W8" t="s">
+      <c r="W8" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="X8" t="s">
+      <c r="X8" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y8" s="4" t="s">
+      <c r="Y8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9">
+    <row r="9" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>2007</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="5">
         <v>30700</v>
       </c>
-      <c r="C9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
         <v>5</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="5">
         <v>12</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="5">
         <v>31</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="5">
         <v>3000</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="5">
         <v>22</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="5">
         <v>38</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="5">
         <v>4</v>
       </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9">
+      <c r="O9" s="5">
+        <v>1</v>
+      </c>
+      <c r="P9" s="5">
         <v>99</v>
       </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
+      <c r="Q9" s="5">
+        <v>1</v>
+      </c>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
         <v>5</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9" t="s">
+      <c r="T9" s="5">
+        <v>0</v>
+      </c>
+      <c r="U9" s="5">
+        <v>0</v>
+      </c>
+      <c r="V9" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="W9" t="s">
+      <c r="W9" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="X9" t="s">
+      <c r="X9" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y9" s="4" t="s">
+      <c r="Y9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4961,10 +4961,10 @@
         <v>46</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G11" s="5">
         <v>0</v>
@@ -5018,7 +5018,7 @@
         <v>122</v>
       </c>
       <c r="X11" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Y11" s="6" t="s">
         <v>20</v>
@@ -5129,651 +5129,651 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2">
+    <row r="2" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="5">
         <f t="shared" ref="A2:A9" si="0">ROW()-2+3000</f>
         <v>3000</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="5">
         <v>40000</v>
       </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
+      <c r="F2" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5">
         <v>12</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="5">
         <v>31</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
+      <c r="K2" s="5">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5">
+        <v>1</v>
+      </c>
+      <c r="M2" s="5">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5">
+        <v>1</v>
+      </c>
+      <c r="O2" s="5">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5">
         <v>99</v>
       </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
+      <c r="Q2" s="5">
+        <v>1</v>
+      </c>
+      <c r="R2" s="5">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5">
         <v>3</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="T2" s="5">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="Y2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3">
+    <row r="3" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="5">
         <f t="shared" si="0"/>
         <v>3001</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="5">
         <v>40100</v>
       </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
         <v>2</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="5">
         <v>12</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="5">
         <v>31</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="5">
         <v>800</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="5">
         <v>30</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="5">
         <v>15</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="5">
         <v>3</v>
       </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="5">
         <v>99</v>
       </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
+      <c r="Q3" s="5">
+        <v>1</v>
+      </c>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
         <v>5</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3" t="s">
+      <c r="T3" s="5">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5">
+        <v>0</v>
+      </c>
+      <c r="V3" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W3" t="s">
+      <c r="W3" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="X3" t="s">
+      <c r="X3" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="Y3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z3">
+      <c r="Z3" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4">
+    <row r="4" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="5">
         <f t="shared" si="0"/>
         <v>3002</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>40200</v>
       </c>
-      <c r="C4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="5">
         <v>12</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="5">
         <v>31</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="5">
         <v>1000</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="5">
         <v>30</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="5">
         <v>20</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="5">
         <v>4</v>
       </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="5">
         <v>99</v>
       </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
+      <c r="Q4" s="5">
+        <v>1</v>
+      </c>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
         <v>5</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4" t="s">
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W4" t="s">
+      <c r="W4" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="X4" t="s">
+      <c r="X4" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="Y4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5">
+    <row r="5" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>3003</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>40300</v>
       </c>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="F5" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
         <v>2</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="5">
         <v>12</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="5">
         <v>31</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="5">
         <v>1200</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="5">
         <v>31</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="5">
         <v>30</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="5">
         <v>3</v>
       </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="5">
         <v>99</v>
       </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
+      <c r="Q5" s="5">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
         <v>7</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5" t="s">
+      <c r="T5" s="5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5">
+        <v>0</v>
+      </c>
+      <c r="V5" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W5" t="s">
+      <c r="W5" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="X5" t="s">
+      <c r="X5" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y5" s="4" t="s">
+      <c r="Y5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6">
+    <row r="6" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3004</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>40400</v>
       </c>
-      <c r="C6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E6" t="s">
-        <v>141</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
+      <c r="E6" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
         <v>3</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="5">
         <v>12</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="5">
         <v>31</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="5">
         <v>1000</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="5">
         <v>30</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="5">
         <v>40</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="5">
         <v>4</v>
       </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="5">
         <v>99</v>
       </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
+      <c r="Q6" s="5">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
         <v>7</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6" t="s">
+      <c r="T6" s="5">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W6" t="s">
+      <c r="W6" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="X6" t="s">
+      <c r="X6" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y6" s="4" t="s">
+      <c r="Y6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7">
+    <row r="7" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>3005</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>40500</v>
       </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
         <v>5</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="5">
         <v>12</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="5">
         <v>31</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="5">
         <v>700</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="5">
         <v>31</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="5">
         <v>45</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="5">
         <v>5</v>
       </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="5">
         <v>99</v>
       </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
+      <c r="Q7" s="5">
+        <v>1</v>
+      </c>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
         <v>7</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7" t="s">
+      <c r="T7" s="5">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W7" t="s">
+      <c r="W7" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="X7" t="s">
+      <c r="X7" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y7" s="4" t="s">
+      <c r="Y7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8">
+    <row r="8" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>3006</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="5">
         <v>40600</v>
       </c>
-      <c r="C8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
+      <c r="F8" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
         <v>5</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="5">
         <v>12</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="5">
         <v>31</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="5">
         <v>1500</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="5">
         <v>32</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="5">
         <v>60</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="5">
         <v>5</v>
       </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
+      <c r="O8" s="5">
+        <v>1</v>
+      </c>
+      <c r="P8" s="5">
         <v>99</v>
       </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
+      <c r="Q8" s="5">
+        <v>1</v>
+      </c>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
         <v>7</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8" t="s">
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W8" t="s">
+      <c r="W8" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="X8" t="s">
+      <c r="X8" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y8" s="4" t="s">
+      <c r="Y8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9">
+    <row r="9" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>3007</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="5">
         <v>40700</v>
       </c>
-      <c r="C9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C9" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="F9" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
         <v>6</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="5">
         <v>12</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="5">
         <v>31</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="5">
         <v>3000</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="5">
         <v>32</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="5">
         <v>65</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="5">
         <v>5</v>
       </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9">
+      <c r="O9" s="5">
+        <v>1</v>
+      </c>
+      <c r="P9" s="5">
         <v>99</v>
       </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
+      <c r="Q9" s="5">
+        <v>1</v>
+      </c>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
         <v>10</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9" t="s">
+      <c r="T9" s="5">
+        <v>0</v>
+      </c>
+      <c r="U9" s="5">
+        <v>0</v>
+      </c>
+      <c r="V9" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W9" t="s">
+      <c r="W9" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="X9" t="s">
+      <c r="X9" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="Y9" s="4" t="s">
+      <c r="Y9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="5">
         <v>0</v>
       </c>
     </row>
@@ -5792,10 +5792,10 @@
         <v>47</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B46D78-B08C-480B-800E-6072740C6720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F7A28F-7279-48F5-B133-531DD1FF24BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2775" yWindow="900" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -966,45 +966,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>鉱石お菓子限定※実装まだ
-エメラルド・サファイア.. 美しい石は、私たちを魅了してやみません。
-キラもの好きの大富豪がうなるお菓子を募集します♪</t>
-    <rPh sb="0" eb="2">
-      <t>コウセキ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ウツク</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>イシ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ワタシ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ミリョウ</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="55" eb="58">
-      <t>ダイフゴウ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="66" eb="68">
-      <t>ボシュウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>愛をテーマにしたチョコレート限定
 心あたたまる、愛にあふれたチョコレートを、お届けください。</t>
     <rPh sb="0" eb="1">
@@ -1138,36 +1099,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ケーキ限定
-王国プラムで行われるケーキコンテストです。
-各界隈の著名人が注目するトップレベルのコンテストです。</t>
-    <rPh sb="3" eb="5">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>オウコク</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="28" eb="31">
-      <t>カクカイワイ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>チョメイ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ジン</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>チュウモク</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ダイチュウモク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>大人な雰囲気のお菓子を募集
 アダルトな雰囲気で、紳士向けのお菓子を募集しております。
 ブラックなお菓子を見せてくださいませ。</t>
@@ -1651,63 +1582,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>見た目が派手なお菓子限定
-名門ハイネ家の招待パーティーに飾るお菓子を募集しています。
-パーティーの目玉になる、派手な見た目のお菓子が希望ですわ♪</t>
-    <rPh sb="0" eb="1">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ハデ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>メイモン</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ケ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ショウタイ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>カザ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>メダマ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>ハデ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="60" eb="61">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="66" eb="68">
-      <t>キボウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>自由課題
 メルヘンでかわいいお菓子を募集しています♪
 食べた人に夢を見せるかわいいお菓子を見せてくださ～い！</t>
@@ -1889,6 +1763,117 @@
     </rPh>
     <rPh sb="54" eb="56">
       <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ケーキ限定
+隣国プラムで行われるケーキコンテストです。
+各界隈の著名人が注目するトップレベルのコンテストです。</t>
+    <rPh sb="3" eb="5">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>リンコク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>カクカイワイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>チョメイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ジン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>チュウモク</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ダイチュウモク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キラキラお菓子限定
+エメラルド・サファイア.. 美しい石は、私たちを魅了してやみません。
+キラもの好きの大富豪がうなるお菓子を募集します♪</t>
+    <rPh sb="5" eb="7">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>イシ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ミリョウ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="52" eb="55">
+      <t>ダイフゴウ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ボシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>芸術的なおかしお菓子限定
+名門ハイネン家の招待パーティーに飾るお菓子を募集しています。
+パーティーの目玉になる、芸術的なお菓子が希望ですわ♪</t>
+    <rPh sb="8" eb="10">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>メイモン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ショウタイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>カザ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>メダマ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ゲイジュツ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>キボウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1966,7 +1951,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1984,6 +1969,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2405,13 +2396,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -2735,7 +2726,7 @@
         <v>89</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -3059,7 +3050,7 @@
         <v>85</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3221,7 +3212,7 @@
         <v>29</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3404,7 +3395,7 @@
         <v>65</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -3566,7 +3557,7 @@
         <v>101</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3629,408 +3620,408 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="5">
+    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
         <f t="shared" si="0"/>
         <v>1003</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>20300</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="F5" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>3</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5">
         <v>12</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5">
         <v>31</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5">
         <v>500</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5">
         <v>11</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5">
         <v>7</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N5">
         <v>3</v>
       </c>
-      <c r="O5" s="5">
-        <v>1</v>
-      </c>
-      <c r="P5" s="5">
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
         <v>99</v>
       </c>
-      <c r="Q5" s="5">
-        <v>1</v>
-      </c>
-      <c r="R5" s="5">
-        <v>0</v>
-      </c>
-      <c r="S5" s="5">
-        <v>3</v>
-      </c>
-      <c r="T5" s="5">
-        <v>0</v>
-      </c>
-      <c r="U5" s="5">
-        <v>0</v>
-      </c>
-      <c r="V5" s="5" t="s">
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>5</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
         <v>117</v>
       </c>
-      <c r="W5" s="5" t="s">
+      <c r="W5" t="s">
         <v>120</v>
       </c>
-      <c r="X5" s="5" t="s">
+      <c r="X5" t="s">
         <v>116</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Y5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z5" s="5">
+      <c r="Z5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="5">
+    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6">
         <f t="shared" si="0"/>
         <v>1004</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>20400</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>4</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6">
         <v>12</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6">
         <v>31</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6">
         <v>1000</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6">
         <v>11</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6">
         <v>10</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6">
         <v>4</v>
       </c>
-      <c r="O6" s="5">
-        <v>1</v>
-      </c>
-      <c r="P6" s="5">
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
         <v>99</v>
       </c>
-      <c r="Q6" s="5">
-        <v>1</v>
-      </c>
-      <c r="R6" s="5">
-        <v>0</v>
-      </c>
-      <c r="S6" s="5">
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>5</v>
       </c>
-      <c r="T6" s="5">
-        <v>0</v>
-      </c>
-      <c r="U6" s="5">
-        <v>0</v>
-      </c>
-      <c r="V6" s="5" t="s">
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
         <v>117</v>
       </c>
-      <c r="W6" s="5" t="s">
+      <c r="W6" t="s">
         <v>120</v>
       </c>
-      <c r="X6" s="5" t="s">
+      <c r="X6" t="s">
         <v>116</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="Y6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z6" s="5">
+      <c r="Z6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="5">
+    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>1005</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>20500</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>4</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7">
         <v>12</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7">
         <v>31</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7">
         <v>1500</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7">
         <v>10</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7">
         <v>10</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7">
         <v>4</v>
       </c>
-      <c r="O7" s="5">
-        <v>1</v>
-      </c>
-      <c r="P7" s="5">
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
         <v>99</v>
       </c>
-      <c r="Q7" s="5">
-        <v>1</v>
-      </c>
-      <c r="R7" s="5">
-        <v>0</v>
-      </c>
-      <c r="S7" s="5">
-        <v>7</v>
-      </c>
-      <c r="T7" s="5">
-        <v>0</v>
-      </c>
-      <c r="U7" s="5">
-        <v>0</v>
-      </c>
-      <c r="V7" s="5" t="s">
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>5</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
         <v>117</v>
       </c>
-      <c r="W7" s="5" t="s">
+      <c r="W7" t="s">
         <v>120</v>
       </c>
-      <c r="X7" s="5" t="s">
+      <c r="X7" t="s">
         <v>116</v>
       </c>
-      <c r="Y7" s="6" t="s">
+      <c r="Y7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z7" s="5">
+      <c r="Z7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="5">
+    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>1006</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>20600</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="H8" s="5">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>3</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8">
         <v>12</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8">
         <v>31</v>
       </c>
-      <c r="K8" s="5">
-        <v>2000</v>
-      </c>
-      <c r="L8" s="5">
+      <c r="K8">
+        <v>1500</v>
+      </c>
+      <c r="L8">
         <v>12</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8">
         <v>15</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8">
         <v>4</v>
       </c>
-      <c r="O8" s="5">
-        <v>1</v>
-      </c>
-      <c r="P8" s="5">
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
         <v>99</v>
       </c>
-      <c r="Q8" s="5">
-        <v>1</v>
-      </c>
-      <c r="R8" s="5">
-        <v>0</v>
-      </c>
-      <c r="S8" s="5">
-        <v>7</v>
-      </c>
-      <c r="T8" s="5">
-        <v>0</v>
-      </c>
-      <c r="U8" s="5">
-        <v>0</v>
-      </c>
-      <c r="V8" s="5" t="s">
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>5</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8" t="s">
         <v>117</v>
       </c>
-      <c r="W8" s="5" t="s">
+      <c r="W8" t="s">
         <v>120</v>
       </c>
-      <c r="X8" s="5" t="s">
+      <c r="X8" t="s">
         <v>116</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="Y8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z8" s="5">
+      <c r="Z8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="5">
+    <row r="9" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="7">
         <f>ROW()-2+1000</f>
         <v>1007</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="7">
         <v>20700</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="C9" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5">
+      <c r="F9" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
         <v>5</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="7">
         <v>12</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="7">
         <v>31</v>
       </c>
-      <c r="K9" s="5">
-        <v>5000</v>
-      </c>
-      <c r="L9" s="5">
+      <c r="K9" s="7">
+        <v>3000</v>
+      </c>
+      <c r="L9" s="7">
         <v>12</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="7">
         <v>18</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9" s="7">
         <v>5</v>
       </c>
-      <c r="O9" s="5">
-        <v>1</v>
-      </c>
-      <c r="P9" s="5">
+      <c r="O9" s="7">
+        <v>1</v>
+      </c>
+      <c r="P9" s="7">
         <v>99</v>
       </c>
-      <c r="Q9" s="5">
-        <v>1</v>
-      </c>
-      <c r="R9" s="5">
-        <v>0</v>
-      </c>
-      <c r="S9" s="5">
-        <v>10</v>
-      </c>
-      <c r="T9" s="5">
-        <v>0</v>
-      </c>
-      <c r="U9" s="5">
-        <v>0</v>
-      </c>
-      <c r="V9" s="5" t="s">
+      <c r="Q9" s="7">
+        <v>1</v>
+      </c>
+      <c r="R9" s="7">
+        <v>0</v>
+      </c>
+      <c r="S9" s="7">
+        <v>8</v>
+      </c>
+      <c r="T9" s="7">
+        <v>0</v>
+      </c>
+      <c r="U9" s="7">
+        <v>0</v>
+      </c>
+      <c r="V9" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="W9" s="5" t="s">
+      <c r="W9" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="X9" s="5" t="s">
+      <c r="X9" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="Y9" s="6" t="s">
+      <c r="Y9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="Z9" s="5">
+      <c r="Z9" s="7">
         <v>0</v>
       </c>
     </row>
@@ -4049,10 +4040,10 @@
         <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -4217,651 +4208,651 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="5">
+    <row r="2" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="7">
         <f t="shared" ref="A2:A10" si="0">ROW()-2+2000</f>
         <v>2000</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="7">
         <v>30000</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
-        <v>1</v>
-      </c>
-      <c r="I2" s="5">
+      <c r="G2" s="7">
+        <v>0</v>
+      </c>
+      <c r="H2" s="7">
+        <v>1</v>
+      </c>
+      <c r="I2" s="7">
         <v>12</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="7">
         <v>31</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="7">
         <v>300</v>
       </c>
-      <c r="L2" s="5">
-        <v>1</v>
-      </c>
-      <c r="M2" s="5">
-        <v>0</v>
-      </c>
-      <c r="N2" s="5">
+      <c r="L2" s="7">
+        <v>1</v>
+      </c>
+      <c r="M2" s="7">
+        <v>0</v>
+      </c>
+      <c r="N2" s="7">
         <v>2</v>
       </c>
-      <c r="O2" s="5">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5">
+      <c r="O2" s="7">
+        <v>0</v>
+      </c>
+      <c r="P2" s="7">
         <v>99</v>
       </c>
-      <c r="Q2" s="5">
-        <v>1</v>
-      </c>
-      <c r="R2" s="5">
-        <v>0</v>
-      </c>
-      <c r="S2" s="5">
+      <c r="Q2" s="7">
+        <v>1</v>
+      </c>
+      <c r="R2" s="7">
+        <v>0</v>
+      </c>
+      <c r="S2" s="7">
         <v>3</v>
       </c>
-      <c r="T2" s="5">
-        <v>0</v>
-      </c>
-      <c r="U2" s="5">
-        <v>0</v>
-      </c>
-      <c r="V2" s="5" t="s">
+      <c r="T2" s="7">
+        <v>0</v>
+      </c>
+      <c r="U2" s="7">
+        <v>0</v>
+      </c>
+      <c r="V2" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="W2" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="X2" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="Y2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="Z2" s="5">
+      <c r="Z2" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="5">
+    <row r="3" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="7">
         <f t="shared" si="0"/>
         <v>2001</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="7">
         <v>30100</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="F3" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7">
         <v>2</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="7">
         <v>12</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="7">
         <v>31</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="7">
         <v>500</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="7">
         <v>20</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="7">
         <v>10</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3" s="7">
         <v>2</v>
       </c>
-      <c r="O3" s="5">
-        <v>1</v>
-      </c>
-      <c r="P3" s="5">
+      <c r="O3" s="7">
+        <v>1</v>
+      </c>
+      <c r="P3" s="7">
         <v>99</v>
       </c>
-      <c r="Q3" s="5">
-        <v>1</v>
-      </c>
-      <c r="R3" s="5">
-        <v>0</v>
-      </c>
-      <c r="S3" s="5">
+      <c r="Q3" s="7">
+        <v>1</v>
+      </c>
+      <c r="R3" s="7">
+        <v>0</v>
+      </c>
+      <c r="S3" s="7">
         <v>3</v>
       </c>
-      <c r="T3" s="5">
-        <v>0</v>
-      </c>
-      <c r="U3" s="5">
-        <v>0</v>
-      </c>
-      <c r="V3" s="5" t="s">
+      <c r="T3" s="7">
+        <v>0</v>
+      </c>
+      <c r="U3" s="7">
+        <v>0</v>
+      </c>
+      <c r="V3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="W3" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="X3" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Y3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="Z3" s="5">
+      <c r="Z3" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="5">
+    <row r="4" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="7">
         <f t="shared" si="0"/>
         <v>2002</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="7">
         <v>30200</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="F4" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7">
         <v>3</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="7">
         <v>12</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="7">
         <v>31</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="7">
         <v>1200</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="7">
         <v>20</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="7">
         <v>15</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4" s="7">
         <v>3</v>
       </c>
-      <c r="O4" s="5">
-        <v>1</v>
-      </c>
-      <c r="P4" s="5">
+      <c r="O4" s="7">
+        <v>1</v>
+      </c>
+      <c r="P4" s="7">
         <v>99</v>
       </c>
-      <c r="Q4" s="5">
-        <v>1</v>
-      </c>
-      <c r="R4" s="5">
-        <v>0</v>
-      </c>
-      <c r="S4" s="5">
+      <c r="Q4" s="7">
+        <v>1</v>
+      </c>
+      <c r="R4" s="7">
+        <v>0</v>
+      </c>
+      <c r="S4" s="7">
         <v>5</v>
       </c>
-      <c r="T4" s="5">
-        <v>0</v>
-      </c>
-      <c r="U4" s="5">
-        <v>0</v>
-      </c>
-      <c r="V4" s="5" t="s">
+      <c r="T4" s="7">
+        <v>0</v>
+      </c>
+      <c r="U4" s="7">
+        <v>0</v>
+      </c>
+      <c r="V4" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="W4" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="X4" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Y4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="Z4" s="5">
+      <c r="Z4" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="5">
+    <row r="5" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="7">
         <f t="shared" si="0"/>
         <v>2003</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="7">
         <v>30300</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="F5" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
         <v>4</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="7">
         <v>12</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="7">
         <v>31</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="7">
         <v>500</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="7">
         <v>20</v>
       </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-      <c r="N5" s="5">
+      <c r="M5" s="7">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7">
         <v>3</v>
       </c>
-      <c r="O5" s="5">
-        <v>1</v>
-      </c>
-      <c r="P5" s="5">
+      <c r="O5" s="7">
+        <v>1</v>
+      </c>
+      <c r="P5" s="7">
         <v>99</v>
       </c>
-      <c r="Q5" s="5">
-        <v>1</v>
-      </c>
-      <c r="R5" s="5">
-        <v>0</v>
-      </c>
-      <c r="S5" s="5">
-        <v>3</v>
-      </c>
-      <c r="T5" s="5">
-        <v>0</v>
-      </c>
-      <c r="U5" s="5">
-        <v>0</v>
-      </c>
-      <c r="V5" s="5" t="s">
+      <c r="Q5" s="7">
+        <v>1</v>
+      </c>
+      <c r="R5" s="7">
+        <v>0</v>
+      </c>
+      <c r="S5" s="7">
+        <v>5</v>
+      </c>
+      <c r="T5" s="7">
+        <v>0</v>
+      </c>
+      <c r="U5" s="7">
+        <v>0</v>
+      </c>
+      <c r="V5" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="W5" s="5" t="s">
+      <c r="W5" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="X5" s="5" t="s">
+      <c r="X5" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Y5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="Z5" s="5">
+      <c r="Z5" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="5">
+    <row r="6" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="7">
         <f t="shared" si="0"/>
         <v>2004</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="7">
         <v>30400</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="C6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5">
+      <c r="F6" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
         <v>3</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="7">
         <v>12</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="7">
         <v>31</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="7">
         <v>1000</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="7">
         <v>21</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="7">
         <v>20</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="7">
         <v>4</v>
       </c>
-      <c r="O6" s="5">
-        <v>1</v>
-      </c>
-      <c r="P6" s="5">
+      <c r="O6" s="7">
+        <v>1</v>
+      </c>
+      <c r="P6" s="7">
         <v>99</v>
       </c>
-      <c r="Q6" s="5">
-        <v>1</v>
-      </c>
-      <c r="R6" s="5">
-        <v>0</v>
-      </c>
-      <c r="S6" s="5">
-        <v>3</v>
-      </c>
-      <c r="T6" s="5">
-        <v>0</v>
-      </c>
-      <c r="U6" s="5">
-        <v>0</v>
-      </c>
-      <c r="V6" s="5" t="s">
+      <c r="Q6" s="7">
+        <v>1</v>
+      </c>
+      <c r="R6" s="7">
+        <v>0</v>
+      </c>
+      <c r="S6" s="7">
+        <v>5</v>
+      </c>
+      <c r="T6" s="7">
+        <v>0</v>
+      </c>
+      <c r="U6" s="7">
+        <v>0</v>
+      </c>
+      <c r="V6" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="W6" s="5" t="s">
+      <c r="W6" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="X6" s="5" t="s">
+      <c r="X6" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="Y6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="Z6" s="5">
+      <c r="Z6" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="5">
+    <row r="7" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="7">
         <f t="shared" si="0"/>
         <v>2005</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="7">
         <v>30500</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5">
+      <c r="F7" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7">
         <v>5</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="7">
         <v>12</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="7">
         <v>31</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="7">
         <v>2000</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="7">
         <v>21</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="7">
         <v>23</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="7">
         <v>5</v>
       </c>
-      <c r="O7" s="5">
-        <v>1</v>
-      </c>
-      <c r="P7" s="5">
+      <c r="O7" s="7">
+        <v>1</v>
+      </c>
+      <c r="P7" s="7">
         <v>99</v>
       </c>
-      <c r="Q7" s="5">
-        <v>1</v>
-      </c>
-      <c r="R7" s="5">
-        <v>0</v>
-      </c>
-      <c r="S7" s="5">
+      <c r="Q7" s="7">
+        <v>1</v>
+      </c>
+      <c r="R7" s="7">
+        <v>0</v>
+      </c>
+      <c r="S7" s="7">
         <v>5</v>
       </c>
-      <c r="T7" s="5">
-        <v>0</v>
-      </c>
-      <c r="U7" s="5">
-        <v>0</v>
-      </c>
-      <c r="V7" s="5" t="s">
+      <c r="T7" s="7">
+        <v>0</v>
+      </c>
+      <c r="U7" s="7">
+        <v>0</v>
+      </c>
+      <c r="V7" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="W7" s="5" t="s">
+      <c r="W7" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="X7" s="5" t="s">
+      <c r="X7" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="Y7" s="6" t="s">
+      <c r="Y7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="Z7" s="5">
+      <c r="Z7" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="5">
+    <row r="8" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="7">
         <f t="shared" si="0"/>
         <v>2006</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="7">
         <v>30600</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="C8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="H8" s="5">
+      <c r="F8" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
         <v>3</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="7">
         <v>12</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="7">
         <v>31</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="7">
         <v>2000</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="7">
         <v>22</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="7">
         <v>30</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" s="7">
         <v>5</v>
       </c>
-      <c r="O8" s="5">
-        <v>1</v>
-      </c>
-      <c r="P8" s="5">
+      <c r="O8" s="7">
+        <v>1</v>
+      </c>
+      <c r="P8" s="7">
         <v>99</v>
       </c>
-      <c r="Q8" s="5">
-        <v>1</v>
-      </c>
-      <c r="R8" s="5">
-        <v>0</v>
-      </c>
-      <c r="S8" s="5">
+      <c r="Q8" s="7">
+        <v>1</v>
+      </c>
+      <c r="R8" s="7">
+        <v>0</v>
+      </c>
+      <c r="S8" s="7">
         <v>5</v>
       </c>
-      <c r="T8" s="5">
-        <v>0</v>
-      </c>
-      <c r="U8" s="5">
-        <v>0</v>
-      </c>
-      <c r="V8" s="5" t="s">
+      <c r="T8" s="7">
+        <v>0</v>
+      </c>
+      <c r="U8" s="7">
+        <v>0</v>
+      </c>
+      <c r="V8" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="W8" s="5" t="s">
+      <c r="W8" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="X8" s="5" t="s">
+      <c r="X8" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="Y8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="Z8" s="5">
+      <c r="Z8" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="5">
+    <row r="9" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="7">
         <f t="shared" si="0"/>
         <v>2007</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="7">
         <v>30700</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="C9" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5">
+      <c r="F9" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
         <v>5</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="7">
         <v>12</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="7">
         <v>31</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="7">
         <v>3000</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="7">
         <v>22</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="7">
         <v>38</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9" s="7">
         <v>4</v>
       </c>
-      <c r="O9" s="5">
-        <v>1</v>
-      </c>
-      <c r="P9" s="5">
+      <c r="O9" s="7">
+        <v>1</v>
+      </c>
+      <c r="P9" s="7">
         <v>99</v>
       </c>
-      <c r="Q9" s="5">
-        <v>1</v>
-      </c>
-      <c r="R9" s="5">
-        <v>0</v>
-      </c>
-      <c r="S9" s="5">
+      <c r="Q9" s="7">
+        <v>1</v>
+      </c>
+      <c r="R9" s="7">
+        <v>0</v>
+      </c>
+      <c r="S9" s="7">
         <v>5</v>
       </c>
-      <c r="T9" s="5">
-        <v>0</v>
-      </c>
-      <c r="U9" s="5">
-        <v>0</v>
-      </c>
-      <c r="V9" s="5" t="s">
+      <c r="T9" s="7">
+        <v>0</v>
+      </c>
+      <c r="U9" s="7">
+        <v>0</v>
+      </c>
+      <c r="V9" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="W9" s="5" t="s">
+      <c r="W9" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="X9" s="5" t="s">
+      <c r="X9" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="Y9" s="6" t="s">
+      <c r="Y9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="Z9" s="5">
+      <c r="Z9" s="7">
         <v>0</v>
       </c>
     </row>
@@ -4883,7 +4874,7 @@
         <v>126</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
@@ -4946,84 +4937,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="5">
+    <row r="11" spans="1:26" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="7">
         <f>ROW()-2+2000</f>
         <v>2009</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="7">
         <v>3000</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="C11" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0</v>
-      </c>
-      <c r="H11" s="5">
+      <c r="E11" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
         <v>5</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="7">
         <v>12</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="7">
         <v>31</v>
       </c>
-      <c r="K11" s="5">
-        <v>0</v>
-      </c>
-      <c r="L11" s="5">
+      <c r="K11" s="7">
+        <v>0</v>
+      </c>
+      <c r="L11" s="7">
         <v>300</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="7">
         <v>25</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N11" s="7">
         <v>5</v>
       </c>
-      <c r="O11" s="5">
-        <v>1</v>
-      </c>
-      <c r="P11" s="5">
+      <c r="O11" s="7">
+        <v>1</v>
+      </c>
+      <c r="P11" s="7">
         <v>99</v>
       </c>
-      <c r="Q11" s="5">
-        <v>0</v>
-      </c>
-      <c r="R11" s="5">
-        <v>0</v>
-      </c>
-      <c r="S11" s="5">
-        <v>0</v>
-      </c>
-      <c r="T11" s="5">
-        <v>0</v>
-      </c>
-      <c r="U11" s="5">
-        <v>0</v>
-      </c>
-      <c r="V11" s="5" t="s">
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7">
+        <v>0</v>
+      </c>
+      <c r="S11" s="7">
+        <v>0</v>
+      </c>
+      <c r="T11" s="7">
+        <v>0</v>
+      </c>
+      <c r="U11" s="7">
+        <v>0</v>
+      </c>
+      <c r="V11" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="W11" s="5" t="s">
+      <c r="W11" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="X11" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y11" s="6" t="s">
+      <c r="X11" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="Z11" s="5">
+      <c r="Z11" s="7">
         <v>1</v>
       </c>
     </row>
@@ -5147,7 +5138,7 @@
         <v>70</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G2" s="5">
         <v>0</v>
@@ -5228,7 +5219,7 @@
         <v>82</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G3" s="5">
         <v>0</v>
@@ -5390,7 +5381,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G5" s="5">
         <v>0</v>
@@ -5468,10 +5459,10 @@
         <v>60</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G6" s="5">
         <v>0</v>
@@ -5633,7 +5624,7 @@
         <v>80</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
@@ -5711,10 +5702,10 @@
         <v>63</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
@@ -5792,10 +5783,10 @@
         <v>47</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F7A28F-7279-48F5-B133-531DD1FF24BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1310B60-5379-4D2B-8887-098911030894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
@@ -1183,121 +1183,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t xml:space="preserve">紅茶限定
-ティータイムを彩る香り高い紅茶を募集しています。
-お菓子を引き立てる大切な名脇役のティー。その誇り高い香りを競い合います。
-</t>
-    <rPh sb="0" eb="2">
-      <t>コウチャ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>イロド</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>カオ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ダカ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>コウチャ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>タイセツ</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ワキヤク</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>ホコ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>タカ</t>
-    </rPh>
-    <rPh sb="56" eb="57">
-      <t>カオ</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>キソ</t>
-    </rPh>
-    <rPh sb="61" eb="62">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>青色をテーマにしたお菓子
-秋の大演奏会で、お客様へのお土産に渡すお菓子を募集しています。
-美しい青のお菓子をぜひ作って頂きたいです。</t>
-    <rPh sb="0" eb="2">
-      <t>アオイロ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>アキ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="16" eb="19">
-      <t>エンソウカイ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>キャク</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>サマ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ミヤゲ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ワタ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="45" eb="46">
-      <t>ウツク</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>アオ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="56" eb="57">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>イタダ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>お花をモチーフにしたお菓子限定
 お花をメインに使った華やかなお菓子を募集しています。
 クッキー・チョコレート・ケーキ・チーズケーキから１種類を募集します。</t>
@@ -1833,9 +1718,66 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t xml:space="preserve">紅茶限定
+ティータイムを彩る香り高い紅茶を募集。
+お菓子を引き立てる大切な名脇役のティー。その誇り高さを競い合ってもらいたい。
+</t>
+    <rPh sb="0" eb="2">
+      <t>コウチャ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>イロド</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ダカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウチャ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>タイセツ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ワキヤク</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ホコ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>芸術的なおかしお菓子限定
-名門ハイネン家の招待パーティーに飾るお菓子を募集しています。
-パーティーの目玉になる、芸術的なお菓子が希望ですわ♪</t>
+名門ハイネン家の招待パーティーに飾るお菓子を募集しています。パーティーの目玉になる、芸術的なお菓子が希望ですわ♪</t>
     <rPh sb="8" eb="10">
       <t>カシ</t>
     </rPh>
@@ -1860,20 +1802,50 @@
     <rPh sb="35" eb="37">
       <t>ボシュウ</t>
     </rPh>
-    <rPh sb="50" eb="52">
+    <rPh sb="49" eb="51">
       <t>メダマ</t>
     </rPh>
-    <rPh sb="56" eb="58">
+    <rPh sb="55" eb="57">
       <t>ゲイジュツ</t>
     </rPh>
-    <rPh sb="58" eb="59">
+    <rPh sb="57" eb="58">
       <t>テキ</t>
     </rPh>
-    <rPh sb="61" eb="63">
+    <rPh sb="60" eb="62">
       <t>カシ</t>
     </rPh>
-    <rPh sb="64" eb="66">
+    <rPh sb="63" eb="65">
       <t>キボウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>青色をテーマにしたお菓子
+ブルー・・それはとても美しい色。
+美しい青をテーマにしたお菓子をぜひ作ってください。</t>
+    <rPh sb="0" eb="2">
+      <t>アオイロ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1951,7 +1923,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1969,12 +1941,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2396,13 +2362,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -3050,7 +3016,7 @@
         <v>85</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3212,7 +3178,7 @@
         <v>29</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3557,7 +3523,7 @@
         <v>101</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3638,7 +3604,7 @@
         <v>67</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -3734,7 +3700,7 @@
         <v>31</v>
       </c>
       <c r="K6">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="L6">
         <v>11</v>
@@ -3944,84 +3910,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="7">
+    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9">
         <f>ROW()-2+1000</f>
         <v>1007</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9">
         <v>20700</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="G9" s="7">
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
+      <c r="F9" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>5</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9">
         <v>12</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9">
         <v>31</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9">
         <v>3000</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9">
         <v>12</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9">
         <v>18</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N9">
         <v>5</v>
       </c>
-      <c r="O9" s="7">
-        <v>1</v>
-      </c>
-      <c r="P9" s="7">
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
         <v>99</v>
       </c>
-      <c r="Q9" s="7">
-        <v>1</v>
-      </c>
-      <c r="R9" s="7">
-        <v>0</v>
-      </c>
-      <c r="S9" s="7">
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>8</v>
       </c>
-      <c r="T9" s="7">
-        <v>0</v>
-      </c>
-      <c r="U9" s="7">
-        <v>0</v>
-      </c>
-      <c r="V9" s="7" t="s">
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
         <v>117</v>
       </c>
-      <c r="W9" s="7" t="s">
+      <c r="W9" t="s">
         <v>120</v>
       </c>
-      <c r="X9" s="7" t="s">
+      <c r="X9" t="s">
         <v>116</v>
       </c>
-      <c r="Y9" s="8" t="s">
+      <c r="Y9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z9" s="7">
+      <c r="Z9">
         <v>0</v>
       </c>
     </row>
@@ -4040,10 +4006,10 @@
         <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -4208,651 +4174,651 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="7">
+    <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2">
         <f t="shared" ref="A2:A10" si="0">ROW()-2+2000</f>
         <v>2000</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2">
         <v>30000</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="7">
-        <v>0</v>
-      </c>
-      <c r="H2" s="7">
-        <v>1</v>
-      </c>
-      <c r="I2" s="7">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>12</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2">
         <v>31</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2">
         <v>300</v>
       </c>
-      <c r="L2" s="7">
-        <v>1</v>
-      </c>
-      <c r="M2" s="7">
-        <v>0</v>
-      </c>
-      <c r="N2" s="7">
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
         <v>2</v>
       </c>
-      <c r="O2" s="7">
-        <v>0</v>
-      </c>
-      <c r="P2" s="7">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
         <v>99</v>
       </c>
-      <c r="Q2" s="7">
-        <v>1</v>
-      </c>
-      <c r="R2" s="7">
-        <v>0</v>
-      </c>
-      <c r="S2" s="7">
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <v>3</v>
       </c>
-      <c r="T2" s="7">
-        <v>0</v>
-      </c>
-      <c r="U2" s="7">
-        <v>0</v>
-      </c>
-      <c r="V2" s="7" t="s">
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2" t="s">
         <v>118</v>
       </c>
-      <c r="W2" s="7" t="s">
+      <c r="W2" t="s">
         <v>122</v>
       </c>
-      <c r="X2" s="7" t="s">
+      <c r="X2" t="s">
         <v>116</v>
       </c>
-      <c r="Y2" s="8" t="s">
+      <c r="Y2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z2" s="7">
+      <c r="Z2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="7">
+    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3">
         <f t="shared" si="0"/>
         <v>2001</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3">
         <v>30100</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" t="s">
         <v>83</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="G3" s="7">
-        <v>0</v>
-      </c>
-      <c r="H3" s="7">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3">
         <v>12</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3">
         <v>31</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3">
         <v>500</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3">
         <v>20</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3">
         <v>10</v>
       </c>
-      <c r="N3" s="7">
+      <c r="N3">
         <v>2</v>
       </c>
-      <c r="O3" s="7">
-        <v>1</v>
-      </c>
-      <c r="P3" s="7">
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
         <v>99</v>
       </c>
-      <c r="Q3" s="7">
-        <v>1</v>
-      </c>
-      <c r="R3" s="7">
-        <v>0</v>
-      </c>
-      <c r="S3" s="7">
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <v>3</v>
       </c>
-      <c r="T3" s="7">
-        <v>0</v>
-      </c>
-      <c r="U3" s="7">
-        <v>0</v>
-      </c>
-      <c r="V3" s="7" t="s">
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3" t="s">
         <v>118</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="W3" t="s">
         <v>122</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="X3" t="s">
         <v>116</v>
       </c>
-      <c r="Y3" s="8" t="s">
+      <c r="Y3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z3" s="7">
+      <c r="Z3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="7">
+    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4">
         <f t="shared" si="0"/>
         <v>2002</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4">
         <v>30200</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="G4" s="7">
-        <v>0</v>
-      </c>
-      <c r="H4" s="7">
+      <c r="F4" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>3</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4">
         <v>12</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4">
         <v>31</v>
       </c>
-      <c r="K4" s="7">
-        <v>1200</v>
-      </c>
-      <c r="L4" s="7">
+      <c r="K4">
+        <v>500</v>
+      </c>
+      <c r="L4">
         <v>20</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4">
         <v>15</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4">
         <v>3</v>
       </c>
-      <c r="O4" s="7">
-        <v>1</v>
-      </c>
-      <c r="P4" s="7">
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
         <v>99</v>
       </c>
-      <c r="Q4" s="7">
-        <v>1</v>
-      </c>
-      <c r="R4" s="7">
-        <v>0</v>
-      </c>
-      <c r="S4" s="7">
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>5</v>
       </c>
-      <c r="T4" s="7">
-        <v>0</v>
-      </c>
-      <c r="U4" s="7">
-        <v>0</v>
-      </c>
-      <c r="V4" s="7" t="s">
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4" t="s">
         <v>118</v>
       </c>
-      <c r="W4" s="7" t="s">
+      <c r="W4" t="s">
         <v>122</v>
       </c>
-      <c r="X4" s="7" t="s">
+      <c r="X4" t="s">
         <v>116</v>
       </c>
-      <c r="Y4" s="8" t="s">
+      <c r="Y4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z4" s="7">
+      <c r="Z4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="7">
+    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
         <f t="shared" si="0"/>
         <v>2003</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5">
         <v>30300</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="G5" s="7">
-        <v>0</v>
-      </c>
-      <c r="H5" s="7">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>4</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5">
         <v>12</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5">
         <v>31</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5">
         <v>500</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5">
         <v>20</v>
       </c>
-      <c r="M5" s="7">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7">
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
         <v>3</v>
       </c>
-      <c r="O5" s="7">
-        <v>1</v>
-      </c>
-      <c r="P5" s="7">
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
         <v>99</v>
       </c>
-      <c r="Q5" s="7">
-        <v>1</v>
-      </c>
-      <c r="R5" s="7">
-        <v>0</v>
-      </c>
-      <c r="S5" s="7">
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>5</v>
       </c>
-      <c r="T5" s="7">
-        <v>0</v>
-      </c>
-      <c r="U5" s="7">
-        <v>0</v>
-      </c>
-      <c r="V5" s="7" t="s">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
         <v>118</v>
       </c>
-      <c r="W5" s="7" t="s">
+      <c r="W5" t="s">
         <v>122</v>
       </c>
-      <c r="X5" s="7" t="s">
+      <c r="X5" t="s">
         <v>116</v>
       </c>
-      <c r="Y5" s="8" t="s">
+      <c r="Y5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z5" s="7">
+      <c r="Z5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="7">
+    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6">
         <f t="shared" si="0"/>
         <v>2004</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6">
         <v>30400</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="G6" s="7">
-        <v>0</v>
-      </c>
-      <c r="H6" s="7">
+      <c r="F6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>3</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6">
         <v>12</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6">
         <v>31</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6">
         <v>1000</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6">
         <v>21</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6">
         <v>20</v>
       </c>
-      <c r="N6" s="7">
+      <c r="N6">
         <v>4</v>
       </c>
-      <c r="O6" s="7">
-        <v>1</v>
-      </c>
-      <c r="P6" s="7">
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
         <v>99</v>
       </c>
-      <c r="Q6" s="7">
-        <v>1</v>
-      </c>
-      <c r="R6" s="7">
-        <v>0</v>
-      </c>
-      <c r="S6" s="7">
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>5</v>
       </c>
-      <c r="T6" s="7">
-        <v>0</v>
-      </c>
-      <c r="U6" s="7">
-        <v>0</v>
-      </c>
-      <c r="V6" s="7" t="s">
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
         <v>118</v>
       </c>
-      <c r="W6" s="7" t="s">
+      <c r="W6" t="s">
         <v>122</v>
       </c>
-      <c r="X6" s="7" t="s">
+      <c r="X6" t="s">
         <v>116</v>
       </c>
-      <c r="Y6" s="8" t="s">
+      <c r="Y6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z6" s="7">
+      <c r="Z6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="7">
+    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>2005</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>30500</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" t="s">
         <v>86</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="G7" s="7">
-        <v>0</v>
-      </c>
-      <c r="H7" s="7">
+      <c r="F7" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>5</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7">
         <v>12</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7">
         <v>31</v>
       </c>
-      <c r="K7" s="7">
-        <v>2000</v>
-      </c>
-      <c r="L7" s="7">
+      <c r="K7">
+        <v>1200</v>
+      </c>
+      <c r="L7">
         <v>21</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7">
         <v>23</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7">
         <v>5</v>
       </c>
-      <c r="O7" s="7">
-        <v>1</v>
-      </c>
-      <c r="P7" s="7">
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
         <v>99</v>
       </c>
-      <c r="Q7" s="7">
-        <v>1</v>
-      </c>
-      <c r="R7" s="7">
-        <v>0</v>
-      </c>
-      <c r="S7" s="7">
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>5</v>
       </c>
-      <c r="T7" s="7">
-        <v>0</v>
-      </c>
-      <c r="U7" s="7">
-        <v>0</v>
-      </c>
-      <c r="V7" s="7" t="s">
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
         <v>118</v>
       </c>
-      <c r="W7" s="7" t="s">
+      <c r="W7" t="s">
         <v>122</v>
       </c>
-      <c r="X7" s="7" t="s">
+      <c r="X7" t="s">
         <v>116</v>
       </c>
-      <c r="Y7" s="8" t="s">
+      <c r="Y7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z7" s="7">
+      <c r="Z7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="7">
+    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>2006</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8">
         <v>30600</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" t="s">
         <v>87</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="G8" s="7">
-        <v>0</v>
-      </c>
-      <c r="H8" s="7">
+      <c r="F8" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>3</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8">
         <v>12</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8">
         <v>31</v>
       </c>
-      <c r="K8" s="7">
-        <v>2000</v>
-      </c>
-      <c r="L8" s="7">
+      <c r="K8">
+        <v>1500</v>
+      </c>
+      <c r="L8">
         <v>22</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8">
         <v>30</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N8">
         <v>5</v>
       </c>
-      <c r="O8" s="7">
-        <v>1</v>
-      </c>
-      <c r="P8" s="7">
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
         <v>99</v>
       </c>
-      <c r="Q8" s="7">
-        <v>1</v>
-      </c>
-      <c r="R8" s="7">
-        <v>0</v>
-      </c>
-      <c r="S8" s="7">
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>5</v>
       </c>
-      <c r="T8" s="7">
-        <v>0</v>
-      </c>
-      <c r="U8" s="7">
-        <v>0</v>
-      </c>
-      <c r="V8" s="7" t="s">
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8" t="s">
         <v>118</v>
       </c>
-      <c r="W8" s="7" t="s">
+      <c r="W8" t="s">
         <v>122</v>
       </c>
-      <c r="X8" s="7" t="s">
+      <c r="X8" t="s">
         <v>116</v>
       </c>
-      <c r="Y8" s="8" t="s">
+      <c r="Y8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z8" s="7">
+      <c r="Z8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="7">
+    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9">
         <f t="shared" si="0"/>
         <v>2007</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9">
         <v>30700</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" t="s">
         <v>74</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="G9" s="7">
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
+      <c r="F9" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>5</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9">
         <v>12</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9">
         <v>31</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9">
         <v>3000</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9">
         <v>22</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9">
         <v>38</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N9">
         <v>4</v>
       </c>
-      <c r="O9" s="7">
-        <v>1</v>
-      </c>
-      <c r="P9" s="7">
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
         <v>99</v>
       </c>
-      <c r="Q9" s="7">
-        <v>1</v>
-      </c>
-      <c r="R9" s="7">
-        <v>0</v>
-      </c>
-      <c r="S9" s="7">
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>5</v>
       </c>
-      <c r="T9" s="7">
-        <v>0</v>
-      </c>
-      <c r="U9" s="7">
-        <v>0</v>
-      </c>
-      <c r="V9" s="7" t="s">
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
         <v>118</v>
       </c>
-      <c r="W9" s="7" t="s">
+      <c r="W9" t="s">
         <v>122</v>
       </c>
-      <c r="X9" s="7" t="s">
+      <c r="X9" t="s">
         <v>116</v>
       </c>
-      <c r="Y9" s="8" t="s">
+      <c r="Y9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z9" s="7">
+      <c r="Z9">
         <v>0</v>
       </c>
     </row>
@@ -4937,84 +4903,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="7">
+    <row r="11" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11">
         <f>ROW()-2+2000</f>
         <v>2009</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11">
         <v>3000</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="C11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="G11" s="7">
-        <v>0</v>
-      </c>
-      <c r="H11" s="7">
+      <c r="E11" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>5</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11">
         <v>12</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11">
         <v>31</v>
       </c>
-      <c r="K11" s="7">
-        <v>0</v>
-      </c>
-      <c r="L11" s="7">
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
         <v>300</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M11">
         <v>25</v>
       </c>
-      <c r="N11" s="7">
+      <c r="N11">
         <v>5</v>
       </c>
-      <c r="O11" s="7">
-        <v>1</v>
-      </c>
-      <c r="P11" s="7">
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
         <v>99</v>
       </c>
-      <c r="Q11" s="7">
-        <v>0</v>
-      </c>
-      <c r="R11" s="7">
-        <v>0</v>
-      </c>
-      <c r="S11" s="7">
-        <v>0</v>
-      </c>
-      <c r="T11" s="7">
-        <v>0</v>
-      </c>
-      <c r="U11" s="7">
-        <v>0</v>
-      </c>
-      <c r="V11" s="7" t="s">
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11" t="s">
         <v>118</v>
       </c>
-      <c r="W11" s="7" t="s">
+      <c r="W11" t="s">
         <v>122</v>
       </c>
-      <c r="X11" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y11" s="8" t="s">
+      <c r="X11" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z11" s="7">
+      <c r="Z11">
         <v>1</v>
       </c>
     </row>
@@ -5138,7 +5104,7 @@
         <v>70</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G2" s="5">
         <v>0</v>
@@ -5234,7 +5200,7 @@
         <v>31</v>
       </c>
       <c r="K3" s="5">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="L3" s="5">
         <v>30</v>
@@ -5315,7 +5281,7 @@
         <v>31</v>
       </c>
       <c r="K4" s="5">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="L4" s="5">
         <v>30</v>
@@ -5381,7 +5347,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G5" s="5">
         <v>0</v>
@@ -5396,7 +5362,7 @@
         <v>31</v>
       </c>
       <c r="K5" s="5">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="L5" s="5">
         <v>31</v>
@@ -5459,10 +5425,10 @@
         <v>60</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G6" s="5">
         <v>0</v>
@@ -5477,7 +5443,7 @@
         <v>31</v>
       </c>
       <c r="K6" s="5">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="L6" s="5">
         <v>30</v>
@@ -5558,7 +5524,7 @@
         <v>31</v>
       </c>
       <c r="K7" s="5">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="L7" s="5">
         <v>31</v>
@@ -5624,7 +5590,7 @@
         <v>80</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
@@ -5705,7 +5671,7 @@
         <v>128</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
@@ -5783,10 +5749,10 @@
         <v>47</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>
@@ -5801,7 +5767,7 @@
         <v>31</v>
       </c>
       <c r="K10" s="5">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5">
         <v>400</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1310B60-5379-4D2B-8887-098911030894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDDD8FBA-0A7E-43E0-BB4C-90A1F4043DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1965" yWindow="1200" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -4858,7 +4858,7 @@
         <v>3000</v>
       </c>
       <c r="L10" s="2">
-        <v>22</v>
+        <v>9999</v>
       </c>
       <c r="M10" s="2">
         <v>38</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDDD8FBA-0A7E-43E0-BB4C-90A1F4043DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B361EC4D-5739-4F19-8D73-8178AF278DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1965" yWindow="1200" windowWidth="25560" windowHeight="14325" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1560" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -2569,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -2650,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -3055,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T10">
         <v>0</v>
@@ -3400,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O4">
         <v>1</v>
@@ -3562,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3724,7 +3724,7 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -3886,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4312,7 +4312,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4474,7 +4474,7 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4555,7 +4555,7 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4621,7 +4621,7 @@
         <v>23</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>1</v>
@@ -4636,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -4798,7 +4798,7 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -5143,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2" s="5">
         <v>0</v>
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" s="5">
         <v>0</v>
@@ -5305,7 +5305,7 @@
         <v>0</v>
       </c>
       <c r="S4" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" s="5">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>0</v>
       </c>
       <c r="S5" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T5" s="5">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T6" s="5">
         <v>0</v>
@@ -5533,7 +5533,7 @@
         <v>45</v>
       </c>
       <c r="N7" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O7" s="5">
         <v>1</v>
@@ -5548,7 +5548,7 @@
         <v>0</v>
       </c>
       <c r="S7" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T7" s="5">
         <v>0</v>
@@ -5614,7 +5614,7 @@
         <v>60</v>
       </c>
       <c r="N8" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O8" s="5">
         <v>1</v>
@@ -5629,7 +5629,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T8" s="5">
         <v>0</v>
@@ -5710,7 +5710,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B361EC4D-5739-4F19-8D73-8178AF278DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF2A63B-AAAA-4389-869A-265BEA337B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1995" yWindow="975" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -421,10 +421,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>マジックパティスリー・アワード</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>クレープ・ドゥ・シャノワール</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -484,16 +480,6 @@
   </si>
   <si>
     <t>コンチェルティーノ・イン・ブルー</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>プラム洋菓子技術コンテスト</t>
-    <rPh sb="3" eb="6">
-      <t>ヨウガシ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ギジュツ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1536,33 +1522,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>◆おかしの国際コンクール◆
-テーマ：自由課題
-優勝者には、特別レシピを進呈します。自信のあるお菓子で参加してください！</t>
-    <rPh sb="5" eb="7">
-      <t>コクサイ</t>
-    </rPh>
-    <rPh sb="23" eb="26">
-      <t>ユウショウシャ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>トクベツ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>シンテイ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>サンカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>sound73</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1648,36 +1607,6 @@
     </rPh>
     <rPh sb="54" eb="56">
       <t>カシ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ケーキ限定
-隣国プラムで行われるケーキコンテストです。
-各界隈の著名人が注目するトップレベルのコンテストです。</t>
-    <rPh sb="3" eb="5">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>リンコク</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="28" eb="31">
-      <t>カクカイワイ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>チョメイ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ジン</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>チュウモク</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ダイチュウモク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1847,6 +1776,89 @@
     <rPh sb="47" eb="48">
       <t>ツク</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>パフェ限定
+隣国プラムで行われるパフェコンテストです。
+各界隈の著名人が注目するトップレベルのコンテストです。</t>
+    <rPh sb="3" eb="5">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>リンコク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>カクカイワイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>チョメイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ジン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>チュウモク</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ダイチュウモク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プラムアイス技術コンテスト</t>
+    <rPh sb="6" eb="8">
+      <t>ギジュツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆秋の伝統的なお菓子コンクール◆
+テーマ：自由課題
+秋エリアの伝統的で由緒あるコンクールです。食べた人を幸せにするお菓子をお待ちしております。</t>
+    <rPh sb="1" eb="2">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>デントウテキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>デントウ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ユイショ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>シアワ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マジカル・パティスリー・アワード</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2329,19 +2341,19 @@
         <v>28</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>19</v>
@@ -2352,7 +2364,7 @@
     </row>
     <row r="2" spans="1:26" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
-        <f t="shared" ref="A2:A11" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A12" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="2">
@@ -2362,13 +2374,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -2416,13 +2428,13 @@
         <v>0</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Y2" s="3" t="s">
         <v>20</v>
@@ -2449,7 +2461,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2497,13 +2509,13 @@
         <v>0</v>
       </c>
       <c r="V3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W3" t="s">
+        <v>112</v>
+      </c>
+      <c r="X3" t="s">
         <v>114</v>
-      </c>
-      <c r="X3" t="s">
-        <v>116</v>
       </c>
       <c r="Y3" s="4" t="s">
         <v>21</v>
@@ -2527,10 +2539,10 @@
         <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2578,16 +2590,16 @@
         <v>0</v>
       </c>
       <c r="V4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W4" t="s">
+        <v>112</v>
+      </c>
+      <c r="X4" t="s">
         <v>114</v>
       </c>
-      <c r="X4" t="s">
-        <v>116</v>
-      </c>
       <c r="Y4" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2608,10 +2620,10 @@
         <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2659,13 +2671,13 @@
         <v>0</v>
       </c>
       <c r="V5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W5" t="s">
+        <v>112</v>
+      </c>
+      <c r="X5" t="s">
         <v>114</v>
-      </c>
-      <c r="X5" t="s">
-        <v>116</v>
       </c>
       <c r="Y5" s="4" t="s">
         <v>21</v>
@@ -2680,25 +2692,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>10100</v>
+        <v>10200</v>
       </c>
       <c r="C6" t="s">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>12</v>
@@ -2707,13 +2719,13 @@
         <v>31</v>
       </c>
       <c r="K6">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N6">
         <v>3</v>
@@ -2740,16 +2752,16 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W6" t="s">
+        <v>112</v>
+      </c>
+      <c r="X6" t="s">
         <v>114</v>
       </c>
-      <c r="X6" t="s">
-        <v>116</v>
-      </c>
       <c r="Y6" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2761,25 +2773,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>10200</v>
+        <v>10400</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>12</v>
@@ -2788,7 +2800,7 @@
         <v>31</v>
       </c>
       <c r="K7">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="L7">
         <v>3</v>
@@ -2821,13 +2833,13 @@
         <v>0</v>
       </c>
       <c r="V7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W7" t="s">
+        <v>112</v>
+      </c>
+      <c r="X7" t="s">
         <v>114</v>
-      </c>
-      <c r="X7" t="s">
-        <v>116</v>
       </c>
       <c r="Y7" s="4" t="s">
         <v>21</v>
@@ -2842,25 +2854,25 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>10400</v>
+        <v>10500</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8">
         <v>12</v>
@@ -2869,16 +2881,16 @@
         <v>31</v>
       </c>
       <c r="K8">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -2902,13 +2914,13 @@
         <v>0</v>
       </c>
       <c r="V8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W8" t="s">
+        <v>112</v>
+      </c>
+      <c r="X8" t="s">
         <v>114</v>
-      </c>
-      <c r="X8" t="s">
-        <v>116</v>
       </c>
       <c r="Y8" s="4" t="s">
         <v>21</v>
@@ -2923,25 +2935,25 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>10500</v>
+        <v>30200</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9">
         <v>12</v>
@@ -2950,19 +2962,19 @@
         <v>31</v>
       </c>
       <c r="K9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9">
         <v>99</v>
@@ -2983,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="V9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W9" t="s">
+        <v>112</v>
+      </c>
+      <c r="X9" t="s">
         <v>114</v>
-      </c>
-      <c r="X9" t="s">
-        <v>116</v>
       </c>
       <c r="Y9" s="4" t="s">
         <v>21</v>
@@ -3004,25 +3016,25 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>10600</v>
+        <v>30300</v>
       </c>
       <c r="C10" t="s">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>12</v>
@@ -3031,19 +3043,19 @@
         <v>31</v>
       </c>
       <c r="K10">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="L10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M10">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10">
         <v>99</v>
@@ -3064,13 +3076,13 @@
         <v>0</v>
       </c>
       <c r="V10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W10" t="s">
+        <v>112</v>
+      </c>
+      <c r="X10" t="s">
         <v>114</v>
-      </c>
-      <c r="X10" t="s">
-        <v>116</v>
       </c>
       <c r="Y10" s="4" t="s">
         <v>21</v>
@@ -3085,19 +3097,19 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>10700</v>
+        <v>30700</v>
       </c>
       <c r="C11" t="s">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -3118,13 +3130,13 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11">
         <v>99</v>
@@ -3136,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="S11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11">
         <v>0</v>
@@ -3145,13 +3157,13 @@
         <v>0</v>
       </c>
       <c r="V11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W11" t="s">
+        <v>112</v>
+      </c>
+      <c r="X11" t="s">
         <v>114</v>
-      </c>
-      <c r="X11" t="s">
-        <v>116</v>
       </c>
       <c r="Y11" s="4" t="s">
         <v>21</v>
@@ -3162,7 +3174,7 @@
     </row>
     <row r="12" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B12">
@@ -3178,7 +3190,7 @@
         <v>29</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3226,13 +3238,13 @@
         <v>0</v>
       </c>
       <c r="V12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="X12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Y12" s="4" t="s">
         <v>20</v>
@@ -3250,6 +3262,918 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B615D1EB-7EB0-40A6-B71A-0773034D7CD2}">
+  <dimension ref="A1:Z11"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="3" max="3" width="13.25" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="20.625" customWidth="1"/>
+    <col min="6" max="6" width="19.75" customWidth="1"/>
+    <col min="7" max="10" width="7.5" customWidth="1"/>
+    <col min="11" max="11" width="8.125" customWidth="1"/>
+    <col min="12" max="24" width="6.75" customWidth="1"/>
+    <col min="25" max="25" width="25.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <f t="shared" ref="A2:A9" si="0">ROW()-2+1000</f>
+        <v>1000</v>
+      </c>
+      <c r="B2">
+        <v>20000</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>12</v>
+      </c>
+      <c r="J2">
+        <v>31</v>
+      </c>
+      <c r="K2">
+        <v>100</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>99</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>2</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2" t="s">
+        <v>115</v>
+      </c>
+      <c r="W2" t="s">
+        <v>118</v>
+      </c>
+      <c r="X2" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <f t="shared" si="0"/>
+        <v>1001</v>
+      </c>
+      <c r="B3">
+        <v>20100</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>12</v>
+      </c>
+      <c r="J3">
+        <v>31</v>
+      </c>
+      <c r="K3">
+        <v>200</v>
+      </c>
+      <c r="L3">
+        <v>10</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>99</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>2</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3" t="s">
+        <v>115</v>
+      </c>
+      <c r="W3" t="s">
+        <v>118</v>
+      </c>
+      <c r="X3" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <f t="shared" si="0"/>
+        <v>1002</v>
+      </c>
+      <c r="B4">
+        <v>20200</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4">
+        <v>31</v>
+      </c>
+      <c r="K4">
+        <v>300</v>
+      </c>
+      <c r="L4">
+        <v>10</v>
+      </c>
+      <c r="M4">
+        <v>5</v>
+      </c>
+      <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>99</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>2</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4" t="s">
+        <v>115</v>
+      </c>
+      <c r="W4" t="s">
+        <v>118</v>
+      </c>
+      <c r="X4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>1003</v>
+      </c>
+      <c r="B5">
+        <v>20300</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
+      <c r="J5">
+        <v>31</v>
+      </c>
+      <c r="K5">
+        <v>500</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>7</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>99</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>3</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
+        <v>115</v>
+      </c>
+      <c r="W5" t="s">
+        <v>118</v>
+      </c>
+      <c r="X5" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>1004</v>
+      </c>
+      <c r="B6">
+        <v>20400</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>31</v>
+      </c>
+      <c r="K6">
+        <v>700</v>
+      </c>
+      <c r="L6">
+        <v>11</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+      <c r="N6">
+        <v>4</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>99</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>3</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
+        <v>115</v>
+      </c>
+      <c r="W6" t="s">
+        <v>118</v>
+      </c>
+      <c r="X6" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>1005</v>
+      </c>
+      <c r="B7">
+        <v>30400</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>12</v>
+      </c>
+      <c r="J7">
+        <v>31</v>
+      </c>
+      <c r="K7">
+        <v>1000</v>
+      </c>
+      <c r="L7">
+        <v>11</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+      <c r="N7">
+        <v>4</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>99</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>3</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
+        <v>115</v>
+      </c>
+      <c r="W7" t="s">
+        <v>118</v>
+      </c>
+      <c r="X7" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>1006</v>
+      </c>
+      <c r="B8">
+        <v>20500</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>31</v>
+      </c>
+      <c r="K8">
+        <v>1500</v>
+      </c>
+      <c r="L8">
+        <v>10</v>
+      </c>
+      <c r="M8">
+        <v>10</v>
+      </c>
+      <c r="N8">
+        <v>4</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>99</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>3</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8" t="s">
+        <v>115</v>
+      </c>
+      <c r="W8" t="s">
+        <v>118</v>
+      </c>
+      <c r="X8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>1007</v>
+      </c>
+      <c r="B9">
+        <v>20600</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9">
+        <v>12</v>
+      </c>
+      <c r="J9">
+        <v>31</v>
+      </c>
+      <c r="K9">
+        <v>1500</v>
+      </c>
+      <c r="L9">
+        <v>12</v>
+      </c>
+      <c r="M9">
+        <v>15</v>
+      </c>
+      <c r="N9">
+        <v>4</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>99</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>3</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
+        <v>115</v>
+      </c>
+      <c r="W9" t="s">
+        <v>118</v>
+      </c>
+      <c r="X9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <f>ROW()-2+1000</f>
+        <v>1008</v>
+      </c>
+      <c r="B10">
+        <v>20700</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>12</v>
+      </c>
+      <c r="J10">
+        <v>31</v>
+      </c>
+      <c r="K10">
+        <v>3000</v>
+      </c>
+      <c r="L10">
+        <v>12</v>
+      </c>
+      <c r="M10">
+        <v>18</v>
+      </c>
+      <c r="N10">
+        <v>5</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>99</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>5</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10" t="s">
+        <v>115</v>
+      </c>
+      <c r="W10" t="s">
+        <v>118</v>
+      </c>
+      <c r="X10" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <f>ROW()-2+1000</f>
+        <v>1009</v>
+      </c>
+      <c r="B11">
+        <v>2000</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" t="s">
+        <v>142</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>12</v>
+      </c>
+      <c r="J11">
+        <v>31</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>200</v>
+      </c>
+      <c r="M11">
+        <v>15</v>
+      </c>
+      <c r="N11">
+        <v>5</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>99</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11" t="s">
+        <v>115</v>
+      </c>
+      <c r="W11" t="s">
+        <v>118</v>
+      </c>
+      <c r="X11" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A66AAA5-0C8D-4F8A-9A3B-33AFE45A42B1}">
   <dimension ref="A1:Z10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -3322,19 +4246,19 @@
         <v>28</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>19</v>
@@ -3345,29 +4269,29 @@
     </row>
     <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A8" si="0">ROW()-2+1000</f>
-        <v>1000</v>
+        <f>ROW()-2+2000</f>
+        <v>2000</v>
       </c>
       <c r="B2">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>12</v>
@@ -3376,7 +4300,7 @@
         <v>31</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -3385,7 +4309,7 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -3409,13 +4333,13 @@
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="W2" t="s">
         <v>120</v>
       </c>
       <c r="X2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y2" s="4" t="s">
         <v>21</v>
@@ -3426,23 +4350,23 @@
     </row>
     <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
-        <f t="shared" si="0"/>
-        <v>1001</v>
+        <f>ROW()-2+2000</f>
+        <v>2001</v>
       </c>
       <c r="B3">
-        <v>20100</v>
+        <v>30100</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -3457,13 +4381,13 @@
         <v>31</v>
       </c>
       <c r="K3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="L3">
+        <v>20</v>
+      </c>
+      <c r="M3">
         <v>10</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
       </c>
       <c r="N3">
         <v>2</v>
@@ -3490,13 +4414,13 @@
         <v>0</v>
       </c>
       <c r="V3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="W3" t="s">
         <v>120</v>
       </c>
       <c r="X3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y3" s="4" t="s">
         <v>24</v>
@@ -3507,23 +4431,23 @@
     </row>
     <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
-        <f t="shared" si="0"/>
-        <v>1002</v>
+        <f>ROW()-2+2000</f>
+        <v>2002</v>
       </c>
       <c r="B4">
-        <v>20200</v>
+        <v>10100</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3538,19 +4462,19 @@
         <v>31</v>
       </c>
       <c r="K4">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="L4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>99</v>
@@ -3562,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3571,16 +4495,16 @@
         <v>0</v>
       </c>
       <c r="V4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="W4" t="s">
         <v>120</v>
       </c>
       <c r="X4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -3588,20 +4512,20 @@
     </row>
     <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
-        <f t="shared" si="0"/>
-        <v>1003</v>
+        <f>ROW()-2+2000</f>
+        <v>2003</v>
       </c>
       <c r="B5">
-        <v>20300</v>
+        <v>30500</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>153</v>
@@ -3610,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>12</v>
@@ -3619,16 +4543,16 @@
         <v>31</v>
       </c>
       <c r="K5">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="M5">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O5">
         <v>1</v>
@@ -3652,13 +4576,13 @@
         <v>0</v>
       </c>
       <c r="V5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="W5" t="s">
         <v>120</v>
       </c>
       <c r="X5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y5" s="4" t="s">
         <v>21</v>
@@ -3669,29 +4593,29 @@
     </row>
     <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
-        <f t="shared" si="0"/>
-        <v>1004</v>
+        <f>ROW()-2+2000</f>
+        <v>2004</v>
       </c>
       <c r="B6">
-        <v>20400</v>
+        <v>30600</v>
       </c>
       <c r="C6" t="s">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>69</v>
+        <v>154</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>12</v>
@@ -3700,16 +4624,16 @@
         <v>31</v>
       </c>
       <c r="K6">
-        <v>700</v>
+        <v>1500</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>1</v>
@@ -3724,7 +4648,7 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -3733,13 +4657,13 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="W6" t="s">
         <v>120</v>
       </c>
       <c r="X6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y6" s="4" t="s">
         <v>21</v>
@@ -3750,29 +4674,29 @@
     </row>
     <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
-        <f t="shared" si="0"/>
-        <v>1005</v>
+        <f t="shared" ref="A7:A8" si="0">ROW()-2+2000</f>
+        <v>2005</v>
       </c>
       <c r="B7">
-        <v>20500</v>
+        <v>10600</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>12</v>
@@ -3781,19 +4705,19 @@
         <v>31</v>
       </c>
       <c r="K7">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="L7">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N7">
         <v>4</v>
       </c>
       <c r="O7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>99</v>
@@ -3814,844 +4738,13 @@
         <v>0</v>
       </c>
       <c r="V7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="W7" t="s">
         <v>120</v>
       </c>
       <c r="X7" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8">
-        <f t="shared" si="0"/>
-        <v>1006</v>
-      </c>
-      <c r="B8">
-        <v>20600</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>31</v>
-      </c>
-      <c r="K8">
-        <v>1500</v>
-      </c>
-      <c r="L8">
-        <v>12</v>
-      </c>
-      <c r="M8">
-        <v>15</v>
-      </c>
-      <c r="N8">
-        <v>4</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
-        <v>99</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>3</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8" t="s">
-        <v>117</v>
-      </c>
-      <c r="W8" t="s">
-        <v>120</v>
-      </c>
-      <c r="X8" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9">
-        <f>ROW()-2+1000</f>
-        <v>1007</v>
-      </c>
-      <c r="B9">
-        <v>20700</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>5</v>
-      </c>
-      <c r="I9">
-        <v>12</v>
-      </c>
-      <c r="J9">
-        <v>31</v>
-      </c>
-      <c r="K9">
-        <v>3000</v>
-      </c>
-      <c r="L9">
-        <v>12</v>
-      </c>
-      <c r="M9">
-        <v>18</v>
-      </c>
-      <c r="N9">
-        <v>5</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9">
-        <v>99</v>
-      </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>5</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9" t="s">
-        <v>117</v>
-      </c>
-      <c r="W9" t="s">
-        <v>120</v>
-      </c>
-      <c r="X9" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10">
-        <f>ROW()-2+1000</f>
-        <v>1008</v>
-      </c>
-      <c r="B10">
-        <v>2000</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" t="s">
-        <v>144</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>5</v>
-      </c>
-      <c r="I10">
-        <v>12</v>
-      </c>
-      <c r="J10">
-        <v>31</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>200</v>
-      </c>
-      <c r="M10">
-        <v>15</v>
-      </c>
-      <c r="N10">
-        <v>5</v>
-      </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
-      <c r="P10">
-        <v>99</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10" t="s">
-        <v>117</v>
-      </c>
-      <c r="W10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X10" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z10">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A66AAA5-0C8D-4F8A-9A3B-33AFE45A42B1}">
-  <dimension ref="A1:Z11"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="3" max="3" width="13.25" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
-    <col min="6" max="6" width="19.75" customWidth="1"/>
-    <col min="7" max="10" width="7.5" customWidth="1"/>
-    <col min="11" max="11" width="8.125" customWidth="1"/>
-    <col min="12" max="24" width="6.75" customWidth="1"/>
-    <col min="25" max="25" width="25.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2">
-        <f t="shared" ref="A2:A10" si="0">ROW()-2+2000</f>
-        <v>2000</v>
-      </c>
-      <c r="B2">
-        <v>30000</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>12</v>
-      </c>
-      <c r="J2">
-        <v>31</v>
-      </c>
-      <c r="K2">
-        <v>300</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>2</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>99</v>
-      </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>2</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2" t="s">
-        <v>118</v>
-      </c>
-      <c r="W2" t="s">
-        <v>122</v>
-      </c>
-      <c r="X2" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3">
-        <f t="shared" si="0"/>
-        <v>2001</v>
-      </c>
-      <c r="B3">
-        <v>30100</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>12</v>
-      </c>
-      <c r="J3">
-        <v>31</v>
-      </c>
-      <c r="K3">
-        <v>500</v>
-      </c>
-      <c r="L3">
-        <v>20</v>
-      </c>
-      <c r="M3">
-        <v>10</v>
-      </c>
-      <c r="N3">
-        <v>2</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
-        <v>99</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>2</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3" t="s">
-        <v>118</v>
-      </c>
-      <c r="W3" t="s">
-        <v>122</v>
-      </c>
-      <c r="X3" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4">
-        <f t="shared" si="0"/>
-        <v>2002</v>
-      </c>
-      <c r="B4">
-        <v>30200</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>12</v>
-      </c>
-      <c r="J4">
-        <v>31</v>
-      </c>
-      <c r="K4">
-        <v>500</v>
-      </c>
-      <c r="L4">
-        <v>20</v>
-      </c>
-      <c r="M4">
-        <v>15</v>
-      </c>
-      <c r="N4">
-        <v>3</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>99</v>
-      </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>3</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4" t="s">
-        <v>118</v>
-      </c>
-      <c r="W4" t="s">
-        <v>122</v>
-      </c>
-      <c r="X4" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5">
-        <f t="shared" si="0"/>
-        <v>2003</v>
-      </c>
-      <c r="B5">
-        <v>30300</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>12</v>
-      </c>
-      <c r="J5">
-        <v>31</v>
-      </c>
-      <c r="K5">
-        <v>500</v>
-      </c>
-      <c r="L5">
-        <v>20</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>3</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>99</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>3</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5" t="s">
-        <v>118</v>
-      </c>
-      <c r="W5" t="s">
-        <v>122</v>
-      </c>
-      <c r="X5" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6">
-        <f t="shared" si="0"/>
-        <v>2004</v>
-      </c>
-      <c r="B6">
-        <v>30400</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>31</v>
-      </c>
-      <c r="K6">
-        <v>1000</v>
-      </c>
-      <c r="L6">
-        <v>21</v>
-      </c>
-      <c r="M6">
-        <v>20</v>
-      </c>
-      <c r="N6">
-        <v>4</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
-        <v>99</v>
-      </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>3</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6" t="s">
-        <v>118</v>
-      </c>
-      <c r="W6" t="s">
-        <v>122</v>
-      </c>
-      <c r="X6" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7">
-        <f t="shared" si="0"/>
-        <v>2005</v>
-      </c>
-      <c r="B7">
-        <v>30500</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>12</v>
-      </c>
-      <c r="J7">
-        <v>31</v>
-      </c>
-      <c r="K7">
-        <v>1200</v>
-      </c>
-      <c r="L7">
-        <v>21</v>
-      </c>
-      <c r="M7">
-        <v>23</v>
-      </c>
-      <c r="N7">
-        <v>4</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>99</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>3</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7" t="s">
-        <v>118</v>
-      </c>
-      <c r="W7" t="s">
-        <v>122</v>
-      </c>
-      <c r="X7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y7" s="4" t="s">
         <v>21</v>
@@ -4666,25 +4759,25 @@
         <v>2006</v>
       </c>
       <c r="B8">
-        <v>30600</v>
+        <v>10700</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>12</v>
@@ -4693,19 +4786,19 @@
         <v>31</v>
       </c>
       <c r="K8">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="L8">
         <v>22</v>
       </c>
       <c r="M8">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <v>99</v>
@@ -4726,13 +4819,13 @@
         <v>0</v>
       </c>
       <c r="V8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="W8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="X8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y8" s="4" t="s">
         <v>21</v>
@@ -4741,246 +4834,165 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9">
-        <f t="shared" si="0"/>
+    <row r="9" spans="1:26" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="2">
+        <f>ROW()-2+2000</f>
         <v>2007</v>
       </c>
-      <c r="B9">
-        <v>30700</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="B9" s="2">
+        <v>30800</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
         <v>5</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>12</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="2">
         <v>31</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="2">
         <v>3000</v>
       </c>
-      <c r="L9">
-        <v>22</v>
-      </c>
-      <c r="M9">
+      <c r="L9" s="2">
+        <v>9999</v>
+      </c>
+      <c r="M9" s="2">
         <v>38</v>
       </c>
-      <c r="N9">
-        <v>4</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9">
+      <c r="N9" s="2">
+        <v>3</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2">
         <v>99</v>
       </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>3</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9" t="s">
-        <v>118</v>
-      </c>
-      <c r="W9" t="s">
-        <v>122</v>
-      </c>
-      <c r="X9" t="s">
+      <c r="Q9" s="2">
+        <v>1</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
+        <v>5</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="Y9" s="4" t="s">
+      <c r="W9" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="2">
-        <f t="shared" si="0"/>
+    <row r="10" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <f>ROW()-2+2000</f>
         <v>2008</v>
       </c>
-      <c r="B10" s="2">
-        <v>30800</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2">
+      <c r="B10">
+        <v>3000</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>138</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>5</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10">
         <v>12</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10">
         <v>31</v>
       </c>
-      <c r="K10" s="2">
-        <v>3000</v>
-      </c>
-      <c r="L10" s="2">
-        <v>9999</v>
-      </c>
-      <c r="M10" s="2">
-        <v>38</v>
-      </c>
-      <c r="N10" s="2">
-        <v>3</v>
-      </c>
-      <c r="O10" s="2">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2">
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>300</v>
+      </c>
+      <c r="M10">
+        <v>25</v>
+      </c>
+      <c r="N10">
+        <v>5</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
         <v>99</v>
       </c>
-      <c r="Q10" s="2">
-        <v>1</v>
-      </c>
-      <c r="R10" s="2">
-        <v>0</v>
-      </c>
-      <c r="S10" s="2">
-        <v>5</v>
-      </c>
-      <c r="T10" s="2">
-        <v>0</v>
-      </c>
-      <c r="U10" s="2">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="X10" s="2" t="s">
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10" t="s">
         <v>116</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z10" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11">
-        <f>ROW()-2+2000</f>
-        <v>2009</v>
-      </c>
-      <c r="B11">
-        <v>3000</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" t="s">
-        <v>140</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>5</v>
-      </c>
-      <c r="I11">
-        <v>12</v>
-      </c>
-      <c r="J11">
-        <v>31</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>300</v>
-      </c>
-      <c r="M11">
-        <v>25</v>
-      </c>
-      <c r="N11">
-        <v>5</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="P11">
-        <v>99</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11" t="s">
-        <v>118</v>
-      </c>
-      <c r="W11" t="s">
-        <v>122</v>
-      </c>
-      <c r="X11" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y11" s="4" t="s">
+      <c r="W10" t="s">
+        <v>120</v>
+      </c>
+      <c r="X10" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z11">
+      <c r="Z10">
         <v>1</v>
       </c>
     </row>
@@ -5065,19 +5077,19 @@
         <v>28</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>19</v>
@@ -5104,7 +5116,7 @@
         <v>70</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G2" s="5">
         <v>0</v>
@@ -5152,13 +5164,13 @@
         <v>0</v>
       </c>
       <c r="V2" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="W2" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W2" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="X2" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y2" s="6" t="s">
         <v>21</v>
@@ -5182,10 +5194,10 @@
         <v>57</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G3" s="5">
         <v>0</v>
@@ -5233,13 +5245,13 @@
         <v>0</v>
       </c>
       <c r="V3" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="W3" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W3" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="X3" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y3" s="6" t="s">
         <v>24</v>
@@ -5263,7 +5275,7 @@
         <v>58</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>71</v>
@@ -5314,13 +5326,13 @@
         <v>0</v>
       </c>
       <c r="V4" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="W4" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W4" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="X4" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y4" s="6" t="s">
         <v>21</v>
@@ -5344,10 +5356,10 @@
         <v>59</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G5" s="5">
         <v>0</v>
@@ -5395,13 +5407,13 @@
         <v>0</v>
       </c>
       <c r="V5" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="W5" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W5" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="X5" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y5" s="6" t="s">
         <v>21</v>
@@ -5425,10 +5437,10 @@
         <v>60</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G6" s="5">
         <v>0</v>
@@ -5476,13 +5488,13 @@
         <v>0</v>
       </c>
       <c r="V6" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="W6" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W6" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="X6" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y6" s="6" t="s">
         <v>21</v>
@@ -5506,10 +5518,10 @@
         <v>61</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="G7" s="5">
         <v>0</v>
@@ -5557,13 +5569,13 @@
         <v>0</v>
       </c>
       <c r="V7" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="W7" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W7" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="X7" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y7" s="6" t="s">
         <v>21</v>
@@ -5587,10 +5599,10 @@
         <v>62</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
@@ -5638,13 +5650,13 @@
         <v>0</v>
       </c>
       <c r="V8" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="W8" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W8" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="X8" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y8" s="6" t="s">
         <v>21</v>
@@ -5668,10 +5680,10 @@
         <v>63</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
@@ -5719,13 +5731,13 @@
         <v>0</v>
       </c>
       <c r="V9" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="W9" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W9" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="X9" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Y9" s="6" t="s">
         <v>21</v>
@@ -5749,10 +5761,10 @@
         <v>47</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>
@@ -5800,13 +5812,13 @@
         <v>0</v>
       </c>
       <c r="V10" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="W10" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="W10" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="X10" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Y10" s="6" t="s">
         <v>20</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF2A63B-AAAA-4389-869A-265BEA337B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46EE316-A96E-4201-B5B1-821809F09F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1995" yWindow="975" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2730" yWindow="1245" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="162">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -1859,6 +1859,47 @@
   </si>
   <si>
     <t>マジカル・パティスリー・アワード</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Or_Contest_280</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコレート初級コンテスト</t>
+    <rPh sb="6" eb="8">
+      <t>ショキュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコレート限定
+夏エリアで毎年開催のチョコレートコンテスト。
+初級～中級までのパティシエの方ぜひご参加ください！</t>
+    <rPh sb="6" eb="8">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>マイトシ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カイサイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ショキュウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>チュウキュウ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>サンカ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1895,7 +1936,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1920,6 +1961,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1935,7 +1982,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1953,6 +2000,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3130,7 +3183,7 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="N11">
         <v>4</v>
@@ -3262,7 +3315,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B615D1EB-7EB0-40A6-B71A-0773034D7CD2}">
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -3357,7 +3410,7 @@
     </row>
     <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A9" si="0">ROW()-2+1000</f>
+        <f t="shared" ref="A2:A10" si="0">ROW()-2+1000</f>
         <v>1000</v>
       </c>
       <c r="B2">
@@ -3493,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3574,7 +3627,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3598,84 +3651,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5">
+    <row r="5" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="7">
         <f t="shared" si="0"/>
         <v>1003</v>
       </c>
-      <c r="B5">
-        <v>20300</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="B5" s="7">
+        <v>20800</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>4</v>
+      </c>
+      <c r="I5" s="7">
+        <v>12</v>
+      </c>
+      <c r="J5" s="7">
+        <v>31</v>
+      </c>
+      <c r="K5" s="7">
+        <v>500</v>
+      </c>
+      <c r="L5" s="7">
+        <v>10</v>
+      </c>
+      <c r="M5" s="7">
+        <v>10</v>
+      </c>
+      <c r="N5" s="7">
         <v>3</v>
       </c>
-      <c r="I5">
-        <v>12</v>
-      </c>
-      <c r="J5">
-        <v>31</v>
-      </c>
-      <c r="K5">
-        <v>500</v>
-      </c>
-      <c r="L5">
-        <v>11</v>
-      </c>
-      <c r="M5">
-        <v>7</v>
-      </c>
-      <c r="N5">
+      <c r="O5" s="7">
+        <v>1</v>
+      </c>
+      <c r="P5" s="7">
+        <v>99</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>1</v>
+      </c>
+      <c r="R5" s="7">
+        <v>0</v>
+      </c>
+      <c r="S5" s="7">
         <v>3</v>
       </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>99</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>3</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5" t="s">
+      <c r="T5" s="7">
+        <v>0</v>
+      </c>
+      <c r="U5" s="7">
+        <v>0</v>
+      </c>
+      <c r="V5" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="W5" t="s">
+      <c r="W5" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="X5" t="s">
+      <c r="X5" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="Y5" s="4" t="s">
+      <c r="Y5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="7">
         <v>0</v>
       </c>
     </row>
@@ -3685,25 +3738,25 @@
         <v>1004</v>
       </c>
       <c r="B6">
-        <v>20400</v>
+        <v>20300</v>
       </c>
       <c r="C6" t="s">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>69</v>
+        <v>150</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>12</v>
@@ -3712,16 +3765,16 @@
         <v>31</v>
       </c>
       <c r="K6">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="L6">
         <v>11</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O6">
         <v>1</v>
@@ -3766,25 +3819,25 @@
         <v>1005</v>
       </c>
       <c r="B7">
-        <v>30400</v>
+        <v>20400</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7">
         <v>12</v>
@@ -3793,7 +3846,7 @@
         <v>31</v>
       </c>
       <c r="K7">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="L7">
         <v>11</v>
@@ -3847,25 +3900,25 @@
         <v>1006</v>
       </c>
       <c r="B8">
-        <v>20500</v>
+        <v>30400</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I8">
         <v>12</v>
@@ -3874,10 +3927,10 @@
         <v>31</v>
       </c>
       <c r="K8">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="L8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -3928,25 +3981,25 @@
         <v>1007</v>
       </c>
       <c r="B9">
-        <v>20600</v>
+        <v>20500</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9">
         <v>12</v>
@@ -3961,10 +4014,10 @@
         <v>12</v>
       </c>
       <c r="M9">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>1</v>
@@ -4005,29 +4058,29 @@
     </row>
     <row r="10" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
-        <f>ROW()-2+1000</f>
+        <f t="shared" si="0"/>
         <v>1008</v>
       </c>
       <c r="B10">
-        <v>20700</v>
+        <v>20600</v>
       </c>
       <c r="C10" t="s">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I10">
         <v>12</v>
@@ -4036,16 +4089,16 @@
         <v>31</v>
       </c>
       <c r="K10">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="L10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M10">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O10">
         <v>1</v>
@@ -4060,7 +4113,7 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T10">
         <v>0</v>
@@ -4084,25 +4137,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11">
         <f>ROW()-2+1000</f>
         <v>1009</v>
       </c>
       <c r="B11">
-        <v>2000</v>
+        <v>20700</v>
       </c>
       <c r="C11" t="s">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -4117,13 +4170,13 @@
         <v>31</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="L11">
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="M11">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N11">
         <v>5</v>
@@ -4135,13 +4188,13 @@
         <v>99</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11">
         <v>0</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>0</v>
@@ -4156,12 +4209,93 @@
         <v>118</v>
       </c>
       <c r="X11" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <f>ROW()-2+1000</f>
+        <v>1010</v>
+      </c>
+      <c r="B12">
+        <v>2000</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>142</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>12</v>
+      </c>
+      <c r="J12">
+        <v>31</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>200</v>
+      </c>
+      <c r="M12">
+        <v>15</v>
+      </c>
+      <c r="N12">
+        <v>5</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>99</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12" t="s">
+        <v>115</v>
+      </c>
+      <c r="W12" t="s">
+        <v>118</v>
+      </c>
+      <c r="X12" t="s">
         <v>113</v>
       </c>
-      <c r="Y11" s="4" t="s">
+      <c r="Y12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z11">
+      <c r="Z12">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46EE316-A96E-4201-B5B1-821809F09F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8E4075-0DA0-46CD-8B10-D3BFC925F028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1245" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2625" yWindow="1245" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8E4075-0DA0-46CD-8B10-D3BFC925F028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD8DE7F-87A4-43E9-8228-2290304FF4ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2625" yWindow="1245" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="163">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -1900,6 +1900,10 @@
     <rPh sb="50" eb="52">
       <t>サンカ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>h02</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2805,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>108</v>
+        <v>162</v>
       </c>
       <c r="W6" t="s">
         <v>112</v>
@@ -4710,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="W5" t="s">
         <v>120</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD8DE7F-87A4-43E9-8228-2290304FF4ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C616CF-D8A3-4559-803F-3D0314689BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="172">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -1169,42 +1169,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>お花をモチーフにしたお菓子限定
-お花をメインに使った華やかなお菓子を募集しています。
-クッキー・チョコレート・ケーキ・チーズケーキから１種類を募集します。</t>
-    <rPh sb="1" eb="2">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="68" eb="70">
-      <t>シュルイ</t>
-    </rPh>
-    <rPh sb="71" eb="73">
-      <t>ボシュウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ルミエール・ドゥ・ソレイユ</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1523,42 +1487,6 @@
   </si>
   <si>
     <t>sound73</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ケーキ限定
-春の大精霊様が年に一度開くケーキコンテストです。
-自信のある豪華なケーキを見せてください！</t>
-    <rPh sb="3" eb="5">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ハル</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>ダイセイレイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>サマ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>イチド</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ヒラ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ゴウカ</t>
-    </rPh>
-    <rPh sb="43" eb="44">
-      <t>ミ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1779,43 +1707,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>パフェ限定
-隣国プラムで行われるパフェコンテストです。
-各界隈の著名人が注目するトップレベルのコンテストです。</t>
-    <rPh sb="3" eb="5">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>リンコク</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="28" eb="31">
-      <t>カクカイワイ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>チョメイ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ジン</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>チュウモク</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ダイチュウモク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>プラムアイス技術コンテスト</t>
-    <rPh sb="6" eb="8">
-      <t>ギジュツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>◆秋の伝統的なお菓子コンクール◆
 テーマ：自由課題
 秋エリアの伝統的で由緒あるコンクールです。食べた人を幸せにするお菓子をお待ちしております。</t>
@@ -1866,13 +1757,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>チョコレート初級コンテスト</t>
-    <rPh sb="6" eb="8">
-      <t>ショキュウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>チョコレート限定
 夏エリアで毎年開催のチョコレートコンテスト。
 初級～中級までのパティシエの方ぜひご参加ください！</t>
@@ -1904,6 +1788,260 @@
   </si>
   <si>
     <t>h02</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プラムお菓子技術コンテスト</t>
+    <rPh sb="4" eb="6">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ギジュツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自由課題
+隣国プラムで行われるおかしコンテストです。
+各界隈の著名人が注目するトップレベルのコンテストです。</t>
+    <rPh sb="0" eb="4">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>リンコク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>カクカイワイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>チョメイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ジン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>チュウモク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ダイチュウモク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>パティシエの森</t>
+    <rPh sb="6" eb="7">
+      <t>モリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Or_Contest_290</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自由課題
+夏エリアで行われる初級パティシエ向けのコンテスト。
+遊園地にくるお客さんを喜ばせよう！！</t>
+    <rPh sb="0" eb="4">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ショキュウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>ユウエンチ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>キャク</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ヨロコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Or_Contest_490</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>秋のお菓子コンテスト</t>
+    <rPh sb="0" eb="1">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自由課題
+秋エリアで定期的に行われるパティシエコンテスト。
+幅広くいろんなお菓子を募集しております！</t>
+    <rPh sb="0" eb="4">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>テイキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ハバヒロ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ボシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>春のおかし大祭典</t>
+    <rPh sb="0" eb="1">
+      <t>ハル</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ダイサイテン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自由課題
+春エリアで行われるパティシエ中級向けのコンテスト。
+春の大妖精様を讃えるおいしいお菓子を希望します♪</t>
+    <rPh sb="0" eb="4">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ハル</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>チュウキュウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ハル</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ヨウセイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>タタ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>キボウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Or_Contest_110</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お花をモチーフにしたお菓子限定
+お花をメインに使った華やかなお菓子を募集しています。
+クッキー・チョコレート・ケーキ・チーズケーキ限定です。</t>
+    <rPh sb="1" eb="2">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>ゲンテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プレミール・ショコラティエ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ケーキ限定
+秋の大精霊様が年に一度開くケーキコンテストです。
+自信のある豪華なケーキを見せてください！</t>
+    <rPh sb="3" eb="5">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ダイセイレイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ゴウカ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ミ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1940,7 +2078,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1965,12 +2103,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1986,7 +2118,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2004,12 +2136,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2326,7 +2452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -2421,7 +2547,7 @@
     </row>
     <row r="2" spans="1:26" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
-        <f t="shared" ref="A2:A12" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A13" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="2">
@@ -2431,13 +2557,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -2809,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="W6" t="s">
         <v>112</v>
@@ -2992,25 +3118,25 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>30200</v>
+        <v>10900</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>168</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9">
         <v>12</v>
@@ -3019,19 +3145,19 @@
         <v>31</v>
       </c>
       <c r="K9">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="L9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M9">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="N9">
         <v>3</v>
       </c>
       <c r="O9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>99</v>
@@ -3052,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="s">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="W9" t="s">
         <v>112</v>
@@ -3073,25 +3199,25 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>30300</v>
+        <v>30200</v>
       </c>
       <c r="C10" t="s">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10">
         <v>12</v>
@@ -3106,7 +3232,7 @@
         <v>4</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N10">
         <v>3</v>
@@ -3154,25 +3280,25 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>30700</v>
+        <v>30300</v>
       </c>
       <c r="C11" t="s">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I11">
         <v>12</v>
@@ -3181,16 +3307,16 @@
         <v>31</v>
       </c>
       <c r="K11">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="L11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O11">
         <v>1</v>
@@ -3229,25 +3355,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B12">
-        <v>1000</v>
+        <v>30700</v>
       </c>
       <c r="C12" t="s">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3262,13 +3388,13 @@
         <v>31</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N12">
         <v>4</v>
@@ -3280,13 +3406,13 @@
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12">
         <v>0</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T12">
         <v>0</v>
@@ -3301,12 +3427,93 @@
         <v>112</v>
       </c>
       <c r="X12" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>1000</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>5</v>
+      </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
+      <c r="J13">
+        <v>31</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>100</v>
+      </c>
+      <c r="M13">
+        <v>5</v>
+      </c>
+      <c r="N13">
+        <v>4</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>99</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13" t="s">
+        <v>108</v>
+      </c>
+      <c r="W13" t="s">
+        <v>112</v>
+      </c>
+      <c r="X13" t="s">
         <v>113</v>
       </c>
-      <c r="Y12" s="4" t="s">
+      <c r="Y13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z12">
+      <c r="Z13">
         <v>1</v>
       </c>
     </row>
@@ -3319,7 +3526,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B615D1EB-7EB0-40A6-B71A-0773034D7CD2}">
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -3414,7 +3621,7 @@
     </row>
     <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A10" si="0">ROW()-2+1000</f>
+        <f t="shared" ref="A2:A11" si="0">ROW()-2+1000</f>
         <v>1000</v>
       </c>
       <c r="B2">
@@ -3499,19 +3706,19 @@
         <v>1001</v>
       </c>
       <c r="B3">
-        <v>20100</v>
+        <v>20900</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>161</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>160</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>66</v>
+        <v>162</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -3526,19 +3733,19 @@
         <v>31</v>
       </c>
       <c r="K3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>99</v>
@@ -3550,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3568,7 +3775,7 @@
         <v>114</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -3580,25 +3787,25 @@
         <v>1002</v>
       </c>
       <c r="B4">
-        <v>20200</v>
+        <v>20100</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>12</v>
@@ -3607,13 +3814,13 @@
         <v>31</v>
       </c>
       <c r="K4">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L4">
         <v>10</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N4">
         <v>2</v>
@@ -3649,90 +3856,90 @@
         <v>114</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="7">
+    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
         <f t="shared" si="0"/>
         <v>1003</v>
       </c>
-      <c r="B5" s="7">
-        <v>20800</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="G5" s="7">
-        <v>0</v>
-      </c>
-      <c r="H5" s="7">
-        <v>4</v>
-      </c>
-      <c r="I5" s="7">
+      <c r="B5">
+        <v>20200</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
         <v>12</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5">
         <v>31</v>
       </c>
-      <c r="K5" s="7">
-        <v>500</v>
-      </c>
-      <c r="L5" s="7">
+      <c r="K5">
+        <v>300</v>
+      </c>
+      <c r="L5">
         <v>10</v>
       </c>
-      <c r="M5" s="7">
-        <v>10</v>
-      </c>
-      <c r="N5" s="7">
+      <c r="M5">
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>99</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>3</v>
       </c>
-      <c r="O5" s="7">
-        <v>1</v>
-      </c>
-      <c r="P5" s="7">
-        <v>99</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>1</v>
-      </c>
-      <c r="R5" s="7">
-        <v>0</v>
-      </c>
-      <c r="S5" s="7">
-        <v>3</v>
-      </c>
-      <c r="T5" s="7">
-        <v>0</v>
-      </c>
-      <c r="U5" s="7">
-        <v>0</v>
-      </c>
-      <c r="V5" s="7" t="s">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
         <v>115</v>
       </c>
-      <c r="W5" s="7" t="s">
+      <c r="W5" t="s">
         <v>118</v>
       </c>
-      <c r="X5" s="7" t="s">
+      <c r="X5" t="s">
         <v>114</v>
       </c>
-      <c r="Y5" s="8" t="s">
+      <c r="Y5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z5" s="7">
+      <c r="Z5">
         <v>0</v>
       </c>
     </row>
@@ -3742,25 +3949,25 @@
         <v>1004</v>
       </c>
       <c r="B6">
-        <v>20300</v>
+        <v>20800</v>
       </c>
       <c r="C6" t="s">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="E6" t="s">
-        <v>67</v>
+        <v>170</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>12</v>
@@ -3772,10 +3979,10 @@
         <v>500</v>
       </c>
       <c r="L6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>3</v>
@@ -3823,25 +4030,25 @@
         <v>1005</v>
       </c>
       <c r="B7">
-        <v>20400</v>
+        <v>20300</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>69</v>
+        <v>148</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>12</v>
@@ -3850,16 +4057,16 @@
         <v>31</v>
       </c>
       <c r="K7">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="L7">
         <v>11</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O7">
         <v>1</v>
@@ -3904,25 +4111,25 @@
         <v>1006</v>
       </c>
       <c r="B8">
-        <v>30400</v>
+        <v>20400</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8">
         <v>12</v>
@@ -3931,7 +4138,7 @@
         <v>31</v>
       </c>
       <c r="K8">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="L8">
         <v>11</v>
@@ -3985,25 +4192,25 @@
         <v>1007</v>
       </c>
       <c r="B9">
-        <v>20500</v>
+        <v>30400</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9">
         <v>12</v>
@@ -4012,16 +4219,16 @@
         <v>31</v>
       </c>
       <c r="K9">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="L9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M9">
         <v>10</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O9">
         <v>1</v>
@@ -4066,25 +4273,25 @@
         <v>1008</v>
       </c>
       <c r="B10">
-        <v>20600</v>
+        <v>20500</v>
       </c>
       <c r="C10" t="s">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>12</v>
@@ -4096,13 +4303,13 @@
         <v>1500</v>
       </c>
       <c r="L10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M10">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>1</v>
@@ -4143,29 +4350,29 @@
     </row>
     <row r="11" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11">
-        <f>ROW()-2+1000</f>
+        <f t="shared" si="0"/>
         <v>1009</v>
       </c>
       <c r="B11">
-        <v>20700</v>
+        <v>20600</v>
       </c>
       <c r="C11" t="s">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I11">
         <v>12</v>
@@ -4174,16 +4381,16 @@
         <v>31</v>
       </c>
       <c r="K11">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="L11">
         <v>13</v>
       </c>
       <c r="M11">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O11">
         <v>1</v>
@@ -4198,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="S11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11">
         <v>0</v>
@@ -4222,25 +4429,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
         <f>ROW()-2+1000</f>
         <v>1010</v>
       </c>
       <c r="B12">
-        <v>2000</v>
+        <v>20700</v>
       </c>
       <c r="C12" t="s">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -4255,13 +4462,13 @@
         <v>31</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="L12">
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="M12">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N12">
         <v>5</v>
@@ -4273,13 +4480,13 @@
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12">
         <v>0</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>0</v>
@@ -4294,12 +4501,93 @@
         <v>118</v>
       </c>
       <c r="X12" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <f>ROW()-2+1000</f>
+        <v>1011</v>
+      </c>
+      <c r="B13">
+        <v>2000</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>5</v>
+      </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
+      <c r="J13">
+        <v>31</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>200</v>
+      </c>
+      <c r="M13">
+        <v>12</v>
+      </c>
+      <c r="N13">
+        <v>5</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>99</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13" t="s">
+        <v>115</v>
+      </c>
+      <c r="W13" t="s">
+        <v>118</v>
+      </c>
+      <c r="X13" t="s">
         <v>113</v>
       </c>
-      <c r="Y12" s="4" t="s">
+      <c r="Y13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z12">
+      <c r="Z13">
         <v>1</v>
       </c>
     </row>
@@ -4312,7 +4600,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A66AAA5-0C8D-4F8A-9A3B-33AFE45A42B1}">
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -4407,7 +4695,7 @@
     </row>
     <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f>ROW()-2+2000</f>
+        <f t="shared" ref="A2:A7" si="0">ROW()-2+2000</f>
         <v>2000</v>
       </c>
       <c r="B2">
@@ -4488,29 +4776,29 @@
     </row>
     <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
-        <f>ROW()-2+2000</f>
+        <f t="shared" si="0"/>
         <v>2001</v>
       </c>
       <c r="B3">
-        <v>30100</v>
+        <v>30900</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>163</v>
       </c>
       <c r="E3" t="s">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>12</v>
@@ -4519,19 +4807,19 @@
         <v>31</v>
       </c>
       <c r="K3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="L3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <v>2</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>99</v>
@@ -4561,7 +4849,7 @@
         <v>114</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -4569,29 +4857,29 @@
     </row>
     <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
-        <f>ROW()-2+2000</f>
+        <f t="shared" si="0"/>
         <v>2002</v>
       </c>
       <c r="B4">
-        <v>10100</v>
+        <v>30100</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>12</v>
@@ -4606,13 +4894,13 @@
         <v>20</v>
       </c>
       <c r="M4">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4">
         <v>99</v>
@@ -4624,7 +4912,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4650,29 +4938,29 @@
     </row>
     <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
-        <f>ROW()-2+2000</f>
+        <f t="shared" si="0"/>
         <v>2003</v>
       </c>
       <c r="B5">
-        <v>30500</v>
+        <v>10100</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>12</v>
@@ -4681,19 +4969,19 @@
         <v>31</v>
       </c>
       <c r="K5">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="L5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M5">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>99</v>
@@ -4714,7 +5002,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="W5" t="s">
         <v>120</v>
@@ -4723,7 +5011,7 @@
         <v>114</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -4731,29 +5019,29 @@
     </row>
     <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
-        <f>ROW()-2+2000</f>
+        <f t="shared" si="0"/>
         <v>2004</v>
       </c>
       <c r="B6">
-        <v>30600</v>
+        <v>30500</v>
       </c>
       <c r="C6" t="s">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>12</v>
@@ -4762,16 +5050,16 @@
         <v>31</v>
       </c>
       <c r="K6">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="L6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M6">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O6">
         <v>1</v>
@@ -4786,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4795,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="W6" t="s">
         <v>120</v>
@@ -4812,29 +5100,29 @@
     </row>
     <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
-        <f t="shared" ref="A7:A8" si="0">ROW()-2+2000</f>
+        <f t="shared" si="0"/>
         <v>2005</v>
       </c>
       <c r="B7">
-        <v>10600</v>
+        <v>30600</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>12</v>
@@ -4843,19 +5131,19 @@
         <v>31</v>
       </c>
       <c r="K7">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="L7">
         <v>22</v>
       </c>
       <c r="M7">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7">
         <v>99</v>
@@ -4867,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -4893,23 +5181,23 @@
     </row>
     <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A8:A9" si="1">ROW()-2+2000</f>
         <v>2006</v>
       </c>
       <c r="B8">
-        <v>10700</v>
+        <v>10600</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>95</v>
+        <v>171</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -4924,16 +5212,16 @@
         <v>31</v>
       </c>
       <c r="K8">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="L8">
         <v>22</v>
       </c>
       <c r="M8">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -4948,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -4972,165 +5260,246 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="2">
-        <f>ROW()-2+2000</f>
+    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <f t="shared" si="1"/>
         <v>2007</v>
       </c>
-      <c r="B9" s="2">
-        <v>30800</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
+      <c r="B9">
+        <v>10700</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>5</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9">
         <v>12</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9">
         <v>31</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9">
         <v>3000</v>
       </c>
-      <c r="L9" s="2">
-        <v>9999</v>
-      </c>
-      <c r="M9" s="2">
-        <v>38</v>
-      </c>
-      <c r="N9" s="2">
-        <v>3</v>
-      </c>
-      <c r="O9" s="2">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2">
+      <c r="L9">
+        <v>22</v>
+      </c>
+      <c r="M9">
+        <v>30</v>
+      </c>
+      <c r="N9">
+        <v>5</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
         <v>99</v>
       </c>
-      <c r="Q9" s="2">
-        <v>1</v>
-      </c>
-      <c r="R9" s="2">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2">
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>5</v>
       </c>
-      <c r="T9" s="2">
-        <v>0</v>
-      </c>
-      <c r="U9" s="2">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="s">
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
         <v>116</v>
       </c>
-      <c r="W9" s="2" t="s">
+      <c r="W9" t="s">
         <v>120</v>
       </c>
-      <c r="X9" s="2" t="s">
+      <c r="X9" t="s">
         <v>114</v>
       </c>
-      <c r="Y9" s="3" t="s">
+      <c r="Y9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z9" s="2">
+      <c r="Z9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10">
+    <row r="10" spans="1:26" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="2">
         <f>ROW()-2+2000</f>
         <v>2008</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
+        <v>30800</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>5</v>
+      </c>
+      <c r="I10" s="2">
+        <v>12</v>
+      </c>
+      <c r="J10" s="2">
+        <v>31</v>
+      </c>
+      <c r="K10" s="2">
         <v>3000</v>
       </c>
-      <c r="C10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="L10" s="2">
+        <v>9999</v>
+      </c>
+      <c r="M10" s="2">
+        <v>25</v>
+      </c>
+      <c r="N10" s="2">
+        <v>3</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2">
+        <v>99</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>1</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
+        <v>5</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <f>ROW()-2+2000</f>
+        <v>2009</v>
+      </c>
+      <c r="B11">
+        <v>3000</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
         <v>46</v>
       </c>
-      <c r="E10" t="s">
-        <v>138</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="E11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>5</v>
       </c>
-      <c r="I10">
+      <c r="I11">
         <v>12</v>
       </c>
-      <c r="J10">
+      <c r="J11">
         <v>31</v>
       </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
         <v>300</v>
       </c>
-      <c r="M10">
-        <v>25</v>
-      </c>
-      <c r="N10">
+      <c r="M11">
+        <v>18</v>
+      </c>
+      <c r="N11">
         <v>5</v>
       </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
-      <c r="P10">
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
         <v>99</v>
       </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10" t="s">
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11" t="s">
         <v>116</v>
       </c>
-      <c r="W10" t="s">
+      <c r="W11" t="s">
         <v>120</v>
       </c>
-      <c r="X10" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y10" s="4" t="s">
+      <c r="X11" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z10">
+      <c r="Z11">
         <v>1</v>
       </c>
     </row>
@@ -5254,7 +5623,7 @@
         <v>70</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G2" s="5">
         <v>0</v>
@@ -5497,7 +5866,7 @@
         <v>98</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="G5" s="5">
         <v>0</v>
@@ -5518,7 +5887,7 @@
         <v>31</v>
       </c>
       <c r="M5" s="5">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N5" s="5">
         <v>3</v>
@@ -5575,10 +5944,10 @@
         <v>60</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="G6" s="5">
         <v>0</v>
@@ -5599,7 +5968,7 @@
         <v>30</v>
       </c>
       <c r="M6" s="5">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N6" s="5">
         <v>4</v>
@@ -5680,7 +6049,7 @@
         <v>31</v>
       </c>
       <c r="M7" s="5">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N7" s="5">
         <v>4</v>
@@ -5740,7 +6109,7 @@
         <v>79</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
@@ -5761,7 +6130,7 @@
         <v>32</v>
       </c>
       <c r="M8" s="5">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="N8" s="5">
         <v>4</v>
@@ -5821,7 +6190,7 @@
         <v>126</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
@@ -5842,7 +6211,7 @@
         <v>32</v>
       </c>
       <c r="M9" s="5">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="N9" s="5">
         <v>5</v>
@@ -5899,10 +6268,10 @@
         <v>47</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C616CF-D8A3-4559-803F-3D0314689BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2573A8-F0BD-4110-B595-B6A981B549A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2070" yWindow="1245" windowWidth="25560" windowHeight="14355" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -2005,10 +2005,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>プレミール・ショコラティエ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ケーキ限定
 秋の大精霊様が年に一度開くケーキコンテストです。
 自信のある豪華なケーキを見せてください！</t>
@@ -2041,6 +2037,13 @@
     </rPh>
     <rPh sb="43" eb="44">
       <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>初めてのショコラティエ</t>
+    <rPh sb="0" eb="1">
+      <t>ハジ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3958,7 +3961,7 @@
         <v>155</v>
       </c>
       <c r="E6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>156</v>
@@ -4567,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T13">
         <v>0</v>
@@ -5197,7 +5200,7 @@
         <v>84</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -5479,7 +5482,7 @@
         <v>0</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T11">
         <v>0</v>
@@ -6310,7 +6313,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T10" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2573A8-F0BD-4110-B595-B6A981B549A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88437968-BD4F-4427-B48D-01AF79694937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="1245" windowWidth="25560" windowHeight="14355" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3075" yWindow="1095" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -2041,10 +2041,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>初めてのショコラティエ</t>
-    <rPh sb="0" eb="1">
-      <t>ハジ</t>
-    </rPh>
+    <t>エレメンタリー・ショコラティエ</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88437968-BD4F-4427-B48D-01AF79694937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7795215A-9DFA-4EC2-B33D-47E0B0DCB0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="1095" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2835" yWindow="765" windowWidth="25560" windowHeight="14355" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -2118,7 +2118,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2136,6 +2136,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4600,7 +4606,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A66AAA5-0C8D-4F8A-9A3B-33AFE45A42B1}">
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -4695,7 +4701,7 @@
     </row>
     <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A7" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A2:A8" si="0">ROW()-2+2000</f>
         <v>2000</v>
       </c>
       <c r="B2">
@@ -5019,7 +5025,7 @@
     </row>
     <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+2000</f>
         <v>2004</v>
       </c>
       <c r="B6">
@@ -5098,112 +5104,112 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7">
-        <f t="shared" si="0"/>
+    <row r="7" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="7">
+        <f>ROW()-2+2000</f>
         <v>2005</v>
       </c>
-      <c r="B7">
-        <v>30600</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="B7" s="7">
+        <v>40300</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="7">
+        <v>12</v>
+      </c>
+      <c r="J7" s="7">
+        <v>31</v>
+      </c>
+      <c r="K7" s="7">
+        <v>600</v>
+      </c>
+      <c r="L7" s="7">
+        <v>21</v>
+      </c>
+      <c r="M7" s="7">
+        <v>20</v>
+      </c>
+      <c r="N7" s="7">
         <v>3</v>
       </c>
-      <c r="I7">
-        <v>12</v>
-      </c>
-      <c r="J7">
-        <v>31</v>
-      </c>
-      <c r="K7">
-        <v>1500</v>
-      </c>
-      <c r="L7">
-        <v>22</v>
-      </c>
-      <c r="M7">
-        <v>30</v>
-      </c>
-      <c r="N7">
-        <v>5</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
+      <c r="O7" s="7">
+        <v>1</v>
+      </c>
+      <c r="P7" s="7">
         <v>99</v>
       </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>5</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7" t="s">
-        <v>116</v>
-      </c>
-      <c r="W7" t="s">
-        <v>120</v>
-      </c>
-      <c r="X7" t="s">
+      <c r="Q7" s="7">
+        <v>1</v>
+      </c>
+      <c r="R7" s="7">
+        <v>0</v>
+      </c>
+      <c r="S7" s="7">
+        <v>3</v>
+      </c>
+      <c r="T7" s="7">
+        <v>0</v>
+      </c>
+      <c r="U7" s="7">
+        <v>0</v>
+      </c>
+      <c r="V7" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="W7" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="X7" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="Y7" s="4" t="s">
+      <c r="Y7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
-        <f t="shared" ref="A8:A9" si="1">ROW()-2+2000</f>
+        <f t="shared" si="0"/>
         <v>2006</v>
       </c>
       <c r="B8">
-        <v>10600</v>
+        <v>30600</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I8">
         <v>12</v>
@@ -5212,19 +5218,19 @@
         <v>31</v>
       </c>
       <c r="K8">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="L8">
         <v>22</v>
       </c>
       <c r="M8">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8">
         <v>99</v>
@@ -5236,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -5262,23 +5268,23 @@
     </row>
     <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A9:A10" si="1">ROW()-2+2000</f>
         <v>2007</v>
       </c>
       <c r="B9">
-        <v>10700</v>
+        <v>10600</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -5293,16 +5299,16 @@
         <v>31</v>
       </c>
       <c r="K9">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="L9">
         <v>22</v>
       </c>
       <c r="M9">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -5317,7 +5323,7 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -5341,165 +5347,246 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="2">
-        <f>ROW()-2+2000</f>
+    <row r="10" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <f t="shared" si="1"/>
         <v>2008</v>
       </c>
-      <c r="B10" s="2">
-        <v>30800</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2">
+      <c r="B10">
+        <v>10700</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>5</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10">
         <v>12</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10">
         <v>31</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10">
         <v>3000</v>
       </c>
-      <c r="L10" s="2">
-        <v>9999</v>
-      </c>
-      <c r="M10" s="2">
-        <v>25</v>
-      </c>
-      <c r="N10" s="2">
-        <v>3</v>
-      </c>
-      <c r="O10" s="2">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2">
+      <c r="L10">
+        <v>22</v>
+      </c>
+      <c r="M10">
+        <v>30</v>
+      </c>
+      <c r="N10">
+        <v>5</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
         <v>99</v>
       </c>
-      <c r="Q10" s="2">
-        <v>1</v>
-      </c>
-      <c r="R10" s="2">
-        <v>0</v>
-      </c>
-      <c r="S10" s="2">
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <v>5</v>
       </c>
-      <c r="T10" s="2">
-        <v>0</v>
-      </c>
-      <c r="U10" s="2">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="s">
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10" t="s">
         <v>116</v>
       </c>
-      <c r="W10" s="2" t="s">
+      <c r="W10" t="s">
         <v>120</v>
       </c>
-      <c r="X10" s="2" t="s">
+      <c r="X10" t="s">
         <v>114</v>
       </c>
-      <c r="Y10" s="3" t="s">
+      <c r="Y10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z10" s="2">
+      <c r="Z10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11">
+    <row r="11" spans="1:26" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="2">
         <f>ROW()-2+2000</f>
         <v>2009</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
+        <v>30800</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>5</v>
+      </c>
+      <c r="I11" s="2">
+        <v>12</v>
+      </c>
+      <c r="J11" s="2">
+        <v>31</v>
+      </c>
+      <c r="K11" s="2">
         <v>3000</v>
       </c>
-      <c r="C11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="L11" s="2">
+        <v>9999</v>
+      </c>
+      <c r="M11" s="2">
+        <v>25</v>
+      </c>
+      <c r="N11" s="2">
+        <v>3</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2">
+        <v>99</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>1</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>5</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <f>ROW()-2+2000</f>
+        <v>2010</v>
+      </c>
+      <c r="B12">
+        <v>3000</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
         <v>46</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" t="s">
         <v>137</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>5</v>
       </c>
-      <c r="I11">
+      <c r="I12">
         <v>12</v>
       </c>
-      <c r="J11">
+      <c r="J12">
         <v>31</v>
       </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
         <v>300</v>
       </c>
-      <c r="M11">
+      <c r="M12">
         <v>18</v>
       </c>
-      <c r="N11">
+      <c r="N12">
         <v>5</v>
       </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="P11">
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
         <v>99</v>
       </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
         <v>4</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11" t="s">
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12" t="s">
         <v>116</v>
       </c>
-      <c r="W11" t="s">
+      <c r="W12" t="s">
         <v>120</v>
       </c>
-      <c r="X11" t="s">
+      <c r="X12" t="s">
         <v>146</v>
       </c>
-      <c r="Y11" s="4" t="s">
+      <c r="Y12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z11">
+      <c r="Z12">
         <v>1</v>
       </c>
     </row>
@@ -5512,7 +5599,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3990FE8C-49B4-4F17-805B-7287A7C6D5E2}">
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -5607,7 +5694,7 @@
     </row>
     <row r="2" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5">
-        <f t="shared" ref="A2:A9" si="0">ROW()-2+3000</f>
+        <f>ROW()-2+3000</f>
         <v>3000</v>
       </c>
       <c r="B2" s="5">
@@ -5688,7 +5775,7 @@
     </row>
     <row r="3" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+3000</f>
         <v>3001</v>
       </c>
       <c r="B3" s="5">
@@ -5769,7 +5856,7 @@
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+3000</f>
         <v>3002</v>
       </c>
       <c r="B4" s="5">
@@ -5850,29 +5937,29 @@
     </row>
     <row r="5" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="5">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+3000</f>
         <v>3003</v>
       </c>
       <c r="B5" s="5">
-        <v>40300</v>
+        <v>40400</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="G5" s="5">
         <v>0</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="5">
         <v>12</v>
@@ -5884,13 +5971,13 @@
         <v>700</v>
       </c>
       <c r="L5" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M5" s="5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O5" s="5">
         <v>1</v>
@@ -5931,29 +6018,29 @@
     </row>
     <row r="6" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+3000</f>
         <v>3004</v>
       </c>
       <c r="B6" s="5">
-        <v>40400</v>
+        <v>40500</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="G6" s="5">
         <v>0</v>
       </c>
       <c r="H6" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I6" s="5">
         <v>12</v>
@@ -5962,10 +6049,10 @@
         <v>31</v>
       </c>
       <c r="K6" s="5">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="L6" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M6" s="5">
         <v>25</v>
@@ -6012,23 +6099,23 @@
     </row>
     <row r="7" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="5">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+3000</f>
         <v>3005</v>
       </c>
       <c r="B7" s="5">
-        <v>40500</v>
+        <v>40600</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="G7" s="5">
         <v>0</v>
@@ -6043,13 +6130,13 @@
         <v>31</v>
       </c>
       <c r="K7" s="5">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="L7" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M7" s="5">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="N7" s="5">
         <v>4</v>
@@ -6093,29 +6180,29 @@
     </row>
     <row r="8" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+3000</f>
         <v>3006</v>
       </c>
       <c r="B8" s="5">
-        <v>40600</v>
+        <v>40700</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
       </c>
       <c r="H8" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8" s="5">
         <v>12</v>
@@ -6124,16 +6211,16 @@
         <v>31</v>
       </c>
       <c r="K8" s="5">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="L8" s="5">
         <v>32</v>
       </c>
       <c r="M8" s="5">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="N8" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O8" s="5">
         <v>1</v>
@@ -6148,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" s="5">
         <v>0</v>
@@ -6172,31 +6259,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:26" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="5">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+3000</f>
         <v>3007</v>
       </c>
       <c r="B9" s="5">
-        <v>40700</v>
+        <v>4000</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
       </c>
       <c r="H9" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I9" s="5">
         <v>12</v>
@@ -6205,13 +6292,13 @@
         <v>31</v>
       </c>
       <c r="K9" s="5">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>32</v>
+        <v>400</v>
       </c>
       <c r="M9" s="5">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N9" s="5">
         <v>5</v>
@@ -6223,7 +6310,7 @@
         <v>99</v>
       </c>
       <c r="Q9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" s="5">
         <v>0</v>
@@ -6244,93 +6331,12 @@
         <v>119</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y9" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z9" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="5">
-        <f>ROW()-2+3000</f>
-        <v>3008</v>
-      </c>
-      <c r="B10" s="5">
-        <v>4000</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5">
-        <v>5</v>
-      </c>
-      <c r="I10" s="5">
-        <v>12</v>
-      </c>
-      <c r="J10" s="5">
-        <v>31</v>
-      </c>
-      <c r="K10" s="5">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5">
-        <v>400</v>
-      </c>
-      <c r="M10" s="5">
-        <v>50</v>
-      </c>
-      <c r="N10" s="5">
-        <v>5</v>
-      </c>
-      <c r="O10" s="5">
-        <v>1</v>
-      </c>
-      <c r="P10" s="5">
-        <v>99</v>
-      </c>
-      <c r="Q10" s="5">
-        <v>0</v>
-      </c>
-      <c r="R10" s="5">
-        <v>0</v>
-      </c>
-      <c r="S10" s="5">
-        <v>5</v>
-      </c>
-      <c r="T10" s="5">
-        <v>0</v>
-      </c>
-      <c r="U10" s="5">
-        <v>0</v>
-      </c>
-      <c r="V10" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="W10" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="X10" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z10" s="5">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7795215A-9DFA-4EC2-B33D-47E0B0DCB0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A238C8-B9E4-464E-A7D7-71236C0BFCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="765" windowWidth="25560" windowHeight="14355" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3180" yWindow="1110" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="176">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -845,26 +845,6 @@
   </si>
   <si>
     <t>sound46</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>h10</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>h20</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>h30</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>t10</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>t30</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1926,48 +1906,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>自由課題
-春エリアで行われるパティシエ中級向けのコンテスト。
-春の大妖精様を讃えるおいしいお菓子を希望します♪</t>
-    <rPh sb="0" eb="4">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ハル</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>チュウキュウ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>ハル</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ヨウセイ</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>サマ</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>タタ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>キボウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Or_Contest_110</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2042,6 +1980,93 @@
   </si>
   <si>
     <t>エレメンタリー・ショコラティエ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自由課題
+春エリアで行われるパティシエ中級向けのコンテスト。少し難易度高め。
+春の大妖精様を讃えるお菓子を希望します。</t>
+    <rPh sb="0" eb="4">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ハル</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>チュウキュウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ハル</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ヨウセイ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>タタ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>キボウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>h100</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>h200</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>h300</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>t100</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>t200</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>t300</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>h09</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>h101</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>t101</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2118,7 +2143,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2136,12 +2161,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2563,13 +2582,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -2908,7 +2927,7 @@
         <v>31</v>
       </c>
       <c r="K6">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -2941,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="W6" t="s">
         <v>112</v>
@@ -2974,7 +2993,7 @@
         <v>89</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -3055,7 +3074,7 @@
         <v>90</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -3130,13 +3149,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>167</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3163,7 +3182,7 @@
         <v>3</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9">
         <v>99</v>
@@ -3184,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="W9" t="s">
         <v>112</v>
@@ -3217,7 +3236,7 @@
         <v>73</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3298,7 +3317,7 @@
         <v>83</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -3379,7 +3398,7 @@
         <v>74</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3460,7 +3479,7 @@
         <v>29</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3508,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="s">
-        <v>108</v>
+        <v>173</v>
       </c>
       <c r="W13" t="s">
         <v>112</v>
@@ -3643,7 +3662,7 @@
         <v>65</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -3691,10 +3710,10 @@
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="W2" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="X2" t="s">
         <v>114</v>
@@ -3718,13 +3737,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -3772,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="V3" t="s">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="W3" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="X3" t="s">
         <v>114</v>
@@ -3853,10 +3872,10 @@
         <v>0</v>
       </c>
       <c r="V4" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="W4" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="X4" t="s">
         <v>114</v>
@@ -3886,7 +3905,7 @@
         <v>99</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -3934,10 +3953,10 @@
         <v>0</v>
       </c>
       <c r="V5" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="W5" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="X5" t="s">
         <v>114</v>
@@ -3961,13 +3980,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E6" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -4015,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="W6" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="X6" t="s">
         <v>114</v>
@@ -4048,7 +4067,7 @@
         <v>67</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -4096,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="V7" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="W7" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="X7" t="s">
         <v>114</v>
@@ -4177,10 +4196,10 @@
         <v>0</v>
       </c>
       <c r="V8" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="W8" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="X8" t="s">
         <v>114</v>
@@ -4210,7 +4229,7 @@
         <v>64</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -4258,10 +4277,10 @@
         <v>0</v>
       </c>
       <c r="V9" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="W9" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="X9" t="s">
         <v>114</v>
@@ -4339,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="V10" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="W10" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="X10" t="s">
         <v>114</v>
@@ -4369,7 +4388,7 @@
         <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>103</v>
@@ -4420,10 +4439,10 @@
         <v>0</v>
       </c>
       <c r="V11" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="W11" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="X11" t="s">
         <v>114</v>
@@ -4450,10 +4469,10 @@
         <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -4501,10 +4520,10 @@
         <v>0</v>
       </c>
       <c r="V12" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="W12" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="X12" t="s">
         <v>114</v>
@@ -4531,10 +4550,10 @@
         <v>37</v>
       </c>
       <c r="E13" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -4582,10 +4601,10 @@
         <v>0</v>
       </c>
       <c r="V13" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="W13" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="X13" t="s">
         <v>113</v>
@@ -4765,10 +4784,10 @@
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="W2" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="X2" t="s">
         <v>114</v>
@@ -4792,13 +4811,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -4846,10 +4865,10 @@
         <v>0</v>
       </c>
       <c r="V3" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="W3" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="X3" t="s">
         <v>114</v>
@@ -4879,7 +4898,7 @@
         <v>82</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -4927,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="V4" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="W4" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="X4" t="s">
         <v>114</v>
@@ -4960,7 +4979,7 @@
         <v>87</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -5008,10 +5027,10 @@
         <v>0</v>
       </c>
       <c r="V5" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="W5" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="X5" t="s">
         <v>114</v>
@@ -5041,7 +5060,7 @@
         <v>85</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -5089,10 +5108,10 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="W6" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="X6" t="s">
         <v>114</v>
@@ -5104,84 +5123,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="7" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="7">
+    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
         <f>ROW()-2+2000</f>
         <v>2005</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>40300</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" t="s">
         <v>98</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>12</v>
+      </c>
+      <c r="J7">
+        <v>31</v>
+      </c>
+      <c r="K7">
+        <v>600</v>
+      </c>
+      <c r="L7">
+        <v>21</v>
+      </c>
+      <c r="M7">
+        <v>20</v>
+      </c>
+      <c r="N7">
+        <v>3</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>99</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>3</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
         <v>169</v>
       </c>
-      <c r="G7" s="7">
-        <v>0</v>
-      </c>
-      <c r="H7" s="7">
-        <v>2</v>
-      </c>
-      <c r="I7" s="7">
-        <v>12</v>
-      </c>
-      <c r="J7" s="7">
-        <v>31</v>
-      </c>
-      <c r="K7" s="7">
-        <v>600</v>
-      </c>
-      <c r="L7" s="7">
+      <c r="W7" t="s">
+        <v>172</v>
+      </c>
+      <c r="X7" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M7" s="7">
-        <v>20</v>
-      </c>
-      <c r="N7" s="7">
-        <v>3</v>
-      </c>
-      <c r="O7" s="7">
-        <v>1</v>
-      </c>
-      <c r="P7" s="7">
-        <v>99</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>1</v>
-      </c>
-      <c r="R7" s="7">
-        <v>0</v>
-      </c>
-      <c r="S7" s="7">
-        <v>3</v>
-      </c>
-      <c r="T7" s="7">
-        <v>0</v>
-      </c>
-      <c r="U7" s="7">
-        <v>0</v>
-      </c>
-      <c r="V7" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="W7" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="X7" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y7" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z7" s="7">
+      <c r="Z7">
         <v>0</v>
       </c>
     </row>
@@ -5203,7 +5222,7 @@
         <v>86</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -5251,10 +5270,10 @@
         <v>0</v>
       </c>
       <c r="V8" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="W8" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="X8" t="s">
         <v>114</v>
@@ -5284,7 +5303,7 @@
         <v>84</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -5332,10 +5351,10 @@
         <v>0</v>
       </c>
       <c r="V9" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="W9" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="X9" t="s">
         <v>114</v>
@@ -5413,10 +5432,10 @@
         <v>0</v>
       </c>
       <c r="V10" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="W10" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="X10" t="s">
         <v>114</v>
@@ -5440,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
@@ -5494,10 +5513,10 @@
         <v>0</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>114</v>
@@ -5524,10 +5543,10 @@
         <v>46</v>
       </c>
       <c r="E12" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -5575,13 +5594,13 @@
         <v>0</v>
       </c>
       <c r="V12" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="W12" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="X12" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="Y12" s="4" t="s">
         <v>20</v>
@@ -5694,7 +5713,7 @@
     </row>
     <row r="2" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5">
-        <f>ROW()-2+3000</f>
+        <f t="shared" ref="A2:A9" si="0">ROW()-2+3000</f>
         <v>3000</v>
       </c>
       <c r="B2" s="5">
@@ -5710,7 +5729,7 @@
         <v>70</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G2" s="5">
         <v>0</v>
@@ -5758,10 +5777,10 @@
         <v>0</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="X2" s="5" t="s">
         <v>114</v>
@@ -5775,7 +5794,7 @@
     </row>
     <row r="3" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
-        <f>ROW()-2+3000</f>
+        <f t="shared" si="0"/>
         <v>3001</v>
       </c>
       <c r="B3" s="5">
@@ -5791,7 +5810,7 @@
         <v>81</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G3" s="5">
         <v>0</v>
@@ -5839,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="X3" s="5" t="s">
         <v>114</v>
@@ -5856,7 +5875,7 @@
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
-        <f>ROW()-2+3000</f>
+        <f t="shared" si="0"/>
         <v>3002</v>
       </c>
       <c r="B4" s="5">
@@ -5920,10 +5939,10 @@
         <v>0</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="X4" s="5" t="s">
         <v>114</v>
@@ -5937,7 +5956,7 @@
     </row>
     <row r="5" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="5">
-        <f>ROW()-2+3000</f>
+        <f t="shared" si="0"/>
         <v>3003</v>
       </c>
       <c r="B5" s="5">
@@ -5950,10 +5969,10 @@
         <v>60</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G5" s="5">
         <v>0</v>
@@ -6001,10 +6020,10 @@
         <v>0</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="X5" s="5" t="s">
         <v>114</v>
@@ -6018,7 +6037,7 @@
     </row>
     <row r="6" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
-        <f>ROW()-2+3000</f>
+        <f t="shared" si="0"/>
         <v>3004</v>
       </c>
       <c r="B6" s="5">
@@ -6082,10 +6101,10 @@
         <v>0</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="X6" s="5" t="s">
         <v>114</v>
@@ -6099,7 +6118,7 @@
     </row>
     <row r="7" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="5">
-        <f>ROW()-2+3000</f>
+        <f t="shared" si="0"/>
         <v>3005</v>
       </c>
       <c r="B7" s="5">
@@ -6115,7 +6134,7 @@
         <v>79</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G7" s="5">
         <v>0</v>
@@ -6163,10 +6182,10 @@
         <v>0</v>
       </c>
       <c r="V7" s="5" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="X7" s="5" t="s">
         <v>114</v>
@@ -6180,7 +6199,7 @@
     </row>
     <row r="8" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5">
-        <f>ROW()-2+3000</f>
+        <f t="shared" si="0"/>
         <v>3006</v>
       </c>
       <c r="B8" s="5">
@@ -6193,10 +6212,10 @@
         <v>63</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
@@ -6244,10 +6263,10 @@
         <v>0</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="X8" s="5" t="s">
         <v>114</v>
@@ -6261,7 +6280,7 @@
     </row>
     <row r="9" spans="1:26" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="5">
-        <f>ROW()-2+3000</f>
+        <f t="shared" si="0"/>
         <v>3007</v>
       </c>
       <c r="B9" s="5">
@@ -6274,10 +6293,10 @@
         <v>47</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
@@ -6325,10 +6344,10 @@
         <v>0</v>
       </c>
       <c r="V9" s="5" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="X9" s="5" t="s">
         <v>113</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A238C8-B9E4-464E-A7D7-71236C0BFCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F610081-B642-4160-92E5-C5AEEA2683A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="1110" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1965" yWindow="705" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="207">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -1822,36 +1822,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>自由課題
-夏エリアで行われる初級パティシエ向けのコンテスト。
-遊園地にくるお客さんを喜ばせよう！！</t>
-    <rPh sb="0" eb="4">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ナツ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ショキュウ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="31" eb="34">
-      <t>ユウエンチ</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>キャク</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>ヨロコ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Or_Contest_490</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1862,36 +1832,6 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>カシ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>自由課題
-秋エリアで定期的に行われるパティシエコンテスト。
-幅広くいろんなお菓子を募集しております！</t>
-    <rPh sb="0" eb="4">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>アキ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>テイキ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ハバヒロ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ボシュウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2067,6 +2007,259 @@
   </si>
   <si>
     <t>t101</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Contest_EnshutuName</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ラスク
+ブロカント</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フィナンシェ
+バタ～ズカップ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ルミエール
+エピファニア</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ルミエール
+カンデラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メルヘンランド♪
+カップ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キラキラ
+ボンボンズ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ビジョウ・パティスリー
+カップ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プラトンアカデミー
+コンテスト</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クッキーノービス
+カップ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ひんやりお菓子
+コンテスト</t>
+    <rPh sb="5" eb="7">
+      <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フライング・ソーダ
+コンテスト</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ボンボヤージュ
+カップ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エレメンタリー
+ショコラティエ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おみやげおかし
+コンテスト</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>英国ティータイム
+コンテスト</t>
+    <rPh sb="0" eb="2">
+      <t>エイコク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マジカルパティスリー
+アワード</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プラムお菓子技術
+コンテスト</t>
+    <rPh sb="4" eb="6">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ギジュツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サマードリームス
+フェスティバル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クレープ・ドゥ
+シャノワール</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>秋のお菓子
+コンテスト</t>
+    <rPh sb="0" eb="1">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アデュルティ
+ガトー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>オランジーナ
+パティスリーアワード</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コンチェルティーノ
+イン・ブルー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ディオ・ショコラ
+チャンピオンシップ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アムールチョコレイト
+コンテスト</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ネオユニバース
+カップ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ルミエール・ドゥ
+ソレイユ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チーズケーキ
+パティスリーアワード</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>パティスリー
+デュ・モンド</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>夢見るチョコレート
+選手権</t>
+    <rPh sb="0" eb="2">
+      <t>ユメミ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>センシュケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自由課題
+夏エリアで行われる初級パティシエ向けのコンテスト。遊園地そばのソーダの森で開催。
+森にくるお客さんを喜ばせよう！！</t>
+    <rPh sb="0" eb="4">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ショキュウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="30" eb="33">
+      <t>ユウエンチ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>モリ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>カイサイ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>モリ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>キャク</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ヨロコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自由課題
+秋エリアの風物詩的パティシエコンテストです。木枯らしを感じる季節・・いかがおすごしですか？
+幅広くいろんなお菓子を募集しております！</t>
+    <rPh sb="0" eb="4">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>フウブツシ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>コガ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>キセツ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ハバヒロ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ボシュウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2477,20 +2670,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
-    <col min="6" max="6" width="19.75" customWidth="1"/>
-    <col min="7" max="10" width="7.5" customWidth="1"/>
-    <col min="11" max="11" width="8.125" customWidth="1"/>
-    <col min="12" max="24" width="6.75" customWidth="1"/>
-    <col min="25" max="25" width="25.125" customWidth="1"/>
+    <col min="5" max="6" width="20.625" customWidth="1"/>
+    <col min="7" max="7" width="19.75" customWidth="1"/>
+    <col min="8" max="11" width="7.5" customWidth="1"/>
+    <col min="12" max="12" width="8.125" customWidth="1"/>
+    <col min="13" max="25" width="6.75" customWidth="1"/>
+    <col min="26" max="26" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -2507,70 +2700,73 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:27" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <f t="shared" ref="A2:A13" si="0">ROW()-2</f>
         <v>0</v>
@@ -2587,71 +2783,74 @@
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
       <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
         <v>7</v>
       </c>
-      <c r="I2" s="2">
+      <c r="J2" s="2">
         <v>12</v>
       </c>
-      <c r="J2" s="2">
+      <c r="K2" s="2">
         <v>31</v>
       </c>
-      <c r="K2" s="2">
+      <c r="L2" s="2">
         <v>5000</v>
       </c>
-      <c r="L2" s="2">
-        <v>0</v>
-      </c>
       <c r="M2" s="2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2">
         <v>50</v>
       </c>
-      <c r="N2" s="2">
+      <c r="O2" s="2">
         <v>5</v>
       </c>
-      <c r="O2" s="2">
-        <v>0</v>
-      </c>
       <c r="P2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2">
         <v>99</v>
       </c>
-      <c r="Q2" s="2">
-        <v>0</v>
-      </c>
       <c r="R2" s="2">
         <v>0</v>
       </c>
       <c r="S2" s="2">
+        <v>0</v>
+      </c>
+      <c r="T2" s="2">
         <v>10</v>
       </c>
-      <c r="T2" s="2">
-        <v>0</v>
-      </c>
       <c r="U2" s="2">
         <v>0</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" s="2">
+        <v>0</v>
+      </c>
+      <c r="W2" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="Z2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Z2" s="2">
+      <c r="AA2" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2669,70 +2868,73 @@
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
       <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>12</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>31</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
       <c r="L3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
         <v>99</v>
       </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
       <c r="R3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
         <v>2</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
         <v>0</v>
       </c>
-      <c r="V3" t="s">
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3" t="s">
         <v>108</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>112</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>114</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="Z3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -2750,70 +2952,73 @@
         <v>92</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
       <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>2</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>12</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>31</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
       <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
         <v>2</v>
       </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
       <c r="N4">
         <v>1</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
         <v>99</v>
       </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
       <c r="R4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
         <v>2</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
         <v>0</v>
       </c>
-      <c r="V4" t="s">
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4" t="s">
         <v>108</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>112</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>114</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="Z4" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2831,70 +3036,73 @@
         <v>76</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
       <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>2</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>12</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>31</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>300</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>2</v>
       </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
       <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
         <v>2</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
       <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
         <v>99</v>
       </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
       <c r="R5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
         <v>2</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
         <v>0</v>
       </c>
-      <c r="V5" t="s">
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5" t="s">
         <v>108</v>
       </c>
-      <c r="W5" t="s">
+      <c r="X5" t="s">
         <v>112</v>
       </c>
-      <c r="X5" t="s">
+      <c r="Y5" t="s">
         <v>114</v>
       </c>
-      <c r="Y5" s="4" t="s">
+      <c r="Z5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2911,26 +3119,26 @@
       <c r="E6" t="s">
         <v>88</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
       <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>2</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>12</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>31</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>500</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -2939,43 +3147,46 @@
         <v>3</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
         <v>99</v>
       </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
       <c r="R6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
         <v>3</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
         <v>0</v>
       </c>
-      <c r="V6" t="s">
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6" t="s">
         <v>152</v>
       </c>
-      <c r="W6" t="s">
+      <c r="X6" t="s">
         <v>112</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Y6" t="s">
         <v>114</v>
       </c>
-      <c r="Y6" s="4" t="s">
+      <c r="Z6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2993,70 +3204,73 @@
         <v>89</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
       <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>3</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>12</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>31</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>400</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>3</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>5</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>3</v>
       </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
       <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
         <v>99</v>
       </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
       <c r="R7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
         <v>3</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
         <v>0</v>
       </c>
-      <c r="V7" t="s">
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7" t="s">
         <v>108</v>
       </c>
-      <c r="W7" t="s">
+      <c r="X7" t="s">
         <v>112</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Y7" t="s">
         <v>114</v>
       </c>
-      <c r="Y7" s="4" t="s">
+      <c r="Z7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3074,70 +3288,73 @@
         <v>90</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
       <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>4</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>12</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>31</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>1000</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>5</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>10</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>4</v>
       </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
       <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
         <v>99</v>
       </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
       <c r="R8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
         <v>3</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
         <v>0</v>
       </c>
-      <c r="V8" t="s">
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8" t="s">
         <v>108</v>
       </c>
-      <c r="W8" t="s">
+      <c r="X8" t="s">
         <v>112</v>
       </c>
-      <c r="X8" t="s">
+      <c r="Y8" t="s">
         <v>114</v>
       </c>
-      <c r="Y8" s="4" t="s">
+      <c r="Z8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3149,31 +3366,31 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E9" t="s">
-        <v>161</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
+        <v>159</v>
+      </c>
+      <c r="F9" t="s">
+        <v>159</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>2</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>12</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>31</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>700</v>
-      </c>
-      <c r="L9">
-        <v>3</v>
       </c>
       <c r="M9">
         <v>3</v>
@@ -3182,43 +3399,46 @@
         <v>3</v>
       </c>
       <c r="O9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
         <v>99</v>
       </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
       <c r="R9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
         <v>3</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
         <v>0</v>
       </c>
-      <c r="V9" t="s">
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9" t="s">
         <v>152</v>
       </c>
-      <c r="W9" t="s">
+      <c r="X9" t="s">
         <v>112</v>
       </c>
-      <c r="X9" t="s">
+      <c r="Y9" t="s">
         <v>114</v>
       </c>
-      <c r="Y9" s="4" t="s">
+      <c r="Z9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3236,70 +3456,73 @@
         <v>73</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
       <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>3</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>12</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>31</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>500</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>4</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>15</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>3</v>
       </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
       <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
         <v>99</v>
       </c>
-      <c r="Q10">
-        <v>1</v>
-      </c>
       <c r="R10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
         <v>3</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
         <v>0</v>
       </c>
-      <c r="V10" t="s">
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10" t="s">
         <v>108</v>
       </c>
-      <c r="W10" t="s">
+      <c r="X10" t="s">
         <v>112</v>
       </c>
-      <c r="X10" t="s">
+      <c r="Y10" t="s">
         <v>114</v>
       </c>
-      <c r="Y10" s="4" t="s">
+      <c r="Z10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3317,70 +3540,73 @@
         <v>83</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
       <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>4</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>12</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>31</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>500</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>4</v>
       </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
       <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
         <v>3</v>
       </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
       <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
         <v>99</v>
       </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
       <c r="R11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
         <v>3</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
         <v>0</v>
       </c>
-      <c r="V11" t="s">
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11" t="s">
         <v>108</v>
       </c>
-      <c r="W11" t="s">
+      <c r="X11" t="s">
         <v>112</v>
       </c>
-      <c r="X11" t="s">
+      <c r="Y11" t="s">
         <v>114</v>
       </c>
-      <c r="Y11" s="4" t="s">
+      <c r="Z11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3398,70 +3624,73 @@
         <v>74</v>
       </c>
       <c r="F12" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
       <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <v>5</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>12</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>31</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>3000</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>6</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>20</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>4</v>
       </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
       <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
         <v>99</v>
       </c>
-      <c r="Q12">
-        <v>1</v>
-      </c>
       <c r="R12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
         <v>3</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
         <v>0</v>
       </c>
-      <c r="V12" t="s">
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12" t="s">
         <v>108</v>
       </c>
-      <c r="W12" t="s">
+      <c r="X12" t="s">
         <v>112</v>
       </c>
-      <c r="X12" t="s">
+      <c r="Y12" t="s">
         <v>114</v>
       </c>
-      <c r="Y12" s="4" t="s">
+      <c r="Z12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3479,41 +3708,41 @@
         <v>29</v>
       </c>
       <c r="F13" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
       <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>5</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>12</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>31</v>
       </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
       <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>100</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>5</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>4</v>
       </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
       <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
         <v>99</v>
       </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
       <c r="R13">
         <v>0</v>
       </c>
@@ -3526,19 +3755,22 @@
       <c r="U13">
         <v>0</v>
       </c>
-      <c r="V13" t="s">
-        <v>173</v>
+      <c r="V13">
+        <v>0</v>
       </c>
       <c r="W13" t="s">
+        <v>171</v>
+      </c>
+      <c r="X13" t="s">
         <v>112</v>
       </c>
-      <c r="X13" t="s">
+      <c r="Y13" t="s">
         <v>113</v>
       </c>
-      <c r="Y13" s="4" t="s">
+      <c r="Z13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z13">
+      <c r="AA13">
         <v>1</v>
       </c>
     </row>
@@ -3551,20 +3783,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B615D1EB-7EB0-40A6-B71A-0773034D7CD2}">
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
-    <col min="6" max="6" width="19.75" customWidth="1"/>
-    <col min="7" max="10" width="7.5" customWidth="1"/>
-    <col min="11" max="11" width="8.125" customWidth="1"/>
-    <col min="12" max="24" width="6.75" customWidth="1"/>
-    <col min="25" max="25" width="25.125" customWidth="1"/>
+    <col min="5" max="6" width="20.625" customWidth="1"/>
+    <col min="7" max="7" width="19.75" customWidth="1"/>
+    <col min="8" max="11" width="7.5" customWidth="1"/>
+    <col min="12" max="12" width="8.125" customWidth="1"/>
+    <col min="13" max="25" width="6.75" customWidth="1"/>
+    <col min="26" max="26" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3581,70 +3813,73 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
         <f t="shared" ref="A2:A11" si="0">ROW()-2+1000</f>
         <v>1000</v>
@@ -3662,70 +3897,73 @@
         <v>65</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
       <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
         <v>2</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>12</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>31</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>100</v>
       </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
       <c r="M2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
         <v>99</v>
       </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
       <c r="R2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
         <v>2</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
         <v>0</v>
       </c>
-      <c r="V2" t="s">
-        <v>167</v>
+      <c r="V2">
+        <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="X2" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y2" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>1001</v>
@@ -3742,71 +3980,74 @@
       <c r="E3" t="s">
         <v>155</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
+      <c r="F3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>205</v>
       </c>
       <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>12</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>31</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>100</v>
       </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
       <c r="M3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
         <v>99</v>
       </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
       <c r="R3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
         <v>2</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
         <v>0</v>
       </c>
-      <c r="V3" t="s">
-        <v>174</v>
+      <c r="V3">
+        <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="X3" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y3" t="s">
         <v>114</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="Z3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>1002</v>
@@ -3824,70 +4065,73 @@
         <v>101</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
       <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>2</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>12</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>31</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>200</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>10</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>3</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>2</v>
       </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
       <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
         <v>99</v>
       </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
       <c r="R4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
         <v>3</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
         <v>0</v>
       </c>
-      <c r="V4" t="s">
-        <v>167</v>
+      <c r="V4">
+        <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="X4" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y4" t="s">
         <v>114</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="Z4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>1003</v>
@@ -3905,70 +4149,73 @@
         <v>99</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
       <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>3</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>12</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>31</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>300</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>10</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>5</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>2</v>
       </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
       <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
         <v>99</v>
       </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
       <c r="R5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
         <v>3</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
         <v>0</v>
       </c>
-      <c r="V5" t="s">
-        <v>167</v>
+      <c r="V5">
+        <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="X5" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y5" t="s">
         <v>114</v>
       </c>
-      <c r="Y5" s="4" t="s">
+      <c r="Z5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>1004</v>
@@ -3983,73 +4230,76 @@
         <v>150</v>
       </c>
       <c r="E6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
       <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>4</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>12</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>31</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>500</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
       </c>
       <c r="M6">
         <v>10</v>
       </c>
       <c r="N6">
+        <v>10</v>
+      </c>
+      <c r="O6">
         <v>3</v>
       </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
       <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
         <v>99</v>
       </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
       <c r="R6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
         <v>3</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
         <v>0</v>
       </c>
-      <c r="V6" t="s">
-        <v>167</v>
+      <c r="V6">
+        <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="X6" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y6" t="s">
         <v>114</v>
       </c>
-      <c r="Y6" s="4" t="s">
+      <c r="Z6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>1005</v>
@@ -4067,70 +4317,73 @@
         <v>67</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
       <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>3</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>12</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>31</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>500</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>11</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>7</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>3</v>
       </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
       <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
         <v>99</v>
       </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
       <c r="R7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
         <v>3</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
         <v>0</v>
       </c>
-      <c r="V7" t="s">
-        <v>167</v>
+      <c r="V7">
+        <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="X7" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y7" t="s">
         <v>114</v>
       </c>
-      <c r="Y7" s="4" t="s">
+      <c r="Z7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>1006</v>
@@ -4147,71 +4400,74 @@
       <c r="E8" t="s">
         <v>68</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
       <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>4</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>12</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>31</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>700</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>11</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>10</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>4</v>
       </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
       <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
         <v>99</v>
       </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
       <c r="R8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
         <v>3</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
         <v>0</v>
       </c>
-      <c r="V8" t="s">
-        <v>167</v>
+      <c r="V8">
+        <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="X8" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y8" t="s">
         <v>114</v>
       </c>
-      <c r="Y8" s="4" t="s">
+      <c r="Z8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>1007</v>
@@ -4229,70 +4485,73 @@
         <v>64</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
       <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>3</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>12</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>31</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>1000</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>11</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>10</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>4</v>
       </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
       <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
         <v>99</v>
       </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
       <c r="R9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
         <v>3</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
         <v>0</v>
       </c>
-      <c r="V9" t="s">
-        <v>167</v>
+      <c r="V9">
+        <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="X9" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y9" t="s">
         <v>114</v>
       </c>
-      <c r="Y9" s="4" t="s">
+      <c r="Z9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>1008</v>
@@ -4309,71 +4568,74 @@
       <c r="E10" t="s">
         <v>100</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
       <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>4</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>12</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>31</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>1500</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>12</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>10</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>5</v>
       </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
       <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
         <v>99</v>
       </c>
-      <c r="Q10">
-        <v>1</v>
-      </c>
       <c r="R10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
         <v>3</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
         <v>0</v>
       </c>
-      <c r="V10" t="s">
-        <v>167</v>
+      <c r="V10">
+        <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="X10" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y10" t="s">
         <v>114</v>
       </c>
-      <c r="Y10" s="4" t="s">
+      <c r="Z10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>1009</v>
@@ -4391,70 +4653,73 @@
         <v>149</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
       <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>3</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>12</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>31</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>1500</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>13</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>15</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>4</v>
       </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
       <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
         <v>99</v>
       </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
       <c r="R11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
         <v>3</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
         <v>0</v>
       </c>
-      <c r="V11" t="s">
-        <v>167</v>
+      <c r="V11">
+        <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="X11" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y11" t="s">
         <v>114</v>
       </c>
-      <c r="Y11" s="4" t="s">
+      <c r="Z11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
         <f>ROW()-2+1000</f>
         <v>1010</v>
@@ -4472,70 +4737,73 @@
         <v>153</v>
       </c>
       <c r="F12" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
       <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <v>5</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>12</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>31</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>3000</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>13</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>18</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>5</v>
       </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
       <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
         <v>99</v>
       </c>
-      <c r="Q12">
-        <v>1</v>
-      </c>
       <c r="R12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
         <v>5</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
         <v>0</v>
       </c>
-      <c r="V12" t="s">
-        <v>167</v>
+      <c r="V12">
+        <v>0</v>
       </c>
       <c r="W12" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="X12" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y12" t="s">
         <v>114</v>
       </c>
-      <c r="Y12" s="4" t="s">
+      <c r="Z12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13">
         <f>ROW()-2+1000</f>
         <v>1011</v>
@@ -4553,66 +4821,69 @@
         <v>136</v>
       </c>
       <c r="F13" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
       <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>5</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>12</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>31</v>
       </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
       <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>200</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>12</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>5</v>
       </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
       <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
         <v>99</v>
       </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
       <c r="R13">
         <v>0</v>
       </c>
       <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
         <v>4</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
         <v>0</v>
       </c>
-      <c r="V13" t="s">
-        <v>167</v>
+      <c r="V13">
+        <v>0</v>
       </c>
       <c r="W13" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="X13" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y13" t="s">
         <v>113</v>
       </c>
-      <c r="Y13" s="4" t="s">
+      <c r="Z13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z13">
+      <c r="AA13">
         <v>1</v>
       </c>
     </row>
@@ -4625,20 +4896,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A66AAA5-0C8D-4F8A-9A3B-33AFE45A42B1}">
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
-    <col min="6" max="6" width="19.75" customWidth="1"/>
-    <col min="7" max="10" width="7.5" customWidth="1"/>
-    <col min="11" max="11" width="8.125" customWidth="1"/>
-    <col min="12" max="24" width="6.75" customWidth="1"/>
-    <col min="25" max="25" width="25.125" customWidth="1"/>
+    <col min="5" max="6" width="20.625" customWidth="1"/>
+    <col min="7" max="7" width="19.75" customWidth="1"/>
+    <col min="8" max="11" width="7.5" customWidth="1"/>
+    <col min="12" max="12" width="8.125" customWidth="1"/>
+    <col min="13" max="25" width="6.75" customWidth="1"/>
+    <col min="26" max="26" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -4655,70 +4926,73 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
         <f t="shared" ref="A2:A8" si="0">ROW()-2+2000</f>
         <v>2000</v>
@@ -4736,70 +5010,73 @@
         <v>75</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <v>12</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>31</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>300</v>
       </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
       <c r="M2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
         <v>2</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
       <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
         <v>99</v>
       </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
       <c r="R2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
         <v>2</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
         <v>0</v>
       </c>
-      <c r="V2" t="s">
-        <v>168</v>
+      <c r="V2">
+        <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="X2" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y2" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>2001</v>
@@ -4811,76 +5088,79 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E3" t="s">
         <v>158</v>
       </c>
-      <c r="E3" t="s">
-        <v>159</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
+        <v>194</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>206</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
         <v>12</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>31</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>300</v>
       </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
       <c r="M3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
         <v>2</v>
       </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
       <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
         <v>99</v>
       </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
       <c r="R3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
         <v>2</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
         <v>0</v>
       </c>
-      <c r="V3" t="s">
-        <v>168</v>
+      <c r="V3">
+        <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="X3" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y3" t="s">
         <v>114</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="Z3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>2002</v>
@@ -4898,70 +5178,73 @@
         <v>82</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
       <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>2</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>12</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>31</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>500</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>20</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>10</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>2</v>
       </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
       <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
         <v>99</v>
       </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
       <c r="R4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
         <v>2</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
         <v>0</v>
       </c>
-      <c r="V4" t="s">
-        <v>168</v>
+      <c r="V4">
+        <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="X4" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y4" t="s">
         <v>114</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="Z4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>2003</v>
@@ -4979,70 +5262,73 @@
         <v>87</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
       <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>3</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>12</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>31</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>500</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>20</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>15</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>3</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
       <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
         <v>99</v>
       </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
       <c r="R5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
         <v>3</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
         <v>0</v>
       </c>
-      <c r="V5" t="s">
-        <v>168</v>
+      <c r="V5">
+        <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="X5" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y5" t="s">
         <v>114</v>
       </c>
-      <c r="Y5" s="4" t="s">
+      <c r="Z5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <f>ROW()-2+2000</f>
         <v>2004</v>
@@ -5059,71 +5345,74 @@
       <c r="E6" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
       <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>5</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>12</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>31</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>1200</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>21</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>23</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>4</v>
       </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
       <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
         <v>99</v>
       </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
       <c r="R6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
         <v>3</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
         <v>0</v>
       </c>
-      <c r="V6" t="s">
-        <v>168</v>
+      <c r="V6">
+        <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="X6" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y6" t="s">
         <v>114</v>
       </c>
-      <c r="Y6" s="4" t="s">
+      <c r="Z6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
         <f>ROW()-2+2000</f>
         <v>2005</v>
@@ -5140,71 +5429,74 @@
       <c r="E7" t="s">
         <v>98</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
+      <c r="F7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>2</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>12</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>31</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>600</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>21</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>20</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>3</v>
       </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
       <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
         <v>99</v>
       </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
       <c r="R7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
         <v>3</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
         <v>0</v>
       </c>
-      <c r="V7" t="s">
-        <v>169</v>
+      <c r="V7">
+        <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="X7" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y7" t="s">
         <v>114</v>
       </c>
-      <c r="Y7" s="4" t="s">
+      <c r="Z7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>2006</v>
@@ -5222,70 +5514,73 @@
         <v>86</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
       <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>3</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>12</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>31</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>1500</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>22</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>30</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>5</v>
       </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
       <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
         <v>99</v>
       </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
       <c r="R8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
         <v>5</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
         <v>0</v>
       </c>
-      <c r="V8" t="s">
-        <v>168</v>
+      <c r="V8">
+        <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="X8" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y8" t="s">
         <v>114</v>
       </c>
-      <c r="Y8" s="4" t="s">
+      <c r="Z8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
         <f t="shared" ref="A9:A10" si="1">ROW()-2+2000</f>
         <v>2007</v>
@@ -5302,71 +5597,74 @@
       <c r="E9" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
+      <c r="F9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>162</v>
       </c>
       <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>5</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>12</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>31</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>2000</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>22</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>25</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>4</v>
       </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
       <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
         <v>99</v>
       </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
       <c r="R9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
         <v>3</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
         <v>0</v>
       </c>
-      <c r="V9" t="s">
-        <v>168</v>
+      <c r="V9">
+        <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="X9" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y9" t="s">
         <v>114</v>
       </c>
-      <c r="Y9" s="4" t="s">
+      <c r="Z9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
         <f t="shared" si="1"/>
         <v>2008</v>
@@ -5384,70 +5682,73 @@
         <v>91</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
       <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>5</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>12</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>31</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>3000</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>22</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>30</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>5</v>
       </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
       <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
         <v>99</v>
       </c>
-      <c r="Q10">
-        <v>1</v>
-      </c>
       <c r="R10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
         <v>5</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
         <v>0</v>
       </c>
-      <c r="V10" t="s">
-        <v>168</v>
+      <c r="V10">
+        <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="X10" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y10" t="s">
         <v>114</v>
       </c>
-      <c r="Y10" s="4" t="s">
+      <c r="Z10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:27" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <f>ROW()-2+2000</f>
         <v>2009</v>
@@ -5464,71 +5765,74 @@
       <c r="E11" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
       <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
         <v>5</v>
       </c>
-      <c r="I11" s="2">
+      <c r="J11" s="2">
         <v>12</v>
       </c>
-      <c r="J11" s="2">
+      <c r="K11" s="2">
         <v>31</v>
       </c>
-      <c r="K11" s="2">
+      <c r="L11" s="2">
         <v>3000</v>
       </c>
-      <c r="L11" s="2">
+      <c r="M11" s="2">
         <v>9999</v>
       </c>
-      <c r="M11" s="2">
+      <c r="N11" s="2">
         <v>25</v>
       </c>
-      <c r="N11" s="2">
+      <c r="O11" s="2">
         <v>3</v>
       </c>
-      <c r="O11" s="2">
-        <v>0</v>
-      </c>
       <c r="P11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
         <v>99</v>
       </c>
-      <c r="Q11" s="2">
-        <v>1</v>
-      </c>
       <c r="R11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="2">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2">
         <v>5</v>
       </c>
-      <c r="T11" s="2">
-        <v>0</v>
-      </c>
       <c r="U11" s="2">
         <v>0</v>
       </c>
-      <c r="V11" s="2" t="s">
-        <v>168</v>
+      <c r="V11" s="2">
+        <v>0</v>
       </c>
       <c r="W11" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="X11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="X11" s="2" t="s">
+      <c r="Y11" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="Y11" s="3" t="s">
+      <c r="Z11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="Z11" s="2">
+      <c r="AA11" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
         <f>ROW()-2+2000</f>
         <v>2010</v>
@@ -5545,67 +5849,70 @@
       <c r="E12" t="s">
         <v>132</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
       <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <v>5</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>12</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>31</v>
       </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
       <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
         <v>300</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>18</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>5</v>
       </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
       <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
         <v>99</v>
       </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
       <c r="R12">
         <v>0</v>
       </c>
       <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
         <v>4</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
         <v>0</v>
       </c>
-      <c r="V12" t="s">
-        <v>168</v>
+      <c r="V12">
+        <v>0</v>
       </c>
       <c r="W12" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="X12" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y12" t="s">
         <v>141</v>
       </c>
-      <c r="Y12" s="4" t="s">
+      <c r="Z12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <v>1</v>
       </c>
     </row>
@@ -5618,20 +5925,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3990FE8C-49B4-4F17-805B-7287A7C6D5E2}">
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
-    <col min="6" max="6" width="19.75" customWidth="1"/>
-    <col min="7" max="10" width="7.5" customWidth="1"/>
-    <col min="11" max="11" width="8.125" customWidth="1"/>
-    <col min="12" max="24" width="6.75" customWidth="1"/>
-    <col min="25" max="25" width="25.125" customWidth="1"/>
+    <col min="5" max="6" width="20.625" customWidth="1"/>
+    <col min="7" max="7" width="19.75" customWidth="1"/>
+    <col min="8" max="11" width="7.5" customWidth="1"/>
+    <col min="12" max="12" width="8.125" customWidth="1"/>
+    <col min="13" max="25" width="6.75" customWidth="1"/>
+    <col min="26" max="26" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -5648,70 +5955,73 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:27" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5">
         <f t="shared" ref="A2:A9" si="0">ROW()-2+3000</f>
         <v>3000</v>
@@ -5728,71 +6038,74 @@
       <c r="E2" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
       <c r="H2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="5">
+        <v>1</v>
+      </c>
+      <c r="J2" s="5">
         <v>12</v>
       </c>
-      <c r="J2" s="5">
+      <c r="K2" s="5">
         <v>31</v>
       </c>
-      <c r="K2" s="5">
-        <v>0</v>
-      </c>
       <c r="L2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5">
         <v>99</v>
       </c>
-      <c r="Q2" s="5">
-        <v>1</v>
-      </c>
       <c r="R2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" s="5">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5">
         <v>2</v>
       </c>
-      <c r="T2" s="5">
-        <v>0</v>
-      </c>
       <c r="U2" s="5">
         <v>0</v>
       </c>
-      <c r="V2" s="5" t="s">
-        <v>169</v>
+      <c r="V2" s="5">
+        <v>0</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="X2" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y2" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="Z2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z2" s="5">
+      <c r="AA2" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
         <f t="shared" si="0"/>
         <v>3001</v>
@@ -5810,70 +6123,73 @@
         <v>81</v>
       </c>
       <c r="F3" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
       <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
         <v>2</v>
       </c>
-      <c r="I3" s="5">
+      <c r="J3" s="5">
         <v>12</v>
       </c>
-      <c r="J3" s="5">
+      <c r="K3" s="5">
         <v>31</v>
       </c>
-      <c r="K3" s="5">
+      <c r="L3" s="5">
         <v>500</v>
       </c>
-      <c r="L3" s="5">
+      <c r="M3" s="5">
         <v>30</v>
       </c>
-      <c r="M3" s="5">
+      <c r="N3" s="5">
         <v>15</v>
       </c>
-      <c r="N3" s="5">
+      <c r="O3" s="5">
         <v>3</v>
       </c>
-      <c r="O3" s="5">
-        <v>1</v>
-      </c>
       <c r="P3" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="5">
         <v>99</v>
       </c>
-      <c r="Q3" s="5">
-        <v>1</v>
-      </c>
       <c r="R3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" s="5">
+        <v>0</v>
+      </c>
+      <c r="T3" s="5">
         <v>3</v>
       </c>
-      <c r="T3" s="5">
-        <v>0</v>
-      </c>
       <c r="U3" s="5">
         <v>0</v>
       </c>
-      <c r="V3" s="5" t="s">
-        <v>169</v>
+      <c r="V3" s="5">
+        <v>0</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="X3" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y3" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Z3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z3" s="5">
+      <c r="AA3" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
         <f t="shared" si="0"/>
         <v>3002</v>
@@ -5891,70 +6207,73 @@
         <v>80</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
       <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
         <v>3</v>
       </c>
-      <c r="I4" s="5">
+      <c r="J4" s="5">
         <v>12</v>
       </c>
-      <c r="J4" s="5">
+      <c r="K4" s="5">
         <v>31</v>
       </c>
-      <c r="K4" s="5">
+      <c r="L4" s="5">
         <v>700</v>
       </c>
-      <c r="L4" s="5">
+      <c r="M4" s="5">
         <v>30</v>
       </c>
-      <c r="M4" s="5">
+      <c r="N4" s="5">
         <v>20</v>
       </c>
-      <c r="N4" s="5">
+      <c r="O4" s="5">
         <v>4</v>
       </c>
-      <c r="O4" s="5">
-        <v>1</v>
-      </c>
       <c r="P4" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="5">
         <v>99</v>
       </c>
-      <c r="Q4" s="5">
-        <v>1</v>
-      </c>
       <c r="R4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" s="5">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5">
         <v>3</v>
       </c>
-      <c r="T4" s="5">
-        <v>0</v>
-      </c>
       <c r="U4" s="5">
         <v>0</v>
       </c>
-      <c r="V4" s="5" t="s">
-        <v>169</v>
+      <c r="V4" s="5">
+        <v>0</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="X4" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y4" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Z4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z4" s="5">
+      <c r="AA4" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:27" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>3003</v>
@@ -5972,70 +6291,73 @@
         <v>127</v>
       </c>
       <c r="F5" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
       <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
         <v>3</v>
       </c>
-      <c r="I5" s="5">
+      <c r="J5" s="5">
         <v>12</v>
       </c>
-      <c r="J5" s="5">
+      <c r="K5" s="5">
         <v>31</v>
       </c>
-      <c r="K5" s="5">
+      <c r="L5" s="5">
         <v>700</v>
       </c>
-      <c r="L5" s="5">
+      <c r="M5" s="5">
         <v>30</v>
       </c>
-      <c r="M5" s="5">
+      <c r="N5" s="5">
         <v>25</v>
       </c>
-      <c r="N5" s="5">
+      <c r="O5" s="5">
         <v>4</v>
       </c>
-      <c r="O5" s="5">
-        <v>1</v>
-      </c>
       <c r="P5" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="5">
         <v>99</v>
       </c>
-      <c r="Q5" s="5">
-        <v>1</v>
-      </c>
       <c r="R5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" s="5">
+        <v>0</v>
+      </c>
+      <c r="T5" s="5">
         <v>3</v>
       </c>
-      <c r="T5" s="5">
-        <v>0</v>
-      </c>
       <c r="U5" s="5">
         <v>0</v>
       </c>
-      <c r="V5" s="5" t="s">
-        <v>169</v>
+      <c r="V5" s="5">
+        <v>0</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="X5" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y5" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Z5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z5" s="5">
+      <c r="AA5" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:27" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3004</v>
@@ -6052,71 +6374,74 @@
       <c r="E6" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
       <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
         <v>5</v>
       </c>
-      <c r="I6" s="5">
+      <c r="J6" s="5">
         <v>12</v>
       </c>
-      <c r="J6" s="5">
+      <c r="K6" s="5">
         <v>31</v>
       </c>
-      <c r="K6" s="5">
+      <c r="L6" s="5">
         <v>1000</v>
       </c>
-      <c r="L6" s="5">
+      <c r="M6" s="5">
         <v>31</v>
       </c>
-      <c r="M6" s="5">
+      <c r="N6" s="5">
         <v>25</v>
       </c>
-      <c r="N6" s="5">
+      <c r="O6" s="5">
         <v>4</v>
       </c>
-      <c r="O6" s="5">
-        <v>1</v>
-      </c>
       <c r="P6" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="5">
         <v>99</v>
       </c>
-      <c r="Q6" s="5">
-        <v>1</v>
-      </c>
       <c r="R6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" s="5">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5">
         <v>3</v>
       </c>
-      <c r="T6" s="5">
-        <v>0</v>
-      </c>
       <c r="U6" s="5">
         <v>0</v>
       </c>
-      <c r="V6" s="5" t="s">
-        <v>169</v>
+      <c r="V6" s="5">
+        <v>0</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="X6" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y6" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="Z6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z6" s="5">
+      <c r="AA6" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:27" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>3005</v>
@@ -6134,70 +6459,73 @@
         <v>79</v>
       </c>
       <c r="F7" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
       <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
         <v>5</v>
       </c>
-      <c r="I7" s="5">
+      <c r="J7" s="5">
         <v>12</v>
       </c>
-      <c r="J7" s="5">
+      <c r="K7" s="5">
         <v>31</v>
       </c>
-      <c r="K7" s="5">
+      <c r="L7" s="5">
         <v>1500</v>
       </c>
-      <c r="L7" s="5">
+      <c r="M7" s="5">
         <v>32</v>
       </c>
-      <c r="M7" s="5">
+      <c r="N7" s="5">
         <v>35</v>
       </c>
-      <c r="N7" s="5">
+      <c r="O7" s="5">
         <v>4</v>
       </c>
-      <c r="O7" s="5">
-        <v>1</v>
-      </c>
       <c r="P7" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="5">
         <v>99</v>
       </c>
-      <c r="Q7" s="5">
-        <v>1</v>
-      </c>
       <c r="R7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" s="5">
+        <v>0</v>
+      </c>
+      <c r="T7" s="5">
         <v>3</v>
       </c>
-      <c r="T7" s="5">
-        <v>0</v>
-      </c>
       <c r="U7" s="5">
         <v>0</v>
       </c>
-      <c r="V7" s="5" t="s">
-        <v>169</v>
+      <c r="V7" s="5">
+        <v>0</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="X7" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y7" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="Y7" s="6" t="s">
+      <c r="Z7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z7" s="5">
+      <c r="AA7" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:27" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>3006</v>
@@ -6215,70 +6543,73 @@
         <v>121</v>
       </c>
       <c r="F8" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
       <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
         <v>6</v>
       </c>
-      <c r="I8" s="5">
+      <c r="J8" s="5">
         <v>12</v>
       </c>
-      <c r="J8" s="5">
+      <c r="K8" s="5">
         <v>31</v>
       </c>
-      <c r="K8" s="5">
+      <c r="L8" s="5">
         <v>3000</v>
       </c>
-      <c r="L8" s="5">
+      <c r="M8" s="5">
         <v>32</v>
       </c>
-      <c r="M8" s="5">
+      <c r="N8" s="5">
         <v>45</v>
       </c>
-      <c r="N8" s="5">
+      <c r="O8" s="5">
         <v>5</v>
       </c>
-      <c r="O8" s="5">
-        <v>1</v>
-      </c>
       <c r="P8" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="5">
         <v>99</v>
       </c>
-      <c r="Q8" s="5">
-        <v>1</v>
-      </c>
       <c r="R8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="5">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5">
         <v>5</v>
       </c>
-      <c r="T8" s="5">
-        <v>0</v>
-      </c>
       <c r="U8" s="5">
         <v>0</v>
       </c>
-      <c r="V8" s="5" t="s">
-        <v>169</v>
+      <c r="V8" s="5">
+        <v>0</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="X8" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y8" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="Z8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z8" s="5">
+      <c r="AA8" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:27" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>3007</v>
@@ -6296,66 +6627,69 @@
         <v>131</v>
       </c>
       <c r="F9" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
       <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
         <v>5</v>
       </c>
-      <c r="I9" s="5">
+      <c r="J9" s="5">
         <v>12</v>
       </c>
-      <c r="J9" s="5">
+      <c r="K9" s="5">
         <v>31</v>
       </c>
-      <c r="K9" s="5">
-        <v>0</v>
-      </c>
       <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
         <v>400</v>
       </c>
-      <c r="M9" s="5">
+      <c r="N9" s="5">
         <v>50</v>
       </c>
-      <c r="N9" s="5">
+      <c r="O9" s="5">
         <v>5</v>
       </c>
-      <c r="O9" s="5">
-        <v>1</v>
-      </c>
       <c r="P9" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="5">
         <v>99</v>
       </c>
-      <c r="Q9" s="5">
-        <v>0</v>
-      </c>
       <c r="R9" s="5">
         <v>0</v>
       </c>
       <c r="S9" s="5">
+        <v>0</v>
+      </c>
+      <c r="T9" s="5">
         <v>5</v>
       </c>
-      <c r="T9" s="5">
-        <v>0</v>
-      </c>
       <c r="U9" s="5">
         <v>0</v>
       </c>
-      <c r="V9" s="5" t="s">
-        <v>169</v>
+      <c r="V9" s="5">
+        <v>0</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="X9" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y9" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="Y9" s="6" t="s">
+      <c r="Z9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="Z9" s="5">
+      <c r="AA9" s="5">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F610081-B642-4160-92E5-C5AEEA2683A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C0C8B0-FC44-4D2D-8FBE-0E0F3CDB8E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1965" yWindow="705" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2325" yWindow="1065" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="208">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -2260,6 +2260,10 @@
     <rPh sb="62" eb="64">
       <t>ボシュウ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ContestBGMSelectHall</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2670,7 +2674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:AA13"/>
+  <dimension ref="A1:AB13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -2679,11 +2683,11 @@
     <col min="7" max="7" width="19.75" customWidth="1"/>
     <col min="8" max="11" width="7.5" customWidth="1"/>
     <col min="12" max="12" width="8.125" customWidth="1"/>
-    <col min="13" max="25" width="6.75" customWidth="1"/>
-    <col min="26" max="26" width="25.125" customWidth="1"/>
+    <col min="13" max="26" width="6.75" customWidth="1"/>
+    <col min="27" max="27" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -2760,13 +2764,16 @@
         <v>111</v>
       </c>
       <c r="Z1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:28" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <f t="shared" ref="A2:A13" si="0">ROW()-2</f>
         <v>0</v>
@@ -2843,14 +2850,17 @@
       <c r="Y2" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="Z2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AA2" s="2">
+      <c r="AB2" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2927,14 +2937,17 @@
       <c r="Y3" t="s">
         <v>114</v>
       </c>
-      <c r="Z3" s="4" t="s">
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -3011,14 +3024,17 @@
       <c r="Y4" t="s">
         <v>114</v>
       </c>
-      <c r="Z4" s="4" t="s">
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -3095,14 +3111,17 @@
       <c r="Y5" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="4" t="s">
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3179,14 +3198,17 @@
       <c r="Y6" t="s">
         <v>114</v>
       </c>
-      <c r="Z6" s="4" t="s">
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3263,14 +3285,17 @@
       <c r="Y7" t="s">
         <v>114</v>
       </c>
-      <c r="Z7" s="4" t="s">
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3347,14 +3372,17 @@
       <c r="Y8" t="s">
         <v>114</v>
       </c>
-      <c r="Z8" s="4" t="s">
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3431,14 +3459,17 @@
       <c r="Y9" t="s">
         <v>114</v>
       </c>
-      <c r="Z9" s="4" t="s">
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3515,14 +3546,17 @@
       <c r="Y10" t="s">
         <v>114</v>
       </c>
-      <c r="Z10" s="4" t="s">
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3599,14 +3633,17 @@
       <c r="Y11" t="s">
         <v>114</v>
       </c>
-      <c r="Z11" s="4" t="s">
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3683,14 +3720,17 @@
       <c r="Y12" t="s">
         <v>114</v>
       </c>
-      <c r="Z12" s="4" t="s">
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA12">
+      <c r="AB12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3767,10 +3807,13 @@
       <c r="Y13" t="s">
         <v>113</v>
       </c>
-      <c r="Z13" s="4" t="s">
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AA13">
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
@@ -3783,7 +3826,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B615D1EB-7EB0-40A6-B71A-0773034D7CD2}">
-  <dimension ref="A1:AA13"/>
+  <dimension ref="A1:AB13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -3792,11 +3835,11 @@
     <col min="7" max="7" width="19.75" customWidth="1"/>
     <col min="8" max="11" width="7.5" customWidth="1"/>
     <col min="12" max="12" width="8.125" customWidth="1"/>
-    <col min="13" max="25" width="6.75" customWidth="1"/>
-    <col min="26" max="26" width="25.125" customWidth="1"/>
+    <col min="13" max="26" width="6.75" customWidth="1"/>
+    <col min="27" max="27" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3873,13 +3916,16 @@
         <v>111</v>
       </c>
       <c r="Z1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
         <f t="shared" ref="A2:A11" si="0">ROW()-2+1000</f>
         <v>1000</v>
@@ -3956,14 +4002,17 @@
       <c r="Y2" t="s">
         <v>114</v>
       </c>
-      <c r="Z2" s="4" t="s">
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>1001</v>
@@ -4040,14 +4089,17 @@
       <c r="Y3" t="s">
         <v>114</v>
       </c>
-      <c r="Z3" s="4" t="s">
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>1002</v>
@@ -4124,14 +4176,17 @@
       <c r="Y4" t="s">
         <v>114</v>
       </c>
-      <c r="Z4" s="4" t="s">
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>1003</v>
@@ -4208,14 +4263,17 @@
       <c r="Y5" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="4" t="s">
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>1004</v>
@@ -4292,14 +4350,17 @@
       <c r="Y6" t="s">
         <v>114</v>
       </c>
-      <c r="Z6" s="4" t="s">
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>1005</v>
@@ -4376,14 +4437,17 @@
       <c r="Y7" t="s">
         <v>114</v>
       </c>
-      <c r="Z7" s="4" t="s">
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>1006</v>
@@ -4460,14 +4524,17 @@
       <c r="Y8" t="s">
         <v>114</v>
       </c>
-      <c r="Z8" s="4" t="s">
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>1007</v>
@@ -4544,14 +4611,17 @@
       <c r="Y9" t="s">
         <v>114</v>
       </c>
-      <c r="Z9" s="4" t="s">
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>1008</v>
@@ -4628,14 +4698,17 @@
       <c r="Y10" t="s">
         <v>114</v>
       </c>
-      <c r="Z10" s="4" t="s">
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>1009</v>
@@ -4712,14 +4785,17 @@
       <c r="Y11" t="s">
         <v>114</v>
       </c>
-      <c r="Z11" s="4" t="s">
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
         <f>ROW()-2+1000</f>
         <v>1010</v>
@@ -4796,14 +4872,17 @@
       <c r="Y12" t="s">
         <v>114</v>
       </c>
-      <c r="Z12" s="4" t="s">
+      <c r="Z12">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA12">
+      <c r="AB12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13">
         <f>ROW()-2+1000</f>
         <v>1011</v>
@@ -4880,10 +4959,13 @@
       <c r="Y13" t="s">
         <v>113</v>
       </c>
-      <c r="Z13" s="4" t="s">
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AA13">
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
@@ -4896,7 +4978,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A66AAA5-0C8D-4F8A-9A3B-33AFE45A42B1}">
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AB12"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -4905,11 +4987,11 @@
     <col min="7" max="7" width="19.75" customWidth="1"/>
     <col min="8" max="11" width="7.5" customWidth="1"/>
     <col min="12" max="12" width="8.125" customWidth="1"/>
-    <col min="13" max="25" width="6.75" customWidth="1"/>
-    <col min="26" max="26" width="25.125" customWidth="1"/>
+    <col min="13" max="26" width="6.75" customWidth="1"/>
+    <col min="27" max="27" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -4986,13 +5068,16 @@
         <v>111</v>
       </c>
       <c r="Z1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
         <f t="shared" ref="A2:A8" si="0">ROW()-2+2000</f>
         <v>2000</v>
@@ -5069,14 +5154,17 @@
       <c r="Y2" t="s">
         <v>114</v>
       </c>
-      <c r="Z2" s="4" t="s">
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>2001</v>
@@ -5153,14 +5241,17 @@
       <c r="Y3" t="s">
         <v>114</v>
       </c>
-      <c r="Z3" s="4" t="s">
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>2002</v>
@@ -5237,14 +5328,17 @@
       <c r="Y4" t="s">
         <v>114</v>
       </c>
-      <c r="Z4" s="4" t="s">
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>2003</v>
@@ -5321,14 +5415,17 @@
       <c r="Y5" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="4" t="s">
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <f>ROW()-2+2000</f>
         <v>2004</v>
@@ -5405,14 +5502,17 @@
       <c r="Y6" t="s">
         <v>114</v>
       </c>
-      <c r="Z6" s="4" t="s">
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
         <f>ROW()-2+2000</f>
         <v>2005</v>
@@ -5489,14 +5589,17 @@
       <c r="Y7" t="s">
         <v>114</v>
       </c>
-      <c r="Z7" s="4" t="s">
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>2006</v>
@@ -5573,14 +5676,17 @@
       <c r="Y8" t="s">
         <v>114</v>
       </c>
-      <c r="Z8" s="4" t="s">
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
         <f t="shared" ref="A9:A10" si="1">ROW()-2+2000</f>
         <v>2007</v>
@@ -5657,14 +5763,17 @@
       <c r="Y9" t="s">
         <v>114</v>
       </c>
-      <c r="Z9" s="4" t="s">
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
         <f t="shared" si="1"/>
         <v>2008</v>
@@ -5741,14 +5850,17 @@
       <c r="Y10" t="s">
         <v>114</v>
       </c>
-      <c r="Z10" s="4" t="s">
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:28" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <f>ROW()-2+2000</f>
         <v>2009</v>
@@ -5825,14 +5937,17 @@
       <c r="Y11" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="Z11" s="3" t="s">
+      <c r="Z11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AA11" s="2">
+      <c r="AB11" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
         <f>ROW()-2+2000</f>
         <v>2010</v>
@@ -5909,10 +6024,13 @@
       <c r="Y12" t="s">
         <v>141</v>
       </c>
-      <c r="Z12" s="4" t="s">
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AA12">
+      <c r="AB12">
         <v>1</v>
       </c>
     </row>
@@ -5925,7 +6043,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3990FE8C-49B4-4F17-805B-7287A7C6D5E2}">
-  <dimension ref="A1:AA9"/>
+  <dimension ref="A1:AB9"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -5934,11 +6052,11 @@
     <col min="7" max="7" width="19.75" customWidth="1"/>
     <col min="8" max="11" width="7.5" customWidth="1"/>
     <col min="12" max="12" width="8.125" customWidth="1"/>
-    <col min="13" max="25" width="6.75" customWidth="1"/>
-    <col min="26" max="26" width="25.125" customWidth="1"/>
+    <col min="13" max="26" width="6.75" customWidth="1"/>
+    <col min="27" max="27" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -6015,13 +6133,16 @@
         <v>111</v>
       </c>
       <c r="Z1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:28" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5">
         <f t="shared" ref="A2:A9" si="0">ROW()-2+3000</f>
         <v>3000</v>
@@ -6098,14 +6219,17 @@
       <c r="Y2" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="Z2" s="6" t="s">
+      <c r="Z2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AA2" s="5">
+      <c r="AB2" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:28" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
         <f t="shared" si="0"/>
         <v>3001</v>
@@ -6182,14 +6306,17 @@
       <c r="Y3" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="Z3" s="6" t="s">
+      <c r="Z3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AA3" s="5">
+      <c r="AB3" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:28" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
         <f t="shared" si="0"/>
         <v>3002</v>
@@ -6266,14 +6393,17 @@
       <c r="Y4" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="Z4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AA4" s="5">
+      <c r="AB4" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:28" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="5">
         <f t="shared" si="0"/>
         <v>3003</v>
@@ -6350,14 +6480,17 @@
       <c r="Y5" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="6" t="s">
+      <c r="Z5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AA5" s="5">
+      <c r="AB5" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:28" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>3004</v>
@@ -6434,14 +6567,17 @@
       <c r="Y6" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="Z6" s="6" t="s">
+      <c r="Z6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AA6" s="5">
+      <c r="AB6" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:28" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>3005</v>
@@ -6518,14 +6654,17 @@
       <c r="Y7" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="Z7" s="6" t="s">
+      <c r="Z7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AA7" s="5">
+      <c r="AB7" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:28" s="5" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>3006</v>
@@ -6602,14 +6741,17 @@
       <c r="Y8" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="Z8" s="6" t="s">
+      <c r="Z8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AA8" s="5">
+      <c r="AB8" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:28" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>3007</v>
@@ -6686,10 +6828,13 @@
       <c r="Y9" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="Z9" s="6" t="s">
+      <c r="Z9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="AA9" s="5">
+      <c r="AB9" s="5">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C0C8B0-FC44-4D2D-8FBE-0E0F3CDB8E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377E1E1E-538B-458D-AF6C-0121AF6E9173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2325" yWindow="1065" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="212">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -2264,6 +2264,22 @@
   </si>
   <si>
     <t>ContestBGMSelectHall</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>h109</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>t109</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>h209</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>t209</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3826,6 +3842,1071 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B615D1EB-7EB0-40A6-B71A-0773034D7CD2}">
+  <dimension ref="A1:AB12"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="3" max="3" width="13.25" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="6" width="20.625" customWidth="1"/>
+    <col min="7" max="7" width="19.75" customWidth="1"/>
+    <col min="8" max="11" width="7.5" customWidth="1"/>
+    <col min="12" max="12" width="8.125" customWidth="1"/>
+    <col min="13" max="26" width="6.75" customWidth="1"/>
+    <col min="27" max="27" width="25.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <f t="shared" ref="A2:A12" si="0">ROW()-2+1000</f>
+        <v>1000</v>
+      </c>
+      <c r="B2">
+        <v>20000</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>12</v>
+      </c>
+      <c r="K2">
+        <v>31</v>
+      </c>
+      <c r="L2">
+        <v>100</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>99</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>2</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2" t="s">
+        <v>165</v>
+      </c>
+      <c r="X2" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <f t="shared" si="0"/>
+        <v>1001</v>
+      </c>
+      <c r="B3">
+        <v>20900</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>31</v>
+      </c>
+      <c r="L3">
+        <v>100</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>99</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>2</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3" t="s">
+        <v>172</v>
+      </c>
+      <c r="X3" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z3">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <f t="shared" si="0"/>
+        <v>1002</v>
+      </c>
+      <c r="B4">
+        <v>20100</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <v>31</v>
+      </c>
+      <c r="L4">
+        <v>200</v>
+      </c>
+      <c r="M4">
+        <v>10</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4">
+        <v>2</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>99</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>3</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4" t="s">
+        <v>165</v>
+      </c>
+      <c r="X4" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>1003</v>
+      </c>
+      <c r="B5">
+        <v>20200</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>31</v>
+      </c>
+      <c r="L5">
+        <v>300</v>
+      </c>
+      <c r="M5">
+        <v>10</v>
+      </c>
+      <c r="N5">
+        <v>5</v>
+      </c>
+      <c r="O5">
+        <v>2</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>99</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>3</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5" t="s">
+        <v>165</v>
+      </c>
+      <c r="X5" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>1004</v>
+      </c>
+      <c r="B6">
+        <v>20800</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>31</v>
+      </c>
+      <c r="L6">
+        <v>500</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+      <c r="N6">
+        <v>10</v>
+      </c>
+      <c r="O6">
+        <v>3</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>99</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>3</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6" t="s">
+        <v>165</v>
+      </c>
+      <c r="X6" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>1005</v>
+      </c>
+      <c r="B7">
+        <v>20300</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>31</v>
+      </c>
+      <c r="L7">
+        <v>500</v>
+      </c>
+      <c r="M7">
+        <v>11</v>
+      </c>
+      <c r="N7">
+        <v>7</v>
+      </c>
+      <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>99</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>3</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7" t="s">
+        <v>165</v>
+      </c>
+      <c r="X7" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>1006</v>
+      </c>
+      <c r="B8">
+        <v>20400</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>31</v>
+      </c>
+      <c r="L8">
+        <v>700</v>
+      </c>
+      <c r="M8">
+        <v>11</v>
+      </c>
+      <c r="N8">
+        <v>10</v>
+      </c>
+      <c r="O8">
+        <v>4</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>99</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>3</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8" t="s">
+        <v>165</v>
+      </c>
+      <c r="X8" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>1007</v>
+      </c>
+      <c r="B9">
+        <v>20500</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+      <c r="J9">
+        <v>12</v>
+      </c>
+      <c r="K9">
+        <v>31</v>
+      </c>
+      <c r="L9">
+        <v>1500</v>
+      </c>
+      <c r="M9">
+        <v>12</v>
+      </c>
+      <c r="N9">
+        <v>10</v>
+      </c>
+      <c r="O9">
+        <v>5</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>99</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>3</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9" t="s">
+        <v>165</v>
+      </c>
+      <c r="X9" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>1008</v>
+      </c>
+      <c r="B10">
+        <v>20600</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>149</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10">
+        <v>12</v>
+      </c>
+      <c r="K10">
+        <v>31</v>
+      </c>
+      <c r="L10">
+        <v>1500</v>
+      </c>
+      <c r="M10">
+        <v>13</v>
+      </c>
+      <c r="N10">
+        <v>15</v>
+      </c>
+      <c r="O10">
+        <v>4</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>99</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>3</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10" t="s">
+        <v>165</v>
+      </c>
+      <c r="X10" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>1009</v>
+      </c>
+      <c r="B11">
+        <v>20700</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>5</v>
+      </c>
+      <c r="J11">
+        <v>12</v>
+      </c>
+      <c r="K11">
+        <v>31</v>
+      </c>
+      <c r="L11">
+        <v>3000</v>
+      </c>
+      <c r="M11">
+        <v>13</v>
+      </c>
+      <c r="N11">
+        <v>18</v>
+      </c>
+      <c r="O11">
+        <v>5</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>99</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>5</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11" t="s">
+        <v>165</v>
+      </c>
+      <c r="X11" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>1010</v>
+      </c>
+      <c r="B12">
+        <v>2000</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>12</v>
+      </c>
+      <c r="K12">
+        <v>31</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>200</v>
+      </c>
+      <c r="N12">
+        <v>12</v>
+      </c>
+      <c r="O12">
+        <v>5</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>99</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>4</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12" t="s">
+        <v>208</v>
+      </c>
+      <c r="X12" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB12">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A66AAA5-0C8D-4F8A-9A3B-33AFE45A42B1}">
   <dimension ref="A1:AB13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -3927,1159 +5008,7 @@
     </row>
     <row r="2" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A11" si="0">ROW()-2+1000</f>
-        <v>1000</v>
-      </c>
-      <c r="B2">
-        <v>20000</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>12</v>
-      </c>
-      <c r="K2">
-        <v>31</v>
-      </c>
-      <c r="L2">
-        <v>100</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>99</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>2</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2" t="s">
-        <v>165</v>
-      </c>
-      <c r="X2" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z2">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3">
-        <f t="shared" si="0"/>
-        <v>1001</v>
-      </c>
-      <c r="B3">
-        <v>20900</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E3" t="s">
-        <v>155</v>
-      </c>
-      <c r="F3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>31</v>
-      </c>
-      <c r="L3">
-        <v>100</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>99</v>
-      </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>2</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3" t="s">
-        <v>172</v>
-      </c>
-      <c r="X3" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4">
-        <f t="shared" si="0"/>
-        <v>1002</v>
-      </c>
-      <c r="B4">
-        <v>20100</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <v>31</v>
-      </c>
-      <c r="L4">
-        <v>200</v>
-      </c>
-      <c r="M4">
-        <v>10</v>
-      </c>
-      <c r="N4">
-        <v>3</v>
-      </c>
-      <c r="O4">
-        <v>2</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-      <c r="Q4">
-        <v>99</v>
-      </c>
-      <c r="R4">
-        <v>1</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>3</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4" t="s">
-        <v>165</v>
-      </c>
-      <c r="X4" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z4">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5">
-        <f t="shared" si="0"/>
-        <v>1003</v>
-      </c>
-      <c r="B5">
-        <v>20200</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>12</v>
-      </c>
-      <c r="K5">
-        <v>31</v>
-      </c>
-      <c r="L5">
-        <v>300</v>
-      </c>
-      <c r="M5">
-        <v>10</v>
-      </c>
-      <c r="N5">
-        <v>5</v>
-      </c>
-      <c r="O5">
-        <v>2</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>99</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>3</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5" t="s">
-        <v>165</v>
-      </c>
-      <c r="X5" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z5">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6">
-        <f t="shared" si="0"/>
-        <v>1004</v>
-      </c>
-      <c r="B6">
-        <v>20800</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E6" t="s">
-        <v>163</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>31</v>
-      </c>
-      <c r="L6">
-        <v>500</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
-      </c>
-      <c r="N6">
-        <v>10</v>
-      </c>
-      <c r="O6">
-        <v>3</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-      <c r="Q6">
-        <v>99</v>
-      </c>
-      <c r="R6">
-        <v>1</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>3</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6" t="s">
-        <v>165</v>
-      </c>
-      <c r="X6" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z6">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7">
-        <f t="shared" si="0"/>
-        <v>1005</v>
-      </c>
-      <c r="B7">
-        <v>20300</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
-      <c r="K7">
-        <v>31</v>
-      </c>
-      <c r="L7">
-        <v>500</v>
-      </c>
-      <c r="M7">
-        <v>11</v>
-      </c>
-      <c r="N7">
-        <v>7</v>
-      </c>
-      <c r="O7">
-        <v>3</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7">
-        <v>99</v>
-      </c>
-      <c r="R7">
-        <v>1</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>3</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7" t="s">
-        <v>165</v>
-      </c>
-      <c r="X7" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z7">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8">
-        <f t="shared" si="0"/>
-        <v>1006</v>
-      </c>
-      <c r="B8">
-        <v>20400</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>4</v>
-      </c>
-      <c r="J8">
-        <v>12</v>
-      </c>
-      <c r="K8">
-        <v>31</v>
-      </c>
-      <c r="L8">
-        <v>700</v>
-      </c>
-      <c r="M8">
-        <v>11</v>
-      </c>
-      <c r="N8">
-        <v>10</v>
-      </c>
-      <c r="O8">
-        <v>4</v>
-      </c>
-      <c r="P8">
-        <v>1</v>
-      </c>
-      <c r="Q8">
-        <v>99</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>3</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8" t="s">
-        <v>165</v>
-      </c>
-      <c r="X8" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z8">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9">
-        <f t="shared" si="0"/>
-        <v>1007</v>
-      </c>
-      <c r="B9">
-        <v>30400</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>3</v>
-      </c>
-      <c r="J9">
-        <v>12</v>
-      </c>
-      <c r="K9">
-        <v>31</v>
-      </c>
-      <c r="L9">
-        <v>1000</v>
-      </c>
-      <c r="M9">
-        <v>11</v>
-      </c>
-      <c r="N9">
-        <v>10</v>
-      </c>
-      <c r="O9">
-        <v>4</v>
-      </c>
-      <c r="P9">
-        <v>1</v>
-      </c>
-      <c r="Q9">
-        <v>99</v>
-      </c>
-      <c r="R9">
-        <v>1</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>3</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9" t="s">
-        <v>165</v>
-      </c>
-      <c r="X9" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z9">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10">
-        <f t="shared" si="0"/>
-        <v>1008</v>
-      </c>
-      <c r="B10">
-        <v>20500</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" t="s">
-        <v>100</v>
-      </c>
-      <c r="F10" t="s">
-        <v>100</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>4</v>
-      </c>
-      <c r="J10">
-        <v>12</v>
-      </c>
-      <c r="K10">
-        <v>31</v>
-      </c>
-      <c r="L10">
-        <v>1500</v>
-      </c>
-      <c r="M10">
-        <v>12</v>
-      </c>
-      <c r="N10">
-        <v>10</v>
-      </c>
-      <c r="O10">
-        <v>5</v>
-      </c>
-      <c r="P10">
-        <v>1</v>
-      </c>
-      <c r="Q10">
-        <v>99</v>
-      </c>
-      <c r="R10">
-        <v>1</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>3</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10" t="s">
-        <v>165</v>
-      </c>
-      <c r="X10" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z10">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11">
-        <f t="shared" si="0"/>
-        <v>1009</v>
-      </c>
-      <c r="B11">
-        <v>20600</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" t="s">
-        <v>149</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>3</v>
-      </c>
-      <c r="J11">
-        <v>12</v>
-      </c>
-      <c r="K11">
-        <v>31</v>
-      </c>
-      <c r="L11">
-        <v>1500</v>
-      </c>
-      <c r="M11">
-        <v>13</v>
-      </c>
-      <c r="N11">
-        <v>15</v>
-      </c>
-      <c r="O11">
-        <v>4</v>
-      </c>
-      <c r="P11">
-        <v>1</v>
-      </c>
-      <c r="Q11">
-        <v>99</v>
-      </c>
-      <c r="R11">
-        <v>1</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>3</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11" t="s">
-        <v>165</v>
-      </c>
-      <c r="X11" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z11">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12">
-        <f>ROW()-2+1000</f>
-        <v>1010</v>
-      </c>
-      <c r="B12">
-        <v>20700</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" t="s">
-        <v>153</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>5</v>
-      </c>
-      <c r="J12">
-        <v>12</v>
-      </c>
-      <c r="K12">
-        <v>31</v>
-      </c>
-      <c r="L12">
-        <v>3000</v>
-      </c>
-      <c r="M12">
-        <v>13</v>
-      </c>
-      <c r="N12">
-        <v>18</v>
-      </c>
-      <c r="O12">
-        <v>5</v>
-      </c>
-      <c r="P12">
-        <v>1</v>
-      </c>
-      <c r="Q12">
-        <v>99</v>
-      </c>
-      <c r="R12">
-        <v>1</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>5</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12" t="s">
-        <v>165</v>
-      </c>
-      <c r="X12" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z12">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13">
-        <f>ROW()-2+1000</f>
-        <v>1011</v>
-      </c>
-      <c r="B13">
-        <v>2000</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" t="s">
-        <v>136</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>5</v>
-      </c>
-      <c r="J13">
-        <v>12</v>
-      </c>
-      <c r="K13">
-        <v>31</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>200</v>
-      </c>
-      <c r="N13">
-        <v>12</v>
-      </c>
-      <c r="O13">
-        <v>5</v>
-      </c>
-      <c r="P13">
-        <v>1</v>
-      </c>
-      <c r="Q13">
-        <v>99</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>4</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13" t="s">
-        <v>165</v>
-      </c>
-      <c r="X13" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB13">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A66AAA5-0C8D-4F8A-9A3B-33AFE45A42B1}">
-  <dimension ref="A1:AB12"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="3" max="3" width="13.25" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="6" width="20.625" customWidth="1"/>
-    <col min="7" max="7" width="19.75" customWidth="1"/>
-    <col min="8" max="11" width="7.5" customWidth="1"/>
-    <col min="12" max="12" width="8.125" customWidth="1"/>
-    <col min="13" max="26" width="6.75" customWidth="1"/>
-    <col min="27" max="27" width="25.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2">
-        <f t="shared" ref="A2:A8" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A2:A9" si="0">ROW()-2+2000</f>
         <v>2000</v>
       </c>
       <c r="B2">
@@ -5427,32 +5356,32 @@
     </row>
     <row r="6" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
-        <f>ROW()-2+2000</f>
+        <f t="shared" si="0"/>
         <v>2004</v>
       </c>
       <c r="B6">
-        <v>30500</v>
+        <v>30400</v>
       </c>
       <c r="C6" t="s">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" t="s">
-        <v>85</v>
+        <v>64</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>189</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>12</v>
@@ -5461,13 +5390,13 @@
         <v>31</v>
       </c>
       <c r="L6">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N6">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>4</v>
@@ -5518,28 +5447,28 @@
         <v>2005</v>
       </c>
       <c r="B7">
-        <v>40300</v>
+        <v>30500</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="F7" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>12</v>
@@ -5548,16 +5477,16 @@
         <v>31</v>
       </c>
       <c r="L7">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="M7">
         <v>21</v>
       </c>
       <c r="N7">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P7">
         <v>1</v>
@@ -5581,10 +5510,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="X7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Y7" t="s">
         <v>114</v>
@@ -5601,32 +5530,32 @@
     </row>
     <row r="8" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+2000</f>
         <v>2006</v>
       </c>
       <c r="B8">
-        <v>30600</v>
+        <v>40300</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>197</v>
+        <v>98</v>
+      </c>
+      <c r="F8" t="s">
+        <v>98</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8">
         <v>12</v>
@@ -5635,16 +5564,16 @@
         <v>31</v>
       </c>
       <c r="L8">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="M8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N8">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P8">
         <v>1</v>
@@ -5659,7 +5588,7 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U8">
         <v>0</v>
@@ -5668,10 +5597,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="X8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y8" t="s">
         <v>114</v>
@@ -5688,32 +5617,32 @@
     </row>
     <row r="9" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
-        <f t="shared" ref="A9:A10" si="1">ROW()-2+2000</f>
+        <f t="shared" si="0"/>
         <v>2007</v>
       </c>
       <c r="B9">
-        <v>10600</v>
+        <v>30600</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
-      </c>
-      <c r="F9" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>197</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J9">
         <v>12</v>
@@ -5722,19 +5651,19 @@
         <v>31</v>
       </c>
       <c r="L9">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="M9">
         <v>22</v>
       </c>
       <c r="N9">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="O9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9">
         <v>99</v>
@@ -5746,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>0</v>
@@ -5775,26 +5704,26 @@
     </row>
     <row r="10" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A10:A11" si="1">ROW()-2+2000</f>
         <v>2008</v>
       </c>
       <c r="B10">
-        <v>10700</v>
+        <v>10600</v>
       </c>
       <c r="C10" t="s">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>198</v>
+        <v>84</v>
+      </c>
+      <c r="F10" t="s">
+        <v>84</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5809,16 +5738,16 @@
         <v>31</v>
       </c>
       <c r="L10">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="M10">
         <v>22</v>
       </c>
       <c r="N10">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -5833,7 +5762,7 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -5860,177 +5789,264 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="2">
-        <f>ROW()-2+2000</f>
+    <row r="11" spans="1:28" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <f t="shared" si="1"/>
         <v>2009</v>
       </c>
-      <c r="B11" s="2">
-        <v>30800</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
+      <c r="B11">
+        <v>10700</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>5</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11">
         <v>12</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11">
         <v>31</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11">
         <v>3000</v>
       </c>
-      <c r="M11" s="2">
-        <v>9999</v>
-      </c>
-      <c r="N11" s="2">
-        <v>25</v>
-      </c>
-      <c r="O11" s="2">
-        <v>3</v>
-      </c>
-      <c r="P11" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="2">
+      <c r="M11">
+        <v>22</v>
+      </c>
+      <c r="N11">
+        <v>30</v>
+      </c>
+      <c r="O11">
+        <v>5</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
         <v>99</v>
       </c>
-      <c r="R11" s="2">
-        <v>1</v>
-      </c>
-      <c r="S11" s="2">
-        <v>0</v>
-      </c>
-      <c r="T11" s="2">
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
         <v>5</v>
       </c>
-      <c r="U11" s="2">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2">
-        <v>0</v>
-      </c>
-      <c r="W11" s="2" t="s">
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11" t="s">
         <v>166</v>
       </c>
-      <c r="X11" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y11" s="2" t="s">
+      <c r="X11" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y11" t="s">
         <v>114</v>
       </c>
-      <c r="Z11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="3" t="s">
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AB11" s="2">
+      <c r="AB11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12">
+    <row r="12" spans="1:28" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="2">
         <f>ROW()-2+2000</f>
         <v>2010</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
+        <v>30800</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>5</v>
+      </c>
+      <c r="J12" s="2">
+        <v>12</v>
+      </c>
+      <c r="K12" s="2">
+        <v>31</v>
+      </c>
+      <c r="L12" s="2">
         <v>3000</v>
       </c>
-      <c r="C12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="M12" s="2">
+        <v>9999</v>
+      </c>
+      <c r="N12" s="2">
+        <v>25</v>
+      </c>
+      <c r="O12" s="2">
+        <v>3</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>99</v>
+      </c>
+      <c r="R12" s="2">
+        <v>1</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2">
+        <v>5</v>
+      </c>
+      <c r="U12" s="2">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2">
+        <v>0</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <f>ROW()-2+2000</f>
+        <v>2011</v>
+      </c>
+      <c r="B13">
+        <v>3000</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
         <v>46</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" t="s">
         <v>132</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F13" t="s">
         <v>132</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>5</v>
       </c>
-      <c r="J12">
+      <c r="J13">
         <v>12</v>
       </c>
-      <c r="K12">
+      <c r="K13">
         <v>31</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>300</v>
       </c>
-      <c r="N12">
+      <c r="N13">
         <v>18</v>
       </c>
-      <c r="O12">
+      <c r="O13">
         <v>5</v>
       </c>
-      <c r="P12">
-        <v>1</v>
-      </c>
-      <c r="Q12">
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
         <v>99</v>
       </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
         <v>4</v>
       </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12" t="s">
-        <v>166</v>
-      </c>
-      <c r="X12" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y12" t="s">
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13" t="s">
+        <v>210</v>
+      </c>
+      <c r="X13" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y13" t="s">
         <v>141</v>
       </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="4" t="s">
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377E1E1E-538B-458D-AF6C-0121AF6E9173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE50CC8-EF41-4B70-909D-9118849D3DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2295" yWindow="825" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE50CC8-EF41-4B70-909D-9118849D3DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A041D4-9BCF-421D-B8F6-409EB8AA3CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="825" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3240" yWindow="1110" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -6005,7 +6005,7 @@
         <v>300</v>
       </c>
       <c r="N13">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O13">
         <v>5</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A041D4-9BCF-421D-B8F6-409EB8AA3CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383165E4-4423-4EE8-8A0D-EB3A9BC25EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="1110" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2610" yWindow="1110" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383165E4-4423-4EE8-8A0D-EB3A9BC25EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B940CD-E077-4937-8315-99741A4FED9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="1110" windowWidth="25560" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B940CD-E077-4937-8315-99741A4FED9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A25A6F1F-A3BA-4BCF-9FD2-8ABD9DBD8739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -537,48 +537,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>自由課題
-貴族ベオルブ家が、ディナー招待客をもてなすお菓子を、毎年募集しています。
-種類は問いません。華やかなお菓子を希望。</t>
-    <rPh sb="0" eb="4">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>キゾク</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>イエ</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>ショウタイキャク</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>マイトシ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>シュルイ</t>
-    </rPh>
-    <rPh sb="45" eb="46">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>キボウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>チョコレート限定
 とろける、夢見るチョコレートのコンテスト
 はたして、夢を見せてくれるのか・・？</t>
@@ -1826,16 +1784,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>秋のお菓子コンテスト</t>
-    <rPh sb="0" eb="1">
-      <t>アキ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>カシ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>春のおかし大祭典</t>
     <rPh sb="0" eb="1">
       <t>ハル</t>
@@ -2121,17 +2069,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>秋のお菓子
-コンテスト</t>
-    <rPh sb="0" eb="1">
-      <t>アキ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>カシ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>アデュルティ
 ガトー</t>
     <phoneticPr fontId="2"/>
@@ -2280,6 +2217,72 @@
   </si>
   <si>
     <t>t209</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自由課題※飲み物は対象外
+貴族ベオルブ家が、ディナー招待客をもてなすお菓子を、毎年募集しています。
+種類は問いません。華やかなお菓子を希望。</t>
+    <rPh sb="0" eb="4">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>タイショウガイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キゾク</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>イエ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>ショウタイキャク</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>マイトシ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>キボウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>オータムリーヴス鐘の音</t>
+    <rPh sb="8" eb="9">
+      <t>カネ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>オータムリーヴス
+鐘の音</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2720,7 +2723,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -2765,22 +2768,22 @@
         <v>28</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="W1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="Z1" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -2801,7 +2804,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -2810,7 +2813,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -2858,13 +2861,13 @@
         <v>0</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y2" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="Z2" s="2">
         <v>0</v>
@@ -2894,10 +2897,10 @@
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -2945,13 +2948,13 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2981,7 +2984,7 @@
         <v>92</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>93</v>
@@ -3032,19 +3035,19 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB4">
         <v>0</v>
@@ -3068,10 +3071,10 @@
         <v>76</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -3119,13 +3122,13 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -3158,7 +3161,7 @@
         <v>88</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>94</v>
+        <v>209</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -3206,13 +3209,13 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="X6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -3242,10 +3245,10 @@
         <v>89</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -3293,13 +3296,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -3329,10 +3332,10 @@
         <v>90</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -3380,13 +3383,13 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -3410,16 +3413,16 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3467,13 +3470,13 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="X9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -3503,10 +3506,10 @@
         <v>73</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -3554,13 +3557,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -3590,10 +3593,10 @@
         <v>83</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -3641,13 +3644,13 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -3677,10 +3680,10 @@
         <v>74</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -3728,13 +3731,13 @@
         <v>0</v>
       </c>
       <c r="W12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -3764,10 +3767,10 @@
         <v>29</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -3815,13 +3818,13 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="X13" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y13" t="s">
         <v>112</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>113</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -3872,7 +3875,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -3917,22 +3920,22 @@
         <v>28</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="W1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="Z1" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -3959,10 +3962,10 @@
         <v>65</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -4010,13 +4013,13 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Y2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z2">
         <v>1</v>
@@ -4040,16 +4043,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4064,7 +4067,7 @@
         <v>31</v>
       </c>
       <c r="L3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -4073,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -4097,13 +4100,13 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="X3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Y3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z3">
         <v>2</v>
@@ -4130,10 +4133,10 @@
         <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>66</v>
@@ -4151,7 +4154,7 @@
         <v>31</v>
       </c>
       <c r="L4">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -4184,13 +4187,13 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Y4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z4">
         <v>1</v>
@@ -4217,13 +4220,13 @@
         <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -4238,7 +4241,7 @@
         <v>31</v>
       </c>
       <c r="L5">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -4271,13 +4274,13 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Y5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z5">
         <v>1</v>
@@ -4301,16 +4304,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="E6" t="s">
-        <v>163</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>151</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -4358,13 +4361,13 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Y6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -4394,10 +4397,10 @@
         <v>67</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -4445,13 +4448,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Y7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z7">
         <v>1</v>
@@ -4532,13 +4535,13 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Y8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z8">
         <v>1</v>
@@ -4565,13 +4568,13 @@
         <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -4619,13 +4622,13 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Y9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z9">
         <v>1</v>
@@ -4652,13 +4655,13 @@
         <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -4706,13 +4709,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Y10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z10">
         <v>1</v>
@@ -4739,13 +4742,13 @@
         <v>45</v>
       </c>
       <c r="E11" t="s">
+        <v>152</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -4793,13 +4796,13 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Y11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z11">
         <v>1</v>
@@ -4826,13 +4829,13 @@
         <v>37</v>
       </c>
       <c r="E12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -4880,13 +4883,13 @@
         <v>0</v>
       </c>
       <c r="W12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="X12" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Y12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -4937,7 +4940,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -4982,22 +4985,22 @@
         <v>28</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="W1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="Z1" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -5024,10 +5027,10 @@
         <v>75</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -5048,7 +5051,7 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O2">
         <v>2</v>
@@ -5075,13 +5078,13 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="X2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Y2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -5105,16 +5108,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E3" t="s">
-        <v>158</v>
+        <v>210</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5135,7 +5138,7 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O3">
         <v>2</v>
@@ -5162,13 +5165,13 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="X3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Y3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -5198,10 +5201,10 @@
         <v>82</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -5249,13 +5252,13 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="X4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Y4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -5285,10 +5288,10 @@
         <v>87</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -5336,13 +5339,13 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="X5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Y5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -5372,10 +5375,10 @@
         <v>64</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -5423,13 +5426,13 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="X6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Y6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -5462,7 +5465,7 @@
         <v>85</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -5510,13 +5513,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="X7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Y7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -5543,13 +5546,13 @@
         <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -5597,13 +5600,13 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="X8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Y8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -5633,10 +5636,10 @@
         <v>86</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -5684,13 +5687,13 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="X9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Y9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -5723,7 +5726,7 @@
         <v>84</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5771,13 +5774,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="X10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Y10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -5807,10 +5810,10 @@
         <v>91</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -5858,13 +5861,13 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="X11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Y11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -5888,16 +5891,16 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H12" s="2">
         <v>0</v>
@@ -5945,13 +5948,13 @@
         <v>0</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z12" s="2">
         <v>0</v>
@@ -5978,13 +5981,13 @@
         <v>46</v>
       </c>
       <c r="E13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -6032,13 +6035,13 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="X13" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Y13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -6089,7 +6092,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -6134,22 +6137,22 @@
         <v>28</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="W1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="Z1" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -6179,7 +6182,7 @@
         <v>70</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H2" s="5">
         <v>0</v>
@@ -6227,13 +6230,13 @@
         <v>0</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Y2" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z2" s="5">
         <v>0</v>
@@ -6263,10 +6266,10 @@
         <v>81</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
@@ -6314,13 +6317,13 @@
         <v>0</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Y3" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z3" s="5">
         <v>0</v>
@@ -6350,7 +6353,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>71</v>
@@ -6401,13 +6404,13 @@
         <v>0</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Y4" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z4" s="5">
         <v>0</v>
@@ -6434,13 +6437,13 @@
         <v>60</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -6488,13 +6491,13 @@
         <v>0</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Y5" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z5" s="5">
         <v>0</v>
@@ -6575,13 +6578,13 @@
         <v>0</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Y6" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z6" s="5">
         <v>0</v>
@@ -6611,10 +6614,10 @@
         <v>79</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H7" s="5">
         <v>0</v>
@@ -6662,13 +6665,13 @@
         <v>0</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Y7" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z7" s="5">
         <v>0</v>
@@ -6695,13 +6698,13 @@
         <v>63</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>
@@ -6749,13 +6752,13 @@
         <v>0</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Y8" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Z8" s="5">
         <v>0</v>
@@ -6782,13 +6785,13 @@
         <v>47</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H9" s="5">
         <v>0</v>
@@ -6836,13 +6839,13 @@
         <v>0</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Y9" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Z9" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A25A6F1F-A3BA-4BCF-9FD2-8ABD9DBD8739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D476155-78BC-426C-B585-88062B546F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1560" yWindow="1245" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D476155-78BC-426C-B585-88062B546F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBD9DA1-BCF6-4C5F-ABCA-382C448BF87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1245" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2295" yWindow="690" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -1798,39 +1798,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>お花をモチーフにしたお菓子限定
-お花をメインに使った華やかなお菓子を募集しています。
-クッキー・チョコレート・ケーキ・チーズケーキ限定です。</t>
-    <rPh sb="1" eb="2">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>ゲンテイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ケーキ限定
 秋の大精霊様が年に一度開くケーキコンテストです。
 自信のある豪華なケーキを見せてください！</t>
@@ -2283,6 +2250,38 @@
   <si>
     <t>オータムリーヴス
 鐘の音</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お花をモチーフにしたお菓子限定
+お花をメインに使った華やかなお菓子を募集しています。クッキー・チョコレート・ケーキ・チーズケーキ限定。</t>
+    <rPh sb="1" eb="2">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ゲンテイ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2723,7 +2722,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -2783,7 +2782,7 @@
         <v>110</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -2831,7 +2830,7 @@
         <v>5000</v>
       </c>
       <c r="M2" s="2">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N2" s="2">
         <v>50</v>
@@ -2897,7 +2896,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>105</v>
@@ -2984,7 +2983,7 @@
         <v>92</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>93</v>
@@ -3071,7 +3070,7 @@
         <v>76</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>95</v>
@@ -3161,7 +3160,7 @@
         <v>88</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -3245,7 +3244,7 @@
         <v>89</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>115</v>
@@ -3332,7 +3331,7 @@
         <v>90</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>116</v>
@@ -3422,7 +3421,7 @@
         <v>157</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3506,7 +3505,7 @@
         <v>73</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>138</v>
@@ -3593,7 +3592,7 @@
         <v>83</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>125</v>
@@ -3680,7 +3679,7 @@
         <v>74</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>143</v>
@@ -3767,7 +3766,7 @@
         <v>29</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>134</v>
@@ -3818,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="X13" t="s">
         <v>111</v>
@@ -3875,7 +3874,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -3935,7 +3934,7 @@
         <v>110</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -3962,7 +3961,7 @@
         <v>65</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>123</v>
@@ -4013,10 +4012,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y2" t="s">
         <v>113</v>
@@ -4052,7 +4051,7 @@
         <v>154</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4100,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
+        <v>169</v>
+      </c>
+      <c r="X3" t="s">
         <v>170</v>
-      </c>
-      <c r="X3" t="s">
-        <v>171</v>
       </c>
       <c r="Y3" t="s">
         <v>113</v>
@@ -4136,7 +4135,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>66</v>
@@ -4187,10 +4186,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y4" t="s">
         <v>113</v>
@@ -4223,7 +4222,7 @@
         <v>98</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>137</v>
@@ -4274,10 +4273,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y5" t="s">
         <v>113</v>
@@ -4307,10 +4306,10 @@
         <v>149</v>
       </c>
       <c r="E6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>150</v>
@@ -4361,10 +4360,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y6" t="s">
         <v>113</v>
@@ -4397,7 +4396,7 @@
         <v>67</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>142</v>
@@ -4448,10 +4447,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y7" t="s">
         <v>113</v>
@@ -4535,10 +4534,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y8" t="s">
         <v>113</v>
@@ -4622,10 +4621,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y9" t="s">
         <v>113</v>
@@ -4658,7 +4657,7 @@
         <v>148</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>102</v>
@@ -4709,10 +4708,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y10" t="s">
         <v>113</v>
@@ -4745,7 +4744,7 @@
         <v>152</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>153</v>
@@ -4796,10 +4795,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y11" t="s">
         <v>113</v>
@@ -4832,7 +4831,7 @@
         <v>135</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>139</v>
@@ -4883,10 +4882,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="s">
+        <v>204</v>
+      </c>
+      <c r="X12" t="s">
         <v>205</v>
-      </c>
-      <c r="X12" t="s">
-        <v>206</v>
       </c>
       <c r="Y12" t="s">
         <v>112</v>
@@ -4940,7 +4939,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -5000,7 +4999,7 @@
         <v>110</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -5027,7 +5026,7 @@
         <v>75</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>96</v>
@@ -5078,10 +5077,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y2" t="s">
         <v>113</v>
@@ -5111,13 +5110,13 @@
         <v>156</v>
       </c>
       <c r="E3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>211</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5165,10 +5164,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y3" t="s">
         <v>113</v>
@@ -5201,7 +5200,7 @@
         <v>82</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>124</v>
@@ -5252,10 +5251,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y4" t="s">
         <v>113</v>
@@ -5288,7 +5287,7 @@
         <v>87</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>122</v>
@@ -5339,10 +5338,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y5" t="s">
         <v>113</v>
@@ -5375,7 +5374,7 @@
         <v>64</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>144</v>
@@ -5426,10 +5425,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y6" t="s">
         <v>113</v>
@@ -5513,10 +5512,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y7" t="s">
         <v>113</v>
@@ -5552,7 +5551,7 @@
         <v>97</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>159</v>
+        <v>211</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -5600,10 +5599,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="X8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y8" t="s">
         <v>113</v>
@@ -5636,7 +5635,7 @@
         <v>86</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>146</v>
@@ -5687,10 +5686,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y9" t="s">
         <v>113</v>
@@ -5726,7 +5725,7 @@
         <v>84</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5774,10 +5773,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y10" t="s">
         <v>113</v>
@@ -5810,7 +5809,7 @@
         <v>91</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>94</v>
@@ -5861,10 +5860,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y11" t="s">
         <v>113</v>
@@ -5948,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>114</v>
@@ -6035,10 +6034,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
+        <v>206</v>
+      </c>
+      <c r="X13" t="s">
         <v>207</v>
-      </c>
-      <c r="X13" t="s">
-        <v>208</v>
       </c>
       <c r="Y13" t="s">
         <v>140</v>
@@ -6092,7 +6091,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -6152,7 +6151,7 @@
         <v>110</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -6230,10 +6229,10 @@
         <v>0</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y2" s="5" t="s">
         <v>113</v>
@@ -6266,7 +6265,7 @@
         <v>81</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>119</v>
@@ -6317,10 +6316,10 @@
         <v>0</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y3" s="5" t="s">
         <v>113</v>
@@ -6353,7 +6352,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>71</v>
@@ -6404,10 +6403,10 @@
         <v>0</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y4" s="5" t="s">
         <v>113</v>
@@ -6440,7 +6439,7 @@
         <v>126</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>127</v>
@@ -6491,10 +6490,10 @@
         <v>0</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y5" s="5" t="s">
         <v>113</v>
@@ -6578,10 +6577,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y6" s="5" t="s">
         <v>113</v>
@@ -6614,7 +6613,7 @@
         <v>79</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>128</v>
@@ -6665,10 +6664,10 @@
         <v>0</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y7" s="5" t="s">
         <v>113</v>
@@ -6701,7 +6700,7 @@
         <v>120</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>129</v>
@@ -6752,10 +6751,10 @@
         <v>0</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y8" s="5" t="s">
         <v>113</v>
@@ -6788,7 +6787,7 @@
         <v>130</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>133</v>
@@ -6839,10 +6838,10 @@
         <v>0</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y9" s="5" t="s">
         <v>112</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBD9DA1-BCF6-4C5F-ABCA-382C448BF87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB5D5F4-BCEE-470D-885B-7BF3A9126FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="690" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -1287,42 +1287,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>◆アカデミー至高のお菓子の決定戦◆
-テーマ：自由課題
-優勝者には、特別なレシピを進呈します。至高の一品をお待ちしております！</t>
-    <rPh sb="6" eb="8">
-      <t>シコウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="13" eb="16">
-      <t>ケッテイセン</t>
-    </rPh>
-    <rPh sb="22" eb="26">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="27" eb="30">
-      <t>ユウショウシャ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>トクベツ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>シンテイ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>シコウ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>イッピン</t>
-    </rPh>
-    <rPh sb="53" eb="54">
-      <t>マ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>サマードリームスフェスティバル</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2281,6 +2245,36 @@
     </rPh>
     <rPh sb="64" eb="66">
       <t>ゲンテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆パティシエアカデミーの登竜門◆
+テーマ：自由課題
+優勝者には、特別なレシピを進呈します。至高の一品をお待ちしております！</t>
+    <rPh sb="12" eb="15">
+      <t>トウリュウモン</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>ユウショウシャ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>トクベツ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>シンテイ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>シコウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>イッピン</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>マ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2722,7 +2716,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -2782,7 +2776,7 @@
         <v>110</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -2803,7 +2797,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -2812,7 +2806,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -2896,7 +2890,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>105</v>
@@ -2983,7 +2977,7 @@
         <v>92</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>93</v>
@@ -3070,7 +3064,7 @@
         <v>76</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>95</v>
@@ -3160,7 +3154,7 @@
         <v>88</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -3208,7 +3202,7 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X6" t="s">
         <v>111</v>
@@ -3244,7 +3238,7 @@
         <v>89</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>115</v>
@@ -3268,7 +3262,7 @@
         <v>3</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O7">
         <v>3</v>
@@ -3331,7 +3325,7 @@
         <v>90</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>116</v>
@@ -3412,16 +3406,16 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3469,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X9" t="s">
         <v>111</v>
@@ -3505,10 +3499,10 @@
         <v>73</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -3592,7 +3586,7 @@
         <v>83</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>125</v>
@@ -3679,10 +3673,10 @@
         <v>74</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -3766,10 +3760,10 @@
         <v>29</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -3817,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="X13" t="s">
         <v>111</v>
@@ -3874,7 +3868,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -3934,7 +3928,7 @@
         <v>110</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -3961,7 +3955,7 @@
         <v>65</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>123</v>
@@ -4012,10 +4006,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y2" t="s">
         <v>113</v>
@@ -4042,16 +4036,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4099,10 +4093,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
+        <v>168</v>
+      </c>
+      <c r="X3" t="s">
         <v>169</v>
-      </c>
-      <c r="X3" t="s">
-        <v>170</v>
       </c>
       <c r="Y3" t="s">
         <v>113</v>
@@ -4135,7 +4129,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>66</v>
@@ -4186,10 +4180,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y4" t="s">
         <v>113</v>
@@ -4222,10 +4216,10 @@
         <v>98</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -4273,10 +4267,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y5" t="s">
         <v>113</v>
@@ -4303,16 +4297,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="E6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -4360,10 +4354,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y6" t="s">
         <v>113</v>
@@ -4396,10 +4390,10 @@
         <v>67</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -4447,10 +4441,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y7" t="s">
         <v>113</v>
@@ -4534,10 +4528,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y8" t="s">
         <v>113</v>
@@ -4621,10 +4615,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y9" t="s">
         <v>113</v>
@@ -4654,10 +4648,10 @@
         <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>102</v>
@@ -4708,10 +4702,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y10" t="s">
         <v>113</v>
@@ -4741,13 +4735,13 @@
         <v>45</v>
       </c>
       <c r="E11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>153</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -4795,10 +4789,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y11" t="s">
         <v>113</v>
@@ -4828,13 +4822,13 @@
         <v>37</v>
       </c>
       <c r="E12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -4882,10 +4876,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="s">
+        <v>203</v>
+      </c>
+      <c r="X12" t="s">
         <v>204</v>
-      </c>
-      <c r="X12" t="s">
-        <v>205</v>
       </c>
       <c r="Y12" t="s">
         <v>112</v>
@@ -4939,7 +4933,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -4999,7 +4993,7 @@
         <v>110</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -5026,7 +5020,7 @@
         <v>75</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>96</v>
@@ -5077,10 +5071,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y2" t="s">
         <v>113</v>
@@ -5107,16 +5101,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>210</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5164,10 +5158,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y3" t="s">
         <v>113</v>
@@ -5200,7 +5194,7 @@
         <v>82</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>124</v>
@@ -5251,10 +5245,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y4" t="s">
         <v>113</v>
@@ -5287,7 +5281,7 @@
         <v>87</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>122</v>
@@ -5338,10 +5332,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y5" t="s">
         <v>113</v>
@@ -5374,10 +5368,10 @@
         <v>64</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -5425,10 +5419,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y6" t="s">
         <v>113</v>
@@ -5464,7 +5458,7 @@
         <v>85</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -5512,10 +5506,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y7" t="s">
         <v>113</v>
@@ -5551,7 +5545,7 @@
         <v>97</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -5599,10 +5593,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y8" t="s">
         <v>113</v>
@@ -5635,10 +5629,10 @@
         <v>86</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -5686,10 +5680,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y9" t="s">
         <v>113</v>
@@ -5725,7 +5719,7 @@
         <v>84</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5773,10 +5767,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y10" t="s">
         <v>113</v>
@@ -5809,7 +5803,7 @@
         <v>91</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>94</v>
@@ -5860,10 +5854,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y11" t="s">
         <v>113</v>
@@ -5947,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>114</v>
@@ -5986,7 +5980,7 @@
         <v>131</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -6034,13 +6028,13 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
+        <v>205</v>
+      </c>
+      <c r="X13" t="s">
         <v>206</v>
       </c>
-      <c r="X13" t="s">
-        <v>207</v>
-      </c>
       <c r="Y13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -6091,7 +6085,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -6151,7 +6145,7 @@
         <v>110</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -6229,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y2" s="5" t="s">
         <v>113</v>
@@ -6265,7 +6259,7 @@
         <v>81</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>119</v>
@@ -6316,10 +6310,10 @@
         <v>0</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y3" s="5" t="s">
         <v>113</v>
@@ -6352,7 +6346,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>71</v>
@@ -6403,10 +6397,10 @@
         <v>0</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y4" s="5" t="s">
         <v>113</v>
@@ -6439,7 +6433,7 @@
         <v>126</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>127</v>
@@ -6490,10 +6484,10 @@
         <v>0</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y5" s="5" t="s">
         <v>113</v>
@@ -6577,10 +6571,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y6" s="5" t="s">
         <v>113</v>
@@ -6613,7 +6607,7 @@
         <v>79</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>128</v>
@@ -6664,10 +6658,10 @@
         <v>0</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y7" s="5" t="s">
         <v>113</v>
@@ -6700,7 +6694,7 @@
         <v>120</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>129</v>
@@ -6751,10 +6745,10 @@
         <v>0</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y8" s="5" t="s">
         <v>113</v>
@@ -6787,7 +6781,7 @@
         <v>130</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>133</v>
@@ -6838,10 +6832,10 @@
         <v>0</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y9" s="5" t="s">
         <v>112</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB5D5F4-BCEE-470D-885B-7BF3A9126FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BC026F-952F-4863-B9AA-E00DC00FEDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2580" yWindow="870" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="211">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -1385,10 +1385,6 @@
     <rPh sb="55" eb="56">
       <t>マ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>sound73</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2716,7 +2712,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -2776,7 +2772,7 @@
         <v>110</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -2806,7 +2802,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -2890,7 +2886,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>105</v>
@@ -2977,7 +2973,7 @@
         <v>92</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>93</v>
@@ -3064,7 +3060,7 @@
         <v>76</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>95</v>
@@ -3154,7 +3150,7 @@
         <v>88</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -3202,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="X6" t="s">
         <v>111</v>
@@ -3238,7 +3234,7 @@
         <v>89</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>115</v>
@@ -3325,7 +3321,7 @@
         <v>90</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>116</v>
@@ -3406,16 +3402,16 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3463,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="X9" t="s">
         <v>111</v>
@@ -3499,7 +3495,7 @@
         <v>73</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>137</v>
@@ -3586,7 +3582,7 @@
         <v>83</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>125</v>
@@ -3673,10 +3669,10 @@
         <v>74</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -3760,10 +3756,10 @@
         <v>29</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -3811,13 +3807,13 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="X13" t="s">
         <v>111</v>
       </c>
       <c r="Y13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -3868,7 +3864,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -3928,7 +3924,7 @@
         <v>110</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -3955,7 +3951,7 @@
         <v>65</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>123</v>
@@ -4006,10 +4002,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y2" t="s">
         <v>113</v>
@@ -4036,16 +4032,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4093,10 +4089,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
+        <v>167</v>
+      </c>
+      <c r="X3" t="s">
         <v>168</v>
-      </c>
-      <c r="X3" t="s">
-        <v>169</v>
       </c>
       <c r="Y3" t="s">
         <v>113</v>
@@ -4129,7 +4125,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>66</v>
@@ -4180,10 +4176,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y4" t="s">
         <v>113</v>
@@ -4216,7 +4212,7 @@
         <v>98</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>136</v>
@@ -4267,10 +4263,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y5" t="s">
         <v>113</v>
@@ -4297,16 +4293,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" t="s">
+        <v>158</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="E6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>149</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -4354,10 +4350,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y6" t="s">
         <v>113</v>
@@ -4390,10 +4386,10 @@
         <v>67</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -4441,10 +4437,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y7" t="s">
         <v>113</v>
@@ -4528,10 +4524,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y8" t="s">
         <v>113</v>
@@ -4615,10 +4611,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y9" t="s">
         <v>113</v>
@@ -4648,10 +4644,10 @@
         <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>102</v>
@@ -4702,10 +4698,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y10" t="s">
         <v>113</v>
@@ -4735,13 +4731,13 @@
         <v>45</v>
       </c>
       <c r="E11" t="s">
+        <v>150</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>152</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -4789,10 +4785,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y11" t="s">
         <v>113</v>
@@ -4825,7 +4821,7 @@
         <v>134</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>138</v>
@@ -4876,13 +4872,13 @@
         <v>0</v>
       </c>
       <c r="W12" t="s">
+        <v>202</v>
+      </c>
+      <c r="X12" t="s">
         <v>203</v>
       </c>
-      <c r="X12" t="s">
-        <v>204</v>
-      </c>
       <c r="Y12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -4933,7 +4929,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -4993,7 +4989,7 @@
         <v>110</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -5020,7 +5016,7 @@
         <v>75</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>96</v>
@@ -5071,10 +5067,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y2" t="s">
         <v>113</v>
@@ -5101,16 +5097,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>209</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5158,10 +5154,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y3" t="s">
         <v>113</v>
@@ -5194,7 +5190,7 @@
         <v>82</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>124</v>
@@ -5245,10 +5241,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y4" t="s">
         <v>113</v>
@@ -5281,7 +5277,7 @@
         <v>87</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>122</v>
@@ -5332,10 +5328,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y5" t="s">
         <v>113</v>
@@ -5368,10 +5364,10 @@
         <v>64</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -5419,10 +5415,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y6" t="s">
         <v>113</v>
@@ -5458,7 +5454,7 @@
         <v>85</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -5506,10 +5502,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y7" t="s">
         <v>113</v>
@@ -5545,7 +5541,7 @@
         <v>97</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -5593,10 +5589,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y8" t="s">
         <v>113</v>
@@ -5629,10 +5625,10 @@
         <v>86</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -5680,10 +5676,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y9" t="s">
         <v>113</v>
@@ -5719,7 +5715,7 @@
         <v>84</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5767,10 +5763,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y10" t="s">
         <v>113</v>
@@ -5803,7 +5799,7 @@
         <v>91</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>94</v>
@@ -5854,10 +5850,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y11" t="s">
         <v>113</v>
@@ -5941,7 +5937,7 @@
         <v>0</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>114</v>
@@ -5980,7 +5976,7 @@
         <v>131</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -6028,13 +6024,13 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
+        <v>204</v>
+      </c>
+      <c r="X13" t="s">
         <v>205</v>
       </c>
-      <c r="X13" t="s">
-        <v>206</v>
-      </c>
       <c r="Y13" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -6085,7 +6081,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -6145,7 +6141,7 @@
         <v>110</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -6223,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y2" s="5" t="s">
         <v>113</v>
@@ -6259,7 +6255,7 @@
         <v>81</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>119</v>
@@ -6310,10 +6306,10 @@
         <v>0</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y3" s="5" t="s">
         <v>113</v>
@@ -6346,7 +6342,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>71</v>
@@ -6397,10 +6393,10 @@
         <v>0</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y4" s="5" t="s">
         <v>113</v>
@@ -6433,7 +6429,7 @@
         <v>126</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>127</v>
@@ -6484,10 +6480,10 @@
         <v>0</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y5" s="5" t="s">
         <v>113</v>
@@ -6571,10 +6567,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y6" s="5" t="s">
         <v>113</v>
@@ -6607,7 +6603,7 @@
         <v>79</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>128</v>
@@ -6658,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y7" s="5" t="s">
         <v>113</v>
@@ -6694,7 +6690,7 @@
         <v>120</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>129</v>
@@ -6745,10 +6741,10 @@
         <v>0</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y8" s="5" t="s">
         <v>113</v>
@@ -6781,7 +6777,7 @@
         <v>130</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>133</v>
@@ -6832,10 +6828,10 @@
         <v>0</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y9" s="5" t="s">
         <v>112</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BC026F-952F-4863-B9AA-E00DC00FEDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40859256-3C10-478A-B1AD-A7A2154C6BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="870" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2685" yWindow="930" windowWidth="25485" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -329,24 +329,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ソーダ限定
-シュワシュワなソーダは、夏の定番！！
-おいしくてオシャレなソーダでトップを目指せ！</t>
-    <rPh sb="3" eb="5">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ナツ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>テイバン</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>メザ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>おみやげおかしコンテスト</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -355,60 +337,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>いちごのお菓子限定
-お菓子の主役といえば、やはりいちご..！
-いちご好きをうならせるおいしいお菓子を見せてくださいな♪</t>
-    <rPh sb="5" eb="7">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>シュヤク</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>クワイットスノウ</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>宇宙をテーマにしたお菓子
-宇宙・星にちなんだ、ロマンチックなお菓子を募集</t>
-    <rPh sb="0" eb="2">
-      <t>ウチュウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ウチュウ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ホシ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ボシュウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Or_Contest_100</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -426,28 +358,6 @@
   </si>
   <si>
     <t>フィナンシェ・バタ～ズカップ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ミルフイユ・ドゥ・パリ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ミルフイユ限定
-さくさくパリパリのおいしいミルフイユ限定のコンテスト。
-自信のあるミルフイユを見せてください。</t>
-    <rPh sb="5" eb="7">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>ミ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -510,114 +420,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ラスク限定
-ラスクのおいしさを決めるコンテスト
-お手軽で、小さなアンティーク市で食べるおやつとして募集します。</t>
-    <rPh sb="3" eb="5">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>テガル</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>チイ</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>イチ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ボシュウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>チョコレート限定
-とろける、夢見るチョコレートのコンテスト
-はたして、夢を見せてくれるのか・・？</t>
-    <rPh sb="6" eb="8">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ユメミ</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>ユメ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>フィナンシェ限定
-あたたかい出来立てフィナンシェを募集。
-各地のフィナンシェ好きが集まり、審査致します。</t>
-    <rPh sb="6" eb="8">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="14" eb="17">
-      <t>デキタ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>アツ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>シンサ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>イタ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>クレープ限定
-黒猫達も好むおいしくて甘いクレープを募集
-権威ある上流黒猫たちも注目しています♪</t>
-    <rPh sb="4" eb="6">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>クロネコ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>タチ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>コノ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>アマ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ケンイ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ジョウリュウ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>クロネコ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>チュウモク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>フェド・フルラージュ</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -643,125 +445,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>海をテーマにしたチョコレート
-美しい海を讃えるチョコレートを募集します。
-青や白、砂浜の色合い、波の表現.. 地球の海の美しさを表現してください。</t>
-    <rPh sb="0" eb="1">
-      <t>ウミ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ウツク</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ウミ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>タタ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>アオ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>スナハマ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>イロア</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>ナミ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>ヒョウゲン</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>チキュウ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>ウミ</t>
-    </rPh>
-    <rPh sb="60" eb="61">
-      <t>ウツク</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>ヒョウゲン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>魔法のお菓子限定
-魔法で仕上げた、一風変わったオシャレなお菓子を募集♪
-見慣れない不思議なお菓子だと高得点です！</t>
-    <rPh sb="0" eb="2">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="17" eb="20">
-      <t>イップウカ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ミナ</t>
-    </rPh>
-    <rPh sb="41" eb="44">
-      <t>フシギ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="50" eb="53">
-      <t>コウトクテン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ContestVictory</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ContestFightsCount</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>クッキー限定
-クッキーの初級コンテスト
-新米パティシエ達の登竜門。ゆけぃ！パティシエのたまごたちよ！！</t>
-    <rPh sb="4" eb="6">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ショキュウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>シンマイ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>タチ</t>
-    </rPh>
-    <rPh sb="29" eb="32">
-      <t>トウリュウモン</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -810,75 +498,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>光お菓子限定
-国の豊穣を祝うお菓子のお祭りです。
-光をイメージした、ファンタジックなお菓子を募集してます。</t>
-    <rPh sb="0" eb="1">
-      <t>ヒカ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>クニ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ホウジョウ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>イワ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>マツ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ヒカ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>ボシュウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>光お菓子限定
-アフロディーテ様の生誕を祝うお祭りです。
-神々しい光をイメージしたお菓子を募集します！</t>
-    <rPh sb="14" eb="15">
-      <t>サマ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>セイタン</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>イワ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>マツ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>コウゴウ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>ヒカリ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ボシュウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Or_Contest_480</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -886,26 +505,6 @@
     <t>デザインお菓子コンテスト</t>
     <rPh sb="5" eb="7">
       <t>カシ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>愛をテーマにしたチョコレート限定
-心あたたまる、愛にあふれたチョコレートを、お届けください。</t>
-    <rPh sb="0" eb="1">
-      <t>アイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ココロ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>アイ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>トド</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -962,286 +561,15 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ケーキ系orクリームブリュレ
-オランジーナ国の準パティシエ達が競うコンペ
-腕によりをかけた自慢のお菓子を見せてください！</t>
-    <rPh sb="3" eb="4">
-      <t>ケイ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>コク</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ジュン</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>タチ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>キソ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>ウデ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ジマン</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ひんやりお菓子限定
-暑さを吹き飛ばす！
-つめた～いお菓子を募集シテマース！
-アイス・ゼリー・パフェなどなど..。</t>
-    <rPh sb="5" eb="7">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>アツ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ボシュウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>大人な雰囲気のお菓子を募集
-アダルトな雰囲気で、紳士向けのお菓子を募集しております。
-ブラックなお菓子を見せてくださいませ。</t>
-    <rPh sb="0" eb="2">
-      <t>オトナ</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>フンイキ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="19" eb="22">
-      <t>フンイキ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>シンシ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>お子様向けのお菓子限定
-お子様が喜ぶ色々なお菓子を募集しています！
-かわいいや不思議なお菓子など.. ぜひ応募お待ちしてます！</t>
-    <rPh sb="1" eb="3">
-      <t>コサマ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>コサマ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ヨロコ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>イロイロ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="39" eb="42">
-      <t>フシギ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>オウボ</t>
-    </rPh>
-    <rPh sb="56" eb="57">
-      <t>マ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ルミエール・ドゥ・ソレイユ</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>温かいお菓子限定※焼き菓子は除く
-アフォガード・アップルパイ・パンケーキなど..
-冷えた体とこころを癒やす、温かいお菓子を募集いたします。</t>
-    <rPh sb="0" eb="1">
-      <t>アタタ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ガシ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ノゾ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>カラダ</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>イヤ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>アタタ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>ボシュウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>チーズケーキ限定
-おいしいチーズケーキを募集しますわ♪
-香しく、口の中でねっとりとろける.. 至福のチーズケーキお待ちしてますわ♪</t>
-    <rPh sb="6" eb="8">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>カグワ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>クチ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ナカ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>シフク</t>
-    </rPh>
-    <rPh sb="57" eb="58">
-      <t>マ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>愛とメルヘンがテーマのチョコレート限定
-とろける、夢見るチョコレートのコンテスト。
-はたして、夢を見せてくれるのか・・？※チョコケーキも可</t>
-    <rPh sb="17" eb="19">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ユメミ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>ユメ</t>
-    </rPh>
-    <rPh sb="49" eb="50">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="68" eb="69">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>パティスリー・デュ・モンド</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>アルク・アン・シエル</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>自由課題
-冬の名物となる、雪国のお菓子を募集しています。
-どんな種類でも結構です！お気軽にご応募ください。</t>
-    <rPh sb="0" eb="4">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>フユ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>メイブツ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ユキクニ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>シュルイ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ケッコウ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>キガル</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>オウボ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1295,63 +623,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>自由課題
-オランジーナビーチを象徴する、オシャレなおかしを募集してます！
-腕によりをかけたお菓子を見せてください！</t>
-    <rPh sb="0" eb="4">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ショウチョウ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>ウデ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="49" eb="50">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>自由課題
-メルヘンでかわいいお菓子を募集しています♪
-食べた人に夢を見せるかわいいお菓子を見せてくださ～い！</t>
-    <rPh sb="0" eb="4">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>ユメ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="45" eb="46">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>◆夏エリア最大のお菓子エキシビジョン◆
 テーマ：自由課題
 優勝者には、特別なレシピを進呈します。至高の一品をお待ちしております！</t>
@@ -1401,210 +672,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>自由課題＜クッキー・ラスク除く＞
-パパがおみやげに持って帰れるお菓子を募集しますじゃ。
-小さめで子供が喜ぶお菓子がいいのお。</t>
-    <rPh sb="0" eb="4">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ノゾ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>モ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>カエ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>チイ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>コドモ</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>ヨロコ</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>カシ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>キラキラお菓子限定
-エメラルド・サファイア.. 美しい石は、私たちを魅了してやみません。
-キラもの好きの大富豪がうなるお菓子を募集します♪</t>
-    <rPh sb="5" eb="7">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>ウツク</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>イシ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ワタシ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ミリョウ</t>
-    </rPh>
-    <rPh sb="49" eb="50">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="52" eb="55">
-      <t>ダイフゴウ</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>ボシュウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t xml:space="preserve">紅茶限定
-ティータイムを彩る香り高い紅茶を募集。
-お菓子を引き立てる大切な名脇役のティー。その誇り高さを競い合ってもらいたい。
-</t>
-    <rPh sb="0" eb="2">
-      <t>コウチャ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>イロド</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>カオ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ダカ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>コウチャ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>タイセツ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ワキヤク</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>ホコ</t>
-    </rPh>
-    <rPh sb="49" eb="50">
-      <t>タカ</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>キソ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>芸術的なおかしお菓子限定
-名門ハイネン家の招待パーティーに飾るお菓子を募集しています。パーティーの目玉になる、芸術的なお菓子が希望ですわ♪</t>
-    <rPh sb="8" eb="10">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>メイモン</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ケ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ショウタイ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>カザ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>メダマ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>ゲイジュツ</t>
-    </rPh>
-    <rPh sb="57" eb="58">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>キボウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>青色をテーマにしたお菓子
-ブルー・・それはとても美しい色。
-美しい青をテーマにしたお菓子をぜひ作ってください。</t>
-    <rPh sb="0" eb="2">
-      <t>アオイロ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>ウツク</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>イロ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ウツク</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>アオ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>◆秋の伝統的なお菓子コンクール◆
 テーマ：自由課題
 秋エリアの伝統的で由緒あるコンクールです。食べた人を幸せにするお菓子をお待ちしております。</t>
@@ -1655,36 +722,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>チョコレート限定
-夏エリアで毎年開催のチョコレートコンテスト。
-初級～中級までのパティシエの方ぜひご参加ください！</t>
-    <rPh sb="6" eb="8">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ナツ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>マイトシ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>カイサイ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ショキュウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>チュウキュウ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>サンカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>h02</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1699,36 +736,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>自由課題
-隣国プラムで行われるおかしコンテストです。
-各界隈の著名人が注目するトップレベルのコンテストです。</t>
-    <rPh sb="0" eb="4">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>リンコク</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="27" eb="30">
-      <t>カクカイワイ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>チョメイ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ジン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>チュウモク</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ダイチュウモク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>パティシエの森</t>
     <rPh sb="6" eb="7">
       <t>モリ</t>
@@ -1758,94 +765,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ケーキ限定
-秋の大精霊様が年に一度開くケーキコンテストです。
-自信のある豪華なケーキを見せてください！</t>
-    <rPh sb="3" eb="5">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>アキ</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>ダイセイレイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>サマ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>イチド</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ヒラ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ゴウカ</t>
-    </rPh>
-    <rPh sb="43" eb="44">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>エレメンタリー・ショコラティエ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>自由課題
-春エリアで行われるパティシエ中級向けのコンテスト。少し難易度高め。
-春の大妖精様を讃えるお菓子を希望します。</t>
-    <rPh sb="0" eb="4">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ハル</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>チュウキュウ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="32" eb="35">
-      <t>ナンイド</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>タカ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>ハル</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ヨウセイ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>サマ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>タタ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>キボウ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2052,81 +972,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>自由課題
-夏エリアで行われる初級パティシエ向けのコンテスト。遊園地そばのソーダの森で開催。
-森にくるお客さんを喜ばせよう！！</t>
-    <rPh sb="0" eb="4">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ナツ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ショキュウ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="30" eb="33">
-      <t>ユウエンチ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>モリ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>カイサイ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>モリ</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>キャク</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>ヨロコ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>自由課題
-秋エリアの風物詩的パティシエコンテストです。木枯らしを感じる季節・・いかがおすごしですか？
-幅広くいろんなお菓子を募集しております！</t>
-    <rPh sb="0" eb="4">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>アキ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>フウブツシ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>コガ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>キセツ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>ハバヒロ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>ボシュウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ContestBGMSelectHall</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2144,57 +989,6 @@
   </si>
   <si>
     <t>t209</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>自由課題※飲み物は対象外
-貴族ベオルブ家が、ディナー招待客をもてなすお菓子を、毎年募集しています。
-種類は問いません。華やかなお菓子を希望。</t>
-    <rPh sb="0" eb="4">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ノ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>モノ</t>
-    </rPh>
-    <rPh sb="9" eb="12">
-      <t>タイショウガイ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>キゾク</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>イエ</t>
-    </rPh>
-    <rPh sb="26" eb="29">
-      <t>ショウタイキャク</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>マイトシ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>シュルイ</t>
-    </rPh>
-    <rPh sb="53" eb="54">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>キボウ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2210,38 +1004,6 @@
   <si>
     <t>オータムリーヴス
 鐘の音</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>お花をモチーフにしたお菓子限定
-お花をメインに使った華やかなお菓子を募集しています。クッキー・チョコレート・ケーキ・チーズケーキ限定。</t>
-    <rPh sb="1" eb="2">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>ゲンテイ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2271,6 +1033,1247 @@
     </rPh>
     <rPh sb="52" eb="53">
       <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆クッキー限定◆
+クッキーの初級コンテスト
+新米パティシエ達の登竜門。ゆけぃ！パティシエのたまごたちよ！！</t>
+    <rPh sb="5" eb="7">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ショキュウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シンマイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>タチ</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>トウリュウモン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆ラスク限定◆
+ラスクのおいしさを決めるコンテスト
+お手軽で、小さなアンティーク市で食べるおやつとして募集します。</t>
+    <rPh sb="4" eb="6">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>テガル</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>チイ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ボシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆フィナンシェ限定◆
+あたたかい出来立てフィナンシェを募集。
+各地のフィナンシェ好きが集まり、審査致します。</t>
+    <rPh sb="7" eb="9">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>デキタ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>アツ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>シンサ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>イタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆自由課題※飲み物は対象外◆
+貴族ベオルブ家が、ディナー招待客をもてなすお菓子を、毎年募集しています。
+種類は問いません。華やかなお菓子を希望。</t>
+    <rPh sb="1" eb="5">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>タイショウガイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キゾク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>イエ</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>ショウタイキャク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>マイトシ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>キボウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆光お菓子限定◆
+国の豊穣を祝うお菓子のお祭りです。
+光をイメージした、ファンタジックなお菓子を募集してます。</t>
+    <rPh sb="1" eb="2">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>クニ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ホウジョウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>イワ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>マツ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ボシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆光お菓子限定◆
+アフロディーテ様の生誕を祝うお祭りです。
+神々しい光をイメージしたお菓子を募集します！</t>
+    <rPh sb="16" eb="17">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セイタン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>イワ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>マツ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>コウゴウ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ボシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆自由課題◆
+春エリアで行われるパティシエ中級向けのコンテスト。少し難易度高め。
+春の大妖精様を讃えるお菓子を希望します。</t>
+    <rPh sb="1" eb="5">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ハル</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>チュウキュウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="34" eb="37">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ハル</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヨウセイ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>タタ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>キボウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆自由課題◆
+メルヘンでかわいいお菓子を募集しています♪
+食べた人に夢を見せるかわいいお菓子を見せてくださ～い！</t>
+    <rPh sb="1" eb="5">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆お子様向けのお菓子限定◆
+お子様が喜ぶ色々なお菓子を募集しています！
+かわいいや不思議なお菓子など.. ぜひ応募お待ちしてます！</t>
+    <rPh sb="2" eb="4">
+      <t>コサマ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コサマ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヨロコ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イロイロ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="41" eb="44">
+      <t>フシギ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>オウボ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆キラキラお菓子限定◆
+エメラルド・サファイア.. 美しい石は、私たちを魅了してやみません。
+キラもの好きの大富豪がうなるお菓子を募集します♪</t>
+    <rPh sb="6" eb="8">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>イシ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ミリョウ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="54" eb="57">
+      <t>ダイフゴウ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>ボシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆ひんやりお菓子限定◆
+暑さを吹き飛ばす！
+つめた～いお菓子を募集シテマース！
+アイス・ゼリー・パフェなどなど..。</t>
+    <rPh sb="6" eb="8">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ボシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆自由課題◆
+夏エリアで行われる初級パティシエ向けのコンテスト。遊園地そばのソーダの森で開催。
+森にくるお客さんを喜ばせよう！！</t>
+    <rPh sb="1" eb="5">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ショキュウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>ユウエンチ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>モリ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>カイサイ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>モリ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>キャク</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>ヨロコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆ソーダ限定◆
+シュワシュワなソーダは、夏の定番！！
+おいしくてオシャレなソーダでトップを目指せ！</t>
+    <rPh sb="4" eb="6">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>テイバン</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>メザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆自由課題◆
+オランジーナビーチを象徴する、オシャレなおかしを募集してます！
+腕によりをかけたお菓子を見せてください！</t>
+    <rPh sb="1" eb="5">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ショウチョウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ウデ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆チョコレート限定◆
+夏エリアで毎年開催のチョコレートコンテスト。
+初級～中級までのパティシエの方ぜひご参加ください！</t>
+    <rPh sb="7" eb="9">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>マイトシ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カイサイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ショキュウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>チュウキュウ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>サンカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆自由課題＜クッキー・ラスク除く＞◆
+パパがおみやげに持って帰れるお菓子を募集しますじゃ。
+小さめで子供が喜ぶお菓子がいいのお。</t>
+    <rPh sb="1" eb="5">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>チイ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ヨロコ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆いちごのお菓子限定◆
+お菓子の主役といえば、やはりいちご..！
+いちご好きをうならせるおいしいお菓子を見せてくださいな♪</t>
+    <rPh sb="6" eb="8">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シュヤク</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆海をテーマにしたチョコレート◆
+美しい海を讃えるチョコレートを募集します。
+青や白、砂浜の色合い、波の表現.. 地球の海の美しさを表現してください。</t>
+    <rPh sb="1" eb="2">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>タタ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>スナハマ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>イロア</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ナミ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>チキュウ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆魔法のお菓子限定◆
+魔法で仕上げた、一風変わったオシャレなお菓子を募集♪
+見慣れない不思議なお菓子だと高得点です！</t>
+    <rPh sb="1" eb="3">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>イップウカ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ミナ</t>
+    </rPh>
+    <rPh sb="43" eb="46">
+      <t>フシギ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="52" eb="55">
+      <t>コウトクテン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆自由課題◆
+隣国プラムで行われるおかしコンテストです。
+各界隈の著名人が注目するトップレベルのコンテストです。</t>
+    <rPh sb="1" eb="5">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>リンコク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>カクカイワイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>チョメイ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ジン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>チュウモク</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ダイチュウモク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆クレープ限定◆
+黒猫達も好むおいしくて甘いクレープを募集
+権威ある上流黒猫たちも注目しています♪</t>
+    <rPh sb="5" eb="7">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>クロネコ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>タチ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>コノ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ケンイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ジョウリュウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>クロネコ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>チュウモク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆自由課題◆
+秋エリアの風物詩的パティシエコンテストです。木枯らしを感じる季節・・いかがおすごしですか？
+幅広くいろんなお菓子を募集しております！</t>
+    <rPh sb="1" eb="5">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>フウブツシ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>コガ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>キセツ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>ハバヒロ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ボシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆大人な雰囲気のお菓子限定◆
+アダルトな雰囲気で、紳士向けのお菓子を募集しております。
+ブラックなお菓子を見せてくださいませ。</t>
+    <rPh sb="1" eb="3">
+      <t>オトナ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>フンイキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>フンイキ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シンシ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆ケーキ系orクリームブリュレ◆
+オランジーナ国の準パティシエ達が競うコンペ
+腕によりをかけた自慢のお菓子を見せてください！</t>
+    <rPh sb="4" eb="5">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>コク</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>タチ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ウデ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ジマン</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">◆紅茶限定◆
+ティータイムを彩る香り高い紅茶を募集。
+お菓子を引き立てる大切な名脇役のティー。その誇り高さを競い合ってもらいたい。
+</t>
+    <rPh sb="1" eb="3">
+      <t>コウチャ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>イロド</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ダカ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウチャ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>タイセツ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ワキヤク</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ホコ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆芸術的なおかしお菓子限定◆
+名門ハイネン家の招待パーティーに飾るお菓子を募集しています。パーティーの目玉になる、芸術的なお菓子が希望ですわ♪</t>
+    <rPh sb="9" eb="11">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>メイモン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ショウタイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>カザ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>メダマ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ゲイジュツ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>キボウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆お花をモチーフにしたお菓子限定◆
+お花をメインに使った華やかなお菓子を募集しています。クッキー・チョコレート・ケーキ・チーズケーキ限定。</t>
+    <rPh sb="2" eb="3">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ゲンテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆青色をテーマにしたお菓子◆
+ブルー・・それはとても美しい色。
+美しい青をテーマにしたお菓子をぜひ作ってください。</t>
+    <rPh sb="1" eb="3">
+      <t>アオイロ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆ケーキ限定◆
+秋の大精霊様が年に一度開くケーキコンテストです。
+自信のある豪華なケーキを見せてください！</t>
+    <rPh sb="4" eb="6">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ダイセイレイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ゴウカ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆チョコレート限定◆
+とろける、夢見るチョコレートのコンテスト
+はたして、夢を見せてくれるのか・・？</t>
+    <rPh sb="7" eb="9">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ユメミ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆自由課題◆
+冬の名物となる、雪国のお菓子を募集しています。
+どんな種類でも結構です！お気軽にご応募ください。</t>
+    <rPh sb="1" eb="5">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>フユ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>メイブツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ユキクニ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ケッコウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>キガル</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>オウボ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆愛をテーマにしたチョコレート限定◆
+心あたたまる、愛にあふれたチョコレートを、お届けください。</t>
+    <rPh sb="1" eb="2">
+      <t>アイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ココロ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アイ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>トド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆宇宙をテーマにしたお菓子◆
+宇宙・星にちなんだ、ロマンチックなお菓子を募集</t>
+    <rPh sb="1" eb="3">
+      <t>ウチュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ウチュウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ボシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆温かいお菓子限定※焼き菓子は除く◆
+アフォガード・アップルパイ・パンケーキなど..
+冷えた体とこころを癒やす、温かいお菓子を募集いたします。</t>
+    <rPh sb="1" eb="2">
+      <t>アタタ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ガシ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>カラダ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>イヤ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>アタタ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ボシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆ミルフイユ限定◆
+さくさくパリパリのおいしいミルフイユ限定のコンテスト。
+自信のあるミルフイユを見せてください。</t>
+    <rPh sb="6" eb="8">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ミルフイユ・ドゥ・オランジーナ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆チーズケーキ限定◆
+おいしいチーズケーキを募集しますわ♪
+香しく、口の中でねっとりとろける.. 至福のチーズケーキお待ちしてますわ♪</t>
+    <rPh sb="7" eb="9">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>カグワ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>クチ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>シフク</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆愛・メルヘンが高いチョコレート限定◆
+とろける、夢見るチョコレートのコンテスト。
+はたして、夢を見せてくれるのか・・？※チョコケーキも可</t>
+    <rPh sb="8" eb="9">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ユメミ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2712,7 +2715,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -2757,22 +2760,22 @@
         <v>28</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -2793,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -2802,7 +2805,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -2850,13 +2853,13 @@
         <v>0</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="Z2" s="2">
         <v>0</v>
@@ -2886,10 +2889,10 @@
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -2937,13 +2940,13 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="X3" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="Y3" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2970,13 +2973,13 @@
         <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>93</v>
+        <v>174</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -3024,19 +3027,19 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="X4" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="Y4" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4" s="4" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="AB4">
         <v>0</v>
@@ -3054,16 +3057,16 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>95</v>
+        <v>175</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -3111,13 +3114,13 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="X5" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="Y5" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -3144,13 +3147,13 @@
         <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -3198,13 +3201,13 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="X6" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="Y6" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -3231,13 +3234,13 @@
         <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>115</v>
+        <v>177</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -3285,13 +3288,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="X7" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="Y7" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -3318,13 +3321,13 @@
         <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -3372,13 +3375,13 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="X8" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="Y8" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -3402,16 +3405,16 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="F9" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3459,13 +3462,13 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="X9" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="Y9" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -3492,13 +3495,13 @@
         <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>137</v>
+        <v>180</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -3546,13 +3549,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="X10" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="Y10" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -3579,13 +3582,13 @@
         <v>51</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>125</v>
+        <v>181</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -3633,13 +3636,13 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="X11" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="Y11" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -3666,13 +3669,13 @@
         <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -3720,13 +3723,13 @@
         <v>0</v>
       </c>
       <c r="W12" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="X12" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="Y12" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -3756,10 +3759,10 @@
         <v>29</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -3807,13 +3810,13 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="X13" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="Y13" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -3864,7 +3867,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -3909,22 +3912,22 @@
         <v>28</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -3951,10 +3954,10 @@
         <v>65</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -4002,13 +4005,13 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="X2" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="Y2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z2">
         <v>1</v>
@@ -4032,16 +4035,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="F3" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4089,13 +4092,13 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="X3" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="Y3" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z3">
         <v>2</v>
@@ -4122,13 +4125,13 @@
         <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>66</v>
+        <v>185</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -4176,13 +4179,13 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="X4" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="Y4" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z4">
         <v>1</v>
@@ -4209,13 +4212,13 @@
         <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -4263,13 +4266,13 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="X5" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="Y5" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z5">
         <v>1</v>
@@ -4293,16 +4296,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -4350,13 +4353,13 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="X6" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="Y6" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -4383,13 +4386,13 @@
         <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -4437,13 +4440,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="X7" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="Y7" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z7">
         <v>1</v>
@@ -4470,13 +4473,13 @@
         <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -4524,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="X8" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="Y8" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z8">
         <v>1</v>
@@ -4557,13 +4560,13 @@
         <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="F9" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>101</v>
+        <v>190</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -4611,13 +4614,13 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="X9" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="Y9" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z9">
         <v>1</v>
@@ -4644,13 +4647,13 @@
         <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -4698,13 +4701,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="X10" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="Y10" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z10">
         <v>1</v>
@@ -4731,13 +4734,13 @@
         <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>151</v>
+        <v>192</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -4785,13 +4788,13 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="X11" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="Y11" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z11">
         <v>1</v>
@@ -4818,13 +4821,13 @@
         <v>37</v>
       </c>
       <c r="E12" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -4872,13 +4875,13 @@
         <v>0</v>
       </c>
       <c r="W12" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="X12" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="Y12" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -4929,7 +4932,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -4974,22 +4977,22 @@
         <v>28</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -5013,13 +5016,13 @@
         <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>96</v>
+        <v>193</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -5067,13 +5070,13 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="X2" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="Y2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -5097,16 +5100,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>208</v>
+        <v>171</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5154,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="X3" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="Y3" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -5187,13 +5190,13 @@
         <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>124</v>
+        <v>195</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -5241,13 +5244,13 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="X4" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="Y4" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -5274,13 +5277,13 @@
         <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>122</v>
+        <v>196</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -5328,13 +5331,13 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="X5" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="Y5" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -5364,10 +5367,10 @@
         <v>64</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>142</v>
+        <v>197</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -5415,13 +5418,13 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="X6" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="Y6" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -5448,13 +5451,13 @@
         <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>143</v>
+        <v>198</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -5502,13 +5505,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="X7" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="Y7" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -5535,13 +5538,13 @@
         <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -5589,13 +5592,13 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="X8" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="Y8" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -5622,13 +5625,13 @@
         <v>54</v>
       </c>
       <c r="E9" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -5676,13 +5679,13 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="X9" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="Y9" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -5709,13 +5712,13 @@
         <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>157</v>
+        <v>201</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5763,13 +5766,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="X10" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="Y10" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -5796,13 +5799,13 @@
         <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>94</v>
+        <v>202</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -5850,13 +5853,13 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="X11" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="Y11" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -5880,16 +5883,16 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="H12" s="2">
         <v>0</v>
@@ -5937,13 +5940,13 @@
         <v>0</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z12" s="2">
         <v>0</v>
@@ -5970,13 +5973,13 @@
         <v>46</v>
       </c>
       <c r="E13" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="F13" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -6024,13 +6027,13 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="X13" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="Y13" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -6081,7 +6084,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -6126,22 +6129,22 @@
         <v>28</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -6165,13 +6168,13 @@
         <v>56</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
       <c r="H2" s="5">
         <v>0</v>
@@ -6219,13 +6222,13 @@
         <v>0</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="Y2" s="5" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z2" s="5">
         <v>0</v>
@@ -6252,13 +6255,13 @@
         <v>57</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>193</v>
+        <v>159</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>119</v>
+        <v>204</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
@@ -6306,13 +6309,13 @@
         <v>0</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="Y3" s="5" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z3" s="5">
         <v>0</v>
@@ -6339,13 +6342,13 @@
         <v>58</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>71</v>
+        <v>205</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -6393,13 +6396,13 @@
         <v>0</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="Y4" s="5" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z4" s="5">
         <v>0</v>
@@ -6426,13 +6429,13 @@
         <v>60</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>195</v>
+        <v>161</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>127</v>
+        <v>206</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -6480,13 +6483,13 @@
         <v>0</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="Y5" s="5" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z5" s="5">
         <v>0</v>
@@ -6513,13 +6516,13 @@
         <v>61</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>77</v>
+        <v>208</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>77</v>
+        <v>208</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
@@ -6567,13 +6570,13 @@
         <v>0</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="Y6" s="5" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z6" s="5">
         <v>0</v>
@@ -6600,13 +6603,13 @@
         <v>62</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>196</v>
+        <v>162</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>128</v>
+        <v>209</v>
       </c>
       <c r="H7" s="5">
         <v>0</v>
@@ -6654,13 +6657,13 @@
         <v>0</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="Y7" s="5" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z7" s="5">
         <v>0</v>
@@ -6687,13 +6690,13 @@
         <v>63</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>198</v>
+        <v>164</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>129</v>
+        <v>210</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>
@@ -6741,13 +6744,13 @@
         <v>0</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="Y8" s="5" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="Z8" s="5">
         <v>0</v>
@@ -6774,13 +6777,13 @@
         <v>47</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="H9" s="5">
         <v>0</v>
@@ -6828,13 +6831,13 @@
         <v>0</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="Y9" s="5" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="Z9" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40859256-3C10-478A-B1AD-A7A2154C6BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BFD2C3-036F-4D0B-A84B-1D8D692C7A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="930" windowWidth="25485" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2730" yWindow="1230" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -3174,7 +3174,7 @@
         <v>3</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O6">
         <v>3</v>
@@ -3261,7 +3261,7 @@
         <v>3</v>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O7">
         <v>3</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BFD2C3-036F-4D0B-A84B-1D8D692C7A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213F1A7F-76CA-470B-A3CC-821D5C863C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1230" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2925" yWindow="1170" windowWidth="25485" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -3768,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13">
         <v>12</v>
@@ -3846,7 +3846,9 @@
     <col min="7" max="7" width="19.75" customWidth="1"/>
     <col min="8" max="11" width="7.5" customWidth="1"/>
     <col min="12" max="12" width="8.125" customWidth="1"/>
-    <col min="13" max="26" width="6.75" customWidth="1"/>
+    <col min="13" max="24" width="6.75" customWidth="1"/>
+    <col min="25" max="25" width="9.625" customWidth="1"/>
+    <col min="26" max="26" width="6.75" customWidth="1"/>
     <col min="27" max="27" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4833,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J12">
         <v>12</v>
@@ -4911,7 +4913,9 @@
     <col min="7" max="7" width="19.75" customWidth="1"/>
     <col min="8" max="11" width="7.5" customWidth="1"/>
     <col min="12" max="12" width="8.125" customWidth="1"/>
-    <col min="13" max="26" width="6.75" customWidth="1"/>
+    <col min="13" max="24" width="6.75" customWidth="1"/>
+    <col min="25" max="25" width="9.625" customWidth="1"/>
+    <col min="26" max="26" width="6.75" customWidth="1"/>
     <col min="27" max="27" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5985,7 +5989,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J13">
         <v>12</v>
@@ -6528,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J6" s="5">
         <v>12</v>
@@ -6615,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J7" s="5">
         <v>12</v>
@@ -6702,7 +6706,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J8" s="5">
         <v>12</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213F1A7F-76CA-470B-A3CC-821D5C863C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D1059A-86C7-44EC-9AC8-B3AA9643FBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2925" yWindow="1170" windowWidth="25485" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="660" yWindow="525" windowWidth="25485" windowHeight="14370" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -4070,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D1059A-86C7-44EC-9AC8-B3AA9643FBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2D1093-6CDA-483B-A0CB-062C2D971896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="525" windowWidth="25485" windowHeight="14370" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="915" yWindow="390" windowWidth="25485" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -2898,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>12</v>
@@ -2985,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>12</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>12</v>
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>12</v>
@@ -3246,7 +3246,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>12</v>
@@ -3333,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>12</v>
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>12</v>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>12</v>
@@ -3594,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>12</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>12</v>
@@ -3965,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>12</v>
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>12</v>
@@ -4139,7 +4139,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>12</v>
@@ -4226,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>12</v>
@@ -4313,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>12</v>
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>12</v>
@@ -4487,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>12</v>
@@ -4574,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>12</v>
@@ -4661,7 +4661,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>12</v>
@@ -4748,7 +4748,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>12</v>
@@ -5206,7 +5206,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>12</v>
@@ -5293,7 +5293,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>12</v>
@@ -5380,7 +5380,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>12</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>12</v>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>12</v>
@@ -5641,7 +5641,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>12</v>
@@ -5728,7 +5728,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>12</v>
@@ -5815,7 +5815,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>12</v>
@@ -5902,7 +5902,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J12" s="2">
         <v>12</v>
@@ -5989,7 +5989,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13">
         <v>12</v>
@@ -6271,7 +6271,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>12</v>
@@ -6358,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>12</v>
@@ -6445,7 +6445,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>12</v>
@@ -6532,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" s="5">
         <v>12</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7" s="5">
         <v>12</v>
@@ -6706,7 +6706,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J8" s="5">
         <v>12</v>
@@ -6793,7 +6793,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J9" s="5">
         <v>12</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2D1093-6CDA-483B-A0CB-062C2D971896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03693B9-946D-46BD-B44F-38A6E3A952B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="390" windowWidth="25485" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2115" yWindow="315" windowWidth="25485" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03693B9-946D-46BD-B44F-38A6E3A952B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7DE630-F00B-4934-9D6B-B2F9237DB2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2115" yWindow="315" windowWidth="25485" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -3081,7 +3081,7 @@
         <v>31</v>
       </c>
       <c r="L5">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="M5">
         <v>2</v>
@@ -3168,7 +3168,7 @@
         <v>31</v>
       </c>
       <c r="L6">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -3255,7 +3255,7 @@
         <v>31</v>
       </c>
       <c r="L7">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="M7">
         <v>3</v>
@@ -3342,7 +3342,7 @@
         <v>31</v>
       </c>
       <c r="L8">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="M8">
         <v>5</v>
@@ -3438,7 +3438,7 @@
         <v>3</v>
       </c>
       <c r="O9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -3690,7 +3690,7 @@
         <v>31</v>
       </c>
       <c r="L12">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="M12">
         <v>6</v>
@@ -4757,7 +4757,7 @@
         <v>31</v>
       </c>
       <c r="L11">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="M11">
         <v>13</v>
@@ -5041,7 +5041,7 @@
         <v>31</v>
       </c>
       <c r="L2">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -5128,7 +5128,7 @@
         <v>31</v>
       </c>
       <c r="L3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -5215,7 +5215,7 @@
         <v>31</v>
       </c>
       <c r="L4">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="M4">
         <v>20</v>
@@ -5389,7 +5389,7 @@
         <v>31</v>
       </c>
       <c r="L6">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="M6">
         <v>20</v>
@@ -5476,7 +5476,7 @@
         <v>31</v>
       </c>
       <c r="L7">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="M7">
         <v>21</v>
@@ -5650,7 +5650,7 @@
         <v>31</v>
       </c>
       <c r="L9">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="M9">
         <v>22</v>
@@ -5737,7 +5737,7 @@
         <v>31</v>
       </c>
       <c r="L10">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="M10">
         <v>22</v>
@@ -5824,7 +5824,7 @@
         <v>31</v>
       </c>
       <c r="L11">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="M11">
         <v>22</v>
@@ -6280,7 +6280,7 @@
         <v>31</v>
       </c>
       <c r="L3" s="5">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="M3" s="5">
         <v>30</v>
@@ -6367,7 +6367,7 @@
         <v>31</v>
       </c>
       <c r="L4" s="5">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="M4" s="5">
         <v>30</v>
@@ -6454,7 +6454,7 @@
         <v>31</v>
       </c>
       <c r="L5" s="5">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="M5" s="5">
         <v>30</v>
@@ -6541,7 +6541,7 @@
         <v>31</v>
       </c>
       <c r="L6" s="5">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="M6" s="5">
         <v>31</v>
@@ -6628,7 +6628,7 @@
         <v>31</v>
       </c>
       <c r="L7" s="5">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="M7" s="5">
         <v>32</v>
@@ -6715,7 +6715,7 @@
         <v>31</v>
       </c>
       <c r="L8" s="5">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="M8" s="5">
         <v>32</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7DE630-F00B-4934-9D6B-B2F9237DB2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE8D15C-08AE-4F9F-A4D4-D08E960EC5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25485" windowHeight="14370" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -726,16 +726,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>プラムお菓子技術コンテスト</t>
-    <rPh sb="4" eb="6">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ギジュツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>パティシエの森</t>
     <rPh sb="6" eb="7">
       <t>モリ</t>
@@ -892,17 +882,6 @@
   <si>
     <t>マジカルパティスリー
 アワード</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>プラムお菓子技術
-コンテスト</t>
-    <rPh sb="4" eb="6">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ギジュツ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1692,36 +1671,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>◆自由課題◆
-隣国プラムで行われるおかしコンテストです。
-各界隈の著名人が注目するトップレベルのコンテストです。</t>
-    <rPh sb="1" eb="5">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>リンコク</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="29" eb="32">
-      <t>カクカイワイ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>チョメイ</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>ジン</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>チュウモク</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ダイチュウモク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>◆クレープ限定◆
 黒猫達も好むおいしくて甘いクレープを募集
 権威ある上流黒猫たちも注目しています♪</t>
@@ -2030,42 +1979,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>◆ケーキ限定◆
-秋の大精霊様が年に一度開くケーキコンテストです。
-自信のある豪華なケーキを見せてください！</t>
-    <rPh sb="4" eb="6">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>アキ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>ダイセイレイ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>サマ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>イチド</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ヒラ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ゴウカ</t>
-    </rPh>
-    <rPh sb="45" eb="46">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>◆チョコレート限定◆
 とろける、夢見るチョコレートのコンテスト
 はたして、夢を見せてくれるのか・・？</t>
@@ -2274,6 +2187,84 @@
     </rPh>
     <rPh sb="68" eb="69">
       <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆ケーキ限定◆
+秋の大収穫祭を祝うケーキコンテストです。
+お祝いのための豪華なケーキを見せてください！</t>
+    <rPh sb="4" eb="6">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>ダイシュウカクサイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>イワ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>イワ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ゴウカ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プラム洋菓子技術コンテスト</t>
+    <rPh sb="6" eb="8">
+      <t>ギジュツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プラム洋菓子技術
+コンテスト</t>
+    <rPh sb="6" eb="8">
+      <t>ギジュツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆自由課題◆
+隣国プラムで行われる伝統的な洋菓子コンテストです。
+各界隈の著名人が注目するトップレベルのコンテストです。</t>
+    <rPh sb="1" eb="5">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>リンコク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>デントウテキ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>ヨウガシ</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>カクカイワイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>チョメイ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ジン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>チュウモク</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ダイチュウモク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2715,7 +2706,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -2775,7 +2766,7 @@
         <v>98</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -2889,10 +2880,10 @@
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -2976,10 +2967,10 @@
         <v>87</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -3063,10 +3054,10 @@
         <v>73</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -3153,7 +3144,7 @@
         <v>83</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -3237,10 +3228,10 @@
         <v>84</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -3324,10 +3315,10 @@
         <v>85</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -3405,16 +3396,16 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3498,10 +3489,10 @@
         <v>70</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -3585,10 +3576,10 @@
         <v>78</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -3672,10 +3663,10 @@
         <v>71</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -3759,10 +3750,10 @@
         <v>29</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -3810,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="X13" t="s">
         <v>99</v>
@@ -3869,7 +3860,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -3929,7 +3920,7 @@
         <v>98</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -3956,10 +3947,10 @@
         <v>65</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -4007,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y2" t="s">
         <v>101</v>
@@ -4037,16 +4028,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4094,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
+        <v>132</v>
+      </c>
+      <c r="X3" t="s">
         <v>133</v>
-      </c>
-      <c r="X3" t="s">
-        <v>134</v>
       </c>
       <c r="Y3" t="s">
         <v>101</v>
@@ -4130,10 +4121,10 @@
         <v>91</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -4181,10 +4172,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y4" t="s">
         <v>101</v>
@@ -4217,10 +4208,10 @@
         <v>89</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -4268,10 +4259,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y5" t="s">
         <v>101</v>
@@ -4301,13 +4292,13 @@
         <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -4355,10 +4346,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y6" t="s">
         <v>101</v>
@@ -4391,10 +4382,10 @@
         <v>66</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -4442,10 +4433,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y7" t="s">
         <v>101</v>
@@ -4481,7 +4472,7 @@
         <v>67</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -4529,10 +4520,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="X8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y8" t="s">
         <v>101</v>
@@ -4568,7 +4559,7 @@
         <v>90</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -4616,10 +4607,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="X9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y9" t="s">
         <v>101</v>
@@ -4652,10 +4643,10 @@
         <v>116</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -4703,10 +4694,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y10" t="s">
         <v>101</v>
@@ -4736,13 +4727,13 @@
         <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>119</v>
+        <v>208</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>152</v>
+        <v>209</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -4790,10 +4781,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y11" t="s">
         <v>101</v>
@@ -4826,7 +4817,7 @@
         <v>111</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>113</v>
@@ -4877,10 +4868,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="X12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Y12" t="s">
         <v>101</v>
@@ -4936,7 +4927,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -4996,7 +4987,7 @@
         <v>98</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -5023,10 +5014,10 @@
         <v>72</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -5074,10 +5065,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y2" t="s">
         <v>101</v>
@@ -5104,16 +5095,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5161,10 +5152,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y3" t="s">
         <v>101</v>
@@ -5197,10 +5188,10 @@
         <v>77</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -5248,10 +5239,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y4" t="s">
         <v>101</v>
@@ -5284,10 +5275,10 @@
         <v>82</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -5335,10 +5326,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y5" t="s">
         <v>101</v>
@@ -5371,10 +5362,10 @@
         <v>64</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -5422,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y6" t="s">
         <v>101</v>
@@ -5461,7 +5452,7 @@
         <v>80</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -5509,10 +5500,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y7" t="s">
         <v>101</v>
@@ -5548,7 +5539,7 @@
         <v>88</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -5596,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y8" t="s">
         <v>101</v>
@@ -5632,10 +5623,10 @@
         <v>81</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -5683,10 +5674,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y9" t="s">
         <v>101</v>
@@ -5722,7 +5713,7 @@
         <v>79</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5770,10 +5761,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y10" t="s">
         <v>101</v>
@@ -5806,10 +5797,10 @@
         <v>86</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -5857,10 +5848,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y11" t="s">
         <v>101</v>
@@ -5944,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>102</v>
@@ -6031,10 +6022,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="X13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Y13" t="s">
         <v>101</v>
@@ -6088,7 +6079,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -6148,7 +6139,7 @@
         <v>98</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -6178,7 +6169,7 @@
         <v>68</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H2" s="5">
         <v>0</v>
@@ -6226,10 +6217,10 @@
         <v>0</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y2" s="5" t="s">
         <v>101</v>
@@ -6262,10 +6253,10 @@
         <v>76</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
@@ -6313,10 +6304,10 @@
         <v>0</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y3" s="5" t="s">
         <v>101</v>
@@ -6349,10 +6340,10 @@
         <v>75</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -6400,10 +6391,10 @@
         <v>0</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y4" s="5" t="s">
         <v>101</v>
@@ -6436,10 +6427,10 @@
         <v>107</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -6487,10 +6478,10 @@
         <v>0</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y5" s="5" t="s">
         <v>101</v>
@@ -6520,13 +6511,13 @@
         <v>61</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
@@ -6574,10 +6565,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y6" s="5" t="s">
         <v>101</v>
@@ -6610,10 +6601,10 @@
         <v>74</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H7" s="5">
         <v>0</v>
@@ -6661,10 +6652,10 @@
         <v>0</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y7" s="5" t="s">
         <v>101</v>
@@ -6697,10 +6688,10 @@
         <v>105</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>
@@ -6748,10 +6739,10 @@
         <v>0</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y8" s="5" t="s">
         <v>101</v>
@@ -6784,7 +6775,7 @@
         <v>108</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>110</v>
@@ -6835,10 +6826,10 @@
         <v>0</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y9" s="5" t="s">
         <v>100</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE8D15C-08AE-4F9F-A4D4-D08E960EC5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2125F7BE-FEF5-4301-BAA0-8550D41774EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25485" windowHeight="14370" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2820" yWindow="945" windowWidth="25485" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y8" t="s">
         <v>101</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2125F7BE-FEF5-4301-BAA0-8550D41774EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CB9CD5-790D-4B85-843B-8E9F0B1C5E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="945" windowWidth="25485" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2715" yWindow="945" windowWidth="25485" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="215">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -623,42 +623,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>◆夏エリア最大のお菓子エキシビジョン◆
-テーマ：自由課題
-優勝者には、特別なレシピを進呈します。至高の一品をお待ちしております！</t>
-    <rPh sb="1" eb="2">
-      <t>ナツ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>サイダイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="24" eb="28">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="29" eb="32">
-      <t>ユウショウシャ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>トクベツ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>シンテイ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>シコウ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>イッピン</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>マ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>黄色は、まだ判定の未調整</t>
     <rPh sb="0" eb="2">
       <t>キイロ</t>
@@ -983,36 +947,6 @@
   <si>
     <t>オータムリーヴス
 鐘の音</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>◆パティシエアカデミーの登竜門◆
-テーマ：自由課題
-優勝者には、特別なレシピを進呈します。至高の一品をお待ちしております！</t>
-    <rPh sb="12" eb="15">
-      <t>トウリュウモン</t>
-    </rPh>
-    <rPh sb="21" eb="25">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="26" eb="29">
-      <t>ユウショウシャ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>トクベツ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>シンテイ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>シコウ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>イッピン</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>マ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1917,38 +1851,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>◆お花をモチーフにしたお菓子限定◆
-お花をメインに使った華やかなお菓子を募集しています。クッキー・チョコレート・ケーキ・チーズケーキ限定。</t>
-    <rPh sb="2" eb="3">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="66" eb="68">
-      <t>ゲンテイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>◆青色をテーマにしたお菓子◆
 ブルー・・それはとても美しい色。
 美しい青をテーマにしたお菓子をぜひ作ってください。</t>
@@ -2265,6 +2167,125 @@
     </rPh>
     <rPh sb="43" eb="45">
       <t>ダイチュウモク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆夏エリア最大のお菓子エキシビジョン◆
+テーマ：自由課題
+ソーダアイランドで行われるお菓子の一大イベント！
+自慢のお菓子で来客者を喜ばせよう！！</t>
+    <rPh sb="1" eb="2">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="24" eb="28">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>イチダイ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ジマン</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="61" eb="64">
+      <t>ライキャクシャ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ヨロコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆パティシエアカデミーの登竜門◆
+テーマ：焼き菓子と自由課題
+来たれ！パティシエのたまごたちよ！
+至高の一品をお待ちしております！</t>
+    <rPh sb="12" eb="15">
+      <t>トウリュウモン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ガシ</t>
+    </rPh>
+    <rPh sb="26" eb="30">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>シコウ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>イッピン</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>h03</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>t03</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>h04</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sound81</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆お花をモチーフにしたお菓子限定◆
+お花をメインに使った華やかなお菓子を募集しています。クッキー・チョコレート・ケーキ・チーズケーキ・ゼリー限定。</t>
+    <rPh sb="2" eb="3">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ゲンテイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2685,7 +2706,9 @@
     <col min="7" max="7" width="19.75" customWidth="1"/>
     <col min="8" max="11" width="7.5" customWidth="1"/>
     <col min="12" max="12" width="8.125" customWidth="1"/>
-    <col min="13" max="26" width="6.75" customWidth="1"/>
+    <col min="13" max="24" width="6.75" customWidth="1"/>
+    <col min="25" max="25" width="9.625" customWidth="1"/>
+    <col min="26" max="26" width="6.75" customWidth="1"/>
     <col min="27" max="27" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2706,7 +2729,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -2766,7 +2789,7 @@
         <v>98</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -2796,7 +2819,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -2880,10 +2903,10 @@
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -2967,10 +2990,10 @@
         <v>87</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -3018,10 +3041,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="X4" t="s">
-        <v>99</v>
+        <v>211</v>
       </c>
       <c r="Y4" t="s">
         <v>101</v>
@@ -3054,10 +3077,10 @@
         <v>73</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -3144,7 +3167,7 @@
         <v>83</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -3192,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X6" t="s">
         <v>99</v>
@@ -3228,10 +3251,10 @@
         <v>84</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -3279,13 +3302,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="X7" t="s">
         <v>99</v>
       </c>
       <c r="Y7" t="s">
-        <v>101</v>
+        <v>213</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -3315,10 +3338,10 @@
         <v>85</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -3366,13 +3389,13 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="X8" t="s">
         <v>99</v>
       </c>
       <c r="Y8" t="s">
-        <v>101</v>
+        <v>213</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -3396,16 +3419,16 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3429,7 +3452,7 @@
         <v>3</v>
       </c>
       <c r="O9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -3453,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X9" t="s">
         <v>99</v>
@@ -3489,10 +3512,10 @@
         <v>70</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -3576,10 +3599,10 @@
         <v>78</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -3663,10 +3686,10 @@
         <v>71</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -3690,7 +3713,7 @@
         <v>20</v>
       </c>
       <c r="O12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>1</v>
@@ -3750,10 +3773,10 @@
         <v>29</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -3801,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="X13" t="s">
         <v>99</v>
@@ -3860,7 +3883,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -3920,7 +3943,7 @@
         <v>98</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -3947,10 +3970,10 @@
         <v>65</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -3998,10 +4021,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y2" t="s">
         <v>101</v>
@@ -4028,16 +4051,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4085,10 +4108,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
+        <v>131</v>
+      </c>
+      <c r="X3" t="s">
         <v>132</v>
-      </c>
-      <c r="X3" t="s">
-        <v>133</v>
       </c>
       <c r="Y3" t="s">
         <v>101</v>
@@ -4121,10 +4144,10 @@
         <v>91</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -4172,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y4" t="s">
         <v>101</v>
@@ -4208,10 +4231,10 @@
         <v>89</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -4259,10 +4282,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y5" t="s">
         <v>101</v>
@@ -4289,16 +4312,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -4346,10 +4369,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y6" t="s">
         <v>101</v>
@@ -4382,10 +4405,10 @@
         <v>66</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -4433,10 +4456,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y7" t="s">
         <v>101</v>
@@ -4472,7 +4495,7 @@
         <v>67</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -4520,10 +4543,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y8" t="s">
         <v>101</v>
@@ -4559,7 +4582,7 @@
         <v>90</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -4607,10 +4630,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y9" t="s">
         <v>101</v>
@@ -4640,13 +4663,13 @@
         <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -4694,10 +4717,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>125</v>
+        <v>212</v>
       </c>
       <c r="X10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y10" t="s">
         <v>101</v>
@@ -4727,13 +4750,13 @@
         <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -4781,10 +4804,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y11" t="s">
         <v>101</v>
@@ -4817,10 +4840,10 @@
         <v>111</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>113</v>
+        <v>208</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -4868,10 +4891,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="s">
+        <v>163</v>
+      </c>
+      <c r="X12" t="s">
         <v>164</v>
-      </c>
-      <c r="X12" t="s">
-        <v>165</v>
       </c>
       <c r="Y12" t="s">
         <v>101</v>
@@ -4927,7 +4950,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -4987,7 +5010,7 @@
         <v>98</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -5014,10 +5037,10 @@
         <v>72</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -5065,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y2" t="s">
         <v>101</v>
@@ -5095,16 +5118,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>169</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5152,10 +5175,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y3" t="s">
         <v>101</v>
@@ -5188,10 +5211,10 @@
         <v>77</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -5239,10 +5262,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y4" t="s">
         <v>101</v>
@@ -5275,10 +5298,10 @@
         <v>82</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -5326,10 +5349,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y5" t="s">
         <v>101</v>
@@ -5362,10 +5385,10 @@
         <v>64</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -5413,10 +5436,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y6" t="s">
         <v>101</v>
@@ -5452,7 +5475,7 @@
         <v>80</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -5500,10 +5523,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y7" t="s">
         <v>101</v>
@@ -5539,7 +5562,7 @@
         <v>88</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -5587,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y8" t="s">
         <v>101</v>
@@ -5623,10 +5646,10 @@
         <v>81</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -5674,10 +5697,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y9" t="s">
         <v>101</v>
@@ -5713,7 +5736,7 @@
         <v>79</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5761,10 +5784,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y10" t="s">
         <v>101</v>
@@ -5797,10 +5820,10 @@
         <v>86</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -5848,10 +5871,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y11" t="s">
         <v>101</v>
@@ -5935,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>102</v>
@@ -5974,7 +5997,7 @@
         <v>109</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -6022,10 +6045,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
+        <v>165</v>
+      </c>
+      <c r="X13" t="s">
         <v>166</v>
-      </c>
-      <c r="X13" t="s">
-        <v>167</v>
       </c>
       <c r="Y13" t="s">
         <v>101</v>
@@ -6079,7 +6102,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -6139,7 +6162,7 @@
         <v>98</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -6169,7 +6192,7 @@
         <v>68</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H2" s="5">
         <v>0</v>
@@ -6217,10 +6240,10 @@
         <v>0</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y2" s="5" t="s">
         <v>101</v>
@@ -6253,10 +6276,10 @@
         <v>76</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
@@ -6304,10 +6327,10 @@
         <v>0</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y3" s="5" t="s">
         <v>101</v>
@@ -6340,10 +6363,10 @@
         <v>75</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -6391,10 +6414,10 @@
         <v>0</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y4" s="5" t="s">
         <v>101</v>
@@ -6427,10 +6450,10 @@
         <v>107</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -6478,10 +6501,10 @@
         <v>0</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y5" s="5" t="s">
         <v>101</v>
@@ -6511,13 +6534,13 @@
         <v>61</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
@@ -6565,10 +6588,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y6" s="5" t="s">
         <v>101</v>
@@ -6601,10 +6624,10 @@
         <v>74</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H7" s="5">
         <v>0</v>
@@ -6652,10 +6675,10 @@
         <v>0</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y7" s="5" t="s">
         <v>101</v>
@@ -6688,10 +6711,10 @@
         <v>105</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>
@@ -6739,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y8" s="5" t="s">
         <v>101</v>
@@ -6775,7 +6798,7 @@
         <v>108</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>110</v>
@@ -6826,10 +6849,10 @@
         <v>0</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y9" s="5" t="s">
         <v>100</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CB9CD5-790D-4B85-843B-8E9F0B1C5E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56609186-5E87-417C-971C-8231B22BB957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2715" yWindow="945" windowWidth="25485" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2595" yWindow="705" windowWidth="25485" windowHeight="14370" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="216">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -1419,36 +1419,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>◆チョコレート限定◆
-夏エリアで毎年開催のチョコレートコンテスト。
-初級～中級までのパティシエの方ぜひご参加ください！</t>
-    <rPh sb="7" eb="9">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ナツ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>マイトシ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>カイサイ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ショキュウ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>チュウキュウ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>サンカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>◆自由課題＜クッキー・ラスク除く＞◆
 パパがおみやげに持って帰れるお菓子を募集しますじゃ。
 小さめで子供が喜ぶお菓子がいいのお。</t>
@@ -2286,6 +2256,37 @@
     </rPh>
     <rPh sb="70" eb="72">
       <t>ゲンテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sound55</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆チョコレート限定◆
+夏エリアで開催のチョコレートコンテスト。
+初級～中級までのパティシエの方ぜひご参加ください！</t>
+    <rPh sb="7" eb="9">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カイサイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ショキュウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>チュウキュウ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>サンカ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3041,10 +3042,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
+        <v>209</v>
+      </c>
+      <c r="X4" t="s">
         <v>210</v>
-      </c>
-      <c r="X4" t="s">
-        <v>211</v>
       </c>
       <c r="Y4" t="s">
         <v>101</v>
@@ -3302,13 +3303,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="X7" t="s">
         <v>99</v>
       </c>
       <c r="Y7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -3389,13 +3390,13 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="X8" t="s">
         <v>99</v>
       </c>
       <c r="Y8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -3776,7 +3777,7 @@
         <v>141</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -4075,7 +4076,7 @@
         <v>31</v>
       </c>
       <c r="L3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -4087,7 +4088,7 @@
         <v>3</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3">
         <v>99</v>
@@ -4114,7 +4115,7 @@
         <v>132</v>
       </c>
       <c r="Y3" t="s">
-        <v>101</v>
+        <v>214</v>
       </c>
       <c r="Z3">
         <v>2</v>
@@ -4162,7 +4163,7 @@
         <v>31</v>
       </c>
       <c r="L4">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -4249,7 +4250,7 @@
         <v>31</v>
       </c>
       <c r="L5">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -4321,7 +4322,7 @@
         <v>146</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -4336,7 +4337,7 @@
         <v>31</v>
       </c>
       <c r="L6">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -4345,7 +4346,7 @@
         <v>10</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -4408,7 +4409,7 @@
         <v>147</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -4495,7 +4496,7 @@
         <v>67</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -4582,7 +4583,7 @@
         <v>90</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -4669,7 +4670,7 @@
         <v>149</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -4717,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="X10" t="s">
         <v>127</v>
@@ -4750,13 +4751,13 @@
         <v>45</v>
       </c>
       <c r="E11" t="s">
+        <v>204</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>207</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -4843,7 +4844,7 @@
         <v>150</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -5040,7 +5041,7 @@
         <v>151</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -5127,7 +5128,7 @@
         <v>168</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5214,7 +5215,7 @@
         <v>152</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -5301,7 +5302,7 @@
         <v>153</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -5388,7 +5389,7 @@
         <v>148</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -5475,7 +5476,7 @@
         <v>80</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -5562,7 +5563,7 @@
         <v>88</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -5649,7 +5650,7 @@
         <v>154</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -5736,7 +5737,7 @@
         <v>79</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5823,7 +5824,7 @@
         <v>155</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -6192,7 +6193,7 @@
         <v>68</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H2" s="5">
         <v>0</v>
@@ -6279,7 +6280,7 @@
         <v>156</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
@@ -6366,7 +6367,7 @@
         <v>157</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -6453,7 +6454,7 @@
         <v>158</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -6534,13 +6535,13 @@
         <v>61</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
@@ -6627,7 +6628,7 @@
         <v>159</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H7" s="5">
         <v>0</v>
@@ -6714,7 +6715,7 @@
         <v>161</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56609186-5E87-417C-971C-8231B22BB957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C5B93A-1095-42FF-A5CB-B132F336EDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="705" windowWidth="25485" windowHeight="14370" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2220" yWindow="780" windowWidth="25485" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -3711,7 +3711,7 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O12">
         <v>5</v>
@@ -4604,7 +4604,7 @@
         <v>12</v>
       </c>
       <c r="N9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O9">
         <v>5</v>
@@ -4691,7 +4691,7 @@
         <v>13</v>
       </c>
       <c r="N10">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="O10">
         <v>4</v>
@@ -4778,7 +4778,7 @@
         <v>13</v>
       </c>
       <c r="N11">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="O11">
         <v>5</v>
@@ -5758,7 +5758,7 @@
         <v>22</v>
       </c>
       <c r="N10">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="O10">
         <v>4</v>
@@ -5845,7 +5845,7 @@
         <v>22</v>
       </c>
       <c r="N11">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="O11">
         <v>5</v>
@@ -6388,7 +6388,7 @@
         <v>30</v>
       </c>
       <c r="N4" s="5">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="O4" s="5">
         <v>4</v>
@@ -6475,7 +6475,7 @@
         <v>30</v>
       </c>
       <c r="N5" s="5">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="O5" s="5">
         <v>4</v>
@@ -6562,7 +6562,7 @@
         <v>31</v>
       </c>
       <c r="N6" s="5">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="O6" s="5">
         <v>4</v>
@@ -6649,7 +6649,7 @@
         <v>32</v>
       </c>
       <c r="N7" s="5">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="O7" s="5">
         <v>4</v>
@@ -6736,7 +6736,7 @@
         <v>32</v>
       </c>
       <c r="N8" s="5">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="O8" s="5">
         <v>5</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C5B93A-1095-42FF-A5CB-B132F336EDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296DAF76-22CF-449D-919F-2E49D504F04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="780" windowWidth="25485" windowHeight="14370" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2370" yWindow="930" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="217">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -2105,42 +2105,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>◆自由課題◆
-隣国プラムで行われる伝統的な洋菓子コンテストです。
-各界隈の著名人が注目するトップレベルのコンテストです。</t>
-    <rPh sb="1" eb="5">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>リンコク</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="17" eb="20">
-      <t>デントウテキ</t>
-    </rPh>
-    <rPh sb="21" eb="24">
-      <t>ヨウガシ</t>
-    </rPh>
-    <rPh sb="33" eb="36">
-      <t>カクカイワイ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>チョメイ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>ジン</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>チュウモク</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ダイチュウモク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>◆夏エリア最大のお菓子エキシビジョン◆
 テーマ：自由課題
 ソーダアイランドで行われるお菓子の一大イベント！
@@ -2288,6 +2252,45 @@
     <rPh sb="50" eb="52">
       <t>サンカ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆自由課題◆
+隣国プラムで行われる伝統的な洋菓子コンテストです。各界隈の著名人が注目するトップレベルのコンテストです。</t>
+    <rPh sb="1" eb="5">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>リンコク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>デントウテキ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>ヨウガシ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>カクカイワイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>チョメイ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ジン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>チュウモク</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ダイチュウモク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>t04</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3042,10 +3045,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
+        <v>208</v>
+      </c>
+      <c r="X4" t="s">
         <v>209</v>
-      </c>
-      <c r="X4" t="s">
-        <v>210</v>
       </c>
       <c r="Y4" t="s">
         <v>101</v>
@@ -3303,13 +3306,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
+        <v>210</v>
+      </c>
+      <c r="X7" t="s">
+        <v>216</v>
+      </c>
+      <c r="Y7" t="s">
         <v>211</v>
-      </c>
-      <c r="X7" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>212</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -3390,13 +3393,13 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
+        <v>210</v>
+      </c>
+      <c r="X8" t="s">
+        <v>216</v>
+      </c>
+      <c r="Y8" t="s">
         <v>211</v>
-      </c>
-      <c r="X8" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>212</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -3777,7 +3780,7 @@
         <v>141</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -4115,7 +4118,7 @@
         <v>132</v>
       </c>
       <c r="Y3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Z3">
         <v>2</v>
@@ -4322,7 +4325,7 @@
         <v>146</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -4547,7 +4550,7 @@
         <v>117</v>
       </c>
       <c r="X8" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="Y8" t="s">
         <v>101</v>
@@ -4634,7 +4637,7 @@
         <v>117</v>
       </c>
       <c r="X9" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="Y9" t="s">
         <v>101</v>
@@ -4718,10 +4721,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="X10" t="s">
-        <v>127</v>
+        <v>216</v>
       </c>
       <c r="Y10" t="s">
         <v>101</v>
@@ -4757,7 +4760,7 @@
         <v>205</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -4844,7 +4847,7 @@
         <v>150</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -5563,7 +5566,7 @@
         <v>88</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H8">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296DAF76-22CF-449D-919F-2E49D504F04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0675F86A-F2B7-44DA-A2A3-32AF5C1DF5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2370" yWindow="930" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1335" yWindow="870" windowWidth="25005" windowHeight="14370" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -3315,7 +3315,7 @@
         <v>211</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA7" s="4" t="s">
         <v>21</v>
@@ -3402,7 +3402,7 @@
         <v>211</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA8" s="4" t="s">
         <v>21</v>
@@ -3486,10 +3486,10 @@
         <v>99</v>
       </c>
       <c r="Y9" t="s">
-        <v>101</v>
+        <v>211</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA9" s="4" t="s">
         <v>21</v>
@@ -4730,7 +4730,7 @@
         <v>101</v>
       </c>
       <c r="Z10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA10" s="4" t="s">
         <v>21</v>
@@ -4817,7 +4817,7 @@
         <v>101</v>
       </c>
       <c r="Z11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA11" s="4" t="s">
         <v>21</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0675F86A-F2B7-44DA-A2A3-32AF5C1DF5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5766243A-0ED1-4785-A358-B10FC3C7CB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1335" yWindow="870" windowWidth="25005" windowHeight="14370" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="945" yWindow="525" windowWidth="25005" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -3330,22 +3330,22 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>10500</v>
+        <v>30200</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -3360,19 +3360,19 @@
         <v>31</v>
       </c>
       <c r="L8">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8">
         <v>99</v>
@@ -3393,16 +3393,16 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>210</v>
+        <v>95</v>
       </c>
       <c r="X8" t="s">
-        <v>216</v>
+        <v>99</v>
       </c>
       <c r="Y8" t="s">
-        <v>211</v>
+        <v>101</v>
       </c>
       <c r="Z8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="4" t="s">
         <v>21</v>
@@ -3417,22 +3417,22 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>10900</v>
+        <v>30300</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>121</v>
-      </c>
-      <c r="F9" t="s">
-        <v>121</v>
+        <v>78</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3447,16 +3447,16 @@
         <v>31</v>
       </c>
       <c r="L9">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="M9">
+        <v>4</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
         <v>3</v>
-      </c>
-      <c r="N9">
-        <v>3</v>
-      </c>
-      <c r="O9">
-        <v>5</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -3480,16 +3480,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="X9" t="s">
         <v>99</v>
       </c>
       <c r="Y9" t="s">
-        <v>211</v>
+        <v>101</v>
       </c>
       <c r="Z9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="4" t="s">
         <v>21</v>
@@ -3504,22 +3504,22 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>30200</v>
+        <v>10500</v>
       </c>
       <c r="C10" t="s">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -3534,19 +3534,19 @@
         <v>31</v>
       </c>
       <c r="L10">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M10">
+        <v>5</v>
+      </c>
+      <c r="N10">
+        <v>10</v>
+      </c>
+      <c r="O10">
         <v>4</v>
       </c>
-      <c r="N10">
-        <v>15</v>
-      </c>
-      <c r="O10">
-        <v>3</v>
-      </c>
       <c r="P10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>99</v>
@@ -3567,16 +3567,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="X10" t="s">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="Y10" t="s">
-        <v>101</v>
+        <v>211</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA10" s="4" t="s">
         <v>21</v>
@@ -3591,22 +3591,22 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>30300</v>
+        <v>10900</v>
       </c>
       <c r="C11" t="s">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>139</v>
+        <v>121</v>
+      </c>
+      <c r="F11" t="s">
+        <v>121</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -3621,16 +3621,16 @@
         <v>31</v>
       </c>
       <c r="L11">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P11">
         <v>1</v>
@@ -3654,16 +3654,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="X11" t="s">
         <v>99</v>
       </c>
       <c r="Y11" t="s">
-        <v>101</v>
+        <v>211</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA11" s="4" t="s">
         <v>21</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5766243A-0ED1-4785-A358-B10FC3C7CB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8BF1CA-D168-44D6-AE27-0A1F7CF01FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="945" yWindow="525" windowWidth="25005" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2415" yWindow="1230" windowWidth="25005" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -1146,57 +1146,6 @@
   </si>
   <si>
     <t>◆自由課題◆
-春エリアで行われるパティシエ中級向けのコンテスト。少し難易度高め。
-春の大妖精様を讃えるお菓子を希望します。</t>
-    <rPh sb="1" eb="5">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ハル</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>チュウキュウ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="34" eb="37">
-      <t>ナンイド</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>タカ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>ハル</t>
-    </rPh>
-    <rPh sb="43" eb="44">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ヨウセイ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>サマ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>タタ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>キボウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>◆自由課題◆
 メルヘンでかわいいお菓子を募集しています♪
 食べた人に夢を見せるかわいいお菓子を見せてくださ～い！</t>
     <rPh sb="1" eb="5">
@@ -1533,48 +1482,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>◆魔法のお菓子限定◆
-魔法で仕上げた、一風変わったオシャレなお菓子を募集♪
-見慣れない不思議なお菓子だと高得点です！</t>
-    <rPh sb="1" eb="3">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="19" eb="22">
-      <t>イップウカ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ミナ</t>
-    </rPh>
-    <rPh sb="43" eb="46">
-      <t>フシギ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="52" eb="55">
-      <t>コウトクテン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>◆クレープ限定◆
 黒猫達も好むおいしくて甘いクレープを募集
 権威ある上流黒猫たちも注目しています♪</t>
@@ -2291,6 +2198,99 @@
   </si>
   <si>
     <t>t04</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆魔法のお菓子限定◆
+魔法で仕上げた、一風変わったオシャレなお菓子を募集♪
+フシギで芸術的な魔法のおかしを見せてください！</t>
+    <rPh sb="1" eb="3">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>イップウカ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ゲイジュツ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆自由課題◆
+春エリアで行われるパティシエ中～上級向けのコンテスト。難易度高め。
+春の大妖精様を讃えるお菓子を希望します。</t>
+    <rPh sb="1" eb="5">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ハル</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジョウキュウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="34" eb="37">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ハル</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヨウセイ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>タタ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>キボウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3045,10 +3045,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="X4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y4" t="s">
         <v>101</v>
@@ -3198,7 +3198,7 @@
         <v>3</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6">
         <v>99</v>
@@ -3306,13 +3306,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Z7">
         <v>3</v>
@@ -3345,7 +3345,7 @@
         <v>138</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -3432,7 +3432,7 @@
         <v>139</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>4</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10">
         <v>99</v>
@@ -3567,13 +3567,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Z10">
         <v>3</v>
@@ -3606,7 +3606,7 @@
         <v>121</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -3660,7 +3660,7 @@
         <v>99</v>
       </c>
       <c r="Y11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Z11">
         <v>3</v>
@@ -3693,7 +3693,7 @@
         <v>140</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -3780,7 +3780,7 @@
         <v>141</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -3977,7 +3977,7 @@
         <v>143</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -4064,7 +4064,7 @@
         <v>118</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4118,7 +4118,7 @@
         <v>132</v>
       </c>
       <c r="Y3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Z3">
         <v>2</v>
@@ -4151,7 +4151,7 @@
         <v>144</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -4238,7 +4238,7 @@
         <v>145</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -4325,7 +4325,7 @@
         <v>146</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -4352,7 +4352,7 @@
         <v>2</v>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <v>99</v>
@@ -4412,7 +4412,7 @@
         <v>147</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -4499,7 +4499,7 @@
         <v>67</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -4586,7 +4586,7 @@
         <v>90</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -4673,7 +4673,7 @@
         <v>149</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -4721,10 +4721,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Y10" t="s">
         <v>101</v>
@@ -4754,13 +4754,13 @@
         <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -4847,7 +4847,7 @@
         <v>150</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -5044,7 +5044,7 @@
         <v>151</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -5131,7 +5131,7 @@
         <v>168</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5218,7 +5218,7 @@
         <v>152</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -5305,7 +5305,7 @@
         <v>153</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -5332,7 +5332,7 @@
         <v>3</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5">
         <v>99</v>
@@ -5392,7 +5392,7 @@
         <v>148</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -5479,7 +5479,7 @@
         <v>80</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -5566,7 +5566,7 @@
         <v>88</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -5653,7 +5653,7 @@
         <v>154</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -5740,7 +5740,7 @@
         <v>79</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5767,7 +5767,7 @@
         <v>4</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10">
         <v>99</v>
@@ -5827,7 +5827,7 @@
         <v>155</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -5854,7 +5854,7 @@
         <v>5</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11">
         <v>99</v>
@@ -6196,7 +6196,7 @@
         <v>68</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H2" s="5">
         <v>0</v>
@@ -6283,7 +6283,7 @@
         <v>156</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
@@ -6370,7 +6370,7 @@
         <v>157</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -6457,7 +6457,7 @@
         <v>158</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -6538,13 +6538,13 @@
         <v>61</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
@@ -6631,7 +6631,7 @@
         <v>159</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H7" s="5">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>161</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8BF1CA-D168-44D6-AE27-0A1F7CF01FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8CB6FC7-D6C2-45E0-9014-C872037088A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2415" yWindow="1230" windowWidth="25005" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="25005" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -1728,54 +1728,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>◆青色をテーマにしたお菓子◆
-ブルー・・それはとても美しい色。
-美しい青をテーマにしたお菓子をぜひ作ってください。</t>
-    <rPh sb="1" eb="3">
-      <t>アオイロ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ウツク</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>イロ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>ウツク</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>アオ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="49" eb="50">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>◆チョコレート限定◆
-とろける、夢見るチョコレートのコンテスト
-はたして、夢を見せてくれるのか・・？</t>
-    <rPh sb="7" eb="9">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ユメミ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>ユメ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>◆自由課題◆
 冬の名物となる、雪国のお菓子を募集しています。
 どんな種類でも結構です！お気軽にご応募ください。</t>
@@ -2290,6 +2242,76 @@
     </rPh>
     <rPh sb="55" eb="57">
       <t>キボウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆青色をテーマにしたお菓子◆
+ブルー・・それはとても美しい色。
+美しい青をテーマにした最高のお菓子を募集します。難易度高。</t>
+    <rPh sb="1" eb="3">
+      <t>アオイロ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>サイコウ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="56" eb="59">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆チョコレート限定◆
+とろける、夢見るチョコレートのコンテスト
+はたして、夢を見せてくれるのか・・？
+※王者級の難易度なので、心してかかるべし。</t>
+    <rPh sb="7" eb="9">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ユメミ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>オウジャ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="56" eb="59">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ココロ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3045,10 +3067,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="X4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="Y4" t="s">
         <v>101</v>
@@ -3306,13 +3328,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="X7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="Y7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Z7">
         <v>3</v>
@@ -3567,13 +3589,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="X10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="Y10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Z10">
         <v>3</v>
@@ -3606,7 +3628,7 @@
         <v>121</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -3660,7 +3682,7 @@
         <v>99</v>
       </c>
       <c r="Y11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Z11">
         <v>3</v>
@@ -3780,7 +3802,7 @@
         <v>141</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -4118,7 +4140,7 @@
         <v>132</v>
       </c>
       <c r="Y3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Z3">
         <v>2</v>
@@ -4325,7 +4347,7 @@
         <v>146</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -4673,7 +4695,7 @@
         <v>149</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -4721,10 +4743,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="X10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="Y10" t="s">
         <v>101</v>
@@ -4754,13 +4776,13 @@
         <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -4847,7 +4869,7 @@
         <v>150</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -5566,7 +5588,7 @@
         <v>88</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -5653,7 +5675,7 @@
         <v>154</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -5740,7 +5762,7 @@
         <v>79</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5827,7 +5849,7 @@
         <v>155</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -6196,7 +6218,7 @@
         <v>68</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H2" s="5">
         <v>0</v>
@@ -6283,7 +6305,7 @@
         <v>156</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
@@ -6370,7 +6392,7 @@
         <v>157</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -6457,7 +6479,7 @@
         <v>158</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -6538,13 +6560,13 @@
         <v>61</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
@@ -6631,7 +6653,7 @@
         <v>159</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H7" s="5">
         <v>0</v>
@@ -6718,7 +6740,7 @@
         <v>161</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8CB6FC7-D6C2-45E0-9014-C872037088A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56149DC-B987-4468-B35A-4A07BB40B7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="25005" windowHeight="14370" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2190" yWindow="615" windowWidth="25005" windowHeight="14370" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="224">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -2313,6 +2313,34 @@
     <rPh sb="63" eb="64">
       <t>ココロ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>h201</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>h202</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>h203</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>t203</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>h102</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>t102</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sound82</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4575,10 +4603,10 @@
         <v>99</v>
       </c>
       <c r="Y8" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="Z8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA8" s="4" t="s">
         <v>21</v>
@@ -4662,10 +4690,10 @@
         <v>99</v>
       </c>
       <c r="Y9" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="Z9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA9" s="4" t="s">
         <v>21</v>
@@ -4749,7 +4777,7 @@
         <v>212</v>
       </c>
       <c r="Y10" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="Z10">
         <v>3</v>
@@ -4830,16 +4858,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>124</v>
+        <v>221</v>
       </c>
       <c r="X11" t="s">
-        <v>127</v>
+        <v>222</v>
       </c>
       <c r="Y11" t="s">
-        <v>101</v>
+        <v>223</v>
       </c>
       <c r="Z11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA11" s="4" t="s">
         <v>21</v>
@@ -5114,7 +5142,7 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>125</v>
+        <v>217</v>
       </c>
       <c r="X2" t="s">
         <v>128</v>
@@ -5123,7 +5151,7 @@
         <v>101</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA2" s="4" t="s">
         <v>21</v>
@@ -5201,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>125</v>
+        <v>218</v>
       </c>
       <c r="X3" t="s">
         <v>128</v>
@@ -5210,7 +5238,7 @@
         <v>101</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA3" s="4" t="s">
         <v>21</v>
@@ -5297,7 +5325,7 @@
         <v>101</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA4" s="4" t="s">
         <v>24</v>
@@ -5342,7 +5370,7 @@
         <v>31</v>
       </c>
       <c r="L5">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="M5">
         <v>20</v>
@@ -5351,7 +5379,7 @@
         <v>15</v>
       </c>
       <c r="O5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P5">
         <v>1</v>
@@ -5375,16 +5403,16 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="X5" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="Y5" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA5" s="4" t="s">
         <v>24</v>
@@ -5438,7 +5466,7 @@
         <v>10</v>
       </c>
       <c r="O6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -5462,16 +5490,16 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>125</v>
+        <v>219</v>
       </c>
       <c r="X6" t="s">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="Y6" t="s">
         <v>101</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA6" s="4" t="s">
         <v>21</v>
@@ -5636,16 +5664,16 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>125</v>
+        <v>219</v>
       </c>
       <c r="X8" t="s">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="Y8" t="s">
         <v>101</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA8" s="4" t="s">
         <v>21</v>
@@ -5729,10 +5757,10 @@
         <v>128</v>
       </c>
       <c r="Y9" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA9" s="4" t="s">
         <v>21</v>
@@ -5816,10 +5844,10 @@
         <v>128</v>
       </c>
       <c r="Y10" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA10" s="4" t="s">
         <v>21</v>
@@ -5906,7 +5934,7 @@
         <v>101</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA11" s="4" t="s">
         <v>21</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56149DC-B987-4468-B35A-4A07BB40B7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1D9786-F2F8-40FB-B27C-EDCF6E666EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2190" yWindow="615" windowWidth="25005" windowHeight="14370" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3225" yWindow="1380" windowWidth="25005" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="225">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -2341,6 +2341,10 @@
   </si>
   <si>
     <t>sound82</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>h05</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3269,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>117</v>
+        <v>224</v>
       </c>
       <c r="X6" t="s">
         <v>99</v>
@@ -3278,7 +3282,7 @@
         <v>101</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA6" s="4" t="s">
         <v>21</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1D9786-F2F8-40FB-B27C-EDCF6E666EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E03DE650-BECC-4755-93E0-75F06A5AFD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3225" yWindow="1380" windowWidth="25005" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2340" yWindow="1830" windowWidth="25005" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -636,48 +636,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>◆秋の伝統的なお菓子コンクール◆
-テーマ：自由課題
-秋エリアの伝統的で由緒あるコンクールです。食べた人を幸せにするお菓子をお待ちしております。</t>
-    <rPh sb="1" eb="2">
-      <t>アキ</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>デントウテキ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>アキ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>デントウ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ユイショ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>シアワ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="62" eb="63">
-      <t>マ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>マジカル・パティスリー・アワード</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1174,51 +1132,6 @@
     </rPh>
     <rPh sb="47" eb="48">
       <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>◆お子様向けのお菓子限定◆
-お子様が喜ぶ色々なお菓子を募集しています！
-かわいいや不思議なお菓子など.. ぜひ応募お待ちしてます！</t>
-    <rPh sb="2" eb="4">
-      <t>コサマ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>コサマ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ヨロコ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>イロイロ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="41" eb="44">
-      <t>フシギ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>オウボ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>マ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1964,46 +1877,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>◆夏エリア最大のお菓子エキシビジョン◆
-テーマ：自由課題
-ソーダアイランドで行われるお菓子の一大イベント！
-自慢のお菓子で来客者を喜ばせよう！！</t>
-    <rPh sb="1" eb="2">
-      <t>ナツ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>サイダイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="24" eb="28">
-      <t>ジユウカダイ</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>イチダイ</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>ジマン</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="61" eb="64">
-      <t>ライキャクシャ</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>ヨロコ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>◆パティシエアカデミーの登竜門◆
 テーマ：焼き菓子と自由課題
 来たれ！パティシエのたまごたちよ！
@@ -2345,6 +2218,129 @@
   </si>
   <si>
     <t>h05</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆夏エリア最大のお菓子エキシビジョン◆
+テーマ：焼き菓子・自由課題ほか
+ソーダアイランドで行われるお菓子の一大イベント！自慢のお菓子でお客さんを喜ばせよう！！</t>
+    <rPh sb="1" eb="2">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ガシ</t>
+    </rPh>
+    <rPh sb="29" eb="33">
+      <t>ジユウカダイ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>イチダイ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>ジマン</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>キャク</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>ヨロコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆秋の伝統的なお菓子コンクール◆
+テーマ：自由課題
+秋エリアの伝統的で由緒あるコンクールです。自信作をお待ちしております。</t>
+    <rPh sb="1" eb="2">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>デントウテキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>デントウ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ユイショ</t>
+    </rPh>
+    <rPh sb="47" eb="50">
+      <t>ジシンサク</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆お子様向けのお菓子限定◆
+お子様が喜ぶ色々なお菓子を募集しています！
+キャンディや不思議なお菓子など.. ぜひ応募お待ちしてます！</t>
+    <rPh sb="2" eb="4">
+      <t>コサマ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コサマ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヨロコ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イロイロ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="42" eb="45">
+      <t>フシギ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>オウボ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>マ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2787,7 +2783,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -2847,7 +2843,7 @@
         <v>98</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -2961,10 +2957,10 @@
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -3048,10 +3044,10 @@
         <v>87</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -3099,10 +3095,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="X4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Y4" t="s">
         <v>101</v>
@@ -3135,10 +3131,10 @@
         <v>73</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -3225,7 +3221,7 @@
         <v>83</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -3240,7 +3236,7 @@
         <v>31</v>
       </c>
       <c r="L6">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -3273,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="X6" t="s">
         <v>99</v>
@@ -3309,10 +3305,10 @@
         <v>84</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -3336,7 +3332,7 @@
         <v>2</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -3360,13 +3356,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="X7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="Y7" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Z7">
         <v>3</v>
@@ -3396,10 +3392,10 @@
         <v>70</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -3483,10 +3479,10 @@
         <v>78</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>176</v>
+        <v>224</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3570,10 +3566,10 @@
         <v>85</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -3588,7 +3584,7 @@
         <v>31</v>
       </c>
       <c r="L10">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="M10">
         <v>5</v>
@@ -3621,13 +3617,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="X10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="Y10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Z10">
         <v>3</v>
@@ -3651,16 +3647,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -3708,13 +3704,13 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="X11" t="s">
         <v>99</v>
       </c>
       <c r="Y11" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Z11">
         <v>3</v>
@@ -3744,10 +3740,10 @@
         <v>71</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -3831,10 +3827,10 @@
         <v>29</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -3882,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="X13" t="s">
         <v>99</v>
@@ -3941,7 +3937,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -4001,7 +3997,7 @@
         <v>98</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -4028,10 +4024,10 @@
         <v>65</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -4079,10 +4075,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y2" t="s">
         <v>101</v>
@@ -4109,16 +4105,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4142,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P3">
         <v>1</v>
@@ -4166,13 +4162,13 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
+        <v>130</v>
+      </c>
+      <c r="X3" t="s">
         <v>131</v>
       </c>
-      <c r="X3" t="s">
-        <v>132</v>
-      </c>
       <c r="Y3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Z3">
         <v>2</v>
@@ -4202,10 +4198,10 @@
         <v>91</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -4253,10 +4249,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y4" t="s">
         <v>101</v>
@@ -4289,10 +4285,10 @@
         <v>89</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -4319,7 +4315,7 @@
         <v>2</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>99</v>
@@ -4340,10 +4336,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y5" t="s">
         <v>101</v>
@@ -4370,16 +4366,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -4403,7 +4399,7 @@
         <v>10</v>
       </c>
       <c r="O6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -4427,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y6" t="s">
         <v>101</v>
@@ -4463,10 +4459,10 @@
         <v>66</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -4514,10 +4510,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y7" t="s">
         <v>101</v>
@@ -4553,7 +4549,7 @@
         <v>67</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -4601,13 +4597,13 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="X8" t="s">
         <v>99</v>
       </c>
       <c r="Y8" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Z8">
         <v>3</v>
@@ -4640,7 +4636,7 @@
         <v>90</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -4655,7 +4651,7 @@
         <v>31</v>
       </c>
       <c r="L9">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="M9">
         <v>12</v>
@@ -4664,7 +4660,7 @@
         <v>20</v>
       </c>
       <c r="O9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -4688,13 +4684,13 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="X9" t="s">
         <v>99</v>
       </c>
       <c r="Y9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Z9">
         <v>3</v>
@@ -4721,13 +4717,13 @@
         <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -4775,13 +4771,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="X10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="Y10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Z10">
         <v>3</v>
@@ -4808,13 +4804,13 @@
         <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -4862,13 +4858,13 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="X11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="Y11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Z11">
         <v>6</v>
@@ -4898,10 +4894,10 @@
         <v>111</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -4949,10 +4945,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="s">
+        <v>162</v>
+      </c>
+      <c r="X12" t="s">
         <v>163</v>
-      </c>
-      <c r="X12" t="s">
-        <v>164</v>
       </c>
       <c r="Y12" t="s">
         <v>101</v>
@@ -5008,7 +5004,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -5068,7 +5064,7 @@
         <v>98</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -5095,10 +5091,10 @@
         <v>72</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -5122,7 +5118,7 @@
         <v>8</v>
       </c>
       <c r="O2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -5146,10 +5142,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="X2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y2" t="s">
         <v>101</v>
@@ -5176,16 +5172,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5233,10 +5229,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="X3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y3" t="s">
         <v>101</v>
@@ -5269,10 +5265,10 @@
         <v>77</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -5320,10 +5316,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y4" t="s">
         <v>101</v>
@@ -5356,10 +5352,10 @@
         <v>82</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -5407,13 +5403,13 @@
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="X5" t="s">
         <v>99</v>
       </c>
       <c r="Y5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Z5">
         <v>3</v>
@@ -5443,10 +5439,10 @@
         <v>64</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -5494,10 +5490,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="X6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y6" t="s">
         <v>101</v>
@@ -5533,7 +5529,7 @@
         <v>80</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -5581,10 +5577,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y7" t="s">
         <v>101</v>
@@ -5620,7 +5616,7 @@
         <v>88</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -5668,10 +5664,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="X8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y8" t="s">
         <v>101</v>
@@ -5704,10 +5700,10 @@
         <v>81</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -5755,13 +5751,13 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Z9">
         <v>3</v>
@@ -5794,7 +5790,7 @@
         <v>79</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5842,13 +5838,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Z10">
         <v>3</v>
@@ -5878,10 +5874,10 @@
         <v>86</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -5929,10 +5925,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y11" t="s">
         <v>101</v>
@@ -6016,7 +6012,7 @@
         <v>0</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>102</v>
@@ -6055,7 +6051,7 @@
         <v>109</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>114</v>
+        <v>223</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -6103,10 +6099,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="s">
+        <v>164</v>
+      </c>
+      <c r="X13" t="s">
         <v>165</v>
-      </c>
-      <c r="X13" t="s">
-        <v>166</v>
       </c>
       <c r="Y13" t="s">
         <v>101</v>
@@ -6160,7 +6156,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -6220,7 +6216,7 @@
         <v>98</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -6250,7 +6246,7 @@
         <v>68</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H2" s="5">
         <v>0</v>
@@ -6298,10 +6294,10 @@
         <v>0</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y2" s="5" t="s">
         <v>101</v>
@@ -6334,10 +6330,10 @@
         <v>76</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
@@ -6385,10 +6381,10 @@
         <v>0</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y3" s="5" t="s">
         <v>101</v>
@@ -6421,10 +6417,10 @@
         <v>75</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -6472,10 +6468,10 @@
         <v>0</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y4" s="5" t="s">
         <v>101</v>
@@ -6508,10 +6504,10 @@
         <v>107</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -6559,10 +6555,10 @@
         <v>0</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y5" s="5" t="s">
         <v>101</v>
@@ -6592,13 +6588,13 @@
         <v>61</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
@@ -6646,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y6" s="5" t="s">
         <v>101</v>
@@ -6682,10 +6678,10 @@
         <v>74</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H7" s="5">
         <v>0</v>
@@ -6733,10 +6729,10 @@
         <v>0</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y7" s="5" t="s">
         <v>101</v>
@@ -6769,10 +6765,10 @@
         <v>105</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>
@@ -6820,10 +6816,10 @@
         <v>0</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y8" s="5" t="s">
         <v>101</v>
@@ -6856,7 +6852,7 @@
         <v>108</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>110</v>
@@ -6907,10 +6903,10 @@
         <v>0</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y9" s="5" t="s">
         <v>100</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E03DE650-BECC-4755-93E0-75F06A5AFD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FE08A6-90A8-4742-9674-E214A959EF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1830" windowWidth="25005" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3045" yWindow="1020" windowWidth="25005" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="228">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -1132,42 +1132,6 @@
     </rPh>
     <rPh sb="47" eb="48">
       <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>◆キラキラお菓子限定◆
-エメラルド・サファイア.. 美しい石は、私たちを魅了してやみません。
-キラもの好きの大富豪がうなるお菓子を募集します♪</t>
-    <rPh sb="6" eb="8">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ウツク</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>イシ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>ワタシ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ミリョウ</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="54" eb="57">
-      <t>ダイフゴウ</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>ボシュウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2341,6 +2305,51 @@
     <rPh sb="59" eb="60">
       <t>マ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>t202</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆キラキラお菓子限定◆
+エメラルド・サファイア.. 美しい石は、私たちを魅了してやみません。
+キラもの好きの大富豪が待っています。</t>
+    <rPh sb="6" eb="8">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>イシ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ミリョウ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="54" eb="57">
+      <t>ダイフゴウ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>h204</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>t204</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3095,10 +3104,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="s">
+        <v>200</v>
+      </c>
+      <c r="X4" t="s">
         <v>201</v>
-      </c>
-      <c r="X4" t="s">
-        <v>202</v>
       </c>
       <c r="Y4" t="s">
         <v>101</v>
@@ -3269,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X6" t="s">
         <v>99</v>
@@ -3356,13 +3365,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
+        <v>202</v>
+      </c>
+      <c r="X7" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y7" t="s">
         <v>203</v>
-      </c>
-      <c r="X7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>204</v>
       </c>
       <c r="Z7">
         <v>3</v>
@@ -3482,7 +3491,7 @@
         <v>138</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3617,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
+        <v>202</v>
+      </c>
+      <c r="X10" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y10" t="s">
         <v>203</v>
-      </c>
-      <c r="X10" t="s">
-        <v>209</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>204</v>
       </c>
       <c r="Z10">
         <v>3</v>
@@ -3656,7 +3665,7 @@
         <v>120</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -3710,7 +3719,7 @@
         <v>99</v>
       </c>
       <c r="Y11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Z11">
         <v>3</v>
@@ -3743,7 +3752,7 @@
         <v>139</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -3830,7 +3839,7 @@
         <v>140</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -4027,7 +4036,7 @@
         <v>142</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -4114,7 +4123,7 @@
         <v>117</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4168,7 +4177,7 @@
         <v>131</v>
       </c>
       <c r="Y3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Z3">
         <v>2</v>
@@ -4201,7 +4210,7 @@
         <v>143</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -4288,7 +4297,7 @@
         <v>144</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -4375,7 +4384,7 @@
         <v>145</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -4423,10 +4432,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="X6" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="Y6" t="s">
         <v>101</v>
@@ -4462,7 +4471,7 @@
         <v>146</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -4549,7 +4558,7 @@
         <v>67</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -4603,7 +4612,7 @@
         <v>99</v>
       </c>
       <c r="Y8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Z8">
         <v>3</v>
@@ -4636,7 +4645,7 @@
         <v>90</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -4690,7 +4699,7 @@
         <v>99</v>
       </c>
       <c r="Y9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Z9">
         <v>3</v>
@@ -4723,7 +4732,7 @@
         <v>148</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -4771,13 +4780,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="s">
+        <v>202</v>
+      </c>
+      <c r="X10" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y10" t="s">
         <v>203</v>
-      </c>
-      <c r="X10" t="s">
-        <v>209</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>204</v>
       </c>
       <c r="Z10">
         <v>3</v>
@@ -4804,13 +4813,13 @@
         <v>45</v>
       </c>
       <c r="E11" t="s">
+        <v>197</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>199</v>
-      </c>
       <c r="G11" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -4858,13 +4867,13 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
+        <v>217</v>
+      </c>
+      <c r="X11" t="s">
         <v>218</v>
       </c>
-      <c r="X11" t="s">
+      <c r="Y11" t="s">
         <v>219</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>220</v>
       </c>
       <c r="Z11">
         <v>6</v>
@@ -4897,7 +4906,7 @@
         <v>149</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -5094,7 +5103,7 @@
         <v>150</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -5142,7 +5151,7 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="X2" t="s">
         <v>127</v>
@@ -5181,7 +5190,7 @@
         <v>167</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5229,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="X3" t="s">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="Y3" t="s">
         <v>101</v>
@@ -5268,7 +5277,7 @@
         <v>151</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -5355,7 +5364,7 @@
         <v>152</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -5409,7 +5418,7 @@
         <v>99</v>
       </c>
       <c r="Y5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Z5">
         <v>3</v>
@@ -5442,7 +5451,7 @@
         <v>147</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -5490,10 +5499,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
+        <v>215</v>
+      </c>
+      <c r="X6" t="s">
         <v>216</v>
-      </c>
-      <c r="X6" t="s">
-        <v>217</v>
       </c>
       <c r="Y6" t="s">
         <v>101</v>
@@ -5529,7 +5538,7 @@
         <v>80</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -5616,7 +5625,7 @@
         <v>88</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -5664,10 +5673,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="X8" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="Y8" t="s">
         <v>101</v>
@@ -5703,7 +5712,7 @@
         <v>153</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -5757,7 +5766,7 @@
         <v>127</v>
       </c>
       <c r="Y9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Z9">
         <v>3</v>
@@ -5790,7 +5799,7 @@
         <v>79</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5844,7 +5853,7 @@
         <v>127</v>
       </c>
       <c r="Y10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Z10">
         <v>3</v>
@@ -5877,7 +5886,7 @@
         <v>154</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -6051,7 +6060,7 @@
         <v>109</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -6246,7 +6255,7 @@
         <v>68</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H2" s="5">
         <v>0</v>
@@ -6333,7 +6342,7 @@
         <v>155</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
@@ -6420,7 +6429,7 @@
         <v>156</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -6507,7 +6516,7 @@
         <v>157</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -6588,13 +6597,13 @@
         <v>61</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
@@ -6681,7 +6690,7 @@
         <v>158</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H7" s="5">
         <v>0</v>
@@ -6768,7 +6777,7 @@
         <v>160</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mator\OneDrive\ドキュメント\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FE08A6-90A8-4742-9674-E214A959EF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478AA9B8-DC70-461D-AE84-3E9827E7F063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="1020" windowWidth="25005" windowHeight="14355" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3405" yWindow="1185" windowWidth="21915" windowHeight="13455" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -4438,7 +4438,7 @@
         <v>99</v>
       </c>
       <c r="Y6" t="s">
-        <v>101</v>
+        <v>203</v>
       </c>
       <c r="Z6">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mator\OneDrive\ドキュメント\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478AA9B8-DC70-461D-AE84-3E9827E7F063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC52975D-EC6A-4E84-BC3F-EA25A9DDD27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3405" yWindow="1185" windowWidth="21915" windowHeight="13455" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="4005" yWindow="1350" windowWidth="21915" windowHeight="13455" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -5214,7 +5214,7 @@
         <v>6</v>
       </c>
       <c r="O3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -5301,7 +5301,7 @@
         <v>10</v>
       </c>
       <c r="O4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4">
         <v>1</v>
